--- a/results/job_matches_2026-05-01.xlsx
+++ b/results/job_matches_2026-05-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G146"/>
+  <dimension ref="A1:G152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,25 +678,25 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Technical Architect-Datawarehousing</t>
+          <t>AV Safety Engineering Analytics AI/ML Engineer (GPSSC)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Marlborough, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Dataflow, Spark, PySpark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe34bd7ad3cc55cc</t>
+          <t>https://www.indeed.com/viewjob?jk=675259892fa0b51c</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AV Safety Engineering Analytics AI/ML Engineer (GPSSC)</t>
+          <t>Sr Software Engineer II - Enterprise Architecture</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Dataflow, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=675259892fa0b51c</t>
+          <t>https://www.indeed.com/viewjob?jk=f6bd0f139eec27a7</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr Software Engineer II - Enterprise Architecture</t>
+          <t>Cloud Network Automation Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6bd0f139eec27a7</t>
+          <t>https://www.indeed.com/viewjob?jk=0a0cf6116e02d635</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Cloud Network Automation Engineer</t>
+          <t>Cloud Engineer II</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Vibrant Emotional Health</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a0cf6116e02d635</t>
+          <t>https://www.indeed.com/viewjob?jk=3ba39b2a6826c32d</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Engineer - AI &amp; Data Management</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tradeweb</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, GCP, Spark, Kafka, Dask, Snowflake</t>
+          <t>S3, Azure, Data Factory, Cloud Storage, Hadoop, HDFS, Spark, Scala, Kafka, Informatica PowerCenter</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb2021c38a5314d9</t>
+          <t>https://www.indeed.com/viewjob?jk=0f98760c842e5085</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GenAI Threat Intelligence Analyst</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tradeweb</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Blob Storage, Google Cloud Platform, Vertex AI, Scala, MLOps, MLflow</t>
+          <t>AWS, Redshift, S3, IAM, RDS, GCP, Spark, Kafka, Dask, Snowflake</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5efecdb56da9cdd1</t>
+          <t>https://www.indeed.com/viewjob?jk=cb2021c38a5314d9</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>GenAI Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Applied Technology Services</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Adelphi, MD, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,17 +906,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Blob Storage, Google Cloud Platform, Vertex AI, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88d5142fe158dffb</t>
+          <t>https://www.indeed.com/viewjob?jk=5efecdb56da9cdd1</t>
         </is>
       </c>
     </row>
@@ -958,35 +958,35 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer I</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Cox Automotive</t>
+          <t>Credera</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, S3, SQS, SNS, ECS, RDS</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Oozie, Spark, Scala, Kafka, SQL Server</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0a8e6675d7ad8e4</t>
+          <t>https://www.indeed.com/viewjob?jk=a2859c21fcc6b9b6</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2859c21fcc6b9b6</t>
+          <t>https://www.indeed.com/viewjob?jk=9e65ae12c9231691</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e65ae12c9231691</t>
+          <t>https://www.indeed.com/viewjob?jk=deb9ad8464ceb6e6</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,59 +1091,59 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=deb9ad8464ceb6e6</t>
+          <t>https://www.indeed.com/viewjob?jk=0faede29102fb7e1</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Azure Data &amp; Development Architect</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Credera</t>
+          <t>SunStone Consulting</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Oozie, Spark, Scala, Kafka, SQL Server</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Event Hubs, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0faede29102fb7e1</t>
+          <t>https://www.indeed.com/viewjob?jk=1e9052cac6c7210d</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Azure Data &amp; Development Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SunStone Consulting</t>
+          <t>ABCorp NA Inc.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,17 +1151,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Event Hubs, Spark, Scala, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e9052cac6c7210d</t>
+          <t>https://www.indeed.com/viewjob?jk=1e06fd43e0f99777</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ABCorp NA Inc.</t>
+          <t>TeraWatt Infrastructure</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e06fd43e0f99777</t>
+          <t>https://www.indeed.com/viewjob?jk=3cf13a405f291139</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer, Full Stack - AI (Chicago)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Blue Orange Digital</t>
+          <t>Fitch Group</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b7e79accc7c2528</t>
+          <t>https://www.indeed.com/viewjob?jk=d4bb35a3533f1ee6</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Engineering &amp; Quality - Software Engineer, Full Stack - AI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>TeraWatt Infrastructure</t>
+          <t>Fitch Group</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,42 +1256,42 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala</t>
+          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cf13a405f291139</t>
+          <t>https://www.indeed.com/viewjob?jk=cf6b928dd59e0c41</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer, Full Stack - AI (Chicago)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Fitch Group</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
+          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4bb35a3533f1ee6</t>
+          <t>https://www.indeed.com/viewjob?jk=0fc4628968aad9e2</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Engineering &amp; Quality - Software Engineer, Full Stack - AI</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Fitch Group</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
+          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf6b928dd59e0c41</t>
+          <t>https://www.indeed.com/viewjob?jk=0eb5fc1d601c0028</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fc4628968aad9e2</t>
+          <t>https://www.indeed.com/viewjob?jk=acae1b7fc51e9a39</t>
         </is>
       </c>
     </row>
@@ -1383,12 +1383,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Trane Technologies</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0eb5fc1d601c0028</t>
+          <t>https://www.indeed.com/viewjob?jk=f483db2edc8cb83a</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>JUUL Labs</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
+          <t>AWS, S3, ECS, IAM, RDS, GCP, Dataflow, Cloud Storage, Scala, Splunk</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acae1b7fc51e9a39</t>
+          <t>https://www.indeed.com/viewjob?jk=c63edb85327f9aef</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>JUUL Labs</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, GCP, Dataflow, Cloud Storage, Scala, Splunk</t>
+          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, Snowflake, SQL Server, MySQL, ELT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c63edb85327f9aef</t>
+          <t>https://www.indeed.com/viewjob?jk=de10d304d09880c3</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>DEVELOPER L3(CONTRACT)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, Snowflake, SQL Server, MySQL, ELT</t>
+          <t>AWS, Databricks, Cloud Storage, Spark, PySpark, Scala, Snowflake, Time Travel, Databricks Lakehouse, Snowflake Schema</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de10d304d09880c3</t>
+          <t>https://www.indeed.com/viewjob?jk=1c37881d8861b3d6</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DEVELOPER L3(CONTRACT)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Cloud Storage, Spark, PySpark, Scala, Snowflake, Time Travel, Databricks Lakehouse, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, Cassandra, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c37881d8861b3d6</t>
+          <t>https://www.indeed.com/viewjob?jk=fb97e11dedc46f7e</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Ad Ops Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, Cassandra, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb97e11dedc46f7e</t>
+          <t>https://www.indeed.com/viewjob?jk=3d412becc7b99de0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer Seniors – Cloud Technologies | Fintech | Full Stack</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Blue Orange Digital</t>
+          <t>FIS</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Data Factory, Scala, Oracle, SQL Server, NoSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb853658114af880</t>
+          <t>https://www.indeed.com/viewjob?jk=d35fe7a7c554f8b5</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Ad Ops Engineer</t>
+          <t>Platform Engineer Senior</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Texas Capital Bank</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,42 +1641,42 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, Redshift, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d412becc7b99de0</t>
+          <t>https://www.indeed.com/viewjob?jk=09ac756571edd2b5</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineer Seniors – Cloud Technologies | Fintech | Full Stack</t>
+          <t>Senior Dev Ops Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>FIS</t>
+          <t>SkyWater Technology Foundry</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Oracle, SQL Server, NoSQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Photon, GCP, Vertex AI, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d35fe7a7c554f8b5</t>
+          <t>https://www.indeed.com/viewjob?jk=13bfee40249f3478</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Platform Engineer Senior</t>
+          <t>Data Management Architect (Manufacturing)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Texas Capital Bank</t>
+          <t>Infor</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Oracle, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09ac756571edd2b5</t>
+          <t>https://www.indeed.com/viewjob?jk=e45199011cbe2990</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Management Architect (Manufacturing)</t>
+          <t>OnStar Vehicle Data System Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Infor</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Oracle, MySQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Sqoop, Scala, Kafka, Oracle, Cassandra</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e45199011cbe2990</t>
+          <t>https://www.indeed.com/viewjob?jk=23b443a7cc921497</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>OnStar Vehicle Data System Engineer</t>
+          <t>Software Engineer I – AI Assistant Framework, ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Sqoop, Scala, Kafka, Oracle, Cassandra</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23b443a7cc921497</t>
+          <t>https://www.indeed.com/viewjob?jk=2546eaf4a3e50baf</t>
         </is>
       </c>
     </row>
@@ -1833,17 +1833,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer I – AI Assistant Framework, ArcGIS Enterprise</t>
+          <t>Power Automate Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>JCA Surety Group</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,17 +1851,17 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2546eaf4a3e50baf</t>
+          <t>https://www.indeed.com/viewjob?jk=ebd1ccebdb7a4ed2</t>
         </is>
       </c>
     </row>
@@ -2498,17 +2498,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior SRE</t>
+          <t>Quality Assurance Analyst / ETL Tester</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>Briljent</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, Splunk, CI/CD</t>
+          <t>RDS, Azure, Snowflake, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=992bf08b9bf1cd4c</t>
+          <t>https://www.indeed.com/viewjob?jk=d69b1256484e3a82</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Artificial Intelligence/Machine Learning Data Engineer</t>
+          <t>Software Development Engineer II</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Logic, Inc.</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e34c2e31eeb33f9e</t>
+          <t>https://www.indeed.com/viewjob?jk=c0d2f3586b2ed198</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>Senior Site Reliability Engineer II</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0d2f3586b2ed198</t>
+          <t>https://www.indeed.com/viewjob?jk=6fa53cf983e1a6d0</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer II</t>
+          <t>Sr. DevOps Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>Eclypsium</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, Splunk, CI/CD</t>
+          <t>AWS, Lambda, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fa53cf983e1a6d0</t>
+          <t>https://www.indeed.com/viewjob?jk=746eae080f33e9b0</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sr. DevOps Engineer</t>
+          <t>Artificial Intelligence/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Eclypsium</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=746eae080f33e9b0</t>
+          <t>https://www.indeed.com/viewjob?jk=8f6f11467cb82584</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr. API Engineer</t>
+          <t>Artificial Intelligence/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, DynamoDB, ELT</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b02c1c05cdd16b9</t>
+          <t>https://www.indeed.com/viewjob?jk=c9ce81a6707266dd</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr. API Engineer</t>
+          <t>Artificial Intelligence/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>Logic, Inc.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, DynamoDB, ELT</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d9aa07e40090d93</t>
+          <t>https://www.indeed.com/viewjob?jk=e34c2e31eeb33f9e</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sr. API Engineer</t>
+          <t>Senior Machine Learning Engineer (Remote)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, DynamoDB, ELT</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, NoSQL, CI/CD, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4277c27f2f782266</t>
+          <t>https://www.indeed.com/viewjob?jk=fdbdb16275078800</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr. API Engineer</t>
+          <t>Sr. Java Developers</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>Vibotek LLC</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, DynamoDB, ELT</t>
+          <t>AWS, HBase, Spark, Scala, Kafka, Oracle, Cassandra, NoSQL, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,67 +2806,67 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef0f69867247772a</t>
+          <t>https://www.indeed.com/viewjob?jk=061d80fcb09266da</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, APIs</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>First Citizens Bank</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, DynamoDB, ELT</t>
+          <t>AWS, RDS, Hadoop, Hive, Spark, PySpark, Scala, Oracle, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d448f5377465e81</t>
+          <t>https://www.indeed.com/viewjob?jk=8629753fa2cdcb2f</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sr. API Engineer</t>
+          <t>Systems &amp; Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>Kretek International</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>Moorpark, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, DynamoDB, ELT</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Splunk, Terraform</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aca94a7c92083f9d</t>
+          <t>https://www.indeed.com/viewjob?jk=a7d7d86c5d6aef50</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (Remote)</t>
+          <t>Data Engineer - Performance Management</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Lake Buena Vista, FL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, NoSQL, CI/CD, Git, Python, SQL</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdbdb16275078800</t>
+          <t>https://www.indeed.com/viewjob?jk=57b0af5961338ef2</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sr. Java Developers</t>
+          <t>Full Stack, Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Vibotek LLC</t>
+          <t>SCAN Health Plan</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, HBase, Spark, Scala, Kafka, Oracle, Cassandra, NoSQL, Jenkins, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=061d80fcb09266da</t>
+          <t>https://www.indeed.com/viewjob?jk=6b0db4093988ff3c</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>First Citizens Bank</t>
+          <t>Hightower Advisors</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, Spark, PySpark, Scala, Oracle, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8629753fa2cdcb2f</t>
+          <t>https://www.indeed.com/viewjob?jk=bee78aad0ae84553</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data and Analytics Platform Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Motiva Enterprises LLC</t>
+          <t>Tennessee Titans</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, Star Schema</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45b3fd0f3632a8d6</t>
+          <t>https://www.indeed.com/viewjob?jk=b7b90aa43b4806b0</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Systems &amp; Cloud Infrastructure Engineer</t>
+          <t>Software Systems Engineer, Release Reliability &amp; Automation (Autonomous Vehicles)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Kretek International</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Moorpark, CA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Splunk, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Power BI, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7d7d86c5d6aef50</t>
+          <t>https://www.indeed.com/viewjob?jk=f97782145b5d3f94</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Engineer - Performance Management</t>
+          <t>Reliability Engineer (Autonomous Vehicles)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Lake Buena Vista, FL, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Power BI, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57b0af5961338ef2</t>
+          <t>https://www.indeed.com/viewjob?jk=cf25e4c14df46394</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Full Stack, Data &amp; Analytics Engineer</t>
+          <t>AI/ML Developer II (Remote)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SCAN Health Plan</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, NoSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b0db4093988ff3c</t>
+          <t>https://www.indeed.com/viewjob?jk=fb663396a5bc1b79</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Hightower Advisors</t>
+          <t>Accompany Health</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Spark, Scala, Kafka, NoSQL, Data Modeling, Terraform, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bee78aad0ae84553</t>
+          <t>https://www.indeed.com/viewjob?jk=f41df6bde69aeb07</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Quality Automation Engineer (SDET) - Career</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Tennessee Titans</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Data Modeling, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,102 +3191,102 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7b90aa43b4806b0</t>
+          <t>https://www.indeed.com/viewjob?jk=b597edf918184e10</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Software Systems Engineer, Release Reliability &amp; Automation (Autonomous Vehicles)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Power BI, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f97782145b5d3f94</t>
+          <t>https://www.indeed.com/viewjob?jk=d33e81401b69b22c</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Reliability Engineer (Autonomous Vehicles)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Power BI, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf25e4c14df46394</t>
+          <t>https://www.indeed.com/viewjob?jk=ffcaa5c8b2e22e2b</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>AI/ML Developer II (Remote)</t>
+          <t>Data Engineer, Go to Market (Remote)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, NoSQL, ETL, ELT</t>
+          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb663396a5bc1b79</t>
+          <t>https://www.indeed.com/viewjob?jk=8c7e11f90c05edfc</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Infrastructure &amp; Security Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Accompany Health</t>
+          <t>HerculesAI</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Campbell, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Glue, Spark, Scala, Kafka, NoSQL, Data Modeling, Terraform, Airflow, Apache Airflow</t>
+          <t>AWS, Lambda, IAM, Azure, GCP, Splunk, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f41df6bde69aeb07</t>
+          <t>https://www.indeed.com/viewjob?jk=997e47a23e0d8261</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Quality Automation Engineer (SDET) - Career</t>
+          <t>Software Engineer III - Data, AWS, ETL, Java/Python,</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b597edf918184e10</t>
+          <t>https://www.indeed.com/viewjob?jk=24b2eb0df8c7e284</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Cityblock Health</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, IAM, RDS, Azure, GCP, BigQuery, PostgreSQL, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d33e81401b69b22c</t>
+          <t>https://www.indeed.com/viewjob?jk=76d763c610ac1510</t>
         </is>
       </c>
     </row>
@@ -3413,12 +3413,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Carrier</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffcaa5c8b2e22e2b</t>
+          <t>https://www.indeed.com/viewjob?jk=ab7c6d265d3522d2</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Engineer, Go to Market (Remote)</t>
+          <t>Senior Data Engineer - GM Motorsports</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Concord, NC, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, Databricks Lakehouse, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c7e11f90c05edfc</t>
+          <t>https://www.indeed.com/viewjob?jk=c80625f8482f70fb</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Sr. Infrastructure &amp; Security Engineer</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>HerculesAI</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Campbell, CA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, Azure, GCP, Splunk, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=997e47a23e0d8261</t>
+          <t>https://www.indeed.com/viewjob?jk=76b52e35f38bdeca</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data, AWS, ETL, Java/Python,</t>
+          <t>AI Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, ETL, CI/CD, Terraform</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24b2eb0df8c7e284</t>
+          <t>https://www.indeed.com/viewjob?jk=2eeb9a92ff909033</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>AI Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Cityblock Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, BigQuery, PostgreSQL, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76d763c610ac1510</t>
+          <t>https://www.indeed.com/viewjob?jk=1c1b56e7aa8c4561</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Carrier</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab7c6d265d3522d2</t>
+          <t>https://www.indeed.com/viewjob?jk=e9f259bbce0ce033</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GM Motorsports</t>
+          <t>AI Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Concord, NC, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, Databricks Lakehouse, NoSQL, Docker</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c80625f8482f70fb</t>
+          <t>https://www.indeed.com/viewjob?jk=143101384ee45578</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>SW Engineer - Sr. Consultant level</t>
+          <t>Senior DBA / Database Architect</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Opeeka, Inc.</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Folsom, CA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, Oracle, MySQL, NoSQL, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Bitbucket</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83fb65ae6e18206f</t>
+          <t>https://www.indeed.com/viewjob?jk=5142b758be4e8f87</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior DBA / Database Architect</t>
+          <t>Application Developer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Opeeka, Inc.</t>
+          <t>Value Truck of Arizona</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Folsom, CA, US USA</t>
+          <t>South Jordan, UT, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Bitbucket</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5142b758be4e8f87</t>
+          <t>https://www.indeed.com/viewjob?jk=f6c3e26366316cc8</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Application Developer</t>
+          <t>SW Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Value Truck of Arizona</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>South Jordan, UT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
+          <t>RDS, Scala, Kafka, Oracle, MySQL, NoSQL, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6c3e26366316cc8</t>
+          <t>https://www.indeed.com/viewjob?jk=83fb65ae6e18206f</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd22b6d5954a33c2</t>
+          <t>https://www.indeed.com/viewjob?jk=c5c449cb4c336ec2</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d369f55f3c43cd0</t>
+          <t>https://www.indeed.com/viewjob?jk=e57a91ca929fec5b</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5e852e1fb093faa</t>
+          <t>https://www.indeed.com/viewjob?jk=cd22b6d5954a33c2</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=122021b0213972fb</t>
+          <t>https://www.indeed.com/viewjob?jk=2d369f55f3c43cd0</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf263b65906b30ba</t>
+          <t>https://www.indeed.com/viewjob?jk=b5e852e1fb093faa</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=775f4b74d2e0d125</t>
+          <t>https://www.indeed.com/viewjob?jk=122021b0213972fb</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e27aa2f30115d6a9</t>
+          <t>https://www.indeed.com/viewjob?jk=cf263b65906b30ba</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=372ffe4f2e9a605d</t>
+          <t>https://www.indeed.com/viewjob?jk=775f4b74d2e0d125</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a256a77103c9ee18</t>
+          <t>https://www.indeed.com/viewjob?jk=e27aa2f30115d6a9</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b082342159bbdf7</t>
+          <t>https://www.indeed.com/viewjob?jk=372ffe4f2e9a605d</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e06cd5eb56a43b5c</t>
+          <t>https://www.indeed.com/viewjob?jk=a256a77103c9ee18</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daaeb6d16db98abf</t>
+          <t>https://www.indeed.com/viewjob?jk=9b082342159bbdf7</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19a128257d3c2c77</t>
+          <t>https://www.indeed.com/viewjob?jk=e06cd5eb56a43b5c</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d47c2036fa69322</t>
+          <t>https://www.indeed.com/viewjob?jk=daaeb6d16db98abf</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5c449cb4c336ec2</t>
+          <t>https://www.indeed.com/viewjob?jk=5d61083f86948477</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e57a91ca929fec5b</t>
+          <t>https://www.indeed.com/viewjob?jk=71d4be4e91f6174a</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d61083f86948477</t>
+          <t>https://www.indeed.com/viewjob?jk=912b927f8e6b0bc9</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71d4be4e91f6174a</t>
+          <t>https://www.indeed.com/viewjob?jk=697335a3240f02f2</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=912b927f8e6b0bc9</t>
+          <t>https://www.indeed.com/viewjob?jk=e21309c64f987c4d</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=697335a3240f02f2</t>
+          <t>https://www.indeed.com/viewjob?jk=6e4114c9ced06f08</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e21309c64f987c4d</t>
+          <t>https://www.indeed.com/viewjob?jk=0379c77fb1bea285</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e4114c9ced06f08</t>
+          <t>https://www.indeed.com/viewjob?jk=c7404f3dbf25b5d0</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0379c77fb1bea285</t>
+          <t>https://www.indeed.com/viewjob?jk=19a128257d3c2c77</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7404f3dbf25b5d0</t>
+          <t>https://www.indeed.com/viewjob?jk=6a667aa6f915c8e9</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a667aa6f915c8e9</t>
+          <t>https://www.indeed.com/viewjob?jk=8d47c2036fa69322</t>
         </is>
       </c>
     </row>
@@ -5263,7 +5263,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Full‑Stack Developer (Java, React, Microservices) *Hybrid*</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -5281,24 +5281,24 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=229f6840535c3531</t>
+          <t>https://www.indeed.com/viewjob?jk=983d0a4b6df6a34b</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Full‑Stack Developer (Java, React, Microservices) *Hybrid*</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,24 +5316,24 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606324c85c044a5d</t>
+          <t>https://www.indeed.com/viewjob?jk=e39cfd742ca8ccb7</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Full‑Stack Developer (Java, React, Microservices) *Hybrid*</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,34 +5351,34 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f298bb4ddf8e9a0</t>
+          <t>https://www.indeed.com/viewjob?jk=4d24b9bb7d3f81d1</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Evanston, IL, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,34 +5386,34 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3493170e435cd93</t>
+          <t>https://www.indeed.com/viewjob?jk=406f01e6594b2624</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - GM Motorsports</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Concord, NC, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,34 +5421,34 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, GCP, Scala, Kafka, MongoDB, NoSQL, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f660072154c9a61</t>
+          <t>https://www.indeed.com/viewjob?jk=0206f3baae13d0ec</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Developer</t>
+          <t>Full‑Stack Developer (Java, React, Microservices) *Hybrid*</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Douglas Machine Inc.</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Alexandria, MN, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,24 +5466,24 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9d5d216fe71b48e</t>
+          <t>https://www.indeed.com/viewjob?jk=229f6840535c3531</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full‑Stack Developer (Java, React, Microservices) *Hybrid*</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>SEI Investments</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Oaks, PA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Kafka, Snowflake, Oracle, SQL Server, MySQL, MongoDB, Jenkins, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5501,24 +5501,24 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76c94610856b0496</t>
+          <t>https://www.indeed.com/viewjob?jk=606324c85c044a5d</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Backend Cloud Software Engineer</t>
+          <t>Full‑Stack Developer (Java, React, Microservices) *Hybrid*</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>AMPURE CHARGING SYSTEMS INC</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Monrovia, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,15 +5526,225 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0f298bb4ddf8e9a0</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Information Technology - Data Integration Engineer</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Magnolia</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Waco, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=22a077ceb692752f</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>RELX Group</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Evanston, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a3493170e435cd93</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - GM Motorsports</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>General Motors (GM)</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Concord, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Event Hubs, GCP, Scala, Kafka, MongoDB, NoSQL, Docker</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6f660072154c9a61</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Senior Business Intelligence Developer</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Douglas Machine Inc.</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Alexandria, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f9d5d216fe71b48e</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>SEI Investments</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Oaks, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Kafka, Snowflake, Oracle, SQL Server, MySQL, MongoDB, Jenkins, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=76c94610856b0496</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Backend Cloud Software Engineer</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>AMPURE CHARGING SYSTEMS INC</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Monrovia, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
           <t>AWS, Lambda, SQS, ECS, Scala, DynamoDB, CI/CD, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=55f56ffe2c84dc87</t>
         </is>

--- a/results/job_matches_2026-05-01.xlsx
+++ b/results/job_matches_2026-05-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G152"/>
+  <dimension ref="A1:G154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Python / PySpark (Mainframe Modernization) (contract)</t>
+          <t>Data Architecture &amp; Engineering - Senior - Financial Services - Consulting - NYC</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.2</v>
+        <v>24.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Azure, Databricks, Hadoop, HDFS, Hive</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Hadoop, Spark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=015fe1a494f266bf</t>
+          <t>https://www.indeed.com/viewjob?jk=f739fe0e3b71b0c3</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bid Role - Data Architect (STAR 4275)</t>
+          <t>Senior Software Engineer – Python / PySpark (Mainframe Modernization) (contract)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Leading Path Consulting</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.8</v>
+        <v>22.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Azure, Databricks, Hadoop, HDFS, Hive</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1801c08f952fa8a2</t>
+          <t>https://www.indeed.com/viewjob?jk=015fe1a494f266bf</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Bid Role - Data Architect (STAR 4275)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Leading Path Consulting</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>19.4</v>
+        <v>20.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Dataflow, Spark, Scala, Kafka, NoSQL, Data Modeling, ELT</t>
+          <t>AWS, Kinesis, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49b6a92728349bc5</t>
+          <t>https://www.indeed.com/viewjob?jk=1801c08f952fa8a2</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Select Minds LLC</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, Databricks, Spark</t>
+          <t>AWS, RDS, Azure, Dataflow, Spark, Scala, Kafka, NoSQL, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,59 +601,59 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9d0ac6d3cf445a9</t>
+          <t>https://www.indeed.com/viewjob?jk=49b6a92728349bc5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer (SQL, Python, Cloud)</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AEM Corporation</t>
+          <t>Select Minds LLC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, Databricks, Spark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb194f6feb01a9b5</t>
+          <t>https://www.indeed.com/viewjob?jk=d9d0ac6d3cf445a9</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Technical Architect-Datawarehousing</t>
+          <t>Data Engineer (SQL, Python, Cloud)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>AEM Corporation</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Marlborough, MA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,69 +661,69 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10720f22d9d38621</t>
+          <t>https://www.indeed.com/viewjob?jk=eb194f6feb01a9b5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AV Safety Engineering Analytics AI/ML Engineer (GPSSC)</t>
+          <t>Technical Architect-Datawarehousing</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Marlborough, MA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Dataflow, Spark, PySpark</t>
+          <t>AWS, S3, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=675259892fa0b51c</t>
+          <t>https://www.indeed.com/viewjob?jk=10720f22d9d38621</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr Software Engineer II - Enterprise Architecture</t>
+          <t>AV Safety Engineering Analytics AI/ML Engineer (GPSSC)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Dataflow, Spark, PySpark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6bd0f139eec27a7</t>
+          <t>https://www.indeed.com/viewjob?jk=675259892fa0b51c</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Cloud Network Automation Engineer</t>
+          <t>Cons - TC - AI and Data - Enterp Data - Data Eng and Arch - Data Eng - Mgr - MP - 1688246</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,42 +766,42 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Google Cloud Platform, GCP, Hadoop, HDFS, Oracle</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a0cf6116e02d635</t>
+          <t>https://www.indeed.com/viewjob?jk=44bbdbe739d23ea2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Cloud Engineer II</t>
+          <t>Sr Software Engineer II - Enterprise Architecture</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Vibrant Emotional Health</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ba39b2a6826c32d</t>
+          <t>https://www.indeed.com/viewjob?jk=f6bd0f139eec27a7</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Engineer - AI &amp; Data Management</t>
+          <t>Cloud Network Automation Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>S3, Azure, Data Factory, Cloud Storage, Hadoop, HDFS, Spark, Scala, Kafka, Informatica PowerCenter</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,19 +846,19 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f98760c842e5085</t>
+          <t>https://www.indeed.com/viewjob?jk=0a0cf6116e02d635</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Cloud Engineer II</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tradeweb</t>
+          <t>Vibrant Emotional Health</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -867,11 +867,11 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, GCP, Spark, Kafka, Dask, Snowflake</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb2021c38a5314d9</t>
+          <t>https://www.indeed.com/viewjob?jk=3ba39b2a6826c32d</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GenAI Threat Intelligence Analyst</t>
+          <t>Senior Engineer - AI &amp; Data Management</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Blob Storage, Google Cloud Platform, Vertex AI, Scala, MLOps, MLflow</t>
+          <t>S3, Azure, Data Factory, Cloud Storage, Hadoop, HDFS, Spark, Scala, Kafka, Informatica PowerCenter</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,19 +916,19 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5efecdb56da9cdd1</t>
+          <t>https://www.indeed.com/viewjob?jk=0f98760c842e5085</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Metropolitan Commercial Bank</t>
+          <t>Tradeweb</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, NoSQL</t>
+          <t>AWS, Redshift, S3, IAM, RDS, GCP, Spark, Kafka, Dask, Snowflake</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25250927f01c87fd</t>
+          <t>https://www.indeed.com/viewjob?jk=cb2021c38a5314d9</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>GenAI Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Credera</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Oozie, Spark, Scala, Kafka, SQL Server</t>
+          <t>AWS, RDS, Azure, Databricks, Blob Storage, Google Cloud Platform, Vertex AI, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2859c21fcc6b9b6</t>
+          <t>https://www.indeed.com/viewjob?jk=5efecdb56da9cdd1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Credera</t>
+          <t>Metropolitan Commercial Bank</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Oozie, Spark, Scala, Kafka, SQL Server</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e65ae12c9231691</t>
+          <t>https://www.indeed.com/viewjob?jk=25250927f01c87fd</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=deb9ad8464ceb6e6</t>
+          <t>https://www.indeed.com/viewjob?jk=a2859c21fcc6b9b6</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,42 +1091,42 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0faede29102fb7e1</t>
+          <t>https://www.indeed.com/viewjob?jk=9e65ae12c9231691</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Azure Data &amp; Development Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SunStone Consulting</t>
+          <t>Credera</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Event Hubs, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Oozie, Spark, Scala, Kafka, SQL Server</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e9052cac6c7210d</t>
+          <t>https://www.indeed.com/viewjob?jk=deb9ad8464ceb6e6</t>
         </is>
       </c>
     </row>
@@ -1138,20 +1138,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ABCorp NA Inc.</t>
+          <t>Credera</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Oozie, Spark, Scala, Kafka, SQL Server</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e06fd43e0f99777</t>
+          <t>https://www.indeed.com/viewjob?jk=0faede29102fb7e1</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Azure Data &amp; Development Architect</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>TeraWatt Infrastructure</t>
+          <t>SunStone Consulting</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Event Hubs, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cf13a405f291139</t>
+          <t>https://www.indeed.com/viewjob?jk=1e9052cac6c7210d</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineer, Full Stack - AI (Chicago)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Fitch Group</t>
+          <t>ABCorp NA Inc.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,14 +1231,14 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4bb35a3533f1ee6</t>
+          <t>https://www.indeed.com/viewjob?jk=1e06fd43e0f99777</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Engineering &amp; Quality - Software Engineer, Full Stack - AI</t>
+          <t>Software Engineer, Full Stack - AI (Chicago)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,19 +1266,19 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf6b928dd59e0c41</t>
+          <t>https://www.indeed.com/viewjob?jk=d4bb35a3533f1ee6</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Engineering &amp; Quality - Software Engineer, Full Stack - AI</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Fitch Group</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1287,11 +1287,11 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
+          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fc4628968aad9e2</t>
+          <t>https://www.indeed.com/viewjob?jk=cf6b928dd59e0c41</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0eb5fc1d601c0028</t>
+          <t>https://www.indeed.com/viewjob?jk=0fc4628968aad9e2</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acae1b7fc51e9a39</t>
+          <t>https://www.indeed.com/viewjob?jk=0eb5fc1d601c0028</t>
         </is>
       </c>
     </row>
@@ -1383,12 +1383,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Trane Technologies</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f483db2edc8cb83a</t>
+          <t>https://www.indeed.com/viewjob?jk=acae1b7fc51e9a39</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>JUUL Labs</t>
+          <t>Trane Technologies</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, GCP, Dataflow, Cloud Storage, Scala, Splunk</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c63edb85327f9aef</t>
+          <t>https://www.indeed.com/viewjob?jk=f483db2edc8cb83a</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JUUL Labs</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, Snowflake, SQL Server, MySQL, ELT</t>
+          <t>AWS, S3, ECS, IAM, RDS, GCP, Dataflow, Cloud Storage, Scala, Splunk</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de10d304d09880c3</t>
+          <t>https://www.indeed.com/viewjob?jk=c63edb85327f9aef</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>DEVELOPER L3(CONTRACT)</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Cloud Storage, Spark, PySpark, Scala, Snowflake, Time Travel, Databricks Lakehouse, Snowflake Schema</t>
+          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, Snowflake, SQL Server, MySQL, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c37881d8861b3d6</t>
+          <t>https://www.indeed.com/viewjob?jk=de10d304d09880c3</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>DEVELOPER L3(CONTRACT)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, Cassandra, CI/CD, Jenkins</t>
+          <t>AWS, Databricks, Cloud Storage, Spark, PySpark, Scala, Snowflake, Time Travel, Databricks Lakehouse, Snowflake Schema</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb97e11dedc46f7e</t>
+          <t>https://www.indeed.com/viewjob?jk=1c37881d8861b3d6</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Ad Ops Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, Cassandra, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d412becc7b99de0</t>
+          <t>https://www.indeed.com/viewjob?jk=fb97e11dedc46f7e</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Engineer Seniors – Cloud Technologies | Fintech | Full Stack</t>
+          <t>Senior Ad Ops Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FIS</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Oracle, SQL Server, NoSQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d35fe7a7c554f8b5</t>
+          <t>https://www.indeed.com/viewjob?jk=3d412becc7b99de0</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Platform Engineer Senior</t>
+          <t>AI Developer - Senior - A&amp;I - Financial Services - Consulting - NYC, Charlotte, Dallas</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Texas Capital Bank</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,42 +1641,42 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, CI/CD</t>
+          <t>AWS, Lambda, Redshift, RDS, Azure, Synapse Analytics, BigQuery, Hadoop, Hive, HBase</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09ac756571edd2b5</t>
+          <t>https://www.indeed.com/viewjob?jk=3b189ba2f7b20d0b</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Dev Ops Engineer</t>
+          <t>Software Engineer Seniors – Cloud Technologies | Fintech | Full Stack</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SkyWater Technology Foundry</t>
+          <t>FIS</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Photon, GCP, Vertex AI, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Azure, Data Factory, Scala, Oracle, SQL Server, NoSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13bfee40249f3478</t>
+          <t>https://www.indeed.com/viewjob?jk=d35fe7a7c554f8b5</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Management Architect (Manufacturing)</t>
+          <t>Platform Engineer Senior</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Infor</t>
+          <t>Texas Capital Bank</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Oracle, MySQL, Data Modeling, ETL</t>
+          <t>AWS, Lambda, Redshift, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e45199011cbe2990</t>
+          <t>https://www.indeed.com/viewjob?jk=09ac756571edd2b5</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>OnStar Vehicle Data System Engineer</t>
+          <t>Senior Dev Ops Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>SkyWater Technology Foundry</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Sqoop, Scala, Kafka, Oracle, Cassandra</t>
+          <t>AWS, IAM, RDS, Photon, GCP, Vertex AI, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23b443a7cc921497</t>
+          <t>https://www.indeed.com/viewjob?jk=13bfee40249f3478</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer I – AI Assistant Framework, ArcGIS Enterprise</t>
+          <t>Business Intelligence Solutions Architect</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>Mars Technominds</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2546eaf4a3e50baf</t>
+          <t>https://www.indeed.com/viewjob?jk=38246f1a187f1c7d</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Site AI Engineer</t>
+          <t>Data Management Architect (Manufacturing)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Infor</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Temple, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Oracle, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9df42fb6f0e5b92</t>
+          <t>https://www.indeed.com/viewjob?jk=e45199011cbe2990</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Power Automate Engineer</t>
+          <t>Software Engineer I – AI Assistant Framework, ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>JCA Surety Group</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,42 +1851,42 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebd1ccebdb7a4ed2</t>
+          <t>https://www.indeed.com/viewjob?jk=2546eaf4a3e50baf</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>Site AI Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Temple, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, S3, IAM, Hadoop, Spark, Kafka, Snowflake, Splunk</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,59 +1896,59 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f01d239e5c828f6</t>
+          <t>https://www.indeed.com/viewjob?jk=b9df42fb6f0e5b92</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Power Automate Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Intelligent Medical Objects</t>
+          <t>JCA Surety Group</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Spark, Scala, Data Modeling, dbt, Power BI</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4869d3a6ac24136</t>
+          <t>https://www.indeed.com/viewjob?jk=ebd1ccebdb7a4ed2</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Infrastructure-as-Code (IaC) Engineer</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Databricks</t>
+          <t>AWS, Redshift, Athena, S3, IAM, Hadoop, Spark, Kafka, Snowflake, Splunk</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca35900639cbe443</t>
+          <t>https://www.indeed.com/viewjob?jk=0f01d239e5c828f6</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Engineer - Agentic AI</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Intelligent Medical Objects</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Spark, Scala, Data Modeling, dbt, Power BI</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5daf8f72a4fd9ab6</t>
+          <t>https://www.indeed.com/viewjob?jk=c4869d3a6ac24136</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer/SRE - GM Energy</t>
+          <t>Infrastructure-as-Code (IaC) Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Databricks</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0413ce8de5fcca6a</t>
+          <t>https://www.indeed.com/viewjob?jk=ca35900639cbe443</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Developer - Used Car Marketplace</t>
+          <t>Senior Engineer - Agentic AI</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, SQS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d487bcb34632271a</t>
+          <t>https://www.indeed.com/viewjob?jk=5daf8f72a4fd9ab6</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
+          <t>Senior Backend Software Engineer/SRE - GM Energy</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79a2a043dc5cdb8f</t>
+          <t>https://www.indeed.com/viewjob?jk=0413ce8de5fcca6a</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
+          <t>Software Developer - Used Car Marketplace</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,17 +2131,17 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e387db2c2b866baa</t>
+          <t>https://www.indeed.com/viewjob?jk=d487bcb34632271a</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18a022cbc2b4d934</t>
+          <t>https://www.indeed.com/viewjob?jk=79a2a043dc5cdb8f</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cc4f959dd712f8a</t>
+          <t>https://www.indeed.com/viewjob?jk=e387db2c2b866baa</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Yonkers, NY, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=688d7763683eecad</t>
+          <t>https://www.indeed.com/viewjob?jk=18a022cbc2b4d934</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Distinguished Engineer -</t>
+          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, GCP, Snowflake, ELT, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=087eb595cff7bd93</t>
+          <t>https://www.indeed.com/viewjob?jk=5cc4f959dd712f8a</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Smithfield, RI, US USA</t>
+          <t>Yonkers, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,42 +2306,42 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Spark, Scala, Snowflake, Oracle, ETL, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cc22367a2ce3d9f</t>
+          <t>https://www.indeed.com/viewjob?jk=688d7763683eecad</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AI/ML Engineer – Data &amp; Full-Stack Solutions</t>
+          <t>Distinguished Engineer -</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ITC Federal</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, ETL, ELT, CI/CD</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, GCP, Snowflake, ELT, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,59 +2351,59 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce30a23eaa64abcd</t>
+          <t>https://www.indeed.com/viewjob?jk=087eb595cff7bd93</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Commercial Software</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Smithfield, RI, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Oracle, MySQL</t>
+          <t>AWS, EMR, RDS, Spark, Scala, Snowflake, Oracle, ETL, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ca1245fe1b2a956</t>
+          <t>https://www.indeed.com/viewjob?jk=5cc22367a2ce3d9f</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer III ***Raleigh, NC***</t>
+          <t>AI/ML Engineer – Data &amp; Full-Stack Solutions</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>ITC Federal</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Hadoop, Spark, Scala, Kafka, DynamoDB, CI/CD</t>
+          <t>AWS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35085eed81ec8943</t>
+          <t>https://www.indeed.com/viewjob?jk=ce30a23eaa64abcd</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer III ***Raleigh, NC***</t>
+          <t>Senior Software Engineer - Commercial Software</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>LexisNexis Legal &amp; Professional</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Hadoop, Spark, Scala, Kafka, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Oracle, MySQL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70897e01c57b5008</t>
+          <t>https://www.indeed.com/viewjob?jk=4ca1245fe1b2a956</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Senior Machine Learning Engineer III ***Raleigh, NC***</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Snowflake, MLOps, CI/CD, Terraform</t>
+          <t>AWS, S3, SQS, RDS, Hadoop, Spark, Scala, Kafka, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36a73b40629cc484</t>
+          <t>https://www.indeed.com/viewjob?jk=35085eed81ec8943</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Quality Assurance Analyst / ETL Tester</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Briljent</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Snowflake, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL, Data Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Snowflake, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d69b1256484e3a82</t>
+          <t>https://www.indeed.com/viewjob?jk=36a73b40629cc484</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>Quality Assurance Analyst / ETL Tester</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Briljent</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>RDS, Azure, Snowflake, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0d2f3586b2ed198</t>
+          <t>https://www.indeed.com/viewjob?jk=d69b1256484e3a82</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer II</t>
+          <t>Software Development Engineer II</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, Splunk, CI/CD</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fa53cf983e1a6d0</t>
+          <t>https://www.indeed.com/viewjob?jk=c0d2f3586b2ed198</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr. DevOps Engineer</t>
+          <t>Senior Site Reliability Engineer II</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Eclypsium</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=746eae080f33e9b0</t>
+          <t>https://www.indeed.com/viewjob?jk=6fa53cf983e1a6d0</t>
         </is>
       </c>
     </row>
@@ -3128,17 +3128,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer II, Global Servicing Technology</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Accompany Health</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Glue, Spark, Scala, Kafka, NoSQL, Data Modeling, Terraform, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Google Cloud Platform, Cloud Storage, Hive, Spark, Scala, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f41df6bde69aeb07</t>
+          <t>https://www.indeed.com/viewjob?jk=5c5c9f5bf8d54b87</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Quality Automation Engineer (SDET) - Career</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Accompany Health</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Glue, Spark, Scala, Kafka, NoSQL, Data Modeling, Terraform, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b597edf918184e10</t>
+          <t>https://www.indeed.com/viewjob?jk=f41df6bde69aeb07</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Quality Automation Engineer (SDET) - Career</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d33e81401b69b22c</t>
+          <t>https://www.indeed.com/viewjob?jk=b597edf918184e10</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffcaa5c8b2e22e2b</t>
+          <t>https://www.indeed.com/viewjob?jk=d33e81401b69b22c</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Engineer, Go to Market (Remote)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
+          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c7e11f90c05edfc</t>
+          <t>https://www.indeed.com/viewjob?jk=ffcaa5c8b2e22e2b</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Sr. Infrastructure &amp; Security Engineer</t>
+          <t>Data Engineer, Go to Market (Remote)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>HerculesAI</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Campbell, CA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, Azure, GCP, Splunk, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=997e47a23e0d8261</t>
+          <t>https://www.indeed.com/viewjob?jk=8c7e11f90c05edfc</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data, AWS, ETL, Java/Python,</t>
+          <t>Sr. Infrastructure &amp; Security Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>HerculesAI</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Campbell, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, ETL, CI/CD, Terraform</t>
+          <t>AWS, Lambda, IAM, Azure, GCP, Splunk, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24b2eb0df8c7e284</t>
+          <t>https://www.indeed.com/viewjob?jk=997e47a23e0d8261</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Software Engineer III - Data, AWS, ETL, Java/Python,</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Cityblock Health</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, BigQuery, PostgreSQL, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76d763c610ac1510</t>
+          <t>https://www.indeed.com/viewjob?jk=24b2eb0df8c7e284</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Carrier</t>
+          <t>Cityblock Health</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, GCP, BigQuery, PostgreSQL, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab7c6d265d3522d2</t>
+          <t>https://www.indeed.com/viewjob?jk=76d763c610ac1510</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GM Motorsports</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Carrier</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Concord, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, Databricks Lakehouse, NoSQL, Docker</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c80625f8482f70fb</t>
+          <t>https://www.indeed.com/viewjob?jk=ab7c6d265d3522d2</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>AI Engineer Consultant</t>
+          <t>Senior Data Engineer - GM Motorsports</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Concord, NC, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,17 +3496,17 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, Databricks Lakehouse, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76b52e35f38bdeca</t>
+          <t>https://www.indeed.com/viewjob?jk=c80625f8482f70fb</t>
         </is>
       </c>
     </row>
@@ -3653,17 +3653,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior DBA / Database Architect</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Opeeka, Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Folsom, CA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Bitbucket</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5142b758be4e8f87</t>
+          <t>https://www.indeed.com/viewjob?jk=76b52e35f38bdeca</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Application Developer</t>
+          <t>Senior DBA / Database Architect</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Value Truck of Arizona</t>
+          <t>Opeeka, Inc.</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>South Jordan, UT, US USA</t>
+          <t>Folsom, CA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Bitbucket</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6c3e26366316cc8</t>
+          <t>https://www.indeed.com/viewjob?jk=5142b758be4e8f87</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>SW Engineer - Sr. Consultant level</t>
+          <t>Application Developer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Value Truck of Arizona</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>South Jordan, UT, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, Oracle, MySQL, NoSQL, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83fb65ae6e18206f</t>
+          <t>https://www.indeed.com/viewjob?jk=f6c3e26366316cc8</t>
         </is>
       </c>
     </row>
@@ -5088,17 +5088,17 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>PySpark Data Engineer III - Python/Java/SQL</t>
+          <t>FSO LABS - AI Developer Senior - Bay Area</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,34 +5106,34 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>RDS, Azure, Hadoop, Hive, Spark, Kafka, NoSQL, Power BI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=926547138e49a51b</t>
+          <t>https://www.indeed.com/viewjob?jk=1d75a18fe3bc2126</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Cloud Engineering &amp; FinOps</t>
+          <t>Databricks Data Engineer - Senior - Consulting - Location Open</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,34 +5141,34 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, AKS</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d576082b1c56db5c</t>
+          <t>https://www.indeed.com/viewjob?jk=599253e2d33dc75f</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer (R-19149)</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Dun &amp; Bradstreet</t>
+          <t>ObjectStream</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,34 +5176,34 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Blob Storage, Spark, PySpark, ETL, dbt, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb41c4b9d93e0f98</t>
+          <t>https://www.indeed.com/viewjob?jk=06e3854d22cdba89</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Software Architect, Attribution &amp; Integrations</t>
+          <t>PySpark Data Engineer III - Python/Java/SQL</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Invoca</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, MySQL, Data Modeling, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9dd5f05e7d0bdfd</t>
+          <t>https://www.indeed.com/viewjob?jk=926547138e49a51b</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
+          <t>Senior Software Engineer – Cloud Engineering &amp; FinOps</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Smyrna, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef040d1b01903853</t>
+          <t>https://www.indeed.com/viewjob?jk=d576082b1c56db5c</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Cloud Platform Engineer (R-19149)</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Dun &amp; Bradstreet</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,17 +5281,17 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=983d0a4b6df6a34b</t>
+          <t>https://www.indeed.com/viewjob?jk=cb41c4b9d93e0f98</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e39cfd742ca8ccb7</t>
+          <t>https://www.indeed.com/viewjob?jk=983d0a4b6df6a34b</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d24b9bb7d3f81d1</t>
+          <t>https://www.indeed.com/viewjob?jk=e39cfd742ca8ccb7</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=406f01e6594b2624</t>
+          <t>https://www.indeed.com/viewjob?jk=4d24b9bb7d3f81d1</t>
         </is>
       </c>
     </row>
@@ -5431,14 +5431,14 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0206f3baae13d0ec</t>
+          <t>https://www.indeed.com/viewjob?jk=406f01e6594b2624</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Full‑Stack Developer (Java, React, Microservices) *Hybrid*</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,34 +5456,34 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=229f6840535c3531</t>
+          <t>https://www.indeed.com/viewjob?jk=0206f3baae13d0ec</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Full‑Stack Developer (Java, React, Microservices) *Hybrid*</t>
+          <t>Software Architect, Attribution &amp; Integrations</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Invoca</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Scala, Kafka, MySQL, Data Modeling, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606324c85c044a5d</t>
+          <t>https://www.indeed.com/viewjob?jk=e9dd5f05e7d0bdfd</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5536,24 +5536,24 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f298bb4ddf8e9a0</t>
+          <t>https://www.indeed.com/viewjob?jk=229f6840535c3531</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Information Technology - Data Integration Engineer</t>
+          <t>Full‑Stack Developer (Java, React, Microservices) *Hybrid*</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Magnolia</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Waco, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5571,24 +5571,24 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22a077ceb692752f</t>
+          <t>https://www.indeed.com/viewjob?jk=606324c85c044a5d</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Full‑Stack Developer (Java, React, Microservices) *Hybrid*</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Evanston, IL, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,34 +5596,34 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3493170e435cd93</t>
+          <t>https://www.indeed.com/viewjob?jk=0f298bb4ddf8e9a0</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - GM Motorsports</t>
+          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Concord, NC, US USA</t>
+          <t>Smyrna, GA, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5631,34 +5631,34 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, GCP, Scala, Kafka, MongoDB, NoSQL, Docker</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f660072154c9a61</t>
+          <t>https://www.indeed.com/viewjob?jk=ef040d1b01903853</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Developer</t>
+          <t>Information Technology - Data Integration Engineer</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Douglas Machine Inc.</t>
+          <t>Magnolia</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Alexandria, MN, US USA</t>
+          <t>Waco, TX, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5676,24 +5676,24 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9d5d216fe71b48e</t>
+          <t>https://www.indeed.com/viewjob?jk=22a077ceb692752f</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer - GM Motorsports</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>SEI Investments</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Oaks, PA, US USA</t>
+          <t>Concord, NC, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5701,34 +5701,34 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Kafka, Snowflake, Oracle, SQL Server, MySQL, MongoDB, Jenkins, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Event Hubs, GCP, Scala, Kafka, MongoDB, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76c94610856b0496</t>
+          <t>https://www.indeed.com/viewjob?jk=6f660072154c9a61</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Backend Cloud Software Engineer</t>
+          <t>Senior Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>AMPURE CHARGING SYSTEMS INC</t>
+          <t>Douglas Machine Inc.</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Monrovia, CA, US USA</t>
+          <t>Alexandria, MN, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5736,15 +5736,85 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f9d5d216fe71b48e</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>SEI Investments</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Oaks, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Kafka, Snowflake, Oracle, SQL Server, MySQL, MongoDB, Jenkins, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=76c94610856b0496</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Backend Cloud Software Engineer</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>AMPURE CHARGING SYSTEMS INC</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Monrovia, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
           <t>AWS, Lambda, SQS, ECS, Scala, DynamoDB, CI/CD, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=55f56ffe2c84dc87</t>
         </is>

--- a/results/job_matches_2026-05-01.xlsx
+++ b/results/job_matches_2026-05-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G154"/>
+  <dimension ref="A1:G143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Architecture &amp; Engineering - Senior - Financial Services - Consulting - NYC</t>
+          <t>Senior Software Engineer – Python / PySpark (Mainframe Modernization) (contract)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>24.3</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Hadoop, Spark, Scala, Spark Streaming</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Azure, Databricks, Hadoop, HDFS, Hive</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f739fe0e3b71b0c3</t>
+          <t>https://www.indeed.com/viewjob?jk=015fe1a494f266bf</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Python / PySpark (Mainframe Modernization) (contract)</t>
+          <t>Bid Role - Data Architect (STAR 4275)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Leading Path Consulting</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>22.2</v>
+        <v>20.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Azure, Databricks, Hadoop, HDFS, Hive</t>
+          <t>AWS, Kinesis, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=015fe1a494f266bf</t>
+          <t>https://www.indeed.com/viewjob?jk=1801c08f952fa8a2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Bid Role - Data Architect (STAR 4275)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Leading Path Consulting</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.8</v>
+        <v>19.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Dataflow, Spark, Scala, Kafka, NoSQL, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1801c08f952fa8a2</t>
+          <t>https://www.indeed.com/viewjob?jk=49b6a92728349bc5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Select Minds LLC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Dataflow, Spark, Scala, Kafka, NoSQL, Data Modeling, ELT</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, Databricks, Spark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49b6a92728349bc5</t>
+          <t>https://www.indeed.com/viewjob?jk=d9d0ac6d3cf445a9</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Technical Architect-Datawarehousing</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Select Minds LLC</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Marlborough, MA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, Databricks, Spark</t>
+          <t>AWS, S3, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9d0ac6d3cf445a9</t>
+          <t>https://www.indeed.com/viewjob?jk=10720f22d9d38621</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer (SQL, Python, Cloud)</t>
+          <t>AV Safety Engineering Analytics AI/ML Engineer (GPSSC)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AEM Corporation</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Dataflow, Spark, PySpark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,59 +671,59 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb194f6feb01a9b5</t>
+          <t>https://www.indeed.com/viewjob?jk=675259892fa0b51c</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Technical Architect-Datawarehousing</t>
+          <t>Senior Software Engineer (C#/.NET &amp; AI)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Marlborough, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10720f22d9d38621</t>
+          <t>https://www.indeed.com/viewjob?jk=93c21b258a08bd24</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AV Safety Engineering Analytics AI/ML Engineer (GPSSC)</t>
+          <t>Sr Software Engineer II - Enterprise Architecture</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Dataflow, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=675259892fa0b51c</t>
+          <t>https://www.indeed.com/viewjob?jk=f6bd0f139eec27a7</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Cons - TC - AI and Data - Enterp Data - Data Eng and Arch - Data Eng - Mgr - MP - 1688246</t>
+          <t>Cloud Network Automation Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,42 +766,42 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Google Cloud Platform, GCP, Hadoop, HDFS, Oracle</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44bbdbe739d23ea2</t>
+          <t>https://www.indeed.com/viewjob?jk=0a0cf6116e02d635</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr Software Engineer II - Enterprise Architecture</t>
+          <t>Cloud Engineer II</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Vibrant Emotional Health</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6bd0f139eec27a7</t>
+          <t>https://www.indeed.com/viewjob?jk=3ba39b2a6826c32d</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Cloud Network Automation Engineer</t>
+          <t>Senior Engineer - AI &amp; Data Management</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
+          <t>S3, Azure, Data Factory, Cloud Storage, Hadoop, HDFS, Spark, Scala, Kafka, Informatica PowerCenter</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,19 +846,19 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a0cf6116e02d635</t>
+          <t>https://www.indeed.com/viewjob?jk=0f98760c842e5085</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Cloud Engineer II</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Vibrant Emotional Health</t>
+          <t>Tradeweb</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -867,11 +867,11 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, S3, IAM, RDS, GCP, Spark, Kafka, Dask, Snowflake</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ba39b2a6826c32d</t>
+          <t>https://www.indeed.com/viewjob?jk=cb2021c38a5314d9</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Engineer - AI &amp; Data Management</t>
+          <t>GenAI Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>S3, Azure, Data Factory, Cloud Storage, Hadoop, HDFS, Spark, Scala, Kafka, Informatica PowerCenter</t>
+          <t>AWS, RDS, Azure, Databricks, Blob Storage, Google Cloud Platform, Vertex AI, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,19 +916,19 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f98760c842e5085</t>
+          <t>https://www.indeed.com/viewjob?jk=5efecdb56da9cdd1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tradeweb</t>
+          <t>Metropolitan Commercial Bank</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, GCP, Spark, Kafka, Dask, Snowflake</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb2021c38a5314d9</t>
+          <t>https://www.indeed.com/viewjob?jk=25250927f01c87fd</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GenAI Threat Intelligence Analyst</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Credera</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Blob Storage, Google Cloud Platform, Vertex AI, Scala, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Oozie, Spark, Scala, Kafka, SQL Server</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5efecdb56da9cdd1</t>
+          <t>https://www.indeed.com/viewjob?jk=a2859c21fcc6b9b6</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Metropolitan Commercial Bank</t>
+          <t>Credera</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, NoSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Oozie, Spark, Scala, Kafka, SQL Server</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25250927f01c87fd</t>
+          <t>https://www.indeed.com/viewjob?jk=9e65ae12c9231691</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2859c21fcc6b9b6</t>
+          <t>https://www.indeed.com/viewjob?jk=deb9ad8464ceb6e6</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e65ae12c9231691</t>
+          <t>https://www.indeed.com/viewjob?jk=0faede29102fb7e1</t>
         </is>
       </c>
     </row>
@@ -1103,20 +1103,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Credera</t>
+          <t>ABCorp NA Inc.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Oozie, Spark, Scala, Kafka, SQL Server</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,59 +1126,59 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=deb9ad8464ceb6e6</t>
+          <t>https://www.indeed.com/viewjob?jk=1e06fd43e0f99777</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Azure Data &amp; Development Architect</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Credera</t>
+          <t>SunStone Consulting</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Oozie, Spark, Scala, Kafka, SQL Server</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Event Hubs, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0faede29102fb7e1</t>
+          <t>https://www.indeed.com/viewjob?jk=1e9052cac6c7210d</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Azure Data &amp; Development Architect</t>
+          <t>Software Engineer, Full Stack - AI (Chicago)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SunStone Consulting</t>
+          <t>Fitch Group</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Event Hubs, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e9052cac6c7210d</t>
+          <t>https://www.indeed.com/viewjob?jk=d4bb35a3533f1ee6</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Engineering &amp; Quality - Software Engineer, Full Stack - AI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ABCorp NA Inc.</t>
+          <t>Fitch Group</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e06fd43e0f99777</t>
+          <t>https://www.indeed.com/viewjob?jk=cf6b928dd59e0c41</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineer, Full Stack - AI (Chicago)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Fitch Group</t>
+          <t>Trane Technologies</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4bb35a3533f1ee6</t>
+          <t>https://www.indeed.com/viewjob?jk=f483db2edc8cb83a</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Engineering &amp; Quality - Software Engineer, Full Stack - AI</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Fitch Group</t>
+          <t>JUUL Labs</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
+          <t>AWS, S3, ECS, IAM, RDS, GCP, Dataflow, Cloud Storage, Scala, Splunk</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf6b928dd59e0c41</t>
+          <t>https://www.indeed.com/viewjob?jk=c63edb85327f9aef</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
+          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, Snowflake, SQL Server, MySQL, ELT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fc4628968aad9e2</t>
+          <t>https://www.indeed.com/viewjob?jk=de10d304d09880c3</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0eb5fc1d601c0028</t>
+          <t>https://www.indeed.com/viewjob?jk=0fc4628968aad9e2</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acae1b7fc51e9a39</t>
+          <t>https://www.indeed.com/viewjob?jk=0eb5fc1d601c0028</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Trane Technologies</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f483db2edc8cb83a</t>
+          <t>https://www.indeed.com/viewjob?jk=acae1b7fc51e9a39</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>DEVELOPER L3(CONTRACT)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>JUUL Labs</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, GCP, Dataflow, Cloud Storage, Scala, Splunk</t>
+          <t>AWS, Databricks, Cloud Storage, Spark, PySpark, Scala, Snowflake, Time Travel, Databricks Lakehouse, Snowflake Schema</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c63edb85327f9aef</t>
+          <t>https://www.indeed.com/viewjob?jk=1c37881d8861b3d6</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Senior Ad Ops Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, Snowflake, SQL Server, MySQL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de10d304d09880c3</t>
+          <t>https://www.indeed.com/viewjob?jk=3d412becc7b99de0</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DEVELOPER L3(CONTRACT)</t>
+          <t>Software Engineer Seniors – Cloud Technologies | Fintech | Full Stack</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>FIS</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Cloud Storage, Spark, PySpark, Scala, Snowflake, Time Travel, Databricks Lakehouse, Snowflake Schema</t>
+          <t>AWS, Azure, Data Factory, Scala, Oracle, SQL Server, NoSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c37881d8861b3d6</t>
+          <t>https://www.indeed.com/viewjob?jk=d35fe7a7c554f8b5</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Platform Engineer Senior</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Texas Capital Bank</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, Cassandra, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, Redshift, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,102 +1581,102 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb97e11dedc46f7e</t>
+          <t>https://www.indeed.com/viewjob?jk=09ac756571edd2b5</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Ad Ops Engineer</t>
+          <t>Senior Dev Ops Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>SkyWater Technology Foundry</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, IAM, RDS, Photon, GCP, Vertex AI, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d412becc7b99de0</t>
+          <t>https://www.indeed.com/viewjob?jk=13bfee40249f3478</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>AI Developer - Senior - A&amp;I - Financial Services - Consulting - NYC, Charlotte, Dallas</t>
+          <t>Business Intelligence Solutions Architect</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Mars Technominds</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, RDS, Azure, Synapse Analytics, BigQuery, Hadoop, Hive, HBase</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b189ba2f7b20d0b</t>
+          <t>https://www.indeed.com/viewjob?jk=38246f1a187f1c7d</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineer Seniors – Cloud Technologies | Fintech | Full Stack</t>
+          <t>Data Management Architect (Manufacturing)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>FIS</t>
+          <t>Infor</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Oracle, SQL Server, NoSQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Oracle, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d35fe7a7c554f8b5</t>
+          <t>https://www.indeed.com/viewjob?jk=e45199011cbe2990</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Platform Engineer Senior</t>
+          <t>Software Engineer I – AI Assistant Framework, ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Texas Capital Bank</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09ac756571edd2b5</t>
+          <t>https://www.indeed.com/viewjob?jk=2546eaf4a3e50baf</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Dev Ops Engineer</t>
+          <t>Site AI Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SkyWater Technology Foundry</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Temple, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Photon, GCP, Vertex AI, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13bfee40249f3478</t>
+          <t>https://www.indeed.com/viewjob?jk=b9df42fb6f0e5b92</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Business Intelligence Solutions Architect</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Mars Technominds</t>
+          <t>Client Resources, Inc.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, GCP, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38246f1a187f1c7d</t>
+          <t>https://www.indeed.com/viewjob?jk=d1e155aced1efdff</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Management Architect (Manufacturing)</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Infor</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Oracle, MySQL, Data Modeling, ETL</t>
+          <t>AWS, Redshift, Athena, S3, IAM, Hadoop, Spark, Kafka, Snowflake, Splunk</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e45199011cbe2990</t>
+          <t>https://www.indeed.com/viewjob?jk=0f01d239e5c828f6</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer I – AI Assistant Framework, ArcGIS Enterprise</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>Intelligent Medical Objects</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Spark, Scala, Data Modeling, dbt, Power BI</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2546eaf4a3e50baf</t>
+          <t>https://www.indeed.com/viewjob?jk=c4869d3a6ac24136</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Site AI Engineer</t>
+          <t>Infrastructure-as-Code (IaC) Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Temple, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Databricks</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,59 +1896,59 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9df42fb6f0e5b92</t>
+          <t>https://www.indeed.com/viewjob?jk=ca35900639cbe443</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Power Automate Engineer</t>
+          <t>Senior Engineer - Agentic AI</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>JCA Surety Group</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Lambda, SQS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebd1ccebdb7a4ed2</t>
+          <t>https://www.indeed.com/viewjob?jk=5daf8f72a4fd9ab6</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>Senior Backend Software Engineer/SRE - GM Energy</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, S3, IAM, Hadoop, Spark, Kafka, Snowflake, Splunk</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f01d239e5c828f6</t>
+          <t>https://www.indeed.com/viewjob?jk=0413ce8de5fcca6a</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Software Developer - Used Car Marketplace</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Intelligent Medical Objects</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Spark, Scala, Data Modeling, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4869d3a6ac24136</t>
+          <t>https://www.indeed.com/viewjob?jk=d487bcb34632271a</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Infrastructure-as-Code (IaC) Engineer</t>
+          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Databricks</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca35900639cbe443</t>
+          <t>https://www.indeed.com/viewjob?jk=79a2a043dc5cdb8f</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Engineer - Agentic AI</t>
+          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5daf8f72a4fd9ab6</t>
+          <t>https://www.indeed.com/viewjob?jk=e387db2c2b866baa</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer/SRE - GM Energy</t>
+          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0413ce8de5fcca6a</t>
+          <t>https://www.indeed.com/viewjob?jk=18a022cbc2b4d934</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Developer - Used Car Marketplace</t>
+          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,17 +2131,17 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d487bcb34632271a</t>
+          <t>https://www.indeed.com/viewjob?jk=5cc4f959dd712f8a</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Yonkers, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79a2a043dc5cdb8f</t>
+          <t>https://www.indeed.com/viewjob?jk=688d7763683eecad</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
+          <t>Distinguished Engineer -</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, GCP, Snowflake, ELT, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e387db2c2b866baa</t>
+          <t>https://www.indeed.com/viewjob?jk=087eb595cff7bd93</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Smithfield, RI, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,42 +2236,42 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, EMR, RDS, Spark, Scala, Snowflake, Oracle, ETL, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18a022cbc2b4d934</t>
+          <t>https://www.indeed.com/viewjob?jk=5cc22367a2ce3d9f</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Snowflake, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cc4f959dd712f8a</t>
+          <t>https://www.indeed.com/viewjob?jk=36a73b40629cc484</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
+          <t>AI/ML Engineer – Data &amp; Full-Stack Solutions</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>ITC Federal</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Yonkers, NY, US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,94 +2316,94 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=688d7763683eecad</t>
+          <t>https://www.indeed.com/viewjob?jk=ce30a23eaa64abcd</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Distinguished Engineer -</t>
+          <t>Senior Software Engineer - Commercial Software</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, GCP, Snowflake, ELT, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Oracle, MySQL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=087eb595cff7bd93</t>
+          <t>https://www.indeed.com/viewjob?jk=4ca1245fe1b2a956</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Development Engineer II</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Smithfield, RI, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Spark, Scala, Snowflake, Oracle, ETL, Jenkins, Maven</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cc22367a2ce3d9f</t>
+          <t>https://www.indeed.com/viewjob?jk=c0d2f3586b2ed198</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AI/ML Engineer – Data &amp; Full-Stack Solutions</t>
+          <t>Senior Site Reliability Engineer II</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ITC Federal</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce30a23eaa64abcd</t>
+          <t>https://www.indeed.com/viewjob?jk=6fa53cf983e1a6d0</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Commercial Software</t>
+          <t>Quality Assurance Analyst / ETL Tester</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Briljent</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Oracle, MySQL</t>
+          <t>RDS, Azure, Snowflake, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ca1245fe1b2a956</t>
+          <t>https://www.indeed.com/viewjob?jk=d69b1256484e3a82</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer III ***Raleigh, NC***</t>
+          <t>Artificial Intelligence/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Hadoop, Spark, Scala, Kafka, DynamoDB, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35085eed81ec8943</t>
+          <t>https://www.indeed.com/viewjob?jk=8f6f11467cb82584</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Artificial Intelligence/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Snowflake, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36a73b40629cc484</t>
+          <t>https://www.indeed.com/viewjob?jk=c9ce81a6707266dd</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Quality Assurance Analyst / ETL Tester</t>
+          <t>Artificial Intelligence/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Briljent</t>
+          <t>Logic, Inc.</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,42 +2551,42 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Snowflake, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL, Data Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d69b1256484e3a82</t>
+          <t>https://www.indeed.com/viewjob?jk=e34c2e31eeb33f9e</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>Systems &amp; Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Kretek International</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Moorpark, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Splunk, Terraform</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0d2f3586b2ed198</t>
+          <t>https://www.indeed.com/viewjob?jk=a7d7d86c5d6aef50</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer II</t>
+          <t>Data Engineer - Performance Management</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Lake Buena Vista, FL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, Splunk, CI/CD</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fa53cf983e1a6d0</t>
+          <t>https://www.indeed.com/viewjob?jk=57b0af5961338ef2</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Artificial Intelligence/Machine Learning Data Engineer</t>
+          <t>Full Stack, Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>SCAN Health Plan</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f6f11467cb82584</t>
+          <t>https://www.indeed.com/viewjob?jk=6b0db4093988ff3c</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Artificial Intelligence/Machine Learning Data Engineer</t>
+          <t>Senior Machine Learning Engineer (Remote)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, NoSQL, CI/CD, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9ce81a6707266dd</t>
+          <t>https://www.indeed.com/viewjob?jk=fdbdb16275078800</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Artificial Intelligence/Machine Learning Data Engineer</t>
+          <t>Sr. Java Developers</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Logic, Inc.</t>
+          <t>Vibotek LLC</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow</t>
+          <t>AWS, HBase, Spark, Scala, Kafka, Oracle, Cassandra, NoSQL, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e34c2e31eeb33f9e</t>
+          <t>https://www.indeed.com/viewjob?jk=061d80fcb09266da</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (Remote)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>Tennessee Titans</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, NoSQL, CI/CD, Git, Python, SQL</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdbdb16275078800</t>
+          <t>https://www.indeed.com/viewjob?jk=b7b90aa43b4806b0</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr. Java Developers</t>
+          <t>Software Systems Engineer, Release Reliability &amp; Automation (Autonomous Vehicles)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Vibotek LLC</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, HBase, Spark, Scala, Kafka, Oracle, Cassandra, NoSQL, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Power BI, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=061d80fcb09266da</t>
+          <t>https://www.indeed.com/viewjob?jk=f97782145b5d3f94</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Reliability Engineer (Autonomous Vehicles)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>First Citizens Bank</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, Spark, PySpark, Scala, Oracle, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Power BI, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8629753fa2cdcb2f</t>
+          <t>https://www.indeed.com/viewjob?jk=cf25e4c14df46394</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Systems &amp; Cloud Infrastructure Engineer</t>
+          <t>AI/ML Developer II (Remote)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Kretek International</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Moorpark, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Splunk, Terraform</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, NoSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,67 +2876,67 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7d7d86c5d6aef50</t>
+          <t>https://www.indeed.com/viewjob?jk=fb663396a5bc1b79</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer - Performance Management</t>
+          <t>Software Engineer II, Global Servicing Technology</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Lake Buena Vista, FL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Google Cloud Platform, Cloud Storage, Hive, Spark, Scala, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57b0af5961338ef2</t>
+          <t>https://www.indeed.com/viewjob?jk=5c5c9f5bf8d54b87</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Full Stack, Data &amp; Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SCAN Health Plan</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b0db4093988ff3c</t>
+          <t>https://www.indeed.com/viewjob?jk=d33e81401b69b22c</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Hightower Advisors</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bee78aad0ae84553</t>
+          <t>https://www.indeed.com/viewjob?jk=ffcaa5c8b2e22e2b</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Tennessee Titans</t>
+          <t>Accompany Health</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Data Modeling, ELT, dbt</t>
+          <t>AWS, Glue, Spark, Scala, Kafka, NoSQL, Data Modeling, Terraform, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,102 +3016,102 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7b90aa43b4806b0</t>
+          <t>https://www.indeed.com/viewjob?jk=f41df6bde69aeb07</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Systems Engineer, Release Reliability &amp; Automation (Autonomous Vehicles)</t>
+          <t>Data Engineer, Go to Market (Remote)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Power BI, CI/CD, Jenkins</t>
+          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f97782145b5d3f94</t>
+          <t>https://www.indeed.com/viewjob?jk=8c7e11f90c05edfc</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Reliability Engineer (Autonomous Vehicles)</t>
+          <t>Sr. Infrastructure &amp; Security Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>HerculesAI</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Campbell, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Power BI, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, IAM, Azure, GCP, Splunk, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf25e4c14df46394</t>
+          <t>https://www.indeed.com/viewjob?jk=997e47a23e0d8261</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>AI/ML Developer II (Remote)</t>
+          <t>Software Engineer III - Data, AWS, ETL, Java/Python,</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, NoSQL, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb663396a5bc1b79</t>
+          <t>https://www.indeed.com/viewjob?jk=24b2eb0df8c7e284</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Software Engineer II, Global Servicing Technology</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Cityblock Health</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,17 +3146,17 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, Cloud Storage, Hive, Spark, Scala, ETL, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, GCP, BigQuery, PostgreSQL, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c5c9f5bf8d54b87</t>
+          <t>https://www.indeed.com/viewjob?jk=76d763c610ac1510</t>
         </is>
       </c>
     </row>
@@ -3168,12 +3168,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Accompany Health</t>
+          <t>Carrier</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Glue, Spark, Scala, Kafka, NoSQL, Data Modeling, Terraform, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f41df6bde69aeb07</t>
+          <t>https://www.indeed.com/viewjob?jk=ab7c6d265d3522d2</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Quality Automation Engineer (SDET) - Career</t>
+          <t>Senior Data Engineer - GM Motorsports</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Concord, NC, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, Databricks Lakehouse, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b597edf918184e10</t>
+          <t>https://www.indeed.com/viewjob?jk=c80625f8482f70fb</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Quality Automation Engineer (SDET) - Career</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d33e81401b69b22c</t>
+          <t>https://www.indeed.com/viewjob?jk=b597edf918184e10</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DNP Software Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Client Resources, Inc.</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, Glue, RDS, Spark, PySpark, Spark Streaming, CI/CD, Terraform, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffcaa5c8b2e22e2b</t>
+          <t>https://www.indeed.com/viewjob?jk=95f2f4f81bc33a7a</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Engineer, Go to Market (Remote)</t>
+          <t>Senior Backend Software Engineer- GM Energy</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, GCP, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c7e11f90c05edfc</t>
+          <t>https://www.indeed.com/viewjob?jk=51fb08298ca2e944</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Sr. Infrastructure &amp; Security Engineer</t>
+          <t>Data Platform Architect (Snowflake)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>HerculesAI</t>
+          <t>Coastal</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Campbell, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, Azure, GCP, Splunk, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Snowflake, Data Modeling, Kimball, ETL, dbt</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=997e47a23e0d8261</t>
+          <t>https://www.indeed.com/viewjob?jk=58854506afe876e4</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data, AWS, ETL, Java/Python,</t>
+          <t>Software Development Engineer III</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, ETL, CI/CD, Terraform</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24b2eb0df8c7e284</t>
+          <t>https://www.indeed.com/viewjob?jk=1f950bd314b17c8f</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Senior DBA / Database Architect</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Cityblock Health</t>
+          <t>Opeeka, Inc.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Folsom, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, BigQuery, PostgreSQL, dbt, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Bitbucket</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76d763c610ac1510</t>
+          <t>https://www.indeed.com/viewjob?jk=5142b758be4e8f87</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Application Developer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Carrier</t>
+          <t>Value Truck of Arizona</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>South Jordan, UT, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab7c6d265d3522d2</t>
+          <t>https://www.indeed.com/viewjob?jk=f6c3e26366316cc8</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GM Motorsports</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Concord, NC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,24 +3496,24 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, Databricks Lakehouse, NoSQL, Docker</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c80625f8482f70fb</t>
+          <t>https://www.indeed.com/viewjob?jk=c5c449cb4c336ec2</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>AI Engineer Senior Consultant</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,14 +3541,14 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2eeb9a92ff909033</t>
+          <t>https://www.indeed.com/viewjob?jk=e57a91ca929fec5b</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>AI Engineer Senior Consultant</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,14 +3576,14 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c1b56e7aa8c4561</t>
+          <t>https://www.indeed.com/viewjob?jk=cd22b6d5954a33c2</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>AI Engineer Senior Consultant</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,14 +3611,14 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9f259bbce0ce033</t>
+          <t>https://www.indeed.com/viewjob?jk=2d369f55f3c43cd0</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>AI Engineer Senior Consultant</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,14 +3646,14 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=143101384ee45578</t>
+          <t>https://www.indeed.com/viewjob?jk=b5e852e1fb093faa</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>AI Engineer Consultant</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76b52e35f38bdeca</t>
+          <t>https://www.indeed.com/viewjob?jk=122021b0213972fb</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior DBA / Database Architect</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Opeeka, Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Folsom, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Bitbucket</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5142b758be4e8f87</t>
+          <t>https://www.indeed.com/viewjob?jk=cf263b65906b30ba</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Application Developer</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Value Truck of Arizona</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>South Jordan, UT, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6c3e26366316cc8</t>
+          <t>https://www.indeed.com/viewjob?jk=775f4b74d2e0d125</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer- GM Energy</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, GCP, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51fb08298ca2e944</t>
+          <t>https://www.indeed.com/viewjob?jk=e27aa2f30115d6a9</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data Platform Architect (Snowflake)</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Coastal</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Snowflake, Data Modeling, Kimball, ETL, dbt</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58854506afe876e4</t>
+          <t>https://www.indeed.com/viewjob?jk=372ffe4f2e9a605d</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Software Development Engineer III</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f950bd314b17c8f</t>
+          <t>https://www.indeed.com/viewjob?jk=a256a77103c9ee18</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5c449cb4c336ec2</t>
+          <t>https://www.indeed.com/viewjob?jk=9b082342159bbdf7</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e57a91ca929fec5b</t>
+          <t>https://www.indeed.com/viewjob?jk=e06cd5eb56a43b5c</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd22b6d5954a33c2</t>
+          <t>https://www.indeed.com/viewjob?jk=daaeb6d16db98abf</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d369f55f3c43cd0</t>
+          <t>https://www.indeed.com/viewjob?jk=5d61083f86948477</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5e852e1fb093faa</t>
+          <t>https://www.indeed.com/viewjob?jk=71d4be4e91f6174a</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=122021b0213972fb</t>
+          <t>https://www.indeed.com/viewjob?jk=912b927f8e6b0bc9</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf263b65906b30ba</t>
+          <t>https://www.indeed.com/viewjob?jk=697335a3240f02f2</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=775f4b74d2e0d125</t>
+          <t>https://www.indeed.com/viewjob?jk=e21309c64f987c4d</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e27aa2f30115d6a9</t>
+          <t>https://www.indeed.com/viewjob?jk=6e4114c9ced06f08</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=372ffe4f2e9a605d</t>
+          <t>https://www.indeed.com/viewjob?jk=0379c77fb1bea285</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a256a77103c9ee18</t>
+          <t>https://www.indeed.com/viewjob?jk=c7404f3dbf25b5d0</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b082342159bbdf7</t>
+          <t>https://www.indeed.com/viewjob?jk=19a128257d3c2c77</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e06cd5eb56a43b5c</t>
+          <t>https://www.indeed.com/viewjob?jk=6a667aa6f915c8e9</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daaeb6d16db98abf</t>
+          <t>https://www.indeed.com/viewjob?jk=8d47c2036fa69322</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d61083f86948477</t>
+          <t>https://www.indeed.com/viewjob?jk=591077de2df74cfa</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71d4be4e91f6174a</t>
+          <t>https://www.indeed.com/viewjob?jk=8cc254c410ba6f38</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=912b927f8e6b0bc9</t>
+          <t>https://www.indeed.com/viewjob?jk=12339d025b6d4b6f</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=697335a3240f02f2</t>
+          <t>https://www.indeed.com/viewjob?jk=dc7db42760d4627e</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e21309c64f987c4d</t>
+          <t>https://www.indeed.com/viewjob?jk=6c024ec8f500d28f</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e4114c9ced06f08</t>
+          <t>https://www.indeed.com/viewjob?jk=d5c090288e0e4f79</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0379c77fb1bea285</t>
+          <t>https://www.indeed.com/viewjob?jk=c400db066fcfe868</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,137 +4626,137 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7404f3dbf25b5d0</t>
+          <t>https://www.indeed.com/viewjob?jk=e9857bbf535b2768</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>Data Engineer (Snowflake, Teradata, DB2)</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Mutual of Omaha</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, Glue, RDS, Scala, Snowflake, SQL Server, MongoDB, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19a128257d3c2c77</t>
+          <t>https://www.indeed.com/viewjob?jk=aa9d2ce9f1b5528c</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, Terraform, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a667aa6f915c8e9</t>
+          <t>https://www.indeed.com/viewjob?jk=5f72c641c65b5a61</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>ObjectStream</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>RDS, Azure, Data Factory, Blob Storage, Spark, PySpark, ETL, dbt, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d47c2036fa69322</t>
+          <t>https://www.indeed.com/viewjob?jk=06e3854d22cdba89</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>PySpark Data Engineer III - Python/Java/SQL</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,32 +4766,32 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=591077de2df74cfa</t>
+          <t>https://www.indeed.com/viewjob?jk=926547138e49a51b</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>Senior Software Engineer – Cloud Engineering &amp; FinOps</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,32 +4801,32 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cc254c410ba6f38</t>
+          <t>https://www.indeed.com/viewjob?jk=d576082b1c56db5c</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>Senior Cloud Platform Engineer (R-19149)</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Dun &amp; Bradstreet</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,67 +4836,67 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12339d025b6d4b6f</t>
+          <t>https://www.indeed.com/viewjob?jk=cb41c4b9d93e0f98</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>Databricks Data Engineer - Senior - Consulting - Location Open</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, AKS</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc7db42760d4627e</t>
+          <t>https://www.indeed.com/viewjob?jk=599253e2d33dc75f</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>Software Engineer III – Python/PySpark/AWS</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, Lambda, S3, RDS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,129 +4906,129 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c024ec8f500d28f</t>
+          <t>https://www.indeed.com/viewjob?jk=991d5ceb2074b137</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>AV Safety Engineering Analytics Simulation Engineer (GPSSC)</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, RDS, Tableau, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5c090288e0e4f79</t>
+          <t>https://www.indeed.com/viewjob?jk=759f2d176cc08b7e</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>FSO LABS - AI Developer Senior - Bay Area</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>RDS, Azure, Hadoop, Hive, Spark, Kafka, NoSQL, Power BI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c400db066fcfe868</t>
+          <t>https://www.indeed.com/viewjob?jk=1d75a18fe3bc2126</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9857bbf535b2768</t>
+          <t>https://www.indeed.com/viewjob?jk=983d0a4b6df6a34b</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Software Engineer III – Python/PySpark/AWS</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,34 +5036,34 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=991d5ceb2074b137</t>
+          <t>https://www.indeed.com/viewjob?jk=e39cfd742ca8ccb7</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>AV Safety Engineering Analytics Simulation Engineer (GPSSC)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,34 +5071,34 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Tableau, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=759f2d176cc08b7e</t>
+          <t>https://www.indeed.com/viewjob?jk=4d24b9bb7d3f81d1</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>FSO LABS - AI Developer Senior - Bay Area</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,34 +5106,34 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Hive, Spark, Kafka, NoSQL, Power BI, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d75a18fe3bc2126</t>
+          <t>https://www.indeed.com/viewjob?jk=406f01e6594b2624</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer - Senior - Consulting - Location Open</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,34 +5141,34 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=599253e2d33dc75f</t>
+          <t>https://www.indeed.com/viewjob?jk=0206f3baae13d0ec</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Full‑Stack Developer (Java, React, Microservices) *Hybrid*</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>ObjectStream</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,34 +5176,34 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Blob Storage, Spark, PySpark, ETL, dbt, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06e3854d22cdba89</t>
+          <t>https://www.indeed.com/viewjob?jk=229f6840535c3531</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>PySpark Data Engineer III - Python/Java/SQL</t>
+          <t>Full‑Stack Developer (Java, React, Microservices) *Hybrid*</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=926547138e49a51b</t>
+          <t>https://www.indeed.com/viewjob?jk=606324c85c044a5d</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Cloud Engineering &amp; FinOps</t>
+          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Smyrna, GA, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d576082b1c56db5c</t>
+          <t>https://www.indeed.com/viewjob?jk=ef040d1b01903853</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer (R-19149)</t>
+          <t>Full‑Stack Developer (Java, React, Microservices) *Hybrid*</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Dun &amp; Bradstreet</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,24 +5291,24 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb41c4b9d93e0f98</t>
+          <t>https://www.indeed.com/viewjob?jk=0f298bb4ddf8e9a0</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Information Technology - Data Integration Engineer</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Magnolia</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Waco, TX, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,34 +5316,34 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=983d0a4b6df6a34b</t>
+          <t>https://www.indeed.com/viewjob?jk=22a077ceb692752f</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer - GM Motorsports</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Concord, NC, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,34 +5351,34 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Event Hubs, GCP, Scala, Kafka, MongoDB, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e39cfd742ca8ccb7</t>
+          <t>https://www.indeed.com/viewjob?jk=6f660072154c9a61</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Douglas Machine Inc.</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Alexandria, MN, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,17 +5386,17 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d24b9bb7d3f81d1</t>
+          <t>https://www.indeed.com/viewjob?jk=f9d5d216fe71b48e</t>
         </is>
       </c>
     </row>
@@ -5408,12 +5408,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>SEI Investments</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Oaks, PA, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,402 +5421,17 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>Kafka, Snowflake, Oracle, SQL Server, MySQL, MongoDB, Jenkins, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=406f01e6594b2624</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D144" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0206f3baae13d0ec</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Software Architect, Attribution &amp; Integrations</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Invoca</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>CA, US USA</t>
-        </is>
-      </c>
-      <c r="D145" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Kafka, MySQL, Data Modeling, Terraform, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e9dd5f05e7d0bdfd</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>Full‑Stack Developer (Java, React, Microservices) *Hybrid*</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D146" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=229f6840535c3531</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Full‑Stack Developer (Java, React, Microservices) *Hybrid*</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D147" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=606324c85c044a5d</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Full‑Stack Developer (Java, React, Microservices) *Hybrid*</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D148" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0f298bb4ddf8e9a0</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>Smyrna, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D149" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ef040d1b01903853</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>Information Technology - Data Integration Engineer</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>Magnolia</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>Waco, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D150" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=22a077ceb692752f</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - GM Motorsports</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>General Motors (GM)</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>Concord, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D151" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Event Hubs, GCP, Scala, Kafka, MongoDB, NoSQL, Docker</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6f660072154c9a61</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>Senior Business Intelligence Developer</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>Douglas Machine Inc.</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>Alexandria, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D152" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f9d5d216fe71b48e</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>SEI Investments</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Oaks, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D153" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>Kafka, Snowflake, Oracle, SQL Server, MySQL, MongoDB, Jenkins, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=76c94610856b0496</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>Backend Cloud Software Engineer</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>AMPURE CHARGING SYSTEMS INC</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>Monrovia, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D154" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, SQS, ECS, Scala, DynamoDB, CI/CD, Jenkins, Docker, Jenkins</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=55f56ffe2c84dc87</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-01.xlsx
+++ b/results/job_matches_2026-05-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G143"/>
+  <dimension ref="A1:G147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,17 +678,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (C#/.NET &amp; AI)</t>
+          <t>Junior Cloud Security Analyst</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93c21b258a08bd24</t>
+          <t>https://www.indeed.com/viewjob?jk=85598b1d63680693</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr Software Engineer II - Enterprise Architecture</t>
+          <t>Senior Software Engineer (C#/.NET &amp; AI)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6bd0f139eec27a7</t>
+          <t>https://www.indeed.com/viewjob?jk=93c21b258a08bd24</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Cloud Network Automation Engineer</t>
+          <t>Sr Software Engineer II - Enterprise Architecture</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a0cf6116e02d635</t>
+          <t>https://www.indeed.com/viewjob?jk=f6bd0f139eec27a7</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Cloud Engineer II</t>
+          <t>Cloud Network Automation Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Vibrant Emotional Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ba39b2a6826c32d</t>
+          <t>https://www.indeed.com/viewjob?jk=0a0cf6116e02d635</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Engineer - AI &amp; Data Management</t>
+          <t>Cloud Engineer II</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Vibrant Emotional Health</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>S3, Azure, Data Factory, Cloud Storage, Hadoop, HDFS, Spark, Scala, Kafka, Informatica PowerCenter</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f98760c842e5085</t>
+          <t>https://www.indeed.com/viewjob?jk=3ba39b2a6826c32d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Engineer - AI &amp; Data Management</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tradeweb</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, GCP, Spark, Kafka, Dask, Snowflake</t>
+          <t>S3, Azure, Data Factory, Cloud Storage, Hadoop, HDFS, Spark, Scala, Kafka, Informatica PowerCenter</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb2021c38a5314d9</t>
+          <t>https://www.indeed.com/viewjob?jk=0f98760c842e5085</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GenAI Threat Intelligence Analyst</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tradeweb</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Blob Storage, Google Cloud Platform, Vertex AI, Scala, MLOps, MLflow</t>
+          <t>AWS, Redshift, S3, IAM, RDS, GCP, Spark, Kafka, Dask, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5efecdb56da9cdd1</t>
+          <t>https://www.indeed.com/viewjob?jk=cb2021c38a5314d9</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>GenAI Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Metropolitan Commercial Bank</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Blob Storage, Google Cloud Platform, Vertex AI, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25250927f01c87fd</t>
+          <t>https://www.indeed.com/viewjob?jk=5efecdb56da9cdd1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Credera</t>
+          <t>Metropolitan Commercial Bank</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Oozie, Spark, Scala, Kafka, SQL Server</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2859c21fcc6b9b6</t>
+          <t>https://www.indeed.com/viewjob?jk=25250927f01c87fd</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e65ae12c9231691</t>
+          <t>https://www.indeed.com/viewjob?jk=a2859c21fcc6b9b6</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=deb9ad8464ceb6e6</t>
+          <t>https://www.indeed.com/viewjob?jk=9e65ae12c9231691</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0faede29102fb7e1</t>
+          <t>https://www.indeed.com/viewjob?jk=deb9ad8464ceb6e6</t>
         </is>
       </c>
     </row>
@@ -1103,20 +1103,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ABCorp NA Inc.</t>
+          <t>Credera</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Oozie, Spark, Scala, Kafka, SQL Server</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e06fd43e0f99777</t>
+          <t>https://www.indeed.com/viewjob?jk=0faede29102fb7e1</t>
         </is>
       </c>
     </row>
@@ -1168,17 +1168,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer, Full Stack - AI (Chicago)</t>
+          <t>Java Compliance &amp; Governance Developer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Fitch Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
+          <t>IAM, RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4bb35a3533f1ee6</t>
+          <t>https://www.indeed.com/viewjob?jk=8078bc6f1fdb2e7b</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Engineering &amp; Quality - Software Engineer, Full Stack - AI</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Fitch Group</t>
+          <t>ABCorp NA Inc.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf6b928dd59e0c41</t>
+          <t>https://www.indeed.com/viewjob?jk=1e06fd43e0f99777</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer, Full Stack - AI (Chicago)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Trane Technologies</t>
+          <t>Fitch Group</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f483db2edc8cb83a</t>
+          <t>https://www.indeed.com/viewjob?jk=d4bb35a3533f1ee6</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Engineering &amp; Quality - Software Engineer, Full Stack - AI</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>JUUL Labs</t>
+          <t>Fitch Group</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, GCP, Dataflow, Cloud Storage, Scala, Splunk</t>
+          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c63edb85327f9aef</t>
+          <t>https://www.indeed.com/viewjob?jk=cf6b928dd59e0c41</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, Snowflake, SQL Server, MySQL, ELT</t>
+          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de10d304d09880c3</t>
+          <t>https://www.indeed.com/viewjob?jk=0fc4628968aad9e2</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fc4628968aad9e2</t>
+          <t>https://www.indeed.com/viewjob?jk=0eb5fc1d601c0028</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0eb5fc1d601c0028</t>
+          <t>https://www.indeed.com/viewjob?jk=acae1b7fc51e9a39</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Trane Technologies</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acae1b7fc51e9a39</t>
+          <t>https://www.indeed.com/viewjob?jk=f483db2edc8cb83a</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>DEVELOPER L3(CONTRACT)</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>JUUL Labs</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Cloud Storage, Spark, PySpark, Scala, Snowflake, Time Travel, Databricks Lakehouse, Snowflake Schema</t>
+          <t>AWS, S3, ECS, IAM, RDS, GCP, Dataflow, Cloud Storage, Scala, Splunk</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c37881d8861b3d6</t>
+          <t>https://www.indeed.com/viewjob?jk=c63edb85327f9aef</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Ad Ops Engineer</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, Snowflake, SQL Server, MySQL, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d412becc7b99de0</t>
+          <t>https://www.indeed.com/viewjob?jk=de10d304d09880c3</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer Seniors – Cloud Technologies | Fintech | Full Stack</t>
+          <t>DEVELOPER L3(CONTRACT)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FIS</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Oracle, SQL Server, NoSQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Databricks, Cloud Storage, Spark, PySpark, Scala, Snowflake, Time Travel, Databricks Lakehouse, Snowflake Schema</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d35fe7a7c554f8b5</t>
+          <t>https://www.indeed.com/viewjob?jk=1c37881d8861b3d6</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Platform Engineer Senior</t>
+          <t>Senior Ad Ops Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Texas Capital Bank</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,42 +1571,42 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09ac756571edd2b5</t>
+          <t>https://www.indeed.com/viewjob?jk=3d412becc7b99de0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Dev Ops Engineer</t>
+          <t>Software Engineer Seniors – Cloud Technologies | Fintech | Full Stack</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SkyWater Technology Foundry</t>
+          <t>FIS</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Photon, GCP, Vertex AI, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Azure, Data Factory, Scala, Oracle, SQL Server, NoSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13bfee40249f3478</t>
+          <t>https://www.indeed.com/viewjob?jk=d35fe7a7c554f8b5</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Business Intelligence Solutions Architect</t>
+          <t>Platform Engineer Senior</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Mars Technominds</t>
+          <t>Texas Capital Bank</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Lambda, Redshift, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38246f1a187f1c7d</t>
+          <t>https://www.indeed.com/viewjob?jk=09ac756571edd2b5</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Management Architect (Manufacturing)</t>
+          <t>Senior Dev Ops Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Infor</t>
+          <t>SkyWater Technology Foundry</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Oracle, MySQL, Data Modeling, ETL</t>
+          <t>AWS, IAM, RDS, Photon, GCP, Vertex AI, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e45199011cbe2990</t>
+          <t>https://www.indeed.com/viewjob?jk=13bfee40249f3478</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer I – AI Assistant Framework, ArcGIS Enterprise</t>
+          <t>Business Intelligence Solutions Architect</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>Mars Technominds</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2546eaf4a3e50baf</t>
+          <t>https://www.indeed.com/viewjob?jk=38246f1a187f1c7d</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Site AI Engineer</t>
+          <t>Data Management Architect (Manufacturing)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Infor</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Temple, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Oracle, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9df42fb6f0e5b92</t>
+          <t>https://www.indeed.com/viewjob?jk=e45199011cbe2990</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Software Engineer I – AI Assistant Framework, ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Client Resources, Inc.</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, GCP, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1e155aced1efdff</t>
+          <t>https://www.indeed.com/viewjob?jk=2546eaf4a3e50baf</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>Site AI Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Temple, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, S3, IAM, Hadoop, Spark, Kafka, Snowflake, Splunk</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f01d239e5c828f6</t>
+          <t>https://www.indeed.com/viewjob?jk=b9df42fb6f0e5b92</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Intelligent Medical Objects</t>
+          <t>Client Resources, Inc.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Spark, Scala, Data Modeling, dbt, Power BI</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, GCP, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4869d3a6ac24136</t>
+          <t>https://www.indeed.com/viewjob?jk=d1e155aced1efdff</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Infrastructure-as-Code (IaC) Engineer</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Databricks</t>
+          <t>AWS, Redshift, Athena, S3, IAM, Hadoop, Spark, Kafka, Snowflake, Splunk</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca35900639cbe443</t>
+          <t>https://www.indeed.com/viewjob?jk=0f01d239e5c828f6</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Engineer - Agentic AI</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Intelligent Medical Objects</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Spark, Scala, Data Modeling, dbt, Power BI</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5daf8f72a4fd9ab6</t>
+          <t>https://www.indeed.com/viewjob?jk=c4869d3a6ac24136</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer/SRE - GM Energy</t>
+          <t>Infrastructure-as-Code (IaC) Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Databricks</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0413ce8de5fcca6a</t>
+          <t>https://www.indeed.com/viewjob?jk=ca35900639cbe443</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Developer - Used Car Marketplace</t>
+          <t>Senior Engineer - Agentic AI</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, SQS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d487bcb34632271a</t>
+          <t>https://www.indeed.com/viewjob?jk=5daf8f72a4fd9ab6</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
+          <t>Senior Backend Software Engineer/SRE - GM Energy</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79a2a043dc5cdb8f</t>
+          <t>https://www.indeed.com/viewjob?jk=0413ce8de5fcca6a</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
+          <t>Software Developer - Used Car Marketplace</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,17 +2061,17 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e387db2c2b866baa</t>
+          <t>https://www.indeed.com/viewjob?jk=d487bcb34632271a</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18a022cbc2b4d934</t>
+          <t>https://www.indeed.com/viewjob?jk=79a2a043dc5cdb8f</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cc4f959dd712f8a</t>
+          <t>https://www.indeed.com/viewjob?jk=e387db2c2b866baa</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Yonkers, NY, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=688d7763683eecad</t>
+          <t>https://www.indeed.com/viewjob?jk=18a022cbc2b4d934</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Distinguished Engineer -</t>
+          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, GCP, Snowflake, ELT, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=087eb595cff7bd93</t>
+          <t>https://www.indeed.com/viewjob?jk=5cc4f959dd712f8a</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Smithfield, RI, US USA</t>
+          <t>Yonkers, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,42 +2236,42 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Spark, Scala, Snowflake, Oracle, ETL, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cc22367a2ce3d9f</t>
+          <t>https://www.indeed.com/viewjob?jk=688d7763683eecad</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Distinguished Engineer -</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Snowflake, MLOps, CI/CD, Terraform</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, GCP, Snowflake, ELT, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,59 +2281,59 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36a73b40629cc484</t>
+          <t>https://www.indeed.com/viewjob?jk=087eb595cff7bd93</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AI/ML Engineer – Data &amp; Full-Stack Solutions</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ITC Federal</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>Smithfield, RI, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, ETL, ELT, CI/CD</t>
+          <t>AWS, EMR, RDS, Spark, Scala, Snowflake, Oracle, ETL, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce30a23eaa64abcd</t>
+          <t>https://www.indeed.com/viewjob?jk=5cc22367a2ce3d9f</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Commercial Software</t>
+          <t>AI/ML Engineer – Data &amp; Full-Stack Solutions</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>ITC Federal</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Oracle, MySQL</t>
+          <t>AWS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ca1245fe1b2a956</t>
+          <t>https://www.indeed.com/viewjob?jk=ce30a23eaa64abcd</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>Senior Software Engineer - Commercial Software</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Oracle, MySQL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0d2f3586b2ed198</t>
+          <t>https://www.indeed.com/viewjob?jk=4ca1245fe1b2a956</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer II</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, Splunk, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Snowflake, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fa53cf983e1a6d0</t>
+          <t>https://www.indeed.com/viewjob?jk=36a73b40629cc484</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Quality Assurance Analyst / ETL Tester</t>
+          <t>Java Cloud-Native Developer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Briljent</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Snowflake, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL, Data Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d69b1256484e3a82</t>
+          <t>https://www.indeed.com/viewjob?jk=b7fe4ad94b5b821d</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Artificial Intelligence/Machine Learning Data Engineer</t>
+          <t>Software Development Engineer II</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f6f11467cb82584</t>
+          <t>https://www.indeed.com/viewjob?jk=c0d2f3586b2ed198</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence/Machine Learning Data Engineer</t>
+          <t>Senior Site Reliability Engineer II</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9ce81a6707266dd</t>
+          <t>https://www.indeed.com/viewjob?jk=6fa53cf983e1a6d0</t>
         </is>
       </c>
     </row>
@@ -2538,12 +2538,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Logic, Inc.</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e34c2e31eeb33f9e</t>
+          <t>https://www.indeed.com/viewjob?jk=8f6f11467cb82584</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Systems &amp; Cloud Infrastructure Engineer</t>
+          <t>Artificial Intelligence/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Kretek International</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Moorpark, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Splunk, Terraform</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7d7d86c5d6aef50</t>
+          <t>https://www.indeed.com/viewjob?jk=c9ce81a6707266dd</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer - Performance Management</t>
+          <t>Artificial Intelligence/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>Logic, Inc.</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Lake Buena Vista, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,42 +2631,42 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57b0af5961338ef2</t>
+          <t>https://www.indeed.com/viewjob?jk=e34c2e31eeb33f9e</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Full Stack, Data &amp; Analytics Engineer</t>
+          <t>Quality Assurance Analyst / ETL Tester</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SCAN Health Plan</t>
+          <t>Briljent</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Snowflake, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b0db4093988ff3c</t>
+          <t>https://www.indeed.com/viewjob?jk=d69b1256484e3a82</t>
         </is>
       </c>
     </row>
@@ -2743,17 +2743,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Systems &amp; Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Tennessee Titans</t>
+          <t>Kretek International</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Moorpark, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Data Modeling, ELT, dbt</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Splunk, Terraform</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7b90aa43b4806b0</t>
+          <t>https://www.indeed.com/viewjob?jk=a7d7d86c5d6aef50</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Systems Engineer, Release Reliability &amp; Automation (Autonomous Vehicles)</t>
+          <t>Data Engineer - Performance Management</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Lake Buena Vista, FL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Power BI, CI/CD, Jenkins</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f97782145b5d3f94</t>
+          <t>https://www.indeed.com/viewjob?jk=57b0af5961338ef2</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Reliability Engineer (Autonomous Vehicles)</t>
+          <t>Full Stack, Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>SCAN Health Plan</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Power BI, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf25e4c14df46394</t>
+          <t>https://www.indeed.com/viewjob?jk=6b0db4093988ff3c</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>AI/ML Developer II (Remote)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>Tennessee Titans</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, NoSQL, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,102 +2876,102 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb663396a5bc1b79</t>
+          <t>https://www.indeed.com/viewjob?jk=b7b90aa43b4806b0</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineer II, Global Servicing Technology</t>
+          <t>Software Systems Engineer, Release Reliability &amp; Automation (Autonomous Vehicles)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, Cloud Storage, Hive, Spark, Scala, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Power BI, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c5c9f5bf8d54b87</t>
+          <t>https://www.indeed.com/viewjob?jk=f97782145b5d3f94</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Reliability Engineer (Autonomous Vehicles)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Power BI, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d33e81401b69b22c</t>
+          <t>https://www.indeed.com/viewjob?jk=cf25e4c14df46394</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI/ML Developer II (Remote)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, NoSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffcaa5c8b2e22e2b</t>
+          <t>https://www.indeed.com/viewjob?jk=fb663396a5bc1b79</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer II, Global Servicing Technology</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Accompany Health</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Glue, Spark, Scala, Kafka, NoSQL, Data Modeling, Terraform, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Google Cloud Platform, Cloud Storage, Hive, Spark, Scala, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f41df6bde69aeb07</t>
+          <t>https://www.indeed.com/viewjob?jk=5c5c9f5bf8d54b87</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer, Go to Market (Remote)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Accompany Health</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
+          <t>AWS, Glue, Spark, Scala, Kafka, NoSQL, Data Modeling, Terraform, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c7e11f90c05edfc</t>
+          <t>https://www.indeed.com/viewjob?jk=f41df6bde69aeb07</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Sr. Infrastructure &amp; Security Engineer</t>
+          <t>Quality Automation Engineer (SDET) - Career</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>HerculesAI</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Campbell, CA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, Azure, GCP, Splunk, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=997e47a23e0d8261</t>
+          <t>https://www.indeed.com/viewjob?jk=b597edf918184e10</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data, AWS, ETL, Java/Python,</t>
+          <t>Multi-Cloud Networking Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, ETL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24b2eb0df8c7e284</t>
+          <t>https://www.indeed.com/viewjob?jk=5089f26e49e819d7</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Cityblock Health</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, BigQuery, PostgreSQL, dbt, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76d763c610ac1510</t>
+          <t>https://www.indeed.com/viewjob?jk=d33e81401b69b22c</t>
         </is>
       </c>
     </row>
@@ -3168,12 +3168,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Carrier</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab7c6d265d3522d2</t>
+          <t>https://www.indeed.com/viewjob?jk=ffcaa5c8b2e22e2b</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GM Motorsports</t>
+          <t>Data Engineer, Go to Market (Remote)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Concord, NC, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, Databricks Lakehouse, NoSQL, Docker</t>
+          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c80625f8482f70fb</t>
+          <t>https://www.indeed.com/viewjob?jk=8c7e11f90c05edfc</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Quality Automation Engineer (SDET) - Career</t>
+          <t>Sr. Infrastructure &amp; Security Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>HerculesAI</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Campbell, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Lambda, IAM, Azure, GCP, Splunk, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b597edf918184e10</t>
+          <t>https://www.indeed.com/viewjob?jk=997e47a23e0d8261</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>DNP Software Engineer</t>
+          <t>Software Engineer III - Data, AWS, ETL, Java/Python,</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Client Resources, Inc.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Spark, PySpark, Spark Streaming, CI/CD, Terraform, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95f2f4f81bc33a7a</t>
+          <t>https://www.indeed.com/viewjob?jk=24b2eb0df8c7e284</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer- GM Energy</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Cityblock Health</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, GCP, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, BigQuery, PostgreSQL, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51fb08298ca2e944</t>
+          <t>https://www.indeed.com/viewjob?jk=76d763c610ac1510</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Platform Architect (Snowflake)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Coastal</t>
+          <t>Carrier</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Snowflake, Data Modeling, Kimball, ETL, dbt</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58854506afe876e4</t>
+          <t>https://www.indeed.com/viewjob?jk=ab7c6d265d3522d2</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Software Development Engineer III</t>
+          <t>Senior Data Engineer - GM Motorsports</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Concord, NC, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, Databricks Lakehouse, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f950bd314b17c8f</t>
+          <t>https://www.indeed.com/viewjob?jk=c80625f8482f70fb</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior DBA / Database Architect</t>
+          <t>DNP Software Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Opeeka, Inc.</t>
+          <t>Client Resources, Inc.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Folsom, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Bitbucket</t>
+          <t>AWS, Glue, RDS, Spark, PySpark, Spark Streaming, CI/CD, Terraform, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5142b758be4e8f87</t>
+          <t>https://www.indeed.com/viewjob?jk=95f2f4f81bc33a7a</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Application Developer</t>
+          <t>Senior Backend Software Engineer- GM Energy</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Value Truck of Arizona</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>South Jordan, UT, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, GCP, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6c3e26366316cc8</t>
+          <t>https://www.indeed.com/viewjob?jk=51fb08298ca2e944</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>Data Platform Architect (Snowflake)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Coastal</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Snowflake, Data Modeling, Kimball, ETL, dbt</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5c449cb4c336ec2</t>
+          <t>https://www.indeed.com/viewjob?jk=58854506afe876e4</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>Software Development Engineer III</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e57a91ca929fec5b</t>
+          <t>https://www.indeed.com/viewjob?jk=1f950bd314b17c8f</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd22b6d5954a33c2</t>
+          <t>https://www.indeed.com/viewjob?jk=c5c449cb4c336ec2</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d369f55f3c43cd0</t>
+          <t>https://www.indeed.com/viewjob?jk=e57a91ca929fec5b</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5e852e1fb093faa</t>
+          <t>https://www.indeed.com/viewjob?jk=cd22b6d5954a33c2</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=122021b0213972fb</t>
+          <t>https://www.indeed.com/viewjob?jk=2d369f55f3c43cd0</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf263b65906b30ba</t>
+          <t>https://www.indeed.com/viewjob?jk=b5e852e1fb093faa</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=775f4b74d2e0d125</t>
+          <t>https://www.indeed.com/viewjob?jk=122021b0213972fb</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e27aa2f30115d6a9</t>
+          <t>https://www.indeed.com/viewjob?jk=cf263b65906b30ba</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=372ffe4f2e9a605d</t>
+          <t>https://www.indeed.com/viewjob?jk=775f4b74d2e0d125</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a256a77103c9ee18</t>
+          <t>https://www.indeed.com/viewjob?jk=e27aa2f30115d6a9</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b082342159bbdf7</t>
+          <t>https://www.indeed.com/viewjob?jk=372ffe4f2e9a605d</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e06cd5eb56a43b5c</t>
+          <t>https://www.indeed.com/viewjob?jk=a256a77103c9ee18</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daaeb6d16db98abf</t>
+          <t>https://www.indeed.com/viewjob?jk=9b082342159bbdf7</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d61083f86948477</t>
+          <t>https://www.indeed.com/viewjob?jk=e06cd5eb56a43b5c</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71d4be4e91f6174a</t>
+          <t>https://www.indeed.com/viewjob?jk=daaeb6d16db98abf</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=912b927f8e6b0bc9</t>
+          <t>https://www.indeed.com/viewjob?jk=5d61083f86948477</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=697335a3240f02f2</t>
+          <t>https://www.indeed.com/viewjob?jk=71d4be4e91f6174a</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e21309c64f987c4d</t>
+          <t>https://www.indeed.com/viewjob?jk=912b927f8e6b0bc9</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e4114c9ced06f08</t>
+          <t>https://www.indeed.com/viewjob?jk=697335a3240f02f2</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0379c77fb1bea285</t>
+          <t>https://www.indeed.com/viewjob?jk=e21309c64f987c4d</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7404f3dbf25b5d0</t>
+          <t>https://www.indeed.com/viewjob?jk=6e4114c9ced06f08</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19a128257d3c2c77</t>
+          <t>https://www.indeed.com/viewjob?jk=0379c77fb1bea285</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a667aa6f915c8e9</t>
+          <t>https://www.indeed.com/viewjob?jk=c7404f3dbf25b5d0</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d47c2036fa69322</t>
+          <t>https://www.indeed.com/viewjob?jk=19a128257d3c2c77</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=591077de2df74cfa</t>
+          <t>https://www.indeed.com/viewjob?jk=6a667aa6f915c8e9</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cc254c410ba6f38</t>
+          <t>https://www.indeed.com/viewjob?jk=8d47c2036fa69322</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12339d025b6d4b6f</t>
+          <t>https://www.indeed.com/viewjob?jk=591077de2df74cfa</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc7db42760d4627e</t>
+          <t>https://www.indeed.com/viewjob?jk=8cc254c410ba6f38</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c024ec8f500d28f</t>
+          <t>https://www.indeed.com/viewjob?jk=12339d025b6d4b6f</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5c090288e0e4f79</t>
+          <t>https://www.indeed.com/viewjob?jk=dc7db42760d4627e</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c400db066fcfe868</t>
+          <t>https://www.indeed.com/viewjob?jk=6c024ec8f500d28f</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,137 +4626,137 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9857bbf535b2768</t>
+          <t>https://www.indeed.com/viewjob?jk=d5c090288e0e4f79</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Data Engineer (Snowflake, Teradata, DB2)</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Mutual of Omaha</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Scala, Snowflake, SQL Server, MongoDB, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa9d2ce9f1b5528c</t>
+          <t>https://www.indeed.com/viewjob?jk=c400db066fcfe868</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, Terraform, Airflow, Apache Airflow</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f72c641c65b5a61</t>
+          <t>https://www.indeed.com/viewjob?jk=e9857bbf535b2768</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior DBA / Database Architect</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>ObjectStream</t>
+          <t>Opeeka, Inc.</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Folsom, CA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Blob Storage, Spark, PySpark, ETL, dbt, Airflow, Apache Airflow</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Bitbucket</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06e3854d22cdba89</t>
+          <t>https://www.indeed.com/viewjob?jk=5142b758be4e8f87</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>PySpark Data Engineer III - Python/Java/SQL</t>
+          <t>Application Developer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Value Truck of Arizona</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>South Jordan, UT, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=926547138e49a51b</t>
+          <t>https://www.indeed.com/viewjob?jk=f6c3e26366316cc8</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Cloud Engineering &amp; FinOps</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,34 +4791,34 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, Terraform, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d576082b1c56db5c</t>
+          <t>https://www.indeed.com/viewjob?jk=5f72c641c65b5a61</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer (R-19149)</t>
+          <t>Software Engineer III – Python/PySpark/AWS</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Dun &amp; Bradstreet</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, RDS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb41c4b9d93e0f98</t>
+          <t>https://www.indeed.com/viewjob?jk=991d5ceb2074b137</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer - Senior - Consulting - Location Open</t>
+          <t>AV Safety Engineering Analytics Simulation Engineer (GPSSC)</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,34 +4861,34 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, AKS</t>
+          <t>AWS, RDS, Tableau, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=599253e2d33dc75f</t>
+          <t>https://www.indeed.com/viewjob?jk=759f2d176cc08b7e</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Software Engineer III – Python/PySpark/AWS</t>
+          <t>FSO LABS - AI Developer Senior - Bay Area</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,34 +4896,34 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake</t>
+          <t>RDS, Azure, Hadoop, Hive, Spark, Kafka, NoSQL, Power BI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=991d5ceb2074b137</t>
+          <t>https://www.indeed.com/viewjob?jk=1d75a18fe3bc2126</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>AV Safety Engineering Analytics Simulation Engineer (GPSSC)</t>
+          <t>Databricks Data Engineer - Senior - Consulting - Location Open</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,34 +4931,34 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, RDS, Tableau, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, AKS</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=759f2d176cc08b7e</t>
+          <t>https://www.indeed.com/viewjob?jk=599253e2d33dc75f</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>FSO LABS - AI Developer Senior - Bay Area</t>
+          <t>Data Engineer (Snowflake, Teradata, DB2)</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Mutual of Omaha</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,34 +4966,34 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Hive, Spark, Kafka, NoSQL, Power BI, Docker, Kubernetes</t>
+          <t>AWS, Glue, RDS, Scala, Snowflake, SQL Server, MongoDB, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d75a18fe3bc2126</t>
+          <t>https://www.indeed.com/viewjob?jk=aa9d2ce9f1b5528c</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>ObjectStream</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Blob Storage, Spark, PySpark, ETL, dbt, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,24 +5011,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=983d0a4b6df6a34b</t>
+          <t>https://www.indeed.com/viewjob?jk=06e3854d22cdba89</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>PySpark Data Engineer III - Python/Java/SQL</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,34 +5036,34 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e39cfd742ca8ccb7</t>
+          <t>https://www.indeed.com/viewjob?jk=926547138e49a51b</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer – Cloud Engineering &amp; FinOps</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,34 +5071,34 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d24b9bb7d3f81d1</t>
+          <t>https://www.indeed.com/viewjob?jk=d576082b1c56db5c</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Cloud Platform Engineer (R-19149)</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Dun &amp; Bradstreet</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,17 +5106,17 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=406f01e6594b2624</t>
+          <t>https://www.indeed.com/viewjob?jk=cb41c4b9d93e0f98</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,14 +5151,14 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0206f3baae13d0ec</t>
+          <t>https://www.indeed.com/viewjob?jk=983d0a4b6df6a34b</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Full‑Stack Developer (Java, React, Microservices) *Hybrid*</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -5176,24 +5176,24 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=229f6840535c3531</t>
+          <t>https://www.indeed.com/viewjob?jk=e39cfd742ca8ccb7</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Full‑Stack Developer (Java, React, Microservices) *Hybrid*</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -5211,24 +5211,24 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606324c85c044a5d</t>
+          <t>https://www.indeed.com/viewjob?jk=4d24b9bb7d3f81d1</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Smyrna, GA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,24 +5246,24 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef040d1b01903853</t>
+          <t>https://www.indeed.com/viewjob?jk=406f01e6594b2624</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Full‑Stack Developer (Java, React, Microservices) *Hybrid*</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -5281,34 +5281,34 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f298bb4ddf8e9a0</t>
+          <t>https://www.indeed.com/viewjob?jk=0206f3baae13d0ec</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Information Technology - Data Integration Engineer</t>
+          <t>Full‑Stack Developer (Java, React, Microservices) *Hybrid*</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Magnolia</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Waco, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22a077ceb692752f</t>
+          <t>https://www.indeed.com/viewjob?jk=229f6840535c3531</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - GM Motorsports</t>
+          <t>Full‑Stack Developer (Java, React, Microservices) *Hybrid*</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Concord, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,34 +5351,34 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, GCP, Scala, Kafka, MongoDB, NoSQL, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f660072154c9a61</t>
+          <t>https://www.indeed.com/viewjob?jk=606324c85c044a5d</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Developer</t>
+          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Douglas Machine Inc.</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Alexandria, MN, US USA</t>
+          <t>Smyrna, GA, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9d5d216fe71b48e</t>
+          <t>https://www.indeed.com/viewjob?jk=ef040d1b01903853</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full‑Stack Developer (Java, React, Microservices) *Hybrid*</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>SEI Investments</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Oaks, PA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,15 +5421,155 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0f298bb4ddf8e9a0</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Information Technology - Data Integration Engineer</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Magnolia</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Waco, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=22a077ceb692752f</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - GM Motorsports</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>General Motors (GM)</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Concord, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Event Hubs, GCP, Scala, Kafka, MongoDB, NoSQL, Docker</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6f660072154c9a61</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Senior Business Intelligence Developer</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Douglas Machine Inc.</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Alexandria, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f9d5d216fe71b48e</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>SEI Investments</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Oaks, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
           <t>Kafka, Snowflake, Oracle, SQL Server, MySQL, MongoDB, Jenkins, Docker, Kubernetes, AKS</t>
         </is>
       </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=76c94610856b0496</t>
         </is>

--- a/results/job_matches_2026-05-01.xlsx
+++ b/results/job_matches_2026-05-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G147"/>
+  <dimension ref="A1:G148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1308,17 +1308,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer II _ Big Data, GCP _EDAI</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,17 +1326,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fc4628968aad9e2</t>
+          <t>https://www.indeed.com/viewjob?jk=d725c4b26e048534</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0eb5fc1d601c0028</t>
+          <t>https://www.indeed.com/viewjob?jk=0fc4628968aad9e2</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acae1b7fc51e9a39</t>
+          <t>https://www.indeed.com/viewjob?jk=0eb5fc1d601c0028</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Trane Technologies</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f483db2edc8cb83a</t>
+          <t>https://www.indeed.com/viewjob?jk=acae1b7fc51e9a39</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>JUUL Labs</t>
+          <t>Trane Technologies</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, GCP, Dataflow, Cloud Storage, Scala, Splunk</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c63edb85327f9aef</t>
+          <t>https://www.indeed.com/viewjob?jk=f483db2edc8cb83a</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JUUL Labs</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, Snowflake, SQL Server, MySQL, ELT</t>
+          <t>AWS, S3, ECS, IAM, RDS, GCP, Dataflow, Cloud Storage, Scala, Splunk</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de10d304d09880c3</t>
+          <t>https://www.indeed.com/viewjob?jk=c63edb85327f9aef</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DEVELOPER L3(CONTRACT)</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Cloud Storage, Spark, PySpark, Scala, Snowflake, Time Travel, Databricks Lakehouse, Snowflake Schema</t>
+          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, Snowflake, SQL Server, MySQL, ELT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c37881d8861b3d6</t>
+          <t>https://www.indeed.com/viewjob?jk=de10d304d09880c3</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Ad Ops Engineer</t>
+          <t>DEVELOPER L3(CONTRACT)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Databricks, Cloud Storage, Spark, PySpark, Scala, Snowflake, Time Travel, Databricks Lakehouse, Snowflake Schema</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d412becc7b99de0</t>
+          <t>https://www.indeed.com/viewjob?jk=1c37881d8861b3d6</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Engineer Seniors – Cloud Technologies | Fintech | Full Stack</t>
+          <t>Senior Ad Ops Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FIS</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Oracle, SQL Server, NoSQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d35fe7a7c554f8b5</t>
+          <t>https://www.indeed.com/viewjob?jk=3d412becc7b99de0</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Platform Engineer Senior</t>
+          <t>Software Engineer Seniors – Cloud Technologies | Fintech | Full Stack</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Texas Capital Bank</t>
+          <t>FIS</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, CI/CD</t>
+          <t>AWS, Azure, Data Factory, Scala, Oracle, SQL Server, NoSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09ac756571edd2b5</t>
+          <t>https://www.indeed.com/viewjob?jk=d35fe7a7c554f8b5</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Dev Ops Engineer</t>
+          <t>Platform Engineer Senior</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SkyWater Technology Foundry</t>
+          <t>Texas Capital Bank</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Photon, GCP, Vertex AI, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Lambda, Redshift, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13bfee40249f3478</t>
+          <t>https://www.indeed.com/viewjob?jk=09ac756571edd2b5</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Business Intelligence Solutions Architect</t>
+          <t>Senior Dev Ops Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Mars Technominds</t>
+          <t>SkyWater Technology Foundry</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
+          <t>AWS, IAM, RDS, Photon, GCP, Vertex AI, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38246f1a187f1c7d</t>
+          <t>https://www.indeed.com/viewjob?jk=13bfee40249f3478</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Management Architect (Manufacturing)</t>
+          <t>Business Intelligence Solutions Architect</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Infor</t>
+          <t>Mars Technominds</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Oracle, MySQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e45199011cbe2990</t>
+          <t>https://www.indeed.com/viewjob?jk=38246f1a187f1c7d</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer I – AI Assistant Framework, ArcGIS Enterprise</t>
+          <t>ERP Data Management Architect (Manufacturing)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>Infor</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Oracle, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2546eaf4a3e50baf</t>
+          <t>https://www.indeed.com/viewjob?jk=e45199011cbe2990</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Site AI Engineer</t>
+          <t>Software Engineer I – AI Assistant Framework, ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Temple, TX, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9df42fb6f0e5b92</t>
+          <t>https://www.indeed.com/viewjob?jk=2546eaf4a3e50baf</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Site AI Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Client Resources, Inc.</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Temple, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, GCP, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1e155aced1efdff</t>
+          <t>https://www.indeed.com/viewjob?jk=b9df42fb6f0e5b92</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>Client Resources, Inc.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, S3, IAM, Hadoop, Spark, Kafka, Snowflake, Splunk</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, GCP, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f01d239e5c828f6</t>
+          <t>https://www.indeed.com/viewjob?jk=d1e155aced1efdff</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Intelligent Medical Objects</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Spark, Scala, Data Modeling, dbt, Power BI</t>
+          <t>AWS, Redshift, Athena, S3, IAM, Hadoop, Spark, Kafka, Snowflake, Splunk</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4869d3a6ac24136</t>
+          <t>https://www.indeed.com/viewjob?jk=0f01d239e5c828f6</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Infrastructure-as-Code (IaC) Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Intelligent Medical Objects</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Databricks</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Spark, Scala, Data Modeling, dbt, Power BI</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca35900639cbe443</t>
+          <t>https://www.indeed.com/viewjob?jk=c4869d3a6ac24136</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Engineer - Agentic AI</t>
+          <t>Infrastructure-as-Code (IaC) Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Databricks</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5daf8f72a4fd9ab6</t>
+          <t>https://www.indeed.com/viewjob?jk=ca35900639cbe443</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer/SRE - GM Energy</t>
+          <t>Senior Engineer - Agentic AI</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, SQS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,14 +2036,14 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0413ce8de5fcca6a</t>
+          <t>https://www.indeed.com/viewjob?jk=5daf8f72a4fd9ab6</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Developer - Used Car Marketplace</t>
+          <t>Senior Backend Software Engineer/SRE - GM Energy</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d487bcb34632271a</t>
+          <t>https://www.indeed.com/viewjob?jk=0413ce8de5fcca6a</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
+          <t>Software Developer - Used Car Marketplace</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,17 +2096,17 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79a2a043dc5cdb8f</t>
+          <t>https://www.indeed.com/viewjob?jk=d487bcb34632271a</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e387db2c2b866baa</t>
+          <t>https://www.indeed.com/viewjob?jk=79a2a043dc5cdb8f</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18a022cbc2b4d934</t>
+          <t>https://www.indeed.com/viewjob?jk=e387db2c2b866baa</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cc4f959dd712f8a</t>
+          <t>https://www.indeed.com/viewjob?jk=18a022cbc2b4d934</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Yonkers, NY, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=688d7763683eecad</t>
+          <t>https://www.indeed.com/viewjob?jk=5cc4f959dd712f8a</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Distinguished Engineer -</t>
+          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Yonkers, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, GCP, Snowflake, ELT, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=087eb595cff7bd93</t>
+          <t>https://www.indeed.com/viewjob?jk=688d7763683eecad</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Distinguished Engineer -</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Smithfield, RI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,69 +2306,69 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Spark, Scala, Snowflake, Oracle, ETL, Jenkins, Maven</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, GCP, Snowflake, ELT, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cc22367a2ce3d9f</t>
+          <t>https://www.indeed.com/viewjob?jk=087eb595cff7bd93</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AI/ML Engineer – Data &amp; Full-Stack Solutions</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ITC Federal</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>Smithfield, RI, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, ETL, ELT, CI/CD</t>
+          <t>AWS, EMR, RDS, Spark, Scala, Snowflake, Oracle, ETL, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce30a23eaa64abcd</t>
+          <t>https://www.indeed.com/viewjob?jk=5cc22367a2ce3d9f</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Commercial Software</t>
+          <t>AI/ML Engineer – Data &amp; Full-Stack Solutions</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>ITC Federal</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Oracle, MySQL</t>
+          <t>AWS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ca1245fe1b2a956</t>
+          <t>https://www.indeed.com/viewjob?jk=ce30a23eaa64abcd</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Senior Software Engineer - Commercial Software</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,24 +2411,24 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Snowflake, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Oracle, MySQL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36a73b40629cc484</t>
+          <t>https://www.indeed.com/viewjob?jk=4ca1245fe1b2a956</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Java Cloud-Native Developer</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, DynamoDB, NoSQL</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Snowflake, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7fe4ad94b5b821d</t>
+          <t>https://www.indeed.com/viewjob?jk=36a73b40629cc484</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>Java Cloud-Native Developer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0d2f3586b2ed198</t>
+          <t>https://www.indeed.com/viewjob?jk=b7fe4ad94b5b821d</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer II</t>
+          <t>Software Development Engineer II</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, Splunk, CI/CD</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fa53cf983e1a6d0</t>
+          <t>https://www.indeed.com/viewjob?jk=c0d2f3586b2ed198</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Artificial Intelligence/Machine Learning Data Engineer</t>
+          <t>Senior Site Reliability Engineer II</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f6f11467cb82584</t>
+          <t>https://www.indeed.com/viewjob?jk=6fa53cf983e1a6d0</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9ce81a6707266dd</t>
+          <t>https://www.indeed.com/viewjob?jk=8f6f11467cb82584</t>
         </is>
       </c>
     </row>
@@ -2608,7 +2608,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Logic, Inc.</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e34c2e31eeb33f9e</t>
+          <t>https://www.indeed.com/viewjob?jk=c9ce81a6707266dd</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Quality Assurance Analyst / ETL Tester</t>
+          <t>Artificial Intelligence/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Briljent</t>
+          <t>Logic, Inc.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,69 +2656,69 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Snowflake, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL, Data Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d69b1256484e3a82</t>
+          <t>https://www.indeed.com/viewjob?jk=e34c2e31eeb33f9e</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (Remote)</t>
+          <t>Quality Assurance Analyst / ETL Tester</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>Briljent</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, NoSQL, CI/CD, Git, Python, SQL</t>
+          <t>RDS, Azure, Snowflake, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdbdb16275078800</t>
+          <t>https://www.indeed.com/viewjob?jk=d69b1256484e3a82</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr. Java Developers</t>
+          <t>Senior Machine Learning Engineer (Remote)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Vibotek LLC</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, HBase, Spark, Scala, Kafka, Oracle, Cassandra, NoSQL, Jenkins, Docker</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, NoSQL, CI/CD, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=061d80fcb09266da</t>
+          <t>https://www.indeed.com/viewjob?jk=fdbdb16275078800</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Systems &amp; Cloud Infrastructure Engineer</t>
+          <t>Sr. Java Developers</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Kretek International</t>
+          <t>Vibotek LLC</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Moorpark, CA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Splunk, Terraform</t>
+          <t>AWS, HBase, Spark, Scala, Kafka, Oracle, Cassandra, NoSQL, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7d7d86c5d6aef50</t>
+          <t>https://www.indeed.com/viewjob?jk=061d80fcb09266da</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer - Performance Management</t>
+          <t>Systems &amp; Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>Kretek International</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Lake Buena Vista, FL, US USA</t>
+          <t>Moorpark, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Splunk, Terraform</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57b0af5961338ef2</t>
+          <t>https://www.indeed.com/viewjob?jk=a7d7d86c5d6aef50</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Full Stack, Data &amp; Analytics Engineer</t>
+          <t>Data Engineer - Performance Management</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>SCAN Health Plan</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Lake Buena Vista, FL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b0db4093988ff3c</t>
+          <t>https://www.indeed.com/viewjob?jk=57b0af5961338ef2</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Full Stack, Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Tennessee Titans</t>
+          <t>SCAN Health Plan</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Data Modeling, ELT, dbt</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7b90aa43b4806b0</t>
+          <t>https://www.indeed.com/viewjob?jk=6b0db4093988ff3c</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Systems Engineer, Release Reliability &amp; Automation (Autonomous Vehicles)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Tennessee Titans</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,24 +2901,24 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Power BI, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f97782145b5d3f94</t>
+          <t>https://www.indeed.com/viewjob?jk=b7b90aa43b4806b0</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Reliability Engineer (Autonomous Vehicles)</t>
+          <t>Software Systems Engineer, Release Reliability &amp; Automation (Autonomous Vehicles)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2941,29 +2941,29 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf25e4c14df46394</t>
+          <t>https://www.indeed.com/viewjob?jk=f97782145b5d3f94</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>AI/ML Developer II (Remote)</t>
+          <t>Reliability Engineer (Autonomous Vehicles)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,69 +2971,69 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, NoSQL, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Power BI, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb663396a5bc1b79</t>
+          <t>https://www.indeed.com/viewjob?jk=cf25e4c14df46394</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Engineer II, Global Servicing Technology</t>
+          <t>AI/ML Developer II (Remote)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, Cloud Storage, Hive, Spark, Scala, ETL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, NoSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c5c9f5bf8d54b87</t>
+          <t>https://www.indeed.com/viewjob?jk=fb663396a5bc1b79</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer II, Global Servicing Technology</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Accompany Health</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Glue, Spark, Scala, Kafka, NoSQL, Data Modeling, Terraform, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Google Cloud Platform, Cloud Storage, Hive, Spark, Scala, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f41df6bde69aeb07</t>
+          <t>https://www.indeed.com/viewjob?jk=5c5c9f5bf8d54b87</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Quality Automation Engineer (SDET) - Career</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Accompany Health</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Glue, Spark, Scala, Kafka, NoSQL, Data Modeling, Terraform, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b597edf918184e10</t>
+          <t>https://www.indeed.com/viewjob?jk=f41df6bde69aeb07</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Multi-Cloud Networking Engineer</t>
+          <t>Quality Automation Engineer (SDET) - Career</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5089f26e49e819d7</t>
+          <t>https://www.indeed.com/viewjob?jk=b597edf918184e10</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Multi-Cloud Networking Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,17 +3146,17 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d33e81401b69b22c</t>
+          <t>https://www.indeed.com/viewjob?jk=5089f26e49e819d7</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffcaa5c8b2e22e2b</t>
+          <t>https://www.indeed.com/viewjob?jk=d33e81401b69b22c</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Engineer, Go to Market (Remote)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
+          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c7e11f90c05edfc</t>
+          <t>https://www.indeed.com/viewjob?jk=ffcaa5c8b2e22e2b</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Sr. Infrastructure &amp; Security Engineer</t>
+          <t>Data Engineer, Go to Market (Remote)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>HerculesAI</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Campbell, CA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, Azure, GCP, Splunk, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=997e47a23e0d8261</t>
+          <t>https://www.indeed.com/viewjob?jk=8c7e11f90c05edfc</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data, AWS, ETL, Java/Python,</t>
+          <t>Sr. Infrastructure &amp; Security Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>HerculesAI</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Campbell, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, ETL, CI/CD, Terraform</t>
+          <t>AWS, Lambda, IAM, Azure, GCP, Splunk, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24b2eb0df8c7e284</t>
+          <t>https://www.indeed.com/viewjob?jk=997e47a23e0d8261</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Software Engineer III - Data, AWS, ETL, Java/Python,</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Cityblock Health</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, BigQuery, PostgreSQL, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76d763c610ac1510</t>
+          <t>https://www.indeed.com/viewjob?jk=24b2eb0df8c7e284</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Carrier</t>
+          <t>Cityblock Health</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, GCP, BigQuery, PostgreSQL, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab7c6d265d3522d2</t>
+          <t>https://www.indeed.com/viewjob?jk=76d763c610ac1510</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GM Motorsports</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Carrier</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Concord, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, Databricks Lakehouse, NoSQL, Docker</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c80625f8482f70fb</t>
+          <t>https://www.indeed.com/viewjob?jk=ab7c6d265d3522d2</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>DNP Software Engineer</t>
+          <t>Senior Data Engineer - GM Motorsports</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Client Resources, Inc.</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Concord, NC, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Spark, PySpark, Spark Streaming, CI/CD, Terraform, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, Databricks Lakehouse, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95f2f4f81bc33a7a</t>
+          <t>https://www.indeed.com/viewjob?jk=c80625f8482f70fb</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer- GM Energy</t>
+          <t>DNP Software Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Client Resources, Inc.</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, GCP, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>AWS, Glue, RDS, Spark, PySpark, Spark Streaming, CI/CD, Terraform, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51fb08298ca2e944</t>
+          <t>https://www.indeed.com/viewjob?jk=95f2f4f81bc33a7a</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Platform Architect (Snowflake)</t>
+          <t>Senior Backend Software Engineer- GM Energy</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Coastal</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Snowflake, Data Modeling, Kimball, ETL, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, GCP, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58854506afe876e4</t>
+          <t>https://www.indeed.com/viewjob?jk=51fb08298ca2e944</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Software Development Engineer III</t>
+          <t>Data Platform Architect (Snowflake)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Coastal</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Snowflake, Data Modeling, Kimball, ETL, dbt</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f950bd314b17c8f</t>
+          <t>https://www.indeed.com/viewjob?jk=58854506afe876e4</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>Software Development Engineer III</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5c449cb4c336ec2</t>
+          <t>https://www.indeed.com/viewjob?jk=1f950bd314b17c8f</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e57a91ca929fec5b</t>
+          <t>https://www.indeed.com/viewjob?jk=c5c449cb4c336ec2</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd22b6d5954a33c2</t>
+          <t>https://www.indeed.com/viewjob?jk=e57a91ca929fec5b</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d369f55f3c43cd0</t>
+          <t>https://www.indeed.com/viewjob?jk=cd22b6d5954a33c2</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5e852e1fb093faa</t>
+          <t>https://www.indeed.com/viewjob?jk=2d369f55f3c43cd0</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=122021b0213972fb</t>
+          <t>https://www.indeed.com/viewjob?jk=b5e852e1fb093faa</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf263b65906b30ba</t>
+          <t>https://www.indeed.com/viewjob?jk=122021b0213972fb</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=775f4b74d2e0d125</t>
+          <t>https://www.indeed.com/viewjob?jk=cf263b65906b30ba</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e27aa2f30115d6a9</t>
+          <t>https://www.indeed.com/viewjob?jk=775f4b74d2e0d125</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=372ffe4f2e9a605d</t>
+          <t>https://www.indeed.com/viewjob?jk=e27aa2f30115d6a9</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a256a77103c9ee18</t>
+          <t>https://www.indeed.com/viewjob?jk=372ffe4f2e9a605d</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b082342159bbdf7</t>
+          <t>https://www.indeed.com/viewjob?jk=a256a77103c9ee18</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e06cd5eb56a43b5c</t>
+          <t>https://www.indeed.com/viewjob?jk=9b082342159bbdf7</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daaeb6d16db98abf</t>
+          <t>https://www.indeed.com/viewjob?jk=e06cd5eb56a43b5c</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d61083f86948477</t>
+          <t>https://www.indeed.com/viewjob?jk=daaeb6d16db98abf</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71d4be4e91f6174a</t>
+          <t>https://www.indeed.com/viewjob?jk=5d61083f86948477</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=912b927f8e6b0bc9</t>
+          <t>https://www.indeed.com/viewjob?jk=71d4be4e91f6174a</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=697335a3240f02f2</t>
+          <t>https://www.indeed.com/viewjob?jk=912b927f8e6b0bc9</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e21309c64f987c4d</t>
+          <t>https://www.indeed.com/viewjob?jk=697335a3240f02f2</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e4114c9ced06f08</t>
+          <t>https://www.indeed.com/viewjob?jk=e21309c64f987c4d</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0379c77fb1bea285</t>
+          <t>https://www.indeed.com/viewjob?jk=6e4114c9ced06f08</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7404f3dbf25b5d0</t>
+          <t>https://www.indeed.com/viewjob?jk=0379c77fb1bea285</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19a128257d3c2c77</t>
+          <t>https://www.indeed.com/viewjob?jk=c7404f3dbf25b5d0</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a667aa6f915c8e9</t>
+          <t>https://www.indeed.com/viewjob?jk=19a128257d3c2c77</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d47c2036fa69322</t>
+          <t>https://www.indeed.com/viewjob?jk=6a667aa6f915c8e9</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=591077de2df74cfa</t>
+          <t>https://www.indeed.com/viewjob?jk=8d47c2036fa69322</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cc254c410ba6f38</t>
+          <t>https://www.indeed.com/viewjob?jk=591077de2df74cfa</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12339d025b6d4b6f</t>
+          <t>https://www.indeed.com/viewjob?jk=8cc254c410ba6f38</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc7db42760d4627e</t>
+          <t>https://www.indeed.com/viewjob?jk=12339d025b6d4b6f</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c024ec8f500d28f</t>
+          <t>https://www.indeed.com/viewjob?jk=dc7db42760d4627e</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5c090288e0e4f79</t>
+          <t>https://www.indeed.com/viewjob?jk=6c024ec8f500d28f</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c400db066fcfe868</t>
+          <t>https://www.indeed.com/viewjob?jk=d5c090288e0e4f79</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9857bbf535b2768</t>
+          <t>https://www.indeed.com/viewjob?jk=c400db066fcfe868</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior DBA / Database Architect</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Opeeka, Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Folsom, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Bitbucket</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5142b758be4e8f87</t>
+          <t>https://www.indeed.com/viewjob?jk=e9857bbf535b2768</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Application Developer</t>
+          <t>Senior DBA / Database Architect</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Value Truck of Arizona</t>
+          <t>Opeeka, Inc.</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>South Jordan, UT, US USA</t>
+          <t>Folsom, CA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Bitbucket</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,59 +4766,59 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6c3e26366316cc8</t>
+          <t>https://www.indeed.com/viewjob?jk=5142b758be4e8f87</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Application Developer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Value Truck of Arizona</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>South Jordan, UT, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, Terraform, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f72c641c65b5a61</t>
+          <t>https://www.indeed.com/viewjob?jk=f6c3e26366316cc8</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Software Engineer III – Python/PySpark/AWS</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,34 +4826,34 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, Terraform, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=991d5ceb2074b137</t>
+          <t>https://www.indeed.com/viewjob?jk=5f72c641c65b5a61</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>AV Safety Engineering Analytics Simulation Engineer (GPSSC)</t>
+          <t>Software Engineer III – Python/PySpark/AWS</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,34 +4861,34 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, Tableau, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, Lambda, S3, RDS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=759f2d176cc08b7e</t>
+          <t>https://www.indeed.com/viewjob?jk=991d5ceb2074b137</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>FSO LABS - AI Developer Senior - Bay Area</t>
+          <t>AV Safety Engineering Analytics Simulation Engineer (GPSSC)</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,24 +4896,24 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Hive, Spark, Kafka, NoSQL, Power BI, Docker, Kubernetes</t>
+          <t>AWS, RDS, Tableau, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d75a18fe3bc2126</t>
+          <t>https://www.indeed.com/viewjob?jk=759f2d176cc08b7e</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer - Senior - Consulting - Location Open</t>
+          <t>FSO LABS - AI Developer Senior - Bay Area</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,34 +4931,34 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, AKS</t>
+          <t>RDS, Azure, Hadoop, Hive, Spark, Kafka, NoSQL, Power BI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=599253e2d33dc75f</t>
+          <t>https://www.indeed.com/viewjob?jk=1d75a18fe3bc2126</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Data Engineer (Snowflake, Teradata, DB2)</t>
+          <t>Databricks Data Engineer - Senior - Consulting - Location Open</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Mutual of Omaha</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,34 +4966,34 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Scala, Snowflake, SQL Server, MongoDB, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, AKS</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa9d2ce9f1b5528c</t>
+          <t>https://www.indeed.com/viewjob?jk=599253e2d33dc75f</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer (Snowflake, Teradata, DB2)</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>ObjectStream</t>
+          <t>Mutual of Omaha</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Blob Storage, Spark, PySpark, ETL, dbt, Airflow, Apache Airflow</t>
+          <t>AWS, Glue, RDS, Scala, Snowflake, SQL Server, MongoDB, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,24 +5011,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06e3854d22cdba89</t>
+          <t>https://www.indeed.com/viewjob?jk=aa9d2ce9f1b5528c</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>PySpark Data Engineer III - Python/Java/SQL</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>ObjectStream</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,34 +5036,34 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Blob Storage, Spark, PySpark, ETL, dbt, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=926547138e49a51b</t>
+          <t>https://www.indeed.com/viewjob?jk=06e3854d22cdba89</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Cloud Engineering &amp; FinOps</t>
+          <t>PySpark Data Engineer III - Python/Java/SQL</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d576082b1c56db5c</t>
+          <t>https://www.indeed.com/viewjob?jk=926547138e49a51b</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer (R-19149)</t>
+          <t>Senior Software Engineer – Cloud Engineering &amp; FinOps</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Dun &amp; Bradstreet</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb41c4b9d93e0f98</t>
+          <t>https://www.indeed.com/viewjob?jk=d576082b1c56db5c</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Cloud Platform Engineer (R-19149)</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Dun &amp; Bradstreet</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,17 +5141,17 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=983d0a4b6df6a34b</t>
+          <t>https://www.indeed.com/viewjob?jk=cb41c4b9d93e0f98</t>
         </is>
       </c>
     </row>
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e39cfd742ca8ccb7</t>
+          <t>https://www.indeed.com/viewjob?jk=983d0a4b6df6a34b</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d24b9bb7d3f81d1</t>
+          <t>https://www.indeed.com/viewjob?jk=e39cfd742ca8ccb7</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=406f01e6594b2624</t>
+          <t>https://www.indeed.com/viewjob?jk=4d24b9bb7d3f81d1</t>
         </is>
       </c>
     </row>
@@ -5291,14 +5291,14 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0206f3baae13d0ec</t>
+          <t>https://www.indeed.com/viewjob?jk=406f01e6594b2624</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Full‑Stack Developer (Java, React, Microservices) *Hybrid*</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,17 +5316,17 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=229f6840535c3531</t>
+          <t>https://www.indeed.com/viewjob?jk=0206f3baae13d0ec</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,14 +5361,14 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606324c85c044a5d</t>
+          <t>https://www.indeed.com/viewjob?jk=229f6840535c3531</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
+          <t>Full‑Stack Developer (Java, React, Microservices) *Hybrid*</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Smyrna, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,14 +5396,14 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef040d1b01903853</t>
+          <t>https://www.indeed.com/viewjob?jk=606324c85c044a5d</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Full‑Stack Developer (Java, React, Microservices) *Hybrid*</t>
+          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Smyrna, GA, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,24 +5431,24 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f298bb4ddf8e9a0</t>
+          <t>https://www.indeed.com/viewjob?jk=ef040d1b01903853</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Information Technology - Data Integration Engineer</t>
+          <t>Full‑Stack Developer (Java, React, Microservices) *Hybrid*</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Magnolia</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Waco, TX, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,24 +5466,24 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22a077ceb692752f</t>
+          <t>https://www.indeed.com/viewjob?jk=0f298bb4ddf8e9a0</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - GM Motorsports</t>
+          <t>Information Technology - Data Integration Engineer</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Magnolia</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Concord, NC, US USA</t>
+          <t>Waco, TX, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,34 +5491,34 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, GCP, Scala, Kafka, MongoDB, NoSQL, Docker</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f660072154c9a61</t>
+          <t>https://www.indeed.com/viewjob?jk=22a077ceb692752f</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Developer</t>
+          <t>Senior Software Engineer - GM Motorsports</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Douglas Machine Inc.</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Alexandria, MN, US USA</t>
+          <t>Concord, NC, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,34 +5526,34 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Event Hubs, GCP, Scala, Kafka, MongoDB, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9d5d216fe71b48e</t>
+          <t>https://www.indeed.com/viewjob?jk=6f660072154c9a61</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>SEI Investments</t>
+          <t>Douglas Machine Inc.</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Oaks, PA, US USA</t>
+          <t>Alexandria, MN, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,15 +5561,50 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f9d5d216fe71b48e</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>SEI Investments</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Oaks, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
           <t>Kafka, Snowflake, Oracle, SQL Server, MySQL, MongoDB, Jenkins, Docker, Kubernetes, AKS</t>
         </is>
       </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=76c94610856b0496</t>
         </is>

--- a/results/job_matches_2026-05-01.xlsx
+++ b/results/job_matches_2026-05-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G148"/>
+  <dimension ref="A1:G153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,52 +538,52 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Neomax</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Dataflow, Spark, Scala, Kafka, NoSQL, Data Modeling, ELT</t>
+          <t>AWS, Kinesis, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49b6a92728349bc5</t>
+          <t>https://www.indeed.com/viewjob?jk=776692a890b58814</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Select Minds LLC</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, Databricks, Spark</t>
+          <t>AWS, RDS, Azure, Dataflow, Spark, Scala, Kafka, NoSQL, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9d0ac6d3cf445a9</t>
+          <t>https://www.indeed.com/viewjob?jk=49b6a92728349bc5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Technical Architect-Datawarehousing</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Select Minds LLC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Marlborough, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, Databricks, Spark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,59 +636,59 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10720f22d9d38621</t>
+          <t>https://www.indeed.com/viewjob?jk=d9d0ac6d3cf445a9</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AV Safety Engineering Analytics AI/ML Engineer (GPSSC)</t>
+          <t>Technical Architect-Datawarehousing</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Marlborough, MA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Dataflow, Spark, PySpark</t>
+          <t>AWS, S3, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=675259892fa0b51c</t>
+          <t>https://www.indeed.com/viewjob?jk=10720f22d9d38621</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Junior Cloud Security Analyst</t>
+          <t>AV Safety Engineering Analytics AI/ML Engineer (GPSSC)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,34 +696,34 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Dataflow, Spark, PySpark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85598b1d63680693</t>
+          <t>https://www.indeed.com/viewjob?jk=675259892fa0b51c</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (C#/.NET &amp; AI)</t>
+          <t>Junior Cloud Security Analyst</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93c21b258a08bd24</t>
+          <t>https://www.indeed.com/viewjob?jk=85598b1d63680693</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr Software Engineer II - Enterprise Architecture</t>
+          <t>Senior Software Engineer (C#/.NET &amp; AI)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,34 +766,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6bd0f139eec27a7</t>
+          <t>https://www.indeed.com/viewjob?jk=93c21b258a08bd24</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Cloud Network Automation Engineer</t>
+          <t>Sr Software Engineer II - Enterprise Architecture</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a0cf6116e02d635</t>
+          <t>https://www.indeed.com/viewjob?jk=f6bd0f139eec27a7</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Cloud Engineer II</t>
+          <t>Cloud Network Automation Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Vibrant Emotional Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ba39b2a6826c32d</t>
+          <t>https://www.indeed.com/viewjob?jk=0a0cf6116e02d635</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Engineer - AI &amp; Data Management</t>
+          <t>Cloud Engineer II</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Vibrant Emotional Health</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>S3, Azure, Data Factory, Cloud Storage, Hadoop, HDFS, Spark, Scala, Kafka, Informatica PowerCenter</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f98760c842e5085</t>
+          <t>https://www.indeed.com/viewjob?jk=3ba39b2a6826c32d</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Engineer - AI &amp; Data Management</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tradeweb</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, GCP, Spark, Kafka, Dask, Snowflake</t>
+          <t>S3, Azure, Data Factory, Cloud Storage, Hadoop, HDFS, Spark, Scala, Kafka, Informatica PowerCenter</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb2021c38a5314d9</t>
+          <t>https://www.indeed.com/viewjob?jk=0f98760c842e5085</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GenAI Threat Intelligence Analyst</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tradeweb</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Blob Storage, Google Cloud Platform, Vertex AI, Scala, MLOps, MLflow</t>
+          <t>AWS, Redshift, S3, IAM, RDS, GCP, Spark, Kafka, Dask, Snowflake</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5efecdb56da9cdd1</t>
+          <t>https://www.indeed.com/viewjob?jk=cb2021c38a5314d9</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>GenAI Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Metropolitan Commercial Bank</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Blob Storage, Google Cloud Platform, Vertex AI, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25250927f01c87fd</t>
+          <t>https://www.indeed.com/viewjob?jk=5efecdb56da9cdd1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Credera</t>
+          <t>Metropolitan Commercial Bank</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Oozie, Spark, Scala, Kafka, SQL Server</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2859c21fcc6b9b6</t>
+          <t>https://www.indeed.com/viewjob?jk=25250927f01c87fd</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e65ae12c9231691</t>
+          <t>https://www.indeed.com/viewjob?jk=a2859c21fcc6b9b6</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=deb9ad8464ceb6e6</t>
+          <t>https://www.indeed.com/viewjob?jk=9e65ae12c9231691</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,42 +1126,42 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0faede29102fb7e1</t>
+          <t>https://www.indeed.com/viewjob?jk=deb9ad8464ceb6e6</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Azure Data &amp; Development Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SunStone Consulting</t>
+          <t>Credera</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Event Hubs, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Oozie, Spark, Scala, Kafka, SQL Server</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e9052cac6c7210d</t>
+          <t>https://www.indeed.com/viewjob?jk=0faede29102fb7e1</t>
         </is>
       </c>
     </row>
@@ -1238,17 +1238,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineer, Full Stack - AI (Chicago)</t>
+          <t>Azure Data &amp; Development Architect</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Fitch Group</t>
+          <t>SunStone Consulting</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,24 +1256,24 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Event Hubs, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4bb35a3533f1ee6</t>
+          <t>https://www.indeed.com/viewjob?jk=1e9052cac6c7210d</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Engineering &amp; Quality - Software Engineer, Full Stack - AI</t>
+          <t>Software Engineer, Full Stack - AI (Chicago)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,94 +1301,94 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf6b928dd59e0c41</t>
+          <t>https://www.indeed.com/viewjob?jk=d4bb35a3533f1ee6</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer II _ Big Data, GCP _EDAI</t>
+          <t>Engineering &amp; Quality - Software Engineer, Full Stack - AI</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Fitch Group</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d725c4b26e048534</t>
+          <t>https://www.indeed.com/viewjob?jk=cf6b928dd59e0c41</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Business System Analyst with Property and Casualty Domain</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>SRR Consultants</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Glen Allen, VA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fc4628968aad9e2</t>
+          <t>https://www.indeed.com/viewjob?jk=7446cde797c8f4de</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer II _ Big Data, GCP _EDAI</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,17 +1396,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0eb5fc1d601c0028</t>
+          <t>https://www.indeed.com/viewjob?jk=d725c4b26e048534</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Trane Technologies</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acae1b7fc51e9a39</t>
+          <t>https://www.indeed.com/viewjob?jk=f483db2edc8cb83a</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Trane Technologies</t>
+          <t>JUUL Labs</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, S3, ECS, IAM, RDS, GCP, Dataflow, Cloud Storage, Scala, Splunk</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f483db2edc8cb83a</t>
+          <t>https://www.indeed.com/viewjob?jk=c63edb85327f9aef</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>JUUL Labs</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, GCP, Dataflow, Cloud Storage, Scala, Splunk</t>
+          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, Snowflake, SQL Server, MySQL, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c63edb85327f9aef</t>
+          <t>https://www.indeed.com/viewjob?jk=de10d304d09880c3</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, Snowflake, SQL Server, MySQL, ELT</t>
+          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de10d304d09880c3</t>
+          <t>https://www.indeed.com/viewjob?jk=0fc4628968aad9e2</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>DEVELOPER L3(CONTRACT)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Cloud Storage, Spark, PySpark, Scala, Snowflake, Time Travel, Databricks Lakehouse, Snowflake Schema</t>
+          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c37881d8861b3d6</t>
+          <t>https://www.indeed.com/viewjob?jk=0eb5fc1d601c0028</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Ad Ops Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d412becc7b99de0</t>
+          <t>https://www.indeed.com/viewjob?jk=acae1b7fc51e9a39</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer Seniors – Cloud Technologies | Fintech | Full Stack</t>
+          <t>DEVELOPER L3(CONTRACT)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>FIS</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Oracle, SQL Server, NoSQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Databricks, Cloud Storage, Spark, PySpark, Scala, Snowflake, Time Travel, Databricks Lakehouse, Snowflake Schema</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d35fe7a7c554f8b5</t>
+          <t>https://www.indeed.com/viewjob?jk=1c37881d8861b3d6</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Platform Engineer Senior</t>
+          <t>Senior Ad Ops Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Texas Capital Bank</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,112 +1676,112 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09ac756571edd2b5</t>
+          <t>https://www.indeed.com/viewjob?jk=3d412becc7b99de0</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Dev Ops Engineer</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SkyWater Technology Foundry</t>
+          <t>Matillion</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Photon, GCP, Vertex AI, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13bfee40249f3478</t>
+          <t>https://www.indeed.com/viewjob?jk=95bbbaf8fbe8db68</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Business Intelligence Solutions Architect</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Mars Technominds</t>
+          <t>Matillion</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38246f1a187f1c7d</t>
+          <t>https://www.indeed.com/viewjob?jk=2c7ffe9dfedc9c5d</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ERP Data Management Architect (Manufacturing)</t>
+          <t>Software Engineer Seniors – Cloud Technologies | Fintech | Full Stack</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Infor</t>
+          <t>FIS</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Oracle, MySQL, Data Modeling, ETL</t>
+          <t>AWS, Azure, Data Factory, Scala, Oracle, SQL Server, NoSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e45199011cbe2990</t>
+          <t>https://www.indeed.com/viewjob?jk=d35fe7a7c554f8b5</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineer I – AI Assistant Framework, ArcGIS Enterprise</t>
+          <t>Platform Engineer Senior</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>Texas Capital Bank</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, Redshift, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2546eaf4a3e50baf</t>
+          <t>https://www.indeed.com/viewjob?jk=09ac756571edd2b5</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Site AI Engineer</t>
+          <t>Senior Dev Ops Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>SkyWater Technology Foundry</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Temple, TX, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Photon, GCP, Vertex AI, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9df42fb6f0e5b92</t>
+          <t>https://www.indeed.com/viewjob?jk=13bfee40249f3478</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Business Intelligence Solutions Architect</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Client Resources, Inc.</t>
+          <t>Mars Technominds</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, GCP, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1e155aced1efdff</t>
+          <t>https://www.indeed.com/viewjob?jk=38246f1a187f1c7d</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>ERP Data Management Architect (Manufacturing)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>Infor</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, S3, IAM, Hadoop, Spark, Kafka, Snowflake, Splunk</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Oracle, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,67 +1931,67 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f01d239e5c828f6</t>
+          <t>https://www.indeed.com/viewjob?jk=e45199011cbe2990</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Oracle Financials Functional Consultant</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Intelligent Medical Objects</t>
+          <t>SRR Consultants</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Spark, Scala, Data Modeling, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4869d3a6ac24136</t>
+          <t>https://www.indeed.com/viewjob?jk=b7d13b47b7b7c8a2</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Infrastructure-as-Code (IaC) Engineer</t>
+          <t>Software Engineer I – AI Assistant Framework, ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Databricks</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca35900639cbe443</t>
+          <t>https://www.indeed.com/viewjob?jk=2546eaf4a3e50baf</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Engineer - Agentic AI</t>
+          <t>Site AI Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Temple, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5daf8f72a4fd9ab6</t>
+          <t>https://www.indeed.com/viewjob?jk=b9df42fb6f0e5b92</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer/SRE - GM Energy</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Client Resources, Inc.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, GCP, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0413ce8de5fcca6a</t>
+          <t>https://www.indeed.com/viewjob?jk=d1e155aced1efdff</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Developer - Used Car Marketplace</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Redshift, Athena, S3, IAM, Hadoop, Spark, Kafka, Snowflake, Splunk</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d487bcb34632271a</t>
+          <t>https://www.indeed.com/viewjob?jk=0f01d239e5c828f6</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Intelligent Medical Objects</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Spark, Scala, Data Modeling, dbt, Power BI</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79a2a043dc5cdb8f</t>
+          <t>https://www.indeed.com/viewjob?jk=c4869d3a6ac24136</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
+          <t>Infrastructure-as-Code (IaC) Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Databricks</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e387db2c2b866baa</t>
+          <t>https://www.indeed.com/viewjob?jk=ca35900639cbe443</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
+          <t>Senior Engineer - Agentic AI</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, Lambda, SQS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18a022cbc2b4d934</t>
+          <t>https://www.indeed.com/viewjob?jk=5daf8f72a4fd9ab6</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
+          <t>Senior Backend Software Engineer/SRE - GM Energy</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cc4f959dd712f8a</t>
+          <t>https://www.indeed.com/viewjob?jk=0413ce8de5fcca6a</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
+          <t>Software Developer - Used Car Marketplace</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Yonkers, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=688d7763683eecad</t>
+          <t>https://www.indeed.com/viewjob?jk=d487bcb34632271a</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Distinguished Engineer -</t>
+          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, GCP, Snowflake, ELT, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=087eb595cff7bd93</t>
+          <t>https://www.indeed.com/viewjob?jk=79a2a043dc5cdb8f</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Smithfield, RI, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,42 +2341,42 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Spark, Scala, Snowflake, Oracle, ETL, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cc22367a2ce3d9f</t>
+          <t>https://www.indeed.com/viewjob?jk=e387db2c2b866baa</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AI/ML Engineer – Data &amp; Full-Stack Solutions</t>
+          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ITC Federal</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,67 +2386,67 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce30a23eaa64abcd</t>
+          <t>https://www.indeed.com/viewjob?jk=18a022cbc2b4d934</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Commercial Software</t>
+          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Oracle, MySQL</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ca1245fe1b2a956</t>
+          <t>https://www.indeed.com/viewjob?jk=5cc4f959dd712f8a</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Yonkers, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Snowflake, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,94 +2456,94 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36a73b40629cc484</t>
+          <t>https://www.indeed.com/viewjob?jk=688d7763683eecad</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Java Cloud-Native Developer</t>
+          <t>Distinguished Engineer -</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, DynamoDB, NoSQL</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, GCP, Snowflake, ELT, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7fe4ad94b5b821d</t>
+          <t>https://www.indeed.com/viewjob?jk=087eb595cff7bd93</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Smithfield, RI, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, EMR, RDS, Spark, Scala, Snowflake, Oracle, ETL, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0d2f3586b2ed198</t>
+          <t>https://www.indeed.com/viewjob?jk=5cc22367a2ce3d9f</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer II</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, Splunk, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Snowflake, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fa53cf983e1a6d0</t>
+          <t>https://www.indeed.com/viewjob?jk=36a73b40629cc484</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Artificial Intelligence/Machine Learning Data Engineer</t>
+          <t>AI/ML Engineer – Data &amp; Full-Stack Solutions</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>ITC Federal</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow</t>
+          <t>AWS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f6f11467cb82584</t>
+          <t>https://www.indeed.com/viewjob?jk=ce30a23eaa64abcd</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Artificial Intelligence/Machine Learning Data Engineer</t>
+          <t>Senior Software Engineer - Commercial Software</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Oracle, MySQL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9ce81a6707266dd</t>
+          <t>https://www.indeed.com/viewjob?jk=4ca1245fe1b2a956</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Artificial Intelligence/Machine Learning Data Engineer</t>
+          <t>Java Cloud-Native Developer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Logic, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e34c2e31eeb33f9e</t>
+          <t>https://www.indeed.com/viewjob?jk=b7fe4ad94b5b821d</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Quality Assurance Analyst / ETL Tester</t>
+          <t>Software Development Engineer II</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Briljent</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,42 +2691,42 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Snowflake, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL, Data Modeling, Snowflake Schema, ETL</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d69b1256484e3a82</t>
+          <t>https://www.indeed.com/viewjob?jk=c0d2f3586b2ed198</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (Remote)</t>
+          <t>Senior Site Reliability Engineer II</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, NoSQL, CI/CD, Git, Python, SQL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdbdb16275078800</t>
+          <t>https://www.indeed.com/viewjob?jk=6fa53cf983e1a6d0</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sr. Java Developers</t>
+          <t>Artificial Intelligence/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Vibotek LLC</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, HBase, Spark, Scala, Kafka, Oracle, Cassandra, NoSQL, Jenkins, Docker</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=061d80fcb09266da</t>
+          <t>https://www.indeed.com/viewjob?jk=8f6f11467cb82584</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Systems &amp; Cloud Infrastructure Engineer</t>
+          <t>Artificial Intelligence/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Kretek International</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Moorpark, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Splunk, Terraform</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7d7d86c5d6aef50</t>
+          <t>https://www.indeed.com/viewjob?jk=c9ce81a6707266dd</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer - Performance Management</t>
+          <t>Artificial Intelligence/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>Logic, Inc.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Lake Buena Vista, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,59 +2841,59 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57b0af5961338ef2</t>
+          <t>https://www.indeed.com/viewjob?jk=e34c2e31eeb33f9e</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Full Stack, Data &amp; Analytics Engineer</t>
+          <t>Quality Assurance Analyst / ETL Tester</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SCAN Health Plan</t>
+          <t>Briljent</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Snowflake, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b0db4093988ff3c</t>
+          <t>https://www.indeed.com/viewjob?jk=d69b1256484e3a82</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer - Performance Management</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Tennessee Titans</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Lake Buena Vista, FL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Data Modeling, ELT, dbt</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7b90aa43b4806b0</t>
+          <t>https://www.indeed.com/viewjob?jk=b85eeb0fd5a3a862</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Systems Engineer, Release Reliability &amp; Automation (Autonomous Vehicles)</t>
+          <t>Systems &amp; Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Kretek International</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Moorpark, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Power BI, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Splunk, Terraform</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f97782145b5d3f94</t>
+          <t>https://www.indeed.com/viewjob?jk=a7d7d86c5d6aef50</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Reliability Engineer (Autonomous Vehicles)</t>
+          <t>Data Engineer - Performance Management</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Lake Buena Vista, FL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Power BI, CI/CD, Jenkins</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf25e4c14df46394</t>
+          <t>https://www.indeed.com/viewjob?jk=57b0af5961338ef2</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>AI/ML Developer II (Remote)</t>
+          <t>Full Stack, Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>SCAN Health Plan</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, NoSQL, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,172 +3016,172 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb663396a5bc1b79</t>
+          <t>https://www.indeed.com/viewjob?jk=6b0db4093988ff3c</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Engineer II, Global Servicing Technology</t>
+          <t>Senior Machine Learning Engineer (Remote)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, Cloud Storage, Hive, Spark, Scala, ETL, CI/CD, Jenkins</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, NoSQL, CI/CD, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c5c9f5bf8d54b87</t>
+          <t>https://www.indeed.com/viewjob?jk=fdbdb16275078800</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Accompany Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Glue, Spark, Scala, Kafka, NoSQL, Data Modeling, Terraform, Airflow, Apache Airflow</t>
+          <t>RDS, Databricks, Scala, Snowflake, PostgreSQL, MySQL, Splunk, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f41df6bde69aeb07</t>
+          <t>https://www.indeed.com/viewjob?jk=1869e5a8847d426e</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Quality Automation Engineer (SDET) - Career</t>
+          <t>Software Systems Engineer, Release Reliability &amp; Automation (Autonomous Vehicles)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Power BI, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b597edf918184e10</t>
+          <t>https://www.indeed.com/viewjob?jk=f97782145b5d3f94</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Multi-Cloud Networking Engineer</t>
+          <t>Reliability Engineer (Autonomous Vehicles)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Power BI, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5089f26e49e819d7</t>
+          <t>https://www.indeed.com/viewjob?jk=cf25e4c14df46394</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI/ML Developer II (Remote)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, NoSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d33e81401b69b22c</t>
+          <t>https://www.indeed.com/viewjob?jk=fb663396a5bc1b79</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Multi-Cloud Networking Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffcaa5c8b2e22e2b</t>
+          <t>https://www.indeed.com/viewjob?jk=5089f26e49e819d7</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Engineer, Go to Market (Remote)</t>
+          <t>Software Engineer II, Global Servicing Technology</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
+          <t>AWS, RDS, Google Cloud Platform, Cloud Storage, Hive, Spark, Scala, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c7e11f90c05edfc</t>
+          <t>https://www.indeed.com/viewjob?jk=5c5c9f5bf8d54b87</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Sr. Infrastructure &amp; Security Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>HerculesAI</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Campbell, CA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, Azure, GCP, Splunk, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=997e47a23e0d8261</t>
+          <t>https://www.indeed.com/viewjob?jk=d33e81401b69b22c</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data, AWS, ETL, Java/Python,</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, ETL, CI/CD, Terraform</t>
+          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24b2eb0df8c7e284</t>
+          <t>https://www.indeed.com/viewjob?jk=ffcaa5c8b2e22e2b</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Cityblock Health</t>
+          <t>Accompany Health</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, BigQuery, PostgreSQL, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Spark, Scala, Kafka, NoSQL, Data Modeling, Terraform, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76d763c610ac1510</t>
+          <t>https://www.indeed.com/viewjob?jk=f41df6bde69aeb07</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer, Go to Market (Remote)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Carrier</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab7c6d265d3522d2</t>
+          <t>https://www.indeed.com/viewjob?jk=8c7e11f90c05edfc</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GM Motorsports</t>
+          <t>Sr. Infrastructure &amp; Security Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>HerculesAI</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Concord, NC, US USA</t>
+          <t>Campbell, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, Databricks Lakehouse, NoSQL, Docker</t>
+          <t>AWS, Lambda, IAM, Azure, GCP, Splunk, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c80625f8482f70fb</t>
+          <t>https://www.indeed.com/viewjob?jk=997e47a23e0d8261</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>DNP Software Engineer</t>
+          <t>Software Engineer III - Data, AWS, ETL, Java/Python,</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Client Resources, Inc.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Spark, PySpark, Spark Streaming, CI/CD, Terraform, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95f2f4f81bc33a7a</t>
+          <t>https://www.indeed.com/viewjob?jk=24b2eb0df8c7e284</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer- GM Energy</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Cityblock Health</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, GCP, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, BigQuery, PostgreSQL, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51fb08298ca2e944</t>
+          <t>https://www.indeed.com/viewjob?jk=76d763c610ac1510</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Platform Architect (Snowflake)</t>
+          <t>Senior Data Engineer - GM Motorsports</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Coastal</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Concord, NC, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Snowflake, Data Modeling, Kimball, ETL, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, Databricks Lakehouse, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58854506afe876e4</t>
+          <t>https://www.indeed.com/viewjob?jk=c80625f8482f70fb</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Software Development Engineer III</t>
+          <t>Quality Automation Engineer (SDET) - Career</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f950bd314b17c8f</t>
+          <t>https://www.indeed.com/viewjob?jk=b597edf918184e10</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>SR DBA / DATABASE ARCHITECT (AZURE / MSSQL)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Opeeka, Inc.</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Folsom, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Bitbucket</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5c449cb4c336ec2</t>
+          <t>https://www.indeed.com/viewjob?jk=d57af04f58fc4f3b</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>DNP Software Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Client Resources, Inc.</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, Glue, RDS, Spark, PySpark, Spark Streaming, CI/CD, Terraform, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e57a91ca929fec5b</t>
+          <t>https://www.indeed.com/viewjob?jk=95f2f4f81bc33a7a</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>Senior Backend Software Engineer- GM Energy</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, GCP, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd22b6d5954a33c2</t>
+          <t>https://www.indeed.com/viewjob?jk=51fb08298ca2e944</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>Data Platform Architect (Snowflake)</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Coastal</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Snowflake, Data Modeling, Kimball, ETL, dbt</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d369f55f3c43cd0</t>
+          <t>https://www.indeed.com/viewjob?jk=58854506afe876e4</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>Software Development Engineer III</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5e852e1fb093faa</t>
+          <t>https://www.indeed.com/viewjob?jk=1f950bd314b17c8f</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=122021b0213972fb</t>
+          <t>https://www.indeed.com/viewjob?jk=c5c449cb4c336ec2</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf263b65906b30ba</t>
+          <t>https://www.indeed.com/viewjob?jk=e57a91ca929fec5b</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=775f4b74d2e0d125</t>
+          <t>https://www.indeed.com/viewjob?jk=cd22b6d5954a33c2</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e27aa2f30115d6a9</t>
+          <t>https://www.indeed.com/viewjob?jk=2d369f55f3c43cd0</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=372ffe4f2e9a605d</t>
+          <t>https://www.indeed.com/viewjob?jk=b5e852e1fb093faa</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a256a77103c9ee18</t>
+          <t>https://www.indeed.com/viewjob?jk=122021b0213972fb</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b082342159bbdf7</t>
+          <t>https://www.indeed.com/viewjob?jk=cf263b65906b30ba</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e06cd5eb56a43b5c</t>
+          <t>https://www.indeed.com/viewjob?jk=775f4b74d2e0d125</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daaeb6d16db98abf</t>
+          <t>https://www.indeed.com/viewjob?jk=e27aa2f30115d6a9</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d61083f86948477</t>
+          <t>https://www.indeed.com/viewjob?jk=372ffe4f2e9a605d</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71d4be4e91f6174a</t>
+          <t>https://www.indeed.com/viewjob?jk=a256a77103c9ee18</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=912b927f8e6b0bc9</t>
+          <t>https://www.indeed.com/viewjob?jk=9b082342159bbdf7</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=697335a3240f02f2</t>
+          <t>https://www.indeed.com/viewjob?jk=e06cd5eb56a43b5c</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e21309c64f987c4d</t>
+          <t>https://www.indeed.com/viewjob?jk=daaeb6d16db98abf</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e4114c9ced06f08</t>
+          <t>https://www.indeed.com/viewjob?jk=5d61083f86948477</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0379c77fb1bea285</t>
+          <t>https://www.indeed.com/viewjob?jk=71d4be4e91f6174a</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7404f3dbf25b5d0</t>
+          <t>https://www.indeed.com/viewjob?jk=912b927f8e6b0bc9</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19a128257d3c2c77</t>
+          <t>https://www.indeed.com/viewjob?jk=697335a3240f02f2</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a667aa6f915c8e9</t>
+          <t>https://www.indeed.com/viewjob?jk=e21309c64f987c4d</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d47c2036fa69322</t>
+          <t>https://www.indeed.com/viewjob?jk=6e4114c9ced06f08</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=591077de2df74cfa</t>
+          <t>https://www.indeed.com/viewjob?jk=0379c77fb1bea285</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cc254c410ba6f38</t>
+          <t>https://www.indeed.com/viewjob?jk=c7404f3dbf25b5d0</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12339d025b6d4b6f</t>
+          <t>https://www.indeed.com/viewjob?jk=19a128257d3c2c77</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc7db42760d4627e</t>
+          <t>https://www.indeed.com/viewjob?jk=6a667aa6f915c8e9</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c024ec8f500d28f</t>
+          <t>https://www.indeed.com/viewjob?jk=8d47c2036fa69322</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5c090288e0e4f79</t>
+          <t>https://www.indeed.com/viewjob?jk=591077de2df74cfa</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c400db066fcfe868</t>
+          <t>https://www.indeed.com/viewjob?jk=8cc254c410ba6f38</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9857bbf535b2768</t>
+          <t>https://www.indeed.com/viewjob?jk=12339d025b6d4b6f</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior DBA / Database Architect</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Opeeka, Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Folsom, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Bitbucket</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5142b758be4e8f87</t>
+          <t>https://www.indeed.com/viewjob?jk=dc7db42760d4627e</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Application Developer</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Value Truck of Arizona</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>South Jordan, UT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,67 +4801,67 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6c3e26366316cc8</t>
+          <t>https://www.indeed.com/viewjob?jk=6c024ec8f500d28f</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, Terraform, Airflow, Apache Airflow</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f72c641c65b5a61</t>
+          <t>https://www.indeed.com/viewjob?jk=d5c090288e0e4f79</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Software Engineer III – Python/PySpark/AWS</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,112 +4871,112 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=991d5ceb2074b137</t>
+          <t>https://www.indeed.com/viewjob?jk=c400db066fcfe868</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>AV Safety Engineering Analytics Simulation Engineer (GPSSC)</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, RDS, Tableau, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=759f2d176cc08b7e</t>
+          <t>https://www.indeed.com/viewjob?jk=e9857bbf535b2768</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>FSO LABS - AI Developer Senior - Bay Area</t>
+          <t>Senior DBA / Database Architect</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Opeeka, Inc.</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Folsom, CA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Hive, Spark, Kafka, NoSQL, Power BI, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Bitbucket</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d75a18fe3bc2126</t>
+          <t>https://www.indeed.com/viewjob?jk=5142b758be4e8f87</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer - Senior - Consulting - Location Open</t>
+          <t>Application Developer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Value Truck of Arizona</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>South Jordan, UT, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=599253e2d33dc75f</t>
+          <t>https://www.indeed.com/viewjob?jk=f6c3e26366316cc8</t>
         </is>
       </c>
     </row>
@@ -5018,17 +5018,17 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>ObjectStream</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Blob Storage, Spark, PySpark, ETL, dbt, Airflow, Apache Airflow</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, Terraform, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06e3854d22cdba89</t>
+          <t>https://www.indeed.com/viewjob?jk=5f72c641c65b5a61</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>PySpark Data Engineer III - Python/Java/SQL</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>ObjectStream</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,34 +5071,34 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Blob Storage, Spark, PySpark, ETL, dbt, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=926547138e49a51b</t>
+          <t>https://www.indeed.com/viewjob?jk=06e3854d22cdba89</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Cloud Engineering &amp; FinOps</t>
+          <t>PySpark Data Engineer III - Python/Java/SQL</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d576082b1c56db5c</t>
+          <t>https://www.indeed.com/viewjob?jk=926547138e49a51b</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer (R-19149)</t>
+          <t>Senior Software Engineer – Cloud Engineering &amp; FinOps</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Dun &amp; Bradstreet</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb41c4b9d93e0f98</t>
+          <t>https://www.indeed.com/viewjob?jk=d576082b1c56db5c</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Cloud Platform Engineer (R-19149)</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Dun &amp; Bradstreet</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,34 +5176,34 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=983d0a4b6df6a34b</t>
+          <t>https://www.indeed.com/viewjob?jk=cb41c4b9d93e0f98</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Databricks Data Engineer - Senior - Consulting - Location Open</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,34 +5211,34 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, AKS</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e39cfd742ca8ccb7</t>
+          <t>https://www.indeed.com/viewjob?jk=599253e2d33dc75f</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer III – Python/PySpark/AWS</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,34 +5246,34 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, RDS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d24b9bb7d3f81d1</t>
+          <t>https://www.indeed.com/viewjob?jk=991d5ceb2074b137</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AV Safety Engineering Analytics Simulation Engineer (GPSSC)</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,34 +5281,34 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Tableau, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=406f01e6594b2624</t>
+          <t>https://www.indeed.com/viewjob?jk=759f2d176cc08b7e</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>FSO LABS - AI Developer Senior - Bay Area</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,24 +5316,24 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Hadoop, Hive, Spark, Kafka, NoSQL, Power BI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0206f3baae13d0ec</t>
+          <t>https://www.indeed.com/viewjob?jk=1d75a18fe3bc2126</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Full‑Stack Developer (Java, React, Microservices) *Hybrid*</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -5351,24 +5351,24 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=229f6840535c3531</t>
+          <t>https://www.indeed.com/viewjob?jk=983d0a4b6df6a34b</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Full‑Stack Developer (Java, React, Microservices) *Hybrid*</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,24 +5386,24 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606324c85c044a5d</t>
+          <t>https://www.indeed.com/viewjob?jk=e39cfd742ca8ccb7</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Smyrna, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,24 +5421,24 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef040d1b01903853</t>
+          <t>https://www.indeed.com/viewjob?jk=4d24b9bb7d3f81d1</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Full‑Stack Developer (Java, React, Microservices) *Hybrid*</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -5456,34 +5456,34 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f298bb4ddf8e9a0</t>
+          <t>https://www.indeed.com/viewjob?jk=406f01e6594b2624</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Information Technology - Data Integration Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Magnolia</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Waco, TX, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,34 +5491,34 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22a077ceb692752f</t>
+          <t>https://www.indeed.com/viewjob?jk=0206f3baae13d0ec</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - GM Motorsports</t>
+          <t>Full‑Stack Developer (Java, React, Microservices) *Hybrid*</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Concord, NC, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,34 +5526,34 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, GCP, Scala, Kafka, MongoDB, NoSQL, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f660072154c9a61</t>
+          <t>https://www.indeed.com/viewjob?jk=229f6840535c3531</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Developer</t>
+          <t>Full‑Stack Developer (Java, React, Microservices) *Hybrid*</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Douglas Machine Inc.</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Alexandria, MN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5571,24 +5571,24 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9d5d216fe71b48e</t>
+          <t>https://www.indeed.com/viewjob?jk=606324c85c044a5d</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>SEI Investments</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Oaks, PA, US USA</t>
+          <t>Smyrna, GA, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,15 +5596,190 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ef040d1b01903853</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Full‑Stack Developer (Java, React, Microservices) *Hybrid*</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0f298bb4ddf8e9a0</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Information Technology - Data Integration Engineer</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Magnolia</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Waco, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=22a077ceb692752f</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - GM Motorsports</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>General Motors (GM)</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Concord, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Event Hubs, GCP, Scala, Kafka, MongoDB, NoSQL, Docker</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6f660072154c9a61</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Senior Business Intelligence Developer</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Douglas Machine Inc.</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Alexandria, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f9d5d216fe71b48e</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>SEI Investments</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Oaks, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
           <t>Kafka, Snowflake, Oracle, SQL Server, MySQL, MongoDB, Jenkins, Docker, Kubernetes, AKS</t>
         </is>
       </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=76c94610856b0496</t>
         </is>

--- a/results/job_matches_2026-05-01.xlsx
+++ b/results/job_matches_2026-05-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G153"/>
+  <dimension ref="A1:G149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,17 +713,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Junior Cloud Security Analyst</t>
+          <t>Senior Software Engineer (C#/.NET &amp; AI)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85598b1d63680693</t>
+          <t>https://www.indeed.com/viewjob?jk=93c21b258a08bd24</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (C#/.NET &amp; AI)</t>
+          <t>Sr Software Engineer II - Enterprise Architecture</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,34 +766,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93c21b258a08bd24</t>
+          <t>https://www.indeed.com/viewjob?jk=f6bd0f139eec27a7</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr Software Engineer II - Enterprise Architecture</t>
+          <t>Cloud Network Automation Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6bd0f139eec27a7</t>
+          <t>https://www.indeed.com/viewjob?jk=0a0cf6116e02d635</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Cloud Network Automation Engineer</t>
+          <t>Cloud Engineer II</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Vibrant Emotional Health</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a0cf6116e02d635</t>
+          <t>https://www.indeed.com/viewjob?jk=3ba39b2a6826c32d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Cloud Engineer II</t>
+          <t>Senior Engineer - AI &amp; Data Management</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Vibrant Emotional Health</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins</t>
+          <t>S3, Azure, Data Factory, Cloud Storage, Hadoop, HDFS, Spark, Scala, Kafka, Informatica PowerCenter</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ba39b2a6826c32d</t>
+          <t>https://www.indeed.com/viewjob?jk=0f98760c842e5085</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Engineer - AI &amp; Data Management</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Tradeweb</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>S3, Azure, Data Factory, Cloud Storage, Hadoop, HDFS, Spark, Scala, Kafka, Informatica PowerCenter</t>
+          <t>AWS, Redshift, S3, IAM, RDS, GCP, Spark, Kafka, Dask, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f98760c842e5085</t>
+          <t>https://www.indeed.com/viewjob?jk=cb2021c38a5314d9</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>GenAI Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tradeweb</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, GCP, Spark, Kafka, Dask, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Blob Storage, Google Cloud Platform, Vertex AI, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb2021c38a5314d9</t>
+          <t>https://www.indeed.com/viewjob?jk=5efecdb56da9cdd1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GenAI Threat Intelligence Analyst</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Metropolitan Commercial Bank</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Blob Storage, Google Cloud Platform, Vertex AI, Scala, MLOps, MLflow</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5efecdb56da9cdd1</t>
+          <t>https://www.indeed.com/viewjob?jk=25250927f01c87fd</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Metropolitan Commercial Bank</t>
+          <t>Credera</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, NoSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Oozie, Spark, Scala, Kafka, SQL Server</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25250927f01c87fd</t>
+          <t>https://www.indeed.com/viewjob?jk=a2859c21fcc6b9b6</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2859c21fcc6b9b6</t>
+          <t>https://www.indeed.com/viewjob?jk=9e65ae12c9231691</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e65ae12c9231691</t>
+          <t>https://www.indeed.com/viewjob?jk=deb9ad8464ceb6e6</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=deb9ad8464ceb6e6</t>
+          <t>https://www.indeed.com/viewjob?jk=0faede29102fb7e1</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>SRE/Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Credera</t>
+          <t>Sign In Solutions</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Oozie, Spark, Scala, Kafka, SQL Server</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0faede29102fb7e1</t>
+          <t>https://www.indeed.com/viewjob?jk=78107cea029977e8</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Java Compliance &amp; Governance Developer</t>
+          <t>Azure Data &amp; Development Architect</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SunStone Consulting</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, ELT, dbt</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Event Hubs, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8078bc6f1fdb2e7b</t>
+          <t>https://www.indeed.com/viewjob?jk=1e9052cac6c7210d</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Java Compliance &amp; Governance Developer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ABCorp NA Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>IAM, RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e06fd43e0f99777</t>
+          <t>https://www.indeed.com/viewjob?jk=8078bc6f1fdb2e7b</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Azure Data &amp; Development Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SunStone Consulting</t>
+          <t>ABCorp NA Inc.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,17 +1256,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Event Hubs, Spark, Scala, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e9052cac6c7210d</t>
+          <t>https://www.indeed.com/viewjob?jk=1e06fd43e0f99777</t>
         </is>
       </c>
     </row>
@@ -1343,25 +1343,25 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Business System Analyst with Property and Casualty Domain</t>
+          <t>Data Engineer II _ Big Data, GCP _EDAI</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SRR Consultants</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Glen Allen, VA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7446cde797c8f4de</t>
+          <t>https://www.indeed.com/viewjob?jk=d725c4b26e048534</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer II _ Big Data, GCP _EDAI</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,17 +1396,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d725c4b26e048534</t>
+          <t>https://www.indeed.com/viewjob?jk=0fc4628968aad9e2</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Trane Technologies</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f483db2edc8cb83a</t>
+          <t>https://www.indeed.com/viewjob?jk=0eb5fc1d601c0028</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>JUUL Labs</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, GCP, Dataflow, Cloud Storage, Scala, Splunk</t>
+          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c63edb85327f9aef</t>
+          <t>https://www.indeed.com/viewjob?jk=acae1b7fc51e9a39</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JUUL Labs</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, Snowflake, SQL Server, MySQL, ELT</t>
+          <t>AWS, S3, ECS, IAM, RDS, GCP, Dataflow, Cloud Storage, Scala, Splunk</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de10d304d09880c3</t>
+          <t>https://www.indeed.com/viewjob?jk=c63edb85327f9aef</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
+          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, Snowflake, SQL Server, MySQL, ELT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fc4628968aad9e2</t>
+          <t>https://www.indeed.com/viewjob?jk=de10d304d09880c3</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DEVELOPER L3(CONTRACT)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
+          <t>AWS, Databricks, Cloud Storage, Spark, PySpark, Scala, Snowflake, Time Travel, Databricks Lakehouse, Snowflake Schema</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0eb5fc1d601c0028</t>
+          <t>https://www.indeed.com/viewjob?jk=1c37881d8861b3d6</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Ad Ops Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acae1b7fc51e9a39</t>
+          <t>https://www.indeed.com/viewjob?jk=3d412becc7b99de0</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>DEVELOPER L3(CONTRACT)</t>
+          <t>Software Engineer Seniors – Cloud Technologies | Fintech | Full Stack</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>FIS</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Cloud Storage, Spark, PySpark, Scala, Snowflake, Time Travel, Databricks Lakehouse, Snowflake Schema</t>
+          <t>AWS, Azure, Data Factory, Scala, Oracle, SQL Server, NoSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,19 +1651,19 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c37881d8861b3d6</t>
+          <t>https://www.indeed.com/viewjob?jk=d35fe7a7c554f8b5</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Ad Ops Engineer</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Matillion</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1676,17 +1676,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d412becc7b99de0</t>
+          <t>https://www.indeed.com/viewjob?jk=95bbbaf8fbe8db68</t>
         </is>
       </c>
     </row>
@@ -1721,67 +1721,67 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95bbbaf8fbe8db68</t>
+          <t>https://www.indeed.com/viewjob?jk=2c7ffe9dfedc9c5d</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Senior Dev Ops Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Matillion</t>
+          <t>SkyWater Technology Foundry</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, IAM, RDS, Photon, GCP, Vertex AI, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c7ffe9dfedc9c5d</t>
+          <t>https://www.indeed.com/viewjob?jk=13bfee40249f3478</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer Seniors – Cloud Technologies | Fintech | Full Stack</t>
+          <t>Business Intelligence Solutions Architect</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>FIS</t>
+          <t>Mars Technominds</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Oracle, SQL Server, NoSQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d35fe7a7c554f8b5</t>
+          <t>https://www.indeed.com/viewjob?jk=38246f1a187f1c7d</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Platform Engineer Senior</t>
+          <t>ERP Data Management Architect (Manufacturing)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Texas Capital Bank</t>
+          <t>Infor</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Oracle, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09ac756571edd2b5</t>
+          <t>https://www.indeed.com/viewjob?jk=e45199011cbe2990</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Dev Ops Engineer</t>
+          <t>Software Engineer I – AI Assistant Framework, ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SkyWater Technology Foundry</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Photon, GCP, Vertex AI, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13bfee40249f3478</t>
+          <t>https://www.indeed.com/viewjob?jk=2546eaf4a3e50baf</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Business Intelligence Solutions Architect</t>
+          <t>Site AI Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Mars Technominds</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Temple, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38246f1a187f1c7d</t>
+          <t>https://www.indeed.com/viewjob?jk=b9df42fb6f0e5b92</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ERP Data Management Architect (Manufacturing)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Infor</t>
+          <t>Client Resources, Inc.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Oracle, MySQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, GCP, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,67 +1931,67 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e45199011cbe2990</t>
+          <t>https://www.indeed.com/viewjob?jk=d1e155aced1efdff</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Oracle Financials Functional Consultant</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SRR Consultants</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>AWS, Redshift, Athena, S3, IAM, Hadoop, Spark, Kafka, Snowflake, Splunk</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7d13b47b7b7c8a2</t>
+          <t>https://www.indeed.com/viewjob?jk=0f01d239e5c828f6</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Engineer I – AI Assistant Framework, ArcGIS Enterprise</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>Intelligent Medical Objects</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Spark, Scala, Data Modeling, dbt, Power BI</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2546eaf4a3e50baf</t>
+          <t>https://www.indeed.com/viewjob?jk=c4869d3a6ac24136</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Site AI Engineer</t>
+          <t>Infrastructure-as-Code (IaC) Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Temple, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Databricks</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9df42fb6f0e5b92</t>
+          <t>https://www.indeed.com/viewjob?jk=ca35900639cbe443</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Engineer - Agentic AI</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Client Resources, Inc.</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, GCP, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Lambda, SQS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1e155aced1efdff</t>
+          <t>https://www.indeed.com/viewjob?jk=5daf8f72a4fd9ab6</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>Senior Backend Software Engineer/SRE - GM Energy</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, S3, IAM, Hadoop, Spark, Kafka, Snowflake, Splunk</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f01d239e5c828f6</t>
+          <t>https://www.indeed.com/viewjob?jk=0413ce8de5fcca6a</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Software Developer - Used Car Marketplace</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Intelligent Medical Objects</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Spark, Scala, Data Modeling, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4869d3a6ac24136</t>
+          <t>https://www.indeed.com/viewjob?jk=d487bcb34632271a</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Infrastructure-as-Code (IaC) Engineer</t>
+          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Databricks</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca35900639cbe443</t>
+          <t>https://www.indeed.com/viewjob?jk=79a2a043dc5cdb8f</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Engineer - Agentic AI</t>
+          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5daf8f72a4fd9ab6</t>
+          <t>https://www.indeed.com/viewjob?jk=e387db2c2b866baa</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer/SRE - GM Energy</t>
+          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0413ce8de5fcca6a</t>
+          <t>https://www.indeed.com/viewjob?jk=18a022cbc2b4d934</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Developer - Used Car Marketplace</t>
+          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,17 +2271,17 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d487bcb34632271a</t>
+          <t>https://www.indeed.com/viewjob?jk=5cc4f959dd712f8a</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Yonkers, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79a2a043dc5cdb8f</t>
+          <t>https://www.indeed.com/viewjob?jk=688d7763683eecad</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
+          <t>Distinguished Engineer -</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, GCP, Snowflake, ELT, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e387db2c2b866baa</t>
+          <t>https://www.indeed.com/viewjob?jk=087eb595cff7bd93</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Smithfield, RI, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,42 +2376,42 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, EMR, RDS, Spark, Scala, Snowflake, Oracle, ETL, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18a022cbc2b4d934</t>
+          <t>https://www.indeed.com/viewjob?jk=5cc22367a2ce3d9f</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
+          <t>AI/ML Engineer – Data &amp; Full-Stack Solutions</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>ITC Federal</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,67 +2421,67 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cc4f959dd712f8a</t>
+          <t>https://www.indeed.com/viewjob?jk=ce30a23eaa64abcd</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
+          <t>Senior Software Engineer - Commercial Software</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Yonkers, NY, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Oracle, MySQL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=688d7763683eecad</t>
+          <t>https://www.indeed.com/viewjob?jk=4ca1245fe1b2a956</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Distinguished Engineer -</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, GCP, Snowflake, ELT, Splunk, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Snowflake, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,59 +2491,59 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=087eb595cff7bd93</t>
+          <t>https://www.indeed.com/viewjob?jk=36a73b40629cc484</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Development Engineer II</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Smithfield, RI, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Spark, Scala, Snowflake, Oracle, ETL, Jenkins, Maven</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cc22367a2ce3d9f</t>
+          <t>https://www.indeed.com/viewjob?jk=c0d2f3586b2ed198</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Senior Site Reliability Engineer II</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Snowflake, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36a73b40629cc484</t>
+          <t>https://www.indeed.com/viewjob?jk=6fa53cf983e1a6d0</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AI/ML Engineer – Data &amp; Full-Stack Solutions</t>
+          <t>Quality Assurance Analyst / ETL Tester</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>ITC Federal</t>
+          <t>Briljent</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Snowflake, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce30a23eaa64abcd</t>
+          <t>https://www.indeed.com/viewjob?jk=d69b1256484e3a82</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Commercial Software</t>
+          <t>Artificial Intelligence/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Oracle, MySQL</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ca1245fe1b2a956</t>
+          <t>https://www.indeed.com/viewjob?jk=8f6f11467cb82584</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Java Cloud-Native Developer</t>
+          <t>Artificial Intelligence/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, DynamoDB, NoSQL</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7fe4ad94b5b821d</t>
+          <t>https://www.indeed.com/viewjob?jk=c9ce81a6707266dd</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>Artificial Intelligence/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Logic, Inc.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0d2f3586b2ed198</t>
+          <t>https://www.indeed.com/viewjob?jk=e34c2e31eeb33f9e</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer II</t>
+          <t>Senior Machine Learning Engineer (Remote)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, Splunk, CI/CD</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, NoSQL, CI/CD, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,67 +2736,67 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fa53cf983e1a6d0</t>
+          <t>https://www.indeed.com/viewjob?jk=fdbdb16275078800</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Artificial Intelligence/Machine Learning Data Engineer</t>
+          <t>Data Engineer - Performance Management</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Lake Buena Vista, FL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f6f11467cb82584</t>
+          <t>https://www.indeed.com/viewjob?jk=b85eeb0fd5a3a862</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Artificial Intelligence/Machine Learning Data Engineer</t>
+          <t>Systems &amp; Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Kretek International</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Moorpark, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Splunk, Terraform</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9ce81a6707266dd</t>
+          <t>https://www.indeed.com/viewjob?jk=a7d7d86c5d6aef50</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Artificial Intelligence/Machine Learning Data Engineer</t>
+          <t>Data Engineer - Performance Management</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Logic, Inc.</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Lake Buena Vista, FL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,59 +2841,59 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e34c2e31eeb33f9e</t>
+          <t>https://www.indeed.com/viewjob?jk=57b0af5961338ef2</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Quality Assurance Analyst / ETL Tester</t>
+          <t>Full Stack, Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Briljent</t>
+          <t>SCAN Health Plan</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Snowflake, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL, Data Modeling, Snowflake Schema, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d69b1256484e3a82</t>
+          <t>https://www.indeed.com/viewjob?jk=6b0db4093988ff3c</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer - Performance Management</t>
+          <t>Senior Backend Engineer (Remote, US)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>Openly</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Lake Buena Vista, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b85eeb0fd5a3a862</t>
+          <t>https://www.indeed.com/viewjob?jk=2353cb4c2ecb06b9</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Systems &amp; Cloud Infrastructure Engineer</t>
+          <t>Software Systems Engineer, Release Reliability &amp; Automation (Autonomous Vehicles)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Kretek International</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Moorpark, CA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Splunk, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Power BI, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7d7d86c5d6aef50</t>
+          <t>https://www.indeed.com/viewjob?jk=f97782145b5d3f94</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer - Performance Management</t>
+          <t>Reliability Engineer (Autonomous Vehicles)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Lake Buena Vista, FL, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Power BI, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57b0af5961338ef2</t>
+          <t>https://www.indeed.com/viewjob?jk=cf25e4c14df46394</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Full Stack, Data &amp; Analytics Engineer</t>
+          <t>AI/ML Developer II (Remote)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SCAN Health Plan</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, NoSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b0db4093988ff3c</t>
+          <t>https://www.indeed.com/viewjob?jk=fb663396a5bc1b79</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (Remote)</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,42 +3041,42 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, NoSQL, CI/CD, Git, Python, SQL</t>
+          <t>RDS, Databricks, Scala, Snowflake, PostgreSQL, MySQL, Splunk, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdbdb16275078800</t>
+          <t>https://www.indeed.com/viewjob?jk=1869e5a8847d426e</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Software Engineer II, Global Servicing Technology</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Snowflake, PostgreSQL, MySQL, Splunk, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Google Cloud Platform, Cloud Storage, Hive, Spark, Scala, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,112 +3086,112 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1869e5a8847d426e</t>
+          <t>https://www.indeed.com/viewjob?jk=5c5c9f5bf8d54b87</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Software Systems Engineer, Release Reliability &amp; Automation (Autonomous Vehicles)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Accompany Health</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Power BI, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Spark, Scala, Kafka, NoSQL, Data Modeling, Terraform, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f97782145b5d3f94</t>
+          <t>https://www.indeed.com/viewjob?jk=f41df6bde69aeb07</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Reliability Engineer (Autonomous Vehicles)</t>
+          <t>Quality Automation Engineer (SDET) - Career</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Power BI, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf25e4c14df46394</t>
+          <t>https://www.indeed.com/viewjob?jk=b597edf918184e10</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>AI/ML Developer II (Remote)</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>Axis Residential</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Spokane, WA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, NoSQL, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Kimball, ETL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb663396a5bc1b79</t>
+          <t>https://www.indeed.com/viewjob?jk=7970a51178c2d8ba</t>
         </is>
       </c>
     </row>
@@ -3233,17 +3233,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Software Engineer II, Global Servicing Technology</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,17 +3251,17 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, Cloud Storage, Hive, Spark, Scala, ETL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c5c9f5bf8d54b87</t>
+          <t>https://www.indeed.com/viewjob?jk=d33e81401b69b22c</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d33e81401b69b22c</t>
+          <t>https://www.indeed.com/viewjob?jk=ffcaa5c8b2e22e2b</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer, Go to Market (Remote)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
+          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffcaa5c8b2e22e2b</t>
+          <t>https://www.indeed.com/viewjob?jk=8c7e11f90c05edfc</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Infrastructure &amp; Security Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Accompany Health</t>
+          <t>HerculesAI</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Campbell, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Glue, Spark, Scala, Kafka, NoSQL, Data Modeling, Terraform, Airflow, Apache Airflow</t>
+          <t>AWS, Lambda, IAM, Azure, GCP, Splunk, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f41df6bde69aeb07</t>
+          <t>https://www.indeed.com/viewjob?jk=997e47a23e0d8261</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Engineer, Go to Market (Remote)</t>
+          <t>Software Engineer III - Data, AWS, ETL, Java/Python,</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c7e11f90c05edfc</t>
+          <t>https://www.indeed.com/viewjob?jk=24b2eb0df8c7e284</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Sr. Infrastructure &amp; Security Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>HerculesAI</t>
+          <t>Cityblock Health</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Campbell, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, Azure, GCP, Splunk, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Azure, GCP, BigQuery, PostgreSQL, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=997e47a23e0d8261</t>
+          <t>https://www.indeed.com/viewjob?jk=76d763c610ac1510</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data, AWS, ETL, Java/Python,</t>
+          <t>Senior Data Engineer - GM Motorsports</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Concord, NC, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, ETL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, Databricks Lakehouse, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24b2eb0df8c7e284</t>
+          <t>https://www.indeed.com/viewjob?jk=c80625f8482f70fb</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Senior Backend Software Engineer- GM Energy</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Cityblock Health</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, BigQuery, PostgreSQL, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, GCP, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76d763c610ac1510</t>
+          <t>https://www.indeed.com/viewjob?jk=51fb08298ca2e944</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GM Motorsports</t>
+          <t>Data Platform Architect (Snowflake)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Coastal</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Concord, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, Databricks Lakehouse, NoSQL, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Snowflake, Data Modeling, Kimball, ETL, dbt</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c80625f8482f70fb</t>
+          <t>https://www.indeed.com/viewjob?jk=58854506afe876e4</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Quality Automation Engineer (SDET) - Career</t>
+          <t>Software Development Engineer III</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, CI/CD, Jenkins, Terraform</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b597edf918184e10</t>
+          <t>https://www.indeed.com/viewjob?jk=1f950bd314b17c8f</t>
         </is>
       </c>
     </row>
@@ -3618,17 +3618,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>DNP Software Engineer</t>
+          <t>Senior DBA / Database Architect</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Client Resources, Inc.</t>
+          <t>Opeeka, Inc.</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Folsom, CA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Spark, PySpark, Spark Streaming, CI/CD, Terraform, Airflow, Apache Airflow</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Bitbucket</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95f2f4f81bc33a7a</t>
+          <t>https://www.indeed.com/viewjob?jk=5142b758be4e8f87</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer- GM Energy</t>
+          <t>Application Developer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Value Truck of Arizona</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>South Jordan, UT, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, GCP, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51fb08298ca2e944</t>
+          <t>https://www.indeed.com/viewjob?jk=f6c3e26366316cc8</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Platform Architect (Snowflake)</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Coastal</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Snowflake, Data Modeling, Kimball, ETL, dbt</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58854506afe876e4</t>
+          <t>https://www.indeed.com/viewjob?jk=c5c449cb4c336ec2</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Software Development Engineer III</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f950bd314b17c8f</t>
+          <t>https://www.indeed.com/viewjob?jk=e57a91ca929fec5b</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5c449cb4c336ec2</t>
+          <t>https://www.indeed.com/viewjob?jk=cd22b6d5954a33c2</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e57a91ca929fec5b</t>
+          <t>https://www.indeed.com/viewjob?jk=2d369f55f3c43cd0</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd22b6d5954a33c2</t>
+          <t>https://www.indeed.com/viewjob?jk=b5e852e1fb093faa</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d369f55f3c43cd0</t>
+          <t>https://www.indeed.com/viewjob?jk=122021b0213972fb</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5e852e1fb093faa</t>
+          <t>https://www.indeed.com/viewjob?jk=cf263b65906b30ba</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=122021b0213972fb</t>
+          <t>https://www.indeed.com/viewjob?jk=775f4b74d2e0d125</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf263b65906b30ba</t>
+          <t>https://www.indeed.com/viewjob?jk=e27aa2f30115d6a9</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=775f4b74d2e0d125</t>
+          <t>https://www.indeed.com/viewjob?jk=372ffe4f2e9a605d</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e27aa2f30115d6a9</t>
+          <t>https://www.indeed.com/viewjob?jk=a256a77103c9ee18</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=372ffe4f2e9a605d</t>
+          <t>https://www.indeed.com/viewjob?jk=9b082342159bbdf7</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a256a77103c9ee18</t>
+          <t>https://www.indeed.com/viewjob?jk=e06cd5eb56a43b5c</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b082342159bbdf7</t>
+          <t>https://www.indeed.com/viewjob?jk=daaeb6d16db98abf</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e06cd5eb56a43b5c</t>
+          <t>https://www.indeed.com/viewjob?jk=5d61083f86948477</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daaeb6d16db98abf</t>
+          <t>https://www.indeed.com/viewjob?jk=71d4be4e91f6174a</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d61083f86948477</t>
+          <t>https://www.indeed.com/viewjob?jk=912b927f8e6b0bc9</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71d4be4e91f6174a</t>
+          <t>https://www.indeed.com/viewjob?jk=697335a3240f02f2</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=912b927f8e6b0bc9</t>
+          <t>https://www.indeed.com/viewjob?jk=e21309c64f987c4d</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=697335a3240f02f2</t>
+          <t>https://www.indeed.com/viewjob?jk=6e4114c9ced06f08</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e21309c64f987c4d</t>
+          <t>https://www.indeed.com/viewjob?jk=0379c77fb1bea285</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e4114c9ced06f08</t>
+          <t>https://www.indeed.com/viewjob?jk=c7404f3dbf25b5d0</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0379c77fb1bea285</t>
+          <t>https://www.indeed.com/viewjob?jk=19a128257d3c2c77</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7404f3dbf25b5d0</t>
+          <t>https://www.indeed.com/viewjob?jk=6a667aa6f915c8e9</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19a128257d3c2c77</t>
+          <t>https://www.indeed.com/viewjob?jk=8d47c2036fa69322</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a667aa6f915c8e9</t>
+          <t>https://www.indeed.com/viewjob?jk=591077de2df74cfa</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d47c2036fa69322</t>
+          <t>https://www.indeed.com/viewjob?jk=8cc254c410ba6f38</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=591077de2df74cfa</t>
+          <t>https://www.indeed.com/viewjob?jk=12339d025b6d4b6f</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cc254c410ba6f38</t>
+          <t>https://www.indeed.com/viewjob?jk=dc7db42760d4627e</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12339d025b6d4b6f</t>
+          <t>https://www.indeed.com/viewjob?jk=6c024ec8f500d28f</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc7db42760d4627e</t>
+          <t>https://www.indeed.com/viewjob?jk=d5c090288e0e4f79</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c024ec8f500d28f</t>
+          <t>https://www.indeed.com/viewjob?jk=c400db066fcfe868</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,67 +4836,67 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5c090288e0e4f79</t>
+          <t>https://www.indeed.com/viewjob?jk=e9857bbf535b2768</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, Terraform, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c400db066fcfe868</t>
+          <t>https://www.indeed.com/viewjob?jk=5f72c641c65b5a61</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>Software Engineer III – Python/PySpark/AWS</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, Lambda, S3, RDS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,94 +4906,94 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9857bbf535b2768</t>
+          <t>https://www.indeed.com/viewjob?jk=991d5ceb2074b137</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Senior DBA / Database Architect</t>
+          <t>AV Safety Engineering Analytics Simulation Engineer (GPSSC)</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Opeeka, Inc.</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Folsom, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Bitbucket</t>
+          <t>AWS, RDS, Tableau, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5142b758be4e8f87</t>
+          <t>https://www.indeed.com/viewjob?jk=759f2d176cc08b7e</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Application Developer</t>
+          <t>FSO LABS - AI Developer Senior - Bay Area</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Value Truck of Arizona</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>South Jordan, UT, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
+          <t>RDS, Azure, Hadoop, Hive, Spark, Kafka, NoSQL, Power BI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6c3e26366316cc8</t>
+          <t>https://www.indeed.com/viewjob?jk=1d75a18fe3bc2126</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Data Engineer (Snowflake, Teradata, DB2)</t>
+          <t>Databricks Data Engineer - Senior - Consulting - Location Open</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Mutual of Omaha</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,34 +5001,34 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Scala, Snowflake, SQL Server, MongoDB, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, AKS</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa9d2ce9f1b5528c</t>
+          <t>https://www.indeed.com/viewjob?jk=599253e2d33dc75f</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer (Snowflake, Teradata, DB2)</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Mutual of Omaha</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, Terraform, Airflow, Apache Airflow</t>
+          <t>AWS, Glue, RDS, Scala, Snowflake, SQL Server, MongoDB, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f72c641c65b5a61</t>
+          <t>https://www.indeed.com/viewjob?jk=aa9d2ce9f1b5528c</t>
         </is>
       </c>
     </row>
@@ -5193,17 +5193,17 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer - Senior - Consulting - Location Open</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,34 +5211,34 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=599253e2d33dc75f</t>
+          <t>https://www.indeed.com/viewjob?jk=983d0a4b6df6a34b</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Software Engineer III – Python/PySpark/AWS</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,34 +5246,34 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=991d5ceb2074b137</t>
+          <t>https://www.indeed.com/viewjob?jk=e39cfd742ca8ccb7</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>AV Safety Engineering Analytics Simulation Engineer (GPSSC)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,34 +5281,34 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, RDS, Tableau, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=759f2d176cc08b7e</t>
+          <t>https://www.indeed.com/viewjob?jk=4d24b9bb7d3f81d1</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>FSO LABS - AI Developer Senior - Bay Area</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,17 +5316,17 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Hive, Spark, Kafka, NoSQL, Power BI, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d75a18fe3bc2126</t>
+          <t>https://www.indeed.com/viewjob?jk=406f01e6594b2624</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,14 +5361,14 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=983d0a4b6df6a34b</t>
+          <t>https://www.indeed.com/viewjob?jk=0206f3baae13d0ec</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full‑Stack Developer (Java, React, Microservices) *Hybrid*</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -5386,24 +5386,24 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e39cfd742ca8ccb7</t>
+          <t>https://www.indeed.com/viewjob?jk=229f6840535c3531</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full‑Stack Developer (Java, React, Microservices) *Hybrid*</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -5421,24 +5421,24 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d24b9bb7d3f81d1</t>
+          <t>https://www.indeed.com/viewjob?jk=606324c85c044a5d</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Smyrna, GA, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,24 +5456,24 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=406f01e6594b2624</t>
+          <t>https://www.indeed.com/viewjob?jk=ef040d1b01903853</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full‑Stack Developer (Java, React, Microservices) *Hybrid*</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -5491,34 +5491,34 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0206f3baae13d0ec</t>
+          <t>https://www.indeed.com/viewjob?jk=0f298bb4ddf8e9a0</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Full‑Stack Developer (Java, React, Microservices) *Hybrid*</t>
+          <t>Information Technology - Data Integration Engineer</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Magnolia</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Waco, TX, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5536,24 +5536,24 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=229f6840535c3531</t>
+          <t>https://www.indeed.com/viewjob?jk=22a077ceb692752f</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Full‑Stack Developer (Java, React, Microservices) *Hybrid*</t>
+          <t>Senior Software Engineer - GM Motorsports</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Concord, NC, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,34 +5561,34 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Event Hubs, GCP, Scala, Kafka, MongoDB, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606324c85c044a5d</t>
+          <t>https://www.indeed.com/viewjob?jk=6f660072154c9a61</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
+          <t>Senior Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Douglas Machine Inc.</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Smyrna, GA, US USA</t>
+          <t>Alexandria, MN, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5606,24 +5606,24 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef040d1b01903853</t>
+          <t>https://www.indeed.com/viewjob?jk=f9d5d216fe71b48e</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Full‑Stack Developer (Java, React, Microservices) *Hybrid*</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>SEI Investments</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Oaks, PA, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>Kafka, Snowflake, Oracle, SQL Server, MySQL, MongoDB, Jenkins, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5640,146 +5640,6 @@
         </is>
       </c>
       <c r="G149" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0f298bb4ddf8e9a0</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>Information Technology - Data Integration Engineer</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>Magnolia</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>Waco, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D150" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=22a077ceb692752f</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - GM Motorsports</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>General Motors (GM)</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>Concord, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D151" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Event Hubs, GCP, Scala, Kafka, MongoDB, NoSQL, Docker</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6f660072154c9a61</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>Senior Business Intelligence Developer</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>Douglas Machine Inc.</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>Alexandria, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D152" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f9d5d216fe71b48e</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>SEI Investments</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Oaks, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D153" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>Kafka, Snowflake, Oracle, SQL Server, MySQL, MongoDB, Jenkins, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=76c94610856b0496</t>
         </is>

--- a/results/job_matches_2026-05-01.xlsx
+++ b/results/job_matches_2026-05-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G149"/>
+  <dimension ref="A1:G136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,17 +678,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AV Safety Engineering Analytics AI/ML Engineer (GPSSC)</t>
+          <t>Senior Software Engineer (C#/.NET &amp; AI)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,34 +696,34 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Dataflow, Spark, PySpark</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=675259892fa0b51c</t>
+          <t>https://www.indeed.com/viewjob?jk=93c21b258a08bd24</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (C#/.NET &amp; AI)</t>
+          <t>Sr Software Engineer II - Enterprise Architecture</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,42 +731,42 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93c21b258a08bd24</t>
+          <t>https://www.indeed.com/viewjob?jk=f6bd0f139eec27a7</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr Software Engineer II - Enterprise Architecture</t>
+          <t>Cloud Engineer II</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Vibrant Emotional Health</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6bd0f139eec27a7</t>
+          <t>https://www.indeed.com/viewjob?jk=3ba39b2a6826c32d</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Cloud Network Automation Engineer</t>
+          <t>Senior Engineer - AI &amp; Data Management</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
+          <t>S3, Azure, Data Factory, Cloud Storage, Hadoop, HDFS, Spark, Scala, Kafka, Informatica PowerCenter</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,19 +811,19 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a0cf6116e02d635</t>
+          <t>https://www.indeed.com/viewjob?jk=0f98760c842e5085</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Cloud Engineer II</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Vibrant Emotional Health</t>
+          <t>Tradeweb</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -832,11 +832,11 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, S3, IAM, RDS, GCP, Spark, Kafka, Dask, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ba39b2a6826c32d</t>
+          <t>https://www.indeed.com/viewjob?jk=cb2021c38a5314d9</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Engineer - AI &amp; Data Management</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Metropolitan Commercial Bank</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>S3, Azure, Data Factory, Cloud Storage, Hadoop, HDFS, Spark, Scala, Kafka, Informatica PowerCenter</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f98760c842e5085</t>
+          <t>https://www.indeed.com/viewjob?jk=25250927f01c87fd</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tradeweb</t>
+          <t>Credera</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, GCP, Spark, Kafka, Dask, Snowflake</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Oozie, Spark, Scala, Kafka, SQL Server</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb2021c38a5314d9</t>
+          <t>https://www.indeed.com/viewjob?jk=a2859c21fcc6b9b6</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GenAI Threat Intelligence Analyst</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Credera</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Blob Storage, Google Cloud Platform, Vertex AI, Scala, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Oozie, Spark, Scala, Kafka, SQL Server</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5efecdb56da9cdd1</t>
+          <t>https://www.indeed.com/viewjob?jk=9e65ae12c9231691</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Metropolitan Commercial Bank</t>
+          <t>Credera</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, NoSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Oozie, Spark, Scala, Kafka, SQL Server</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25250927f01c87fd</t>
+          <t>https://www.indeed.com/viewjob?jk=deb9ad8464ceb6e6</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2859c21fcc6b9b6</t>
+          <t>https://www.indeed.com/viewjob?jk=0faede29102fb7e1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>SRE/Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Credera</t>
+          <t>Sign In Solutions</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,139 +1046,139 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Oozie, Spark, Scala, Kafka, SQL Server</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e65ae12c9231691</t>
+          <t>https://www.indeed.com/viewjob?jk=78107cea029977e8</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Azure Data &amp; Development Architect</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Credera</t>
+          <t>SunStone Consulting</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Oozie, Spark, Scala, Kafka, SQL Server</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Event Hubs, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=deb9ad8464ceb6e6</t>
+          <t>https://www.indeed.com/viewjob?jk=1e9052cac6c7210d</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Java Compliance &amp; Governance Developer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Credera</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Oozie, Spark, Scala, Kafka, SQL Server</t>
+          <t>IAM, RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0faede29102fb7e1</t>
+          <t>https://www.indeed.com/viewjob?jk=8078bc6f1fdb2e7b</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SRE/Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Sign In Solutions</t>
+          <t>ABCorp NA Inc.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, Splunk, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78107cea029977e8</t>
+          <t>https://www.indeed.com/viewjob?jk=1e06fd43e0f99777</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Azure Data &amp; Development Architect</t>
+          <t>Software Engineer, Full Stack - AI (Chicago)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SunStone Consulting</t>
+          <t>Fitch Group</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Event Hubs, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e9052cac6c7210d</t>
+          <t>https://www.indeed.com/viewjob?jk=d4bb35a3533f1ee6</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Java Compliance &amp; Governance Developer</t>
+          <t>Engineering &amp; Quality - Software Engineer, Full Stack - AI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fitch Group</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,77 +1221,77 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8078bc6f1fdb2e7b</t>
+          <t>https://www.indeed.com/viewjob?jk=cf6b928dd59e0c41</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer II _ Big Data, GCP _EDAI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ABCorp NA Inc.</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e06fd43e0f99777</t>
+          <t>https://www.indeed.com/viewjob?jk=d725c4b26e048534</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer, Full Stack - AI (Chicago)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Fitch Group</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
+          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4bb35a3533f1ee6</t>
+          <t>https://www.indeed.com/viewjob?jk=0fc4628968aad9e2</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Engineering &amp; Quality - Software Engineer, Full Stack - AI</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Fitch Group</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
+          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf6b928dd59e0c41</t>
+          <t>https://www.indeed.com/viewjob?jk=0eb5fc1d601c0028</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer II _ Big Data, GCP _EDAI</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d725c4b26e048534</t>
+          <t>https://www.indeed.com/viewjob?jk=acae1b7fc51e9a39</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>JUUL Labs</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
+          <t>AWS, S3, ECS, IAM, RDS, GCP, Dataflow, Cloud Storage, Scala, Splunk</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fc4628968aad9e2</t>
+          <t>https://www.indeed.com/viewjob?jk=c63edb85327f9aef</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
+          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, Snowflake, SQL Server, MySQL, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,19 +1441,19 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0eb5fc1d601c0028</t>
+          <t>https://www.indeed.com/viewjob?jk=de10d304d09880c3</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DEVELOPER L3(CONTRACT)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
+          <t>AWS, Databricks, Cloud Storage, Spark, PySpark, Scala, Snowflake, Time Travel, Databricks Lakehouse, Snowflake Schema</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acae1b7fc51e9a39</t>
+          <t>https://www.indeed.com/viewjob?jk=1c37881d8861b3d6</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Software Engineer Seniors – Cloud Technologies | Fintech | Full Stack</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>JUUL Labs</t>
+          <t>FIS</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, GCP, Dataflow, Cloud Storage, Scala, Splunk</t>
+          <t>AWS, Azure, Data Factory, Scala, Oracle, SQL Server, NoSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c63edb85327f9aef</t>
+          <t>https://www.indeed.com/viewjob?jk=d35fe7a7c554f8b5</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Matillion</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, Snowflake, SQL Server, MySQL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de10d304d09880c3</t>
+          <t>https://www.indeed.com/viewjob?jk=95bbbaf8fbe8db68</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>DEVELOPER L3(CONTRACT)</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>Matillion</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,77 +1571,77 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Cloud Storage, Spark, PySpark, Scala, Snowflake, Time Travel, Databricks Lakehouse, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c37881d8861b3d6</t>
+          <t>https://www.indeed.com/viewjob?jk=2c7ffe9dfedc9c5d</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Ad Ops Engineer</t>
+          <t>Senior Dev Ops Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>SkyWater Technology Foundry</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, IAM, RDS, Photon, GCP, Vertex AI, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d412becc7b99de0</t>
+          <t>https://www.indeed.com/viewjob?jk=13bfee40249f3478</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer Seniors – Cloud Technologies | Fintech | Full Stack</t>
+          <t>Business Intelligence Solutions Architect</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>FIS</t>
+          <t>Mars Technominds</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Oracle, SQL Server, NoSQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,19 +1651,19 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d35fe7a7c554f8b5</t>
+          <t>https://www.indeed.com/viewjob?jk=38246f1a187f1c7d</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>ERP Data Management Architect (Manufacturing)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Matillion</t>
+          <t>Infor</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1672,73 +1672,73 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Oracle, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95bbbaf8fbe8db68</t>
+          <t>https://www.indeed.com/viewjob?jk=e45199011cbe2990</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Software Engineer I – AI Assistant Framework, ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Matillion</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c7ffe9dfedc9c5d</t>
+          <t>https://www.indeed.com/viewjob?jk=2546eaf4a3e50baf</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Dev Ops Engineer</t>
+          <t>Site AI Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SkyWater Technology Foundry</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Temple, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Photon, GCP, Vertex AI, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13bfee40249f3478</t>
+          <t>https://www.indeed.com/viewjob?jk=b9df42fb6f0e5b92</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Business Intelligence Solutions Architect</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Mars Technominds</t>
+          <t>Client Resources, Inc.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, GCP, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38246f1a187f1c7d</t>
+          <t>https://www.indeed.com/viewjob?jk=d1e155aced1efdff</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ERP Data Management Architect (Manufacturing)</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Infor</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Oracle, MySQL, Data Modeling, ETL</t>
+          <t>AWS, Redshift, Athena, S3, IAM, Hadoop, Spark, Kafka, Snowflake, Splunk</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e45199011cbe2990</t>
+          <t>https://www.indeed.com/viewjob?jk=0f01d239e5c828f6</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer I – AI Assistant Framework, ArcGIS Enterprise</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>Intelligent Medical Objects</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Spark, Scala, Data Modeling, dbt, Power BI</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2546eaf4a3e50baf</t>
+          <t>https://www.indeed.com/viewjob?jk=c4869d3a6ac24136</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Site AI Engineer</t>
+          <t>Senior Engineer - Agentic AI</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Temple, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, Lambda, SQS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9df42fb6f0e5b92</t>
+          <t>https://www.indeed.com/viewjob?jk=5daf8f72a4fd9ab6</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Backend Software Engineer/SRE - GM Energy</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Client Resources, Inc.</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, GCP, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1e155aced1efdff</t>
+          <t>https://www.indeed.com/viewjob?jk=0413ce8de5fcca6a</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, S3, IAM, Hadoop, Spark, Kafka, Snowflake, Splunk</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f01d239e5c828f6</t>
+          <t>https://www.indeed.com/viewjob?jk=79a2a043dc5cdb8f</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Intelligent Medical Objects</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Spark, Scala, Data Modeling, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4869d3a6ac24136</t>
+          <t>https://www.indeed.com/viewjob?jk=e387db2c2b866baa</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Infrastructure-as-Code (IaC) Engineer</t>
+          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Databricks</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca35900639cbe443</t>
+          <t>https://www.indeed.com/viewjob?jk=18a022cbc2b4d934</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Engineer - Agentic AI</t>
+          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5daf8f72a4fd9ab6</t>
+          <t>https://www.indeed.com/viewjob?jk=5cc4f959dd712f8a</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer/SRE - GM Energy</t>
+          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Yonkers, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0413ce8de5fcca6a</t>
+          <t>https://www.indeed.com/viewjob?jk=688d7763683eecad</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Developer - Used Car Marketplace</t>
+          <t>Distinguished Engineer -</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, GCP, Snowflake, ELT, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d487bcb34632271a</t>
+          <t>https://www.indeed.com/viewjob?jk=087eb595cff7bd93</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Smithfield, RI, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,42 +2166,42 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, EMR, RDS, Spark, Scala, Snowflake, Oracle, ETL, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79a2a043dc5cdb8f</t>
+          <t>https://www.indeed.com/viewjob?jk=5cc22367a2ce3d9f</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
+          <t>AI/ML Engineer – Data &amp; Full-Stack Solutions</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>ITC Federal</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e387db2c2b866baa</t>
+          <t>https://www.indeed.com/viewjob?jk=ce30a23eaa64abcd</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
+          <t>Software Development Engineer II</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18a022cbc2b4d934</t>
+          <t>https://www.indeed.com/viewjob?jk=c0d2f3586b2ed198</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
+          <t>Senior Site Reliability Engineer II</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,67 +2281,67 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cc4f959dd712f8a</t>
+          <t>https://www.indeed.com/viewjob?jk=6fa53cf983e1a6d0</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
+          <t>Quality Assurance Analyst / ETL Tester</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Briljent</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Yonkers, NY, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>RDS, Azure, Snowflake, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=688d7763683eecad</t>
+          <t>https://www.indeed.com/viewjob?jk=d69b1256484e3a82</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Distinguished Engineer -</t>
+          <t>Artificial Intelligence/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, GCP, Snowflake, ELT, Splunk, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,59 +2351,59 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=087eb595cff7bd93</t>
+          <t>https://www.indeed.com/viewjob?jk=8f6f11467cb82584</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Artificial Intelligence/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Smithfield, RI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Spark, Scala, Snowflake, Oracle, ETL, Jenkins, Maven</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cc22367a2ce3d9f</t>
+          <t>https://www.indeed.com/viewjob?jk=c9ce81a6707266dd</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AI/ML Engineer – Data &amp; Full-Stack Solutions</t>
+          <t>Artificial Intelligence/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ITC Federal</t>
+          <t>Logic, Inc.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, ETL, ELT, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,102 +2421,102 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce30a23eaa64abcd</t>
+          <t>https://www.indeed.com/viewjob?jk=e34c2e31eeb33f9e</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Commercial Software</t>
+          <t>Senior Machine Learning Engineer (Remote)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Oracle, MySQL</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, NoSQL, CI/CD, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ca1245fe1b2a956</t>
+          <t>https://www.indeed.com/viewjob?jk=fdbdb16275078800</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Data Engineer - Performance Management</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Lake Buena Vista, FL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Snowflake, MLOps, CI/CD, Terraform</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36a73b40629cc484</t>
+          <t>https://www.indeed.com/viewjob?jk=b85eeb0fd5a3a862</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>Systems &amp; Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Kretek International</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Moorpark, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Splunk, Terraform</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0d2f3586b2ed198</t>
+          <t>https://www.indeed.com/viewjob?jk=a7d7d86c5d6aef50</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer II</t>
+          <t>Data Engineer - Performance Management</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Lake Buena Vista, FL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, Splunk, CI/CD</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,102 +2561,102 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fa53cf983e1a6d0</t>
+          <t>https://www.indeed.com/viewjob?jk=57b0af5961338ef2</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Quality Assurance Analyst / ETL Tester</t>
+          <t>Full Stack, Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Briljent</t>
+          <t>SCAN Health Plan</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Snowflake, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL, Data Modeling, Snowflake Schema, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d69b1256484e3a82</t>
+          <t>https://www.indeed.com/viewjob?jk=6b0db4093988ff3c</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Artificial Intelligence/Machine Learning Data Engineer</t>
+          <t>Senior Backend Engineer (Remote, US)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Openly</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow</t>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f6f11467cb82584</t>
+          <t>https://www.indeed.com/viewjob?jk=2353cb4c2ecb06b9</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Artificial Intelligence/Machine Learning Data Engineer</t>
+          <t>AI/ML Developer II (Remote)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, NoSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,137 +2666,137 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9ce81a6707266dd</t>
+          <t>https://www.indeed.com/viewjob?jk=fb663396a5bc1b79</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Artificial Intelligence/Machine Learning Data Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Logic, Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow</t>
+          <t>RDS, Databricks, Scala, Snowflake, PostgreSQL, MySQL, Splunk, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e34c2e31eeb33f9e</t>
+          <t>https://www.indeed.com/viewjob?jk=1869e5a8847d426e</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (Remote)</t>
+          <t>Software Engineer II, Global Servicing Technology</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, NoSQL, CI/CD, Git, Python, SQL</t>
+          <t>AWS, RDS, Google Cloud Platform, Cloud Storage, Hive, Spark, Scala, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdbdb16275078800</t>
+          <t>https://www.indeed.com/viewjob?jk=5c5c9f5bf8d54b87</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer - Performance Management</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>Accompany Health</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Lake Buena Vista, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Glue, Spark, Scala, Kafka, NoSQL, Data Modeling, Terraform, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b85eeb0fd5a3a862</t>
+          <t>https://www.indeed.com/viewjob?jk=f41df6bde69aeb07</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Systems &amp; Cloud Infrastructure Engineer</t>
+          <t>Quality Automation Engineer (SDET) - Career</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Kretek International</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Moorpark, CA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Splunk, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,207 +2806,207 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7d7d86c5d6aef50</t>
+          <t>https://www.indeed.com/viewjob?jk=b597edf918184e10</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer - Performance Management</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>Axis Residential</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Lake Buena Vista, FL, US USA</t>
+          <t>Spokane, WA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Kimball, ETL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57b0af5961338ef2</t>
+          <t>https://www.indeed.com/viewjob?jk=7970a51178c2d8ba</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Full Stack, Data &amp; Analytics Engineer</t>
+          <t>Multi-Cloud Networking Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SCAN Health Plan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b0db4093988ff3c</t>
+          <t>https://www.indeed.com/viewjob?jk=5089f26e49e819d7</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Remote, US)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Openly</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2353cb4c2ecb06b9</t>
+          <t>https://www.indeed.com/viewjob?jk=d33e81401b69b22c</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Systems Engineer, Release Reliability &amp; Automation (Autonomous Vehicles)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Power BI, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f97782145b5d3f94</t>
+          <t>https://www.indeed.com/viewjob?jk=ffcaa5c8b2e22e2b</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Reliability Engineer (Autonomous Vehicles)</t>
+          <t>Data Engineer, Go to Market (Remote)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Power BI, CI/CD, Jenkins</t>
+          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf25e4c14df46394</t>
+          <t>https://www.indeed.com/viewjob?jk=8c7e11f90c05edfc</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>AI/ML Developer II (Remote)</t>
+          <t>Sr. Infrastructure &amp; Security Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>HerculesAI</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Campbell, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, NoSQL, ETL, ELT</t>
+          <t>AWS, Lambda, IAM, Azure, GCP, Splunk, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,59 +3016,59 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb663396a5bc1b79</t>
+          <t>https://www.indeed.com/viewjob?jk=997e47a23e0d8261</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Software Engineer III - Data, AWS, ETL, Java/Python,</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Snowflake, PostgreSQL, MySQL, Splunk, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1869e5a8847d426e</t>
+          <t>https://www.indeed.com/viewjob?jk=24b2eb0df8c7e284</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Software Engineer II, Global Servicing Technology</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Cityblock Health</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, Cloud Storage, Hive, Spark, Scala, ETL, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, GCP, BigQuery, PostgreSQL, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c5c9f5bf8d54b87</t>
+          <t>https://www.indeed.com/viewjob?jk=76d763c610ac1510</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Backend Software Engineer- GM Energy</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Accompany Health</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Glue, Spark, Scala, Kafka, NoSQL, Data Modeling, Terraform, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, GCP, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f41df6bde69aeb07</t>
+          <t>https://www.indeed.com/viewjob?jk=51fb08298ca2e944</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Quality Automation Engineer (SDET) - Career</t>
+          <t>Data Platform Architect (Snowflake)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Coastal</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Snowflake, Data Modeling, Kimball, ETL, dbt</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b597edf918184e10</t>
+          <t>https://www.indeed.com/viewjob?jk=58854506afe876e4</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Software Development Engineer III</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Axis Residential</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Spokane, WA, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Kimball, ETL</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7970a51178c2d8ba</t>
+          <t>https://www.indeed.com/viewjob?jk=1f950bd314b17c8f</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Multi-Cloud Networking Engineer</t>
+          <t>SR DBA / DATABASE ARCHITECT (AZURE / MSSQL)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Opeeka, Inc.</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Folsom, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Bitbucket</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5089f26e49e819d7</t>
+          <t>https://www.indeed.com/viewjob?jk=d57af04f58fc4f3b</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior DBA / Database Architect</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Opeeka, Inc.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Folsom, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Bitbucket</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d33e81401b69b22c</t>
+          <t>https://www.indeed.com/viewjob?jk=5142b758be4e8f87</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Application Developer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Value Truck of Arizona</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>South Jordan, UT, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffcaa5c8b2e22e2b</t>
+          <t>https://www.indeed.com/viewjob?jk=f6c3e26366316cc8</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Engineer, Go to Market (Remote)</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c7e11f90c05edfc</t>
+          <t>https://www.indeed.com/viewjob?jk=c5c449cb4c336ec2</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Sr. Infrastructure &amp; Security Engineer</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>HerculesAI</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Campbell, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, Azure, GCP, Splunk, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=997e47a23e0d8261</t>
+          <t>https://www.indeed.com/viewjob?jk=e57a91ca929fec5b</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data, AWS, ETL, Java/Python,</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, ETL, CI/CD, Terraform</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24b2eb0df8c7e284</t>
+          <t>https://www.indeed.com/viewjob?jk=cd22b6d5954a33c2</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Cityblock Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, BigQuery, PostgreSQL, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76d763c610ac1510</t>
+          <t>https://www.indeed.com/viewjob?jk=2d369f55f3c43cd0</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GM Motorsports</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Concord, NC, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, Databricks Lakehouse, NoSQL, Docker</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c80625f8482f70fb</t>
+          <t>https://www.indeed.com/viewjob?jk=b5e852e1fb093faa</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer- GM Energy</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, GCP, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51fb08298ca2e944</t>
+          <t>https://www.indeed.com/viewjob?jk=122021b0213972fb</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Platform Architect (Snowflake)</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Coastal</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Snowflake, Data Modeling, Kimball, ETL, dbt</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58854506afe876e4</t>
+          <t>https://www.indeed.com/viewjob?jk=cf263b65906b30ba</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Software Development Engineer III</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f950bd314b17c8f</t>
+          <t>https://www.indeed.com/viewjob?jk=775f4b74d2e0d125</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>SR DBA / DATABASE ARCHITECT (AZURE / MSSQL)</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Opeeka, Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Folsom, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Bitbucket</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d57af04f58fc4f3b</t>
+          <t>https://www.indeed.com/viewjob?jk=e27aa2f30115d6a9</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior DBA / Database Architect</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Opeeka, Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Folsom, CA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Bitbucket</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5142b758be4e8f87</t>
+          <t>https://www.indeed.com/viewjob?jk=372ffe4f2e9a605d</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Application Developer</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Value Truck of Arizona</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>South Jordan, UT, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6c3e26366316cc8</t>
+          <t>https://www.indeed.com/viewjob?jk=a256a77103c9ee18</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5c449cb4c336ec2</t>
+          <t>https://www.indeed.com/viewjob?jk=9b082342159bbdf7</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e57a91ca929fec5b</t>
+          <t>https://www.indeed.com/viewjob?jk=e06cd5eb56a43b5c</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd22b6d5954a33c2</t>
+          <t>https://www.indeed.com/viewjob?jk=daaeb6d16db98abf</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d369f55f3c43cd0</t>
+          <t>https://www.indeed.com/viewjob?jk=5d61083f86948477</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5e852e1fb093faa</t>
+          <t>https://www.indeed.com/viewjob?jk=71d4be4e91f6174a</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=122021b0213972fb</t>
+          <t>https://www.indeed.com/viewjob?jk=912b927f8e6b0bc9</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf263b65906b30ba</t>
+          <t>https://www.indeed.com/viewjob?jk=697335a3240f02f2</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=775f4b74d2e0d125</t>
+          <t>https://www.indeed.com/viewjob?jk=e21309c64f987c4d</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e27aa2f30115d6a9</t>
+          <t>https://www.indeed.com/viewjob?jk=6e4114c9ced06f08</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=372ffe4f2e9a605d</t>
+          <t>https://www.indeed.com/viewjob?jk=0379c77fb1bea285</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a256a77103c9ee18</t>
+          <t>https://www.indeed.com/viewjob?jk=c7404f3dbf25b5d0</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b082342159bbdf7</t>
+          <t>https://www.indeed.com/viewjob?jk=19a128257d3c2c77</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e06cd5eb56a43b5c</t>
+          <t>https://www.indeed.com/viewjob?jk=6a667aa6f915c8e9</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daaeb6d16db98abf</t>
+          <t>https://www.indeed.com/viewjob?jk=8d47c2036fa69322</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d61083f86948477</t>
+          <t>https://www.indeed.com/viewjob?jk=591077de2df74cfa</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71d4be4e91f6174a</t>
+          <t>https://www.indeed.com/viewjob?jk=8cc254c410ba6f38</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=912b927f8e6b0bc9</t>
+          <t>https://www.indeed.com/viewjob?jk=12339d025b6d4b6f</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=697335a3240f02f2</t>
+          <t>https://www.indeed.com/viewjob?jk=dc7db42760d4627e</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e21309c64f987c4d</t>
+          <t>https://www.indeed.com/viewjob?jk=6c024ec8f500d28f</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e4114c9ced06f08</t>
+          <t>https://www.indeed.com/viewjob?jk=d5c090288e0e4f79</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0379c77fb1bea285</t>
+          <t>https://www.indeed.com/viewjob?jk=c400db066fcfe868</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,67 +4451,67 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7404f3dbf25b5d0</t>
+          <t>https://www.indeed.com/viewjob?jk=e9857bbf535b2768</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, Terraform, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19a128257d3c2c77</t>
+          <t>https://www.indeed.com/viewjob?jk=5f72c641c65b5a61</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>Software Engineer III – Python/PySpark/AWS</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, Lambda, S3, RDS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,172 +4521,172 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a667aa6f915c8e9</t>
+          <t>https://www.indeed.com/viewjob?jk=991d5ceb2074b137</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>FSO LABS - AI Developer Senior - Bay Area</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>RDS, Azure, Hadoop, Hive, Spark, Kafka, NoSQL, Power BI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d47c2036fa69322</t>
+          <t>https://www.indeed.com/viewjob?jk=1d75a18fe3bc2126</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>Databricks Data Engineer - Senior - Consulting - Location Open</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, AKS</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=591077de2df74cfa</t>
+          <t>https://www.indeed.com/viewjob?jk=599253e2d33dc75f</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>Data Engineer (Snowflake, Teradata, DB2)</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Mutual of Omaha</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, Glue, RDS, Scala, Snowflake, SQL Server, MongoDB, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cc254c410ba6f38</t>
+          <t>https://www.indeed.com/viewjob?jk=aa9d2ce9f1b5528c</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>ObjectStream</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>RDS, Azure, Data Factory, Blob Storage, Spark, PySpark, ETL, dbt, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12339d025b6d4b6f</t>
+          <t>https://www.indeed.com/viewjob?jk=06e3854d22cdba89</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>PySpark Data Engineer III - Python/Java/SQL</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,19 +4696,19 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc7db42760d4627e</t>
+          <t>https://www.indeed.com/viewjob?jk=926547138e49a51b</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>Senior Software Engineer – Cloud Engineering &amp; FinOps</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4717,11 +4717,11 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,32 +4731,32 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c024ec8f500d28f</t>
+          <t>https://www.indeed.com/viewjob?jk=d576082b1c56db5c</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>Senior Cloud Platform Engineer (R-19149)</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Dun &amp; Bradstreet</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,94 +4766,94 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5c090288e0e4f79</t>
+          <t>https://www.indeed.com/viewjob?jk=cb41c4b9d93e0f98</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>Infrastructure Solutions Architect</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Global Information Technology</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c400db066fcfe868</t>
+          <t>https://www.indeed.com/viewjob?jk=94bea5b95ba94e24</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9857bbf535b2768</t>
+          <t>https://www.indeed.com/viewjob?jk=983d0a4b6df6a34b</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, Terraform, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f72c641c65b5a61</t>
+          <t>https://www.indeed.com/viewjob?jk=e39cfd742ca8ccb7</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Software Engineer III – Python/PySpark/AWS</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,34 +4896,34 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=991d5ceb2074b137</t>
+          <t>https://www.indeed.com/viewjob?jk=4d24b9bb7d3f81d1</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>AV Safety Engineering Analytics Simulation Engineer (GPSSC)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,34 +4931,34 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, RDS, Tableau, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=759f2d176cc08b7e</t>
+          <t>https://www.indeed.com/viewjob?jk=406f01e6594b2624</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>FSO LABS - AI Developer Senior - Bay Area</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,34 +4966,34 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Hive, Spark, Kafka, NoSQL, Power BI, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d75a18fe3bc2126</t>
+          <t>https://www.indeed.com/viewjob?jk=0206f3baae13d0ec</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer - Senior - Consulting - Location Open</t>
+          <t>Full‑Stack Developer (Java, React, Microservices) *Hybrid*</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,34 +5001,34 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=599253e2d33dc75f</t>
+          <t>https://www.indeed.com/viewjob?jk=229f6840535c3531</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Data Engineer (Snowflake, Teradata, DB2)</t>
+          <t>Full‑Stack Developer (Java, React, Microservices) *Hybrid*</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Mutual of Omaha</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,34 +5036,34 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Scala, Snowflake, SQL Server, MongoDB, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa9d2ce9f1b5528c</t>
+          <t>https://www.indeed.com/viewjob?jk=606324c85c044a5d</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>ObjectStream</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Smyrna, GA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,34 +5071,34 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Blob Storage, Spark, PySpark, ETL, dbt, Airflow, Apache Airflow</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06e3854d22cdba89</t>
+          <t>https://www.indeed.com/viewjob?jk=ef040d1b01903853</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>PySpark Data Engineer III - Python/Java/SQL</t>
+          <t>Full‑Stack Developer (Java, React, Microservices) *Hybrid*</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=926547138e49a51b</t>
+          <t>https://www.indeed.com/viewjob?jk=0f298bb4ddf8e9a0</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Cloud Engineering &amp; FinOps</t>
+          <t>Information Technology - Data Integration Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Magnolia</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Waco, TX, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d576082b1c56db5c</t>
+          <t>https://www.indeed.com/viewjob?jk=22a077ceb692752f</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer (R-19149)</t>
+          <t>Senior Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Dun &amp; Bradstreet</t>
+          <t>Douglas Machine Inc.</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Alexandria, MN, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,462 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb41c4b9d93e0f98</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D137" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=983d0a4b6df6a34b</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D138" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e39cfd742ca8ccb7</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D139" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4d24b9bb7d3f81d1</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D140" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=406f01e6594b2624</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D141" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0206f3baae13d0ec</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>Full‑Stack Developer (Java, React, Microservices) *Hybrid*</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D142" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=229f6840535c3531</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>Full‑Stack Developer (Java, React, Microservices) *Hybrid*</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D143" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=606324c85c044a5d</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Smyrna, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D144" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ef040d1b01903853</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Full‑Stack Developer (Java, React, Microservices) *Hybrid*</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D145" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0f298bb4ddf8e9a0</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>Information Technology - Data Integration Engineer</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>Magnolia</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Waco, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D146" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=22a077ceb692752f</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - GM Motorsports</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>General Motors (GM)</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Concord, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D147" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Event Hubs, GCP, Scala, Kafka, MongoDB, NoSQL, Docker</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6f660072154c9a61</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Senior Business Intelligence Developer</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>Douglas Machine Inc.</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>Alexandria, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D148" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=f9d5d216fe71b48e</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>SEI Investments</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>Oaks, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D149" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>Kafka, Snowflake, Oracle, SQL Server, MySQL, MongoDB, Jenkins, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=76c94610856b0496</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-01.xlsx
+++ b/results/job_matches_2026-05-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G136"/>
+  <dimension ref="A1:G155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,17 +503,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bid Role - Data Architect (STAR 4275)</t>
+          <t>Senior Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Leading Path Consulting</t>
+          <t>Omada Health</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,17 +521,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, Redshift, Athena, S3, SQS, SNS, BigQuery, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1801c08f952fa8a2</t>
+          <t>https://www.indeed.com/viewjob?jk=98dbeaca2ef62c98</t>
         </is>
       </c>
     </row>
@@ -783,17 +783,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Engineer - AI &amp; Data Management</t>
+          <t>Junior Automation Engineer (Cloud)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>S3, Azure, Data Factory, Cloud Storage, Hadoop, HDFS, Spark, Scala, Kafka, Informatica PowerCenter</t>
+          <t>AWS, SQS, SNS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Splunk</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f98760c842e5085</t>
+          <t>https://www.indeed.com/viewjob?jk=80278e0d3375f33b</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Engineer - AI &amp; Data Management</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tradeweb</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, GCP, Spark, Kafka, Dask, Snowflake</t>
+          <t>S3, Azure, Data Factory, Cloud Storage, Hadoop, HDFS, Spark, Scala, Kafka, Informatica PowerCenter</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,19 +846,19 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb2021c38a5314d9</t>
+          <t>https://www.indeed.com/viewjob?jk=0f98760c842e5085</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Metropolitan Commercial Bank</t>
+          <t>Tradeweb</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, NoSQL</t>
+          <t>AWS, Redshift, S3, IAM, RDS, GCP, Spark, Kafka, Dask, Snowflake</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25250927f01c87fd</t>
+          <t>https://www.indeed.com/viewjob?jk=cb2021c38a5314d9</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Credera</t>
+          <t>Metropolitan Commercial Bank</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Oozie, Spark, Scala, Kafka, SQL Server</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2859c21fcc6b9b6</t>
+          <t>https://www.indeed.com/viewjob?jk=25250927f01c87fd</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>SRE/Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Credera</t>
+          <t>Sign In Solutions</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,17 +941,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Oozie, Spark, Scala, Kafka, SQL Server</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e65ae12c9231691</t>
+          <t>https://www.indeed.com/viewjob?jk=78107cea029977e8</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=deb9ad8464ceb6e6</t>
+          <t>https://www.indeed.com/viewjob?jk=a2859c21fcc6b9b6</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0faede29102fb7e1</t>
+          <t>https://www.indeed.com/viewjob?jk=9e65ae12c9231691</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SRE/Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Sign In Solutions</t>
+          <t>Credera</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,59 +1046,59 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Oozie, Spark, Scala, Kafka, SQL Server</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78107cea029977e8</t>
+          <t>https://www.indeed.com/viewjob?jk=deb9ad8464ceb6e6</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Azure Data &amp; Development Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SunStone Consulting</t>
+          <t>Credera</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Event Hubs, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Oozie, Spark, Scala, Kafka, SQL Server</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e9052cac6c7210d</t>
+          <t>https://www.indeed.com/viewjob?jk=0faede29102fb7e1</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Java Compliance &amp; Governance Developer</t>
+          <t>Kubernetes Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1112,11 +1112,11 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Azure, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8078bc6f1fdb2e7b</t>
+          <t>https://www.indeed.com/viewjob?jk=5f09eaf9518abf0e</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Java Compliance &amp; Governance Developer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ABCorp NA Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>IAM, RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e06fd43e0f99777</t>
+          <t>https://www.indeed.com/viewjob?jk=8078bc6f1fdb2e7b</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer, Full Stack - AI (Chicago)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Fitch Group</t>
+          <t>ABCorp NA Inc.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4bb35a3533f1ee6</t>
+          <t>https://www.indeed.com/viewjob?jk=1e06fd43e0f99777</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Engineering &amp; Quality - Software Engineer, Full Stack - AI</t>
+          <t>Azure Data &amp; Development Architect</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Fitch Group</t>
+          <t>SunStone Consulting</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,64 +1221,64 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Event Hubs, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf6b928dd59e0c41</t>
+          <t>https://www.indeed.com/viewjob?jk=1e9052cac6c7210d</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer II _ Big Data, GCP _EDAI</t>
+          <t>Software Engineer, Full Stack - AI (Chicago)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Fitch Group</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d725c4b26e048534</t>
+          <t>https://www.indeed.com/viewjob?jk=d4bb35a3533f1ee6</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Engineering &amp; Quality - Software Engineer, Full Stack - AI</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Fitch Group</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1287,11 +1287,11 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
+          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fc4628968aad9e2</t>
+          <t>https://www.indeed.com/viewjob?jk=cf6b928dd59e0c41</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0eb5fc1d601c0028</t>
+          <t>https://www.indeed.com/viewjob?jk=dc5cd30ba1545c61</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acae1b7fc51e9a39</t>
+          <t>https://www.indeed.com/viewjob?jk=6622c031669892fa</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Data Engineer II _ Big Data, GCP _EDAI</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>JUUL Labs</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, GCP, Dataflow, Cloud Storage, Scala, Splunk</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c63edb85327f9aef</t>
+          <t>https://www.indeed.com/viewjob?jk=d725c4b26e048534</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JUUL Labs</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, Snowflake, SQL Server, MySQL, ELT</t>
+          <t>AWS, S3, ECS, IAM, RDS, GCP, Dataflow, Cloud Storage, Scala, Splunk</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de10d304d09880c3</t>
+          <t>https://www.indeed.com/viewjob?jk=c63edb85327f9aef</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>DEVELOPER L3(CONTRACT)</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Cloud Storage, Spark, PySpark, Scala, Snowflake, Time Travel, Databricks Lakehouse, Snowflake Schema</t>
+          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, Snowflake, SQL Server, MySQL, ELT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c37881d8861b3d6</t>
+          <t>https://www.indeed.com/viewjob?jk=de10d304d09880c3</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineer Seniors – Cloud Technologies | Fintech | Full Stack</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>FIS</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Oracle, SQL Server, NoSQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d35fe7a7c554f8b5</t>
+          <t>https://www.indeed.com/viewjob?jk=0fc4628968aad9e2</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Matillion</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95bbbaf8fbe8db68</t>
+          <t>https://www.indeed.com/viewjob?jk=0eb5fc1d601c0028</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Matillion</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,42 +1571,42 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c7ffe9dfedc9c5d</t>
+          <t>https://www.indeed.com/viewjob?jk=acae1b7fc51e9a39</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Dev Ops Engineer</t>
+          <t>DEVELOPER L3(CONTRACT)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SkyWater Technology Foundry</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Photon, GCP, Vertex AI, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Databricks, Cloud Storage, Spark, PySpark, Scala, Snowflake, Time Travel, Databricks Lakehouse, Snowflake Schema</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,137 +1616,137 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13bfee40249f3478</t>
+          <t>https://www.indeed.com/viewjob?jk=1c37881d8861b3d6</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Business Intelligence Solutions Architect</t>
+          <t>Platform Architect</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Mars Technominds</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Google Cloud Platform, Spark, PySpark</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38246f1a187f1c7d</t>
+          <t>https://www.indeed.com/viewjob?jk=0ff622ef0e6ac90d</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ERP Data Management Architect (Manufacturing)</t>
+          <t>Junior Cloud Automation Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Infor</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Oracle, MySQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Google Cloud Platform, Spark, PySpark</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e45199011cbe2990</t>
+          <t>https://www.indeed.com/viewjob?jk=86ef316bc56e1d98</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer I – AI Assistant Framework, ArcGIS Enterprise</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2546eaf4a3e50baf</t>
+          <t>https://www.indeed.com/viewjob?jk=200956ef0d629800</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Site AI Engineer</t>
+          <t>Software Engineer Seniors – Cloud Technologies | Fintech | Full Stack</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>FIS</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Temple, TX, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, Azure, Data Factory, Scala, Oracle, SQL Server, NoSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,102 +1756,102 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9df42fb6f0e5b92</t>
+          <t>https://www.indeed.com/viewjob?jk=d35fe7a7c554f8b5</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Client Resources, Inc.</t>
+          <t>Matillion</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, GCP, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1e155aced1efdff</t>
+          <t>https://www.indeed.com/viewjob?jk=95bbbaf8fbe8db68</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>Matillion</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, S3, IAM, Hadoop, Spark, Kafka, Snowflake, Splunk</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f01d239e5c828f6</t>
+          <t>https://www.indeed.com/viewjob?jk=2c7ffe9dfedc9c5d</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Dev Ops Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Intelligent Medical Objects</t>
+          <t>SkyWater Technology Foundry</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Spark, Scala, Data Modeling, dbt, Power BI</t>
+          <t>AWS, IAM, RDS, Photon, GCP, Vertex AI, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4869d3a6ac24136</t>
+          <t>https://www.indeed.com/viewjob?jk=13bfee40249f3478</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Engineer - Agentic AI</t>
+          <t>Business Intelligence Solutions Architect</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Mars Technominds</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5daf8f72a4fd9ab6</t>
+          <t>https://www.indeed.com/viewjob?jk=38246f1a187f1c7d</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer/SRE - GM Energy</t>
+          <t>ERP Data Management Architect (Manufacturing)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Infor</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Oracle, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,67 +1931,67 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0413ce8de5fcca6a</t>
+          <t>https://www.indeed.com/viewjob?jk=e45199011cbe2990</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
+          <t>AWS SysOps Administrator</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, IAM, RDS, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79a2a043dc5cdb8f</t>
+          <t>https://www.indeed.com/viewjob?jk=c1e9865761b44f05</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
+          <t>Software Engineer I – AI Assistant Framework, ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e387db2c2b866baa</t>
+          <t>https://www.indeed.com/viewjob?jk=2546eaf4a3e50baf</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
+          <t>Site AI Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Temple, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18a022cbc2b4d934</t>
+          <t>https://www.indeed.com/viewjob?jk=b9df42fb6f0e5b92</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cc4f959dd712f8a</t>
+          <t>https://www.indeed.com/viewjob?jk=294c6d2addcb10cf</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
+          <t>AWS Technical Apprentice / Trainee</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Yonkers, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Databricks</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=688d7763683eecad</t>
+          <t>https://www.indeed.com/viewjob?jk=2223f947ee98de60</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Distinguished Engineer -</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Client Resources, Inc.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, GCP, Snowflake, ELT, Splunk, CI/CD</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, GCP, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=087eb595cff7bd93</t>
+          <t>https://www.indeed.com/viewjob?jk=d1e155aced1efdff</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Smithfield, RI, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,42 +2166,42 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Spark, Scala, Snowflake, Oracle, ETL, Jenkins, Maven</t>
+          <t>AWS, Redshift, Athena, S3, IAM, Hadoop, Spark, Kafka, Snowflake, Splunk</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cc22367a2ce3d9f</t>
+          <t>https://www.indeed.com/viewjob?jk=0f01d239e5c828f6</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>AI/ML Engineer – Data &amp; Full-Stack Solutions</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ITC Federal</t>
+          <t>Intelligent Medical Objects</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, ETL, ELT, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Spark, Scala, Data Modeling, dbt, Power BI</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,67 +2211,67 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce30a23eaa64abcd</t>
+          <t>https://www.indeed.com/viewjob?jk=c4869d3a6ac24136</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Scala, NoSQL, Power BI, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0d2f3586b2ed198</t>
+          <t>https://www.indeed.com/viewjob?jk=222a5b676c08f8f0</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer II</t>
+          <t>Senior Engineer - Agentic AI</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, Splunk, CI/CD</t>
+          <t>AWS, Lambda, SQS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,67 +2281,67 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fa53cf983e1a6d0</t>
+          <t>https://www.indeed.com/viewjob?jk=5daf8f72a4fd9ab6</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Quality Assurance Analyst / ETL Tester</t>
+          <t>Senior Backend Software Engineer/SRE - GM Energy</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Briljent</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Snowflake, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL, Data Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d69b1256484e3a82</t>
+          <t>https://www.indeed.com/viewjob?jk=0413ce8de5fcca6a</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Artificial Intelligence/Machine Learning Data Engineer</t>
+          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f6f11467cb82584</t>
+          <t>https://www.indeed.com/viewjob?jk=79a2a043dc5cdb8f</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Artificial Intelligence/Machine Learning Data Engineer</t>
+          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9ce81a6707266dd</t>
+          <t>https://www.indeed.com/viewjob?jk=e387db2c2b866baa</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Artificial Intelligence/Machine Learning Data Engineer</t>
+          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Logic, Inc.</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e34c2e31eeb33f9e</t>
+          <t>https://www.indeed.com/viewjob?jk=18a022cbc2b4d934</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (Remote)</t>
+          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, NoSQL, CI/CD, Git, Python, SQL</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,67 +2456,67 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdbdb16275078800</t>
+          <t>https://www.indeed.com/viewjob?jk=5cc4f959dd712f8a</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer - Performance Management</t>
+          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Lake Buena Vista, FL, US USA</t>
+          <t>Yonkers, NY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b85eeb0fd5a3a862</t>
+          <t>https://www.indeed.com/viewjob?jk=688d7763683eecad</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Systems &amp; Cloud Infrastructure Engineer</t>
+          <t>Distinguished Engineer -</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Kretek International</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Moorpark, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Splunk, Terraform</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, GCP, Snowflake, ELT, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,172 +2526,172 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7d7d86c5d6aef50</t>
+          <t>https://www.indeed.com/viewjob?jk=087eb595cff7bd93</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer - Performance Management</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Lake Buena Vista, FL, US USA</t>
+          <t>Smithfield, RI, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, EMR, RDS, Spark, Scala, Snowflake, Oracle, ETL, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57b0af5961338ef2</t>
+          <t>https://www.indeed.com/viewjob?jk=5cc22367a2ce3d9f</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Full Stack, Data &amp; Analytics Engineer</t>
+          <t>Cloud Support Associate</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SCAN Health Plan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Snowflake, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b0db4093988ff3c</t>
+          <t>https://www.indeed.com/viewjob?jk=39dc124339eab650</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Remote, US)</t>
+          <t>AI/ML Engineer – Data &amp; Full-Stack Solutions</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Openly</t>
+          <t>ITC Federal</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2353cb4c2ecb06b9</t>
+          <t>https://www.indeed.com/viewjob?jk=ce30a23eaa64abcd</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AI/ML Developer II (Remote)</t>
+          <t>Platform Architect</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, NoSQL, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Unity Catalog, Delta Live Tables, Google Cloud Platform, Spark, PySpark, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb663396a5bc1b79</t>
+          <t>https://www.indeed.com/viewjob?jk=4c1348f2e47cd5d6</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Infrastructure Engineer (Cloud Focus)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Snowflake, PostgreSQL, MySQL, Splunk, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, Kinesis, Redshift, S3, API Gateway, Scala, Kafka, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1869e5a8847d426e</t>
+          <t>https://www.indeed.com/viewjob?jk=00e1f01fe85665ee</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer II, Global Servicing Technology</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, Cloud Storage, Hive, Spark, Scala, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,67 +2736,67 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c5c9f5bf8d54b87</t>
+          <t>https://www.indeed.com/viewjob?jk=3c5b06678237c00c</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS Systems Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Accompany Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Glue, Spark, Scala, Kafka, NoSQL, Data Modeling, Terraform, Airflow, Apache Airflow</t>
+          <t>AWS, Glue, Lambda, Athena, S3, SQS, SNS, IAM, Spark, PySpark</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f41df6bde69aeb07</t>
+          <t>https://www.indeed.com/viewjob?jk=e5e7a473ae9d0b96</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Quality Automation Engineer (SDET) - Career</t>
+          <t>Software Development Engineer II</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, CI/CD, Jenkins, Terraform</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,102 +2806,102 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b597edf918184e10</t>
+          <t>https://www.indeed.com/viewjob?jk=c0d2f3586b2ed198</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Site Reliability Engineer II</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Axis Residential</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spokane, WA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Kimball, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7970a51178c2d8ba</t>
+          <t>https://www.indeed.com/viewjob?jk=6fa53cf983e1a6d0</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Multi-Cloud Networking Engineer</t>
+          <t>Artificial Intelligence/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5089f26e49e819d7</t>
+          <t>https://www.indeed.com/viewjob?jk=8f6f11467cb82584</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Artificial Intelligence/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d33e81401b69b22c</t>
+          <t>https://www.indeed.com/viewjob?jk=c9ce81a6707266dd</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Artificial Intelligence/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Logic, Inc.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,137 +2946,137 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffcaa5c8b2e22e2b</t>
+          <t>https://www.indeed.com/viewjob?jk=e34c2e31eeb33f9e</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer, Go to Market (Remote)</t>
+          <t>Quality Assurance Analyst / ETL Tester</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Briljent</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
+          <t>RDS, Azure, Snowflake, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c7e11f90c05edfc</t>
+          <t>https://www.indeed.com/viewjob?jk=d69b1256484e3a82</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sr. Infrastructure &amp; Security Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>HerculesAI</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Campbell, CA, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, Azure, GCP, Splunk, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, ETL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=997e47a23e0d8261</t>
+          <t>https://www.indeed.com/viewjob?jk=77a528b43d8d11a1</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data, AWS, ETL, Java/Python,</t>
+          <t>Data Engineer - Performance Management</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Lake Buena Vista, FL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, ETL, CI/CD, Terraform</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24b2eb0df8c7e284</t>
+          <t>https://www.indeed.com/viewjob?jk=b85eeb0fd5a3a862</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Systems &amp; Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Cityblock Health</t>
+          <t>Kretek International</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Moorpark, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, BigQuery, PostgreSQL, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Splunk, Terraform</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76d763c610ac1510</t>
+          <t>https://www.indeed.com/viewjob?jk=a7d7d86c5d6aef50</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer- GM Energy</t>
+          <t>Data Engineer - Performance Management</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Lake Buena Vista, FL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, GCP, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51fb08298ca2e944</t>
+          <t>https://www.indeed.com/viewjob?jk=57b0af5961338ef2</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Platform Architect (Snowflake)</t>
+          <t>Full Stack, Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Coastal</t>
+          <t>SCAN Health Plan</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Snowflake, Data Modeling, Kimball, ETL, dbt</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,67 +3156,67 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58854506afe876e4</t>
+          <t>https://www.indeed.com/viewjob?jk=6b0db4093988ff3c</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Software Development Engineer III</t>
+          <t>Senior Cloud Migration Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
+          <t>AWS, Lambda, SQS, API Gateway, ECS, RDS, Google Cloud Platform, Vertex AI, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f950bd314b17c8f</t>
+          <t>https://www.indeed.com/viewjob?jk=93321e0d50904658</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>SR DBA / DATABASE ARCHITECT (AZURE / MSSQL)</t>
+          <t>Senior Machine Learning Engineer (Remote)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Opeeka, Inc.</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Folsom, CA, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Bitbucket</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, NoSQL, CI/CD, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,102 +3226,102 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d57af04f58fc4f3b</t>
+          <t>https://www.indeed.com/viewjob?jk=fdbdb16275078800</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior DBA / Database Architect</t>
+          <t>Cloud Service Desk Analyst</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Opeeka, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Folsom, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Bitbucket</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5142b758be4e8f87</t>
+          <t>https://www.indeed.com/viewjob?jk=68f4f33bf88f7f89</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Application Developer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Value Truck of Arizona</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>South Jordan, UT, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
+          <t>RDS, Databricks, Scala, Snowflake, PostgreSQL, MySQL, Splunk, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6c3e26366316cc8</t>
+          <t>https://www.indeed.com/viewjob?jk=1869e5a8847d426e</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>AI/ML Developer II (Remote)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, NoSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5c449cb4c336ec2</t>
+          <t>https://www.indeed.com/viewjob?jk=fb663396a5bc1b79</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>Junior Cloud Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Spark, Kafka, Snowflake, Oracle, ETL</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e57a91ca929fec5b</t>
+          <t>https://www.indeed.com/viewjob?jk=8d85a7cfec698363</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>Junior Cloud Networking Technician</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd22b6d5954a33c2</t>
+          <t>https://www.indeed.com/viewjob?jk=e73f6230be428620</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Axis Residential</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Spokane, WA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Kimball, ETL</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d369f55f3c43cd0</t>
+          <t>https://www.indeed.com/viewjob?jk=7970a51178c2d8ba</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>Multi-Cloud Networking Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5e852e1fb093faa</t>
+          <t>https://www.indeed.com/viewjob?jk=5089f26e49e819d7</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>Software Engineer II, Global Servicing Technology</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, RDS, Google Cloud Platform, Cloud Storage, Hive, Spark, Scala, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=122021b0213972fb</t>
+          <t>https://www.indeed.com/viewjob?jk=5c5c9f5bf8d54b87</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf263b65906b30ba</t>
+          <t>https://www.indeed.com/viewjob?jk=d33e81401b69b22c</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=775f4b74d2e0d125</t>
+          <t>https://www.indeed.com/viewjob?jk=ffcaa5c8b2e22e2b</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Accompany Health</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, Glue, Spark, Scala, Kafka, NoSQL, Data Modeling, Terraform, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e27aa2f30115d6a9</t>
+          <t>https://www.indeed.com/viewjob?jk=f41df6bde69aeb07</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>Data Engineer, Go to Market (Remote)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=372ffe4f2e9a605d</t>
+          <t>https://www.indeed.com/viewjob?jk=8c7e11f90c05edfc</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>Sr. Infrastructure &amp; Security Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>HerculesAI</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Campbell, CA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, Lambda, IAM, Azure, GCP, Splunk, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a256a77103c9ee18</t>
+          <t>https://www.indeed.com/viewjob?jk=997e47a23e0d8261</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>Software Engineer III - Data, AWS, ETL, Java/Python,</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b082342159bbdf7</t>
+          <t>https://www.indeed.com/viewjob?jk=24b2eb0df8c7e284</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Cityblock Health</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, IAM, RDS, Azure, GCP, BigQuery, PostgreSQL, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e06cd5eb56a43b5c</t>
+          <t>https://www.indeed.com/viewjob?jk=76d763c610ac1510</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>Senior Backend Software Engineer- GM Energy</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, GCP, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daaeb6d16db98abf</t>
+          <t>https://www.indeed.com/viewjob?jk=51fb08298ca2e944</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>Data Platform Architect (Snowflake)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Coastal</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Snowflake, Data Modeling, Kimball, ETL, dbt</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d61083f86948477</t>
+          <t>https://www.indeed.com/viewjob?jk=58854506afe876e4</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71d4be4e91f6174a</t>
+          <t>https://www.indeed.com/viewjob?jk=c5c449cb4c336ec2</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=912b927f8e6b0bc9</t>
+          <t>https://www.indeed.com/viewjob?jk=e57a91ca929fec5b</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=697335a3240f02f2</t>
+          <t>https://www.indeed.com/viewjob?jk=cd22b6d5954a33c2</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e21309c64f987c4d</t>
+          <t>https://www.indeed.com/viewjob?jk=2d369f55f3c43cd0</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e4114c9ced06f08</t>
+          <t>https://www.indeed.com/viewjob?jk=b5e852e1fb093faa</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0379c77fb1bea285</t>
+          <t>https://www.indeed.com/viewjob?jk=122021b0213972fb</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7404f3dbf25b5d0</t>
+          <t>https://www.indeed.com/viewjob?jk=cf263b65906b30ba</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19a128257d3c2c77</t>
+          <t>https://www.indeed.com/viewjob?jk=775f4b74d2e0d125</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a667aa6f915c8e9</t>
+          <t>https://www.indeed.com/viewjob?jk=e27aa2f30115d6a9</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d47c2036fa69322</t>
+          <t>https://www.indeed.com/viewjob?jk=372ffe4f2e9a605d</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=591077de2df74cfa</t>
+          <t>https://www.indeed.com/viewjob?jk=a256a77103c9ee18</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cc254c410ba6f38</t>
+          <t>https://www.indeed.com/viewjob?jk=9b082342159bbdf7</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12339d025b6d4b6f</t>
+          <t>https://www.indeed.com/viewjob?jk=e06cd5eb56a43b5c</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc7db42760d4627e</t>
+          <t>https://www.indeed.com/viewjob?jk=daaeb6d16db98abf</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c024ec8f500d28f</t>
+          <t>https://www.indeed.com/viewjob?jk=5d61083f86948477</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5c090288e0e4f79</t>
+          <t>https://www.indeed.com/viewjob?jk=71d4be4e91f6174a</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c400db066fcfe868</t>
+          <t>https://www.indeed.com/viewjob?jk=912b927f8e6b0bc9</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,67 +4451,67 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9857bbf535b2768</t>
+          <t>https://www.indeed.com/viewjob?jk=697335a3240f02f2</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, Terraform, Airflow, Apache Airflow</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f72c641c65b5a61</t>
+          <t>https://www.indeed.com/viewjob?jk=e21309c64f987c4d</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Software Engineer III – Python/PySpark/AWS</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,172 +4521,172 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=991d5ceb2074b137</t>
+          <t>https://www.indeed.com/viewjob?jk=6e4114c9ced06f08</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>FSO LABS - AI Developer Senior - Bay Area</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Hive, Spark, Kafka, NoSQL, Power BI, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d75a18fe3bc2126</t>
+          <t>https://www.indeed.com/viewjob?jk=0379c77fb1bea285</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer - Senior - Consulting - Location Open</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, AKS</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=599253e2d33dc75f</t>
+          <t>https://www.indeed.com/viewjob?jk=c7404f3dbf25b5d0</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Data Engineer (Snowflake, Teradata, DB2)</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Mutual of Omaha</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Scala, Snowflake, SQL Server, MongoDB, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa9d2ce9f1b5528c</t>
+          <t>https://www.indeed.com/viewjob?jk=19a128257d3c2c77</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>ObjectStream</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Blob Storage, Spark, PySpark, ETL, dbt, Airflow, Apache Airflow</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06e3854d22cdba89</t>
+          <t>https://www.indeed.com/viewjob?jk=6a667aa6f915c8e9</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>PySpark Data Engineer III - Python/Java/SQL</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,32 +4696,32 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=926547138e49a51b</t>
+          <t>https://www.indeed.com/viewjob?jk=8d47c2036fa69322</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Cloud Engineering &amp; FinOps</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,32 +4731,32 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d576082b1c56db5c</t>
+          <t>https://www.indeed.com/viewjob?jk=591077de2df74cfa</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer (R-19149)</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Dun &amp; Bradstreet</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,242 +4766,242 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb41c4b9d93e0f98</t>
+          <t>https://www.indeed.com/viewjob?jk=8cc254c410ba6f38</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Infrastructure Solutions Architect</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Global Information Technology</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94bea5b95ba94e24</t>
+          <t>https://www.indeed.com/viewjob?jk=12339d025b6d4b6f</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=983d0a4b6df6a34b</t>
+          <t>https://www.indeed.com/viewjob?jk=dc7db42760d4627e</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e39cfd742ca8ccb7</t>
+          <t>https://www.indeed.com/viewjob?jk=6c024ec8f500d28f</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d24b9bb7d3f81d1</t>
+          <t>https://www.indeed.com/viewjob?jk=d5c090288e0e4f79</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=406f01e6594b2624</t>
+          <t>https://www.indeed.com/viewjob?jk=c400db066fcfe868</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0206f3baae13d0ec</t>
+          <t>https://www.indeed.com/viewjob?jk=e9857bbf535b2768</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Full‑Stack Developer (Java, React, Microservices) *Hybrid*</t>
+          <t>SR DBA / DATABASE ARCHITECT (AZURE / MSSQL)</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Opeeka, Inc.</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Folsom, CA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Bitbucket</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,32 +5011,32 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=229f6840535c3531</t>
+          <t>https://www.indeed.com/viewjob?jk=d57af04f58fc4f3b</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Full‑Stack Developer (Java, React, Microservices) *Hybrid*</t>
+          <t>Senior DBA / Database Architect</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Opeeka, Inc.</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Folsom, CA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Bitbucket</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,32 +5046,32 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606324c85c044a5d</t>
+          <t>https://www.indeed.com/viewjob?jk=5142b758be4e8f87</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
+          <t>Application Developer</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Value Truck of Arizona</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Smyrna, GA, US USA</t>
+          <t>South Jordan, UT, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef040d1b01903853</t>
+          <t>https://www.indeed.com/viewjob?jk=f6c3e26366316cc8</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Full‑Stack Developer (Java, React, Microservices) *Hybrid*</t>
+          <t>AWS Systems Engineer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,34 +5106,34 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f298bb4ddf8e9a0</t>
+          <t>https://www.indeed.com/viewjob?jk=119269e5158f89e8</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Information Technology - Data Integration Engineer</t>
+          <t>Data Engineer (Snowflake, Teradata, DB2)</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Magnolia</t>
+          <t>Mutual of Omaha</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Waco, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,34 +5141,34 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Glue, RDS, Scala, Snowflake, SQL Server, MongoDB, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22a077ceb692752f</t>
+          <t>https://www.indeed.com/viewjob?jk=aa9d2ce9f1b5528c</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Douglas Machine Inc.</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Alexandria, MN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,15 +5176,680 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, Terraform, Airflow, Apache Airflow</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5f72c641c65b5a61</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Sr. Data Engineer</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>ObjectStream</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Oklahoma City, OK, US USA</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Blob Storage, Spark, PySpark, ETL, dbt, Airflow, Apache Airflow</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=06e3854d22cdba89</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>PySpark Data Engineer III - Python/Java/SQL</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=926547138e49a51b</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer – Cloud Engineering &amp; FinOps</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>General Motors (GM)</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d576082b1c56db5c</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Senior Cloud Platform Engineer (R-19149)</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Dun &amp; Bradstreet</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cb41c4b9d93e0f98</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Databricks Data Engineer - Senior - Consulting - Location Open</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>EY</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, AKS</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=599253e2d33dc75f</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Software Engineer III – Python/PySpark/AWS</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, RDS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=991d5ceb2074b137</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>FSO LABS - AI Developer Senior - Bay Area</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>EY</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Hadoop, Hive, Spark, Kafka, NoSQL, Power BI, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1d75a18fe3bc2126</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Cloud Service Desk Analyst</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, ETL, ELT, dbt, Airflow, Git, Python</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2781169a06fdef87</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Infrastructure Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Global Information Technology</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Lansing, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, CI/CD, Jenkins, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=94bea5b95ba94e24</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=983d0a4b6df6a34b</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e39cfd742ca8ccb7</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4d24b9bb7d3f81d1</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=406f01e6594b2624</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0206f3baae13d0ec</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Full‑Stack Developer (Java, React, Microservices) *Hybrid*</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=229f6840535c3531</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Full‑Stack Developer (Java, React, Microservices) *Hybrid*</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=606324c85c044a5d</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Smyrna, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ef040d1b01903853</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Full‑Stack Developer (Java, React, Microservices) *Hybrid*</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0f298bb4ddf8e9a0</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Senior Business Intelligence Developer</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Douglas Machine Inc.</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Alexandria, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
           <t>RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=f9d5d216fe71b48e</t>
         </is>

--- a/results/job_matches_2026-05-01.xlsx
+++ b/results/job_matches_2026-05-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G155"/>
+  <dimension ref="A1:G149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Select Minds LLC</t>
+          <t>Linstarsolution corporation</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Ridgefield Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,42 +626,42 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, Databricks, Spark</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9d0ac6d3cf445a9</t>
+          <t>https://www.indeed.com/viewjob?jk=3825710140df8183</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Technical Architect-Datawarehousing</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Select Minds LLC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Marlborough, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, Databricks, Spark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,59 +671,59 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10720f22d9d38621</t>
+          <t>https://www.indeed.com/viewjob?jk=d9d0ac6d3cf445a9</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (C#/.NET &amp; AI)</t>
+          <t>Technical Architect-Datawarehousing</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Marlborough, MA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, S3, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93c21b258a08bd24</t>
+          <t>https://www.indeed.com/viewjob?jk=10720f22d9d38621</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr Software Engineer II - Enterprise Architecture</t>
+          <t>Senior Software Engineer (C#/.NET &amp; AI)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,42 +731,42 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6bd0f139eec27a7</t>
+          <t>https://www.indeed.com/viewjob?jk=93c21b258a08bd24</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Cloud Engineer II</t>
+          <t>Sr Software Engineer II - Enterprise Architecture</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Vibrant Emotional Health</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,42 +776,42 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ba39b2a6826c32d</t>
+          <t>https://www.indeed.com/viewjob?jk=f6bd0f139eec27a7</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Junior Automation Engineer (Cloud)</t>
+          <t>Cloud Engineer II</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Vibrant Emotional Health</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Splunk</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80278e0d3375f33b</t>
+          <t>https://www.indeed.com/viewjob?jk=3ba39b2a6826c32d</t>
         </is>
       </c>
     </row>
@@ -853,17 +853,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Junior Automation Engineer (Cloud)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tradeweb</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,29 +871,29 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, GCP, Spark, Kafka, Dask, Snowflake</t>
+          <t>AWS, SQS, SNS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Splunk</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb2021c38a5314d9</t>
+          <t>https://www.indeed.com/viewjob?jk=80278e0d3375f33b</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Metropolitan Commercial Bank</t>
+          <t>Tradeweb</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, NoSQL</t>
+          <t>AWS, Redshift, S3, IAM, RDS, GCP, Spark, Kafka, Dask, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25250927f01c87fd</t>
+          <t>https://www.indeed.com/viewjob?jk=cb2021c38a5314d9</t>
         </is>
       </c>
     </row>
@@ -958,17 +958,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Kubernetes Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Credera</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,87 +976,87 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Oozie, Spark, Scala, Kafka, SQL Server</t>
+          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Azure, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2859c21fcc6b9b6</t>
+          <t>https://www.indeed.com/viewjob?jk=5f09eaf9518abf0e</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Azure Data &amp; Development Architect</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Credera</t>
+          <t>SunStone Consulting</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Oozie, Spark, Scala, Kafka, SQL Server</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Event Hubs, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e65ae12c9231691</t>
+          <t>https://www.indeed.com/viewjob?jk=1e9052cac6c7210d</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Java Compliance &amp; Governance Developer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Credera</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Oozie, Spark, Scala, Kafka, SQL Server</t>
+          <t>IAM, RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=deb9ad8464ceb6e6</t>
+          <t>https://www.indeed.com/viewjob?jk=8078bc6f1fdb2e7b</t>
         </is>
       </c>
     </row>
@@ -1068,20 +1068,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Credera</t>
+          <t>ABCorp NA Inc.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Oozie, Spark, Scala, Kafka, SQL Server</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,14 +1091,14 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0faede29102fb7e1</t>
+          <t>https://www.indeed.com/viewjob?jk=1e06fd43e0f99777</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Kubernetes Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1112,11 +1112,11 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Azure, Scala, Snowflake, Oracle</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,14 +1126,14 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f09eaf9518abf0e</t>
+          <t>https://www.indeed.com/viewjob?jk=dc5cd30ba1545c61</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Java Compliance &amp; Governance Developer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1147,11 +1147,11 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,102 +1161,102 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8078bc6f1fdb2e7b</t>
+          <t>https://www.indeed.com/viewjob?jk=6622c031669892fa</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer II _ Big Data, GCP _EDAI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ABCorp NA Inc.</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e06fd43e0f99777</t>
+          <t>https://www.indeed.com/viewjob?jk=d725c4b26e048534</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Azure Data &amp; Development Architect</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SunStone Consulting</t>
+          <t>JUUL Labs</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Event Hubs, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, S3, ECS, IAM, RDS, GCP, Dataflow, Cloud Storage, Scala, Splunk</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e9052cac6c7210d</t>
+          <t>https://www.indeed.com/viewjob?jk=c63edb85327f9aef</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineer, Full Stack - AI (Chicago)</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Fitch Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
+          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, Snowflake, SQL Server, MySQL, ELT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,49 +1266,49 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4bb35a3533f1ee6</t>
+          <t>https://www.indeed.com/viewjob?jk=de10d304d09880c3</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Engineering &amp; Quality - Software Engineer, Full Stack - AI</t>
+          <t>Platform Architect</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Fitch Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Google Cloud Platform, Spark, PySpark</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf6b928dd59e0c41</t>
+          <t>https://www.indeed.com/viewjob?jk=0ff622ef0e6ac90d</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Junior Cloud Automation Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, Hadoop, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Google Cloud Platform, Spark, PySpark</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,14 +1336,14 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc5cd30ba1545c61</t>
+          <t>https://www.indeed.com/viewjob?jk=86ef316bc56e1d98</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, Hadoop, Spark, Scala</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6622c031669892fa</t>
+          <t>https://www.indeed.com/viewjob?jk=200956ef0d629800</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer II _ Big Data, GCP _EDAI</t>
+          <t>Software Engineer Seniors – Cloud Technologies | Fintech | Full Stack</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>FIS</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, Azure, Data Factory, Scala, Oracle, SQL Server, NoSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d725c4b26e048534</t>
+          <t>https://www.indeed.com/viewjob?jk=d35fe7a7c554f8b5</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>JUUL Labs</t>
+          <t>Matillion</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, GCP, Dataflow, Cloud Storage, Scala, Splunk</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c63edb85327f9aef</t>
+          <t>https://www.indeed.com/viewjob?jk=95bbbaf8fbe8db68</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Matillion</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,42 +1466,42 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, Snowflake, SQL Server, MySQL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de10d304d09880c3</t>
+          <t>https://www.indeed.com/viewjob?jk=2c7ffe9dfedc9c5d</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Dev Ops Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>SkyWater Technology Foundry</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
+          <t>AWS, IAM, RDS, Photon, GCP, Vertex AI, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fc4628968aad9e2</t>
+          <t>https://www.indeed.com/viewjob?jk=13bfee40249f3478</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Business Intelligence Solutions Architect</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Mars Technominds</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,67 +1546,67 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0eb5fc1d601c0028</t>
+          <t>https://www.indeed.com/viewjob?jk=38246f1a187f1c7d</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS SysOps Administrator</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, IAM, RDS, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acae1b7fc51e9a39</t>
+          <t>https://www.indeed.com/viewjob?jk=c1e9865761b44f05</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>DEVELOPER L3(CONTRACT)</t>
+          <t>Site AI Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Temple, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Cloud Storage, Spark, PySpark, Scala, Snowflake, Time Travel, Databricks Lakehouse, Snowflake Schema</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c37881d8861b3d6</t>
+          <t>https://www.indeed.com/viewjob?jk=b9df42fb6f0e5b92</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Platform Architect</t>
+          <t>CloudOps Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Google Cloud Platform, Spark, PySpark</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ff622ef0e6ac90d</t>
+          <t>https://www.indeed.com/viewjob?jk=861e821c88461e16</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Junior Cloud Automation Engineer</t>
+          <t>CloudOps Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Google Cloud Platform, Spark, PySpark</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86ef316bc56e1d98</t>
+          <t>https://www.indeed.com/viewjob?jk=61fe23b5a013d06d</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>CloudOps Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Lakewood, CO, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Scala, DynamoDB</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,67 +1721,67 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=200956ef0d629800</t>
+          <t>https://www.indeed.com/viewjob?jk=0590d6bb95b36919</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer Seniors – Cloud Technologies | Fintech | Full Stack</t>
+          <t>CloudOps Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>FIS</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Yarmouth, ME, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Oracle, SQL Server, NoSQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d35fe7a7c554f8b5</t>
+          <t>https://www.indeed.com/viewjob?jk=e9c7752d42fa52c7</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Matillion</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95bbbaf8fbe8db68</t>
+          <t>https://www.indeed.com/viewjob?jk=294c6d2addcb10cf</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>AWS Technical Apprentice / Trainee</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Matillion</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Databricks</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c7ffe9dfedc9c5d</t>
+          <t>https://www.indeed.com/viewjob?jk=2223f947ee98de60</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Dev Ops Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SkyWater Technology Foundry</t>
+          <t>Client Resources, Inc.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Photon, GCP, Vertex AI, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, GCP, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13bfee40249f3478</t>
+          <t>https://www.indeed.com/viewjob?jk=d1e155aced1efdff</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Business Intelligence Solutions Architect</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Mars Technominds</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Redshift, Athena, S3, IAM, Hadoop, Spark, Kafka, Snowflake, Splunk</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,102 +1896,102 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38246f1a187f1c7d</t>
+          <t>https://www.indeed.com/viewjob?jk=0f01d239e5c828f6</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ERP Data Management Architect (Manufacturing)</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Infor</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Oracle, MySQL, Data Modeling, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Scala, NoSQL, Power BI, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e45199011cbe2990</t>
+          <t>https://www.indeed.com/viewjob?jk=222a5b676c08f8f0</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AWS SysOps Administrator</t>
+          <t>Senior Engineer - Agentic AI</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, IAM, RDS, DynamoDB, CI/CD</t>
+          <t>AWS, Lambda, SQS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1e9865761b44f05</t>
+          <t>https://www.indeed.com/viewjob?jk=5daf8f72a4fd9ab6</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Engineer I – AI Assistant Framework, ArcGIS Enterprise</t>
+          <t>Senior Backend Software Engineer/SRE - GM Energy</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2546eaf4a3e50baf</t>
+          <t>https://www.indeed.com/viewjob?jk=0413ce8de5fcca6a</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Site AI Engineer</t>
+          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Temple, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9df42fb6f0e5b92</t>
+          <t>https://www.indeed.com/viewjob?jk=79a2a043dc5cdb8f</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=294c6d2addcb10cf</t>
+          <t>https://www.indeed.com/viewjob?jk=e387db2c2b866baa</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>AWS Technical Apprentice / Trainee</t>
+          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Databricks</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2223f947ee98de60</t>
+          <t>https://www.indeed.com/viewjob?jk=18a022cbc2b4d934</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Client Resources, Inc.</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, GCP, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1e155aced1efdff</t>
+          <t>https://www.indeed.com/viewjob?jk=5cc4f959dd712f8a</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Yonkers, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, S3, IAM, Hadoop, Spark, Kafka, Snowflake, Splunk</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f01d239e5c828f6</t>
+          <t>https://www.indeed.com/viewjob?jk=688d7763683eecad</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Distinguished Engineer -</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Intelligent Medical Objects</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Spark, Scala, Data Modeling, dbt, Power BI</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, GCP, Snowflake, ELT, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4869d3a6ac24136</t>
+          <t>https://www.indeed.com/viewjob?jk=087eb595cff7bd93</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Smithfield, RI, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,42 +2236,42 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, NoSQL, Power BI, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, EMR, RDS, Spark, Scala, Snowflake, Oracle, ETL, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=222a5b676c08f8f0</t>
+          <t>https://www.indeed.com/viewjob?jk=5cc22367a2ce3d9f</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Engineer - Agentic AI</t>
+          <t>AI/ML Engineer – Data &amp; Full-Stack Solutions</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>ITC Federal</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,207 +2281,207 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5daf8f72a4fd9ab6</t>
+          <t>https://www.indeed.com/viewjob?jk=ce30a23eaa64abcd</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer/SRE - GM Energy</t>
+          <t>Cloud Support Associate</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Snowflake, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0413ce8de5fcca6a</t>
+          <t>https://www.indeed.com/viewjob?jk=39dc124339eab650</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
+          <t>Platform Architect</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Unity Catalog, Delta Live Tables, Google Cloud Platform, Spark, PySpark, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79a2a043dc5cdb8f</t>
+          <t>https://www.indeed.com/viewjob?jk=4c1348f2e47cd5d6</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
+          <t>Infrastructure Engineer (Cloud Focus)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, Lambda, Kinesis, Redshift, S3, API Gateway, Scala, Kafka, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e387db2c2b866baa</t>
+          <t>https://www.indeed.com/viewjob?jk=00e1f01fe85665ee</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18a022cbc2b4d934</t>
+          <t>https://www.indeed.com/viewjob?jk=3c5b06678237c00c</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
+          <t>AWS Systems Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Athena, S3, SQS, SNS, IAM, Spark, PySpark</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cc4f959dd712f8a</t>
+          <t>https://www.indeed.com/viewjob?jk=e5e7a473ae9d0b96</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
+          <t>Software Development Engineer II</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Yonkers, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,94 +2491,94 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=688d7763683eecad</t>
+          <t>https://www.indeed.com/viewjob?jk=c0d2f3586b2ed198</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Distinguished Engineer -</t>
+          <t>Quality Assurance Analyst / ETL Tester</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Briljent</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, GCP, Snowflake, ELT, Splunk, CI/CD</t>
+          <t>RDS, Azure, Snowflake, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=087eb595cff7bd93</t>
+          <t>https://www.indeed.com/viewjob?jk=d69b1256484e3a82</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Artificial Intelligence/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Smithfield, RI, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Spark, Scala, Snowflake, Oracle, ETL, Jenkins, Maven</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cc22367a2ce3d9f</t>
+          <t>https://www.indeed.com/viewjob?jk=8f6f11467cb82584</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Cloud Support Associate</t>
+          <t>Artificial Intelligence/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Snowflake, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39dc124339eab650</t>
+          <t>https://www.indeed.com/viewjob?jk=c9ce81a6707266dd</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AI/ML Engineer – Data &amp; Full-Stack Solutions</t>
+          <t>Artificial Intelligence/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ITC Federal</t>
+          <t>Logic, Inc.</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, ETL, ELT, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,14 +2631,14 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce30a23eaa64abcd</t>
+          <t>https://www.indeed.com/viewjob?jk=e34c2e31eeb33f9e</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Platform Architect</t>
+          <t>Senior Cloud Migration Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2652,11 +2652,11 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Unity Catalog, Delta Live Tables, Google Cloud Platform, Spark, PySpark, Oracle, Data Modeling</t>
+          <t>AWS, Lambda, SQS, API Gateway, ECS, RDS, Google Cloud Platform, Vertex AI, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,67 +2666,67 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c1348f2e47cd5d6</t>
+          <t>https://www.indeed.com/viewjob?jk=93321e0d50904658</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer (Cloud Focus)</t>
+          <t>Senior Machine Learning Engineer (Remote)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, S3, API Gateway, Scala, Kafka, DynamoDB, Data Modeling</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, NoSQL, CI/CD, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00e1f01fe85665ee</t>
+          <t>https://www.indeed.com/viewjob?jk=fdbdb16275078800</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Cloud Operations Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>MITSUBISHI ELECTRIC ICONICS DIGITAL SOLUTIONS</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, DynamoDB, NoSQL</t>
+          <t>AWS, Lambda, S3, ECS, RDS, DynamoDB, CI/CD, AWS CodePipeline, CodeBuild, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c5b06678237c00c</t>
+          <t>https://www.indeed.com/viewjob?jk=67d1ed48d145a4f1</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>AWS Systems Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, SQS, SNS, IAM, Spark, PySpark</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, ETL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,67 +2771,67 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5e7a473ae9d0b96</t>
+          <t>https://www.indeed.com/viewjob?jk=77a528b43d8d11a1</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>Data Engineer - Performance Management</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Lake Buena Vista, FL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0d2f3586b2ed198</t>
+          <t>https://www.indeed.com/viewjob?jk=b85eeb0fd5a3a862</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer II</t>
+          <t>Systems &amp; Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>Kretek International</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Moorpark, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, Splunk, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Splunk, Terraform</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fa53cf983e1a6d0</t>
+          <t>https://www.indeed.com/viewjob?jk=a7d7d86c5d6aef50</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Artificial Intelligence/Machine Learning Data Engineer</t>
+          <t>Data Engineer - Performance Management</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Lake Buena Vista, FL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f6f11467cb82584</t>
+          <t>https://www.indeed.com/viewjob?jk=57b0af5961338ef2</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Artificial Intelligence/Machine Learning Data Engineer</t>
+          <t>Full Stack, Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>SCAN Health Plan</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,94 +2911,94 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9ce81a6707266dd</t>
+          <t>https://www.indeed.com/viewjob?jk=6b0db4093988ff3c</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Artificial Intelligence/Machine Learning Data Engineer</t>
+          <t>Cloud Service Desk Analyst</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Logic, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e34c2e31eeb33f9e</t>
+          <t>https://www.indeed.com/viewjob?jk=68f4f33bf88f7f89</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Quality Assurance Analyst / ETL Tester</t>
+          <t>AI/ML Developer II (Remote)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Briljent</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Snowflake, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL, Data Modeling, Snowflake Schema, ETL</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, NoSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d69b1256484e3a82</t>
+          <t>https://www.indeed.com/viewjob?jk=fb663396a5bc1b79</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, ETL</t>
+          <t>RDS, Databricks, Scala, Snowflake, PostgreSQL, MySQL, Splunk, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77a528b43d8d11a1</t>
+          <t>https://www.indeed.com/viewjob?jk=1869e5a8847d426e</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer - Performance Management</t>
+          <t>Software Engineer II, Global Servicing Technology</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Lake Buena Vista, FL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Google Cloud Platform, Cloud Storage, Hive, Spark, Scala, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b85eeb0fd5a3a862</t>
+          <t>https://www.indeed.com/viewjob?jk=5c5c9f5bf8d54b87</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Systems &amp; Cloud Infrastructure Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Kretek International</t>
+          <t>Accompany Health</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Moorpark, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Splunk, Terraform</t>
+          <t>AWS, Glue, Spark, Scala, Kafka, NoSQL, Data Modeling, Terraform, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,102 +3086,102 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7d7d86c5d6aef50</t>
+          <t>https://www.indeed.com/viewjob?jk=f41df6bde69aeb07</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Engineer - Performance Management</t>
+          <t>Junior Cloud Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Lake Buena Vista, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Spark, Kafka, Snowflake, Oracle, ETL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57b0af5961338ef2</t>
+          <t>https://www.indeed.com/viewjob?jk=8d85a7cfec698363</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Full Stack, Data &amp; Analytics Engineer</t>
+          <t>Junior Cloud Networking Technician</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SCAN Health Plan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b0db4093988ff3c</t>
+          <t>https://www.indeed.com/viewjob?jk=e73f6230be428620</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Cloud Migration Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Axis Residential</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Spokane, WA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, API Gateway, ECS, RDS, Google Cloud Platform, Vertex AI, MySQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Kimball, ETL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,137 +3191,137 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93321e0d50904658</t>
+          <t>https://www.indeed.com/viewjob?jk=7970a51178c2d8ba</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (Remote)</t>
+          <t>Multi-Cloud Networking Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, NoSQL, CI/CD, Git, Python, SQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdbdb16275078800</t>
+          <t>https://www.indeed.com/viewjob?jk=5089f26e49e819d7</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Cloud Service Desk Analyst</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68f4f33bf88f7f89</t>
+          <t>https://www.indeed.com/viewjob?jk=d33e81401b69b22c</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Snowflake, PostgreSQL, MySQL, Splunk, CI/CD, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1869e5a8847d426e</t>
+          <t>https://www.indeed.com/viewjob?jk=ffcaa5c8b2e22e2b</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>AI/ML Developer II (Remote)</t>
+          <t>Data Engineer, Go to Market (Remote)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, NoSQL, ETL, ELT</t>
+          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb663396a5bc1b79</t>
+          <t>https://www.indeed.com/viewjob?jk=8c7e11f90c05edfc</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Junior Cloud Engineer</t>
+          <t>Sr. Infrastructure &amp; Security Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>HerculesAI</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Campbell, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Spark, Kafka, Snowflake, Oracle, ETL</t>
+          <t>AWS, Lambda, IAM, Azure, GCP, Splunk, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d85a7cfec698363</t>
+          <t>https://www.indeed.com/viewjob?jk=997e47a23e0d8261</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Junior Cloud Networking Technician</t>
+          <t>Software Engineer III - Data, AWS, ETL, Java/Python,</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e73f6230be428620</t>
+          <t>https://www.indeed.com/viewjob?jk=24b2eb0df8c7e284</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Axis Residential</t>
+          <t>Cityblock Health</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Spokane, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Kimball, ETL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, BigQuery, PostgreSQL, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7970a51178c2d8ba</t>
+          <t>https://www.indeed.com/viewjob?jk=76d763c610ac1510</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Multi-Cloud Networking Engineer</t>
+          <t>Professional Services Consultant</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ataccama</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5089f26e49e819d7</t>
+          <t>https://www.indeed.com/viewjob?jk=e7e7f81d2e0f0ce3</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Software Engineer II, Global Servicing Technology</t>
+          <t>Senior Backend Software Engineer- GM Energy</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, Cloud Storage, Hive, Spark, Scala, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, GCP, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c5c9f5bf8d54b87</t>
+          <t>https://www.indeed.com/viewjob?jk=51fb08298ca2e944</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>SR DBA / DATABASE ARCHITECT (AZURE / MSSQL)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Opeeka, Inc.</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Folsom, CA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Bitbucket</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d33e81401b69b22c</t>
+          <t>https://www.indeed.com/viewjob?jk=d57af04f58fc4f3b</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior DBA / Database Architect</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Opeeka, Inc.</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Folsom, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Bitbucket</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffcaa5c8b2e22e2b</t>
+          <t>https://www.indeed.com/viewjob?jk=5142b758be4e8f87</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Application Developer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Accompany Health</t>
+          <t>Value Truck of Arizona</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>South Jordan, UT, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Glue, Spark, Scala, Kafka, NoSQL, Data Modeling, Terraform, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f41df6bde69aeb07</t>
+          <t>https://www.indeed.com/viewjob?jk=f6c3e26366316cc8</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Engineer, Go to Market (Remote)</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c7e11f90c05edfc</t>
+          <t>https://www.indeed.com/viewjob?jk=c5c449cb4c336ec2</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Sr. Infrastructure &amp; Security Engineer</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>HerculesAI</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Campbell, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, Azure, GCP, Splunk, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=997e47a23e0d8261</t>
+          <t>https://www.indeed.com/viewjob?jk=e57a91ca929fec5b</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data, AWS, ETL, Java/Python,</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, ETL, CI/CD, Terraform</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24b2eb0df8c7e284</t>
+          <t>https://www.indeed.com/viewjob?jk=cd22b6d5954a33c2</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Cityblock Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, BigQuery, PostgreSQL, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76d763c610ac1510</t>
+          <t>https://www.indeed.com/viewjob?jk=2d369f55f3c43cd0</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer- GM Energy</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, GCP, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51fb08298ca2e944</t>
+          <t>https://www.indeed.com/viewjob?jk=b5e852e1fb093faa</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data Platform Architect (Snowflake)</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Coastal</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Snowflake, Data Modeling, Kimball, ETL, dbt</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58854506afe876e4</t>
+          <t>https://www.indeed.com/viewjob?jk=122021b0213972fb</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5c449cb4c336ec2</t>
+          <t>https://www.indeed.com/viewjob?jk=cf263b65906b30ba</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e57a91ca929fec5b</t>
+          <t>https://www.indeed.com/viewjob?jk=775f4b74d2e0d125</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd22b6d5954a33c2</t>
+          <t>https://www.indeed.com/viewjob?jk=e27aa2f30115d6a9</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d369f55f3c43cd0</t>
+          <t>https://www.indeed.com/viewjob?jk=372ffe4f2e9a605d</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5e852e1fb093faa</t>
+          <t>https://www.indeed.com/viewjob?jk=a256a77103c9ee18</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=122021b0213972fb</t>
+          <t>https://www.indeed.com/viewjob?jk=9b082342159bbdf7</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf263b65906b30ba</t>
+          <t>https://www.indeed.com/viewjob?jk=e06cd5eb56a43b5c</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=775f4b74d2e0d125</t>
+          <t>https://www.indeed.com/viewjob?jk=daaeb6d16db98abf</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e27aa2f30115d6a9</t>
+          <t>https://www.indeed.com/viewjob?jk=5d61083f86948477</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=372ffe4f2e9a605d</t>
+          <t>https://www.indeed.com/viewjob?jk=71d4be4e91f6174a</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a256a77103c9ee18</t>
+          <t>https://www.indeed.com/viewjob?jk=912b927f8e6b0bc9</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b082342159bbdf7</t>
+          <t>https://www.indeed.com/viewjob?jk=697335a3240f02f2</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e06cd5eb56a43b5c</t>
+          <t>https://www.indeed.com/viewjob?jk=e21309c64f987c4d</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daaeb6d16db98abf</t>
+          <t>https://www.indeed.com/viewjob?jk=6e4114c9ced06f08</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d61083f86948477</t>
+          <t>https://www.indeed.com/viewjob?jk=0379c77fb1bea285</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71d4be4e91f6174a</t>
+          <t>https://www.indeed.com/viewjob?jk=c7404f3dbf25b5d0</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=912b927f8e6b0bc9</t>
+          <t>https://www.indeed.com/viewjob?jk=19a128257d3c2c77</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=697335a3240f02f2</t>
+          <t>https://www.indeed.com/viewjob?jk=6a667aa6f915c8e9</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e21309c64f987c4d</t>
+          <t>https://www.indeed.com/viewjob?jk=8d47c2036fa69322</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e4114c9ced06f08</t>
+          <t>https://www.indeed.com/viewjob?jk=591077de2df74cfa</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0379c77fb1bea285</t>
+          <t>https://www.indeed.com/viewjob?jk=8cc254c410ba6f38</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7404f3dbf25b5d0</t>
+          <t>https://www.indeed.com/viewjob?jk=12339d025b6d4b6f</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19a128257d3c2c77</t>
+          <t>https://www.indeed.com/viewjob?jk=dc7db42760d4627e</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a667aa6f915c8e9</t>
+          <t>https://www.indeed.com/viewjob?jk=6c024ec8f500d28f</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d47c2036fa69322</t>
+          <t>https://www.indeed.com/viewjob?jk=d5c090288e0e4f79</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=591077de2df74cfa</t>
+          <t>https://www.indeed.com/viewjob?jk=c400db066fcfe868</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,102 +4766,102 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cc254c410ba6f38</t>
+          <t>https://www.indeed.com/viewjob?jk=e9857bbf535b2768</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>MuleSoft QA Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12339d025b6d4b6f</t>
+          <t>https://www.indeed.com/viewjob?jk=6a8b7edc3d29ab01</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, Terraform, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc7db42760d4627e</t>
+          <t>https://www.indeed.com/viewjob?jk=5f72c641c65b5a61</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>Software Engineer III – Python/PySpark/AWS</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, Lambda, S3, RDS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,207 +4871,207 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c024ec8f500d28f</t>
+          <t>https://www.indeed.com/viewjob?jk=991d5ceb2074b137</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>FSO LABS - AI Developer Senior - Bay Area</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>RDS, Azure, Hadoop, Hive, Spark, Kafka, NoSQL, Power BI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5c090288e0e4f79</t>
+          <t>https://www.indeed.com/viewjob?jk=1d75a18fe3bc2126</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>Databricks Data Engineer - Senior - Consulting - Location Open</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, AKS</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c400db066fcfe868</t>
+          <t>https://www.indeed.com/viewjob?jk=599253e2d33dc75f</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>AWS Systems Engineer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9857bbf535b2768</t>
+          <t>https://www.indeed.com/viewjob?jk=119269e5158f89e8</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>SR DBA / DATABASE ARCHITECT (AZURE / MSSQL)</t>
+          <t>Data Engineer (Snowflake, Teradata, DB2)</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Opeeka, Inc.</t>
+          <t>Mutual of Omaha</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Folsom, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Bitbucket</t>
+          <t>AWS, Glue, RDS, Scala, Snowflake, SQL Server, MongoDB, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d57af04f58fc4f3b</t>
+          <t>https://www.indeed.com/viewjob?jk=aa9d2ce9f1b5528c</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Senior DBA / Database Architect</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Opeeka, Inc.</t>
+          <t>ObjectStream</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Folsom, CA, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Bitbucket</t>
+          <t>RDS, Azure, Data Factory, Blob Storage, Spark, PySpark, ETL, dbt, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5142b758be4e8f87</t>
+          <t>https://www.indeed.com/viewjob?jk=06e3854d22cdba89</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Application Developer</t>
+          <t>PySpark Data Engineer III - Python/Java/SQL</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Value Truck of Arizona</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>South Jordan, UT, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6c3e26366316cc8</t>
+          <t>https://www.indeed.com/viewjob?jk=926547138e49a51b</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>AWS Systems Engineer</t>
+          <t>Senior Software Engineer – Cloud Engineering &amp; FinOps</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,34 +5106,34 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=119269e5158f89e8</t>
+          <t>https://www.indeed.com/viewjob?jk=d576082b1c56db5c</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Data Engineer (Snowflake, Teradata, DB2)</t>
+          <t>Cloud Service Desk Analyst</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Mutual of Omaha</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Scala, Snowflake, SQL Server, MongoDB, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, ETL, ELT, dbt, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa9d2ce9f1b5528c</t>
+          <t>https://www.indeed.com/viewjob?jk=2781169a06fdef87</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>MuleSoft Developer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, Terraform, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, Oracle, SQL Server, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f72c641c65b5a61</t>
+          <t>https://www.indeed.com/viewjob?jk=7c7c89957751c232</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>MuleSoft Architect / Developer Remote (Part-Time / Full-Time) – US Client</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>ObjectStream</t>
+          <t>Bowery Software Inc</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Blob Storage, Spark, PySpark, ETL, dbt, Airflow, Apache Airflow</t>
+          <t>AWS, Azure, GCP, Oracle, ETL, Talend, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06e3854d22cdba89</t>
+          <t>https://www.indeed.com/viewjob?jk=fe3a1e183165a854</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>PySpark Data Engineer III - Python/Java/SQL</t>
+          <t>Infrastructure Solutions Architect</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Global Information Technology</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,29 +5246,29 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=926547138e49a51b</t>
+          <t>https://www.indeed.com/viewjob?jk=94bea5b95ba94e24</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Cloud Engineering &amp; FinOps</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -5281,34 +5281,34 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d576082b1c56db5c</t>
+          <t>https://www.indeed.com/viewjob?jk=afb2f5fe2a396169</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer (R-19149)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Dun &amp; Bradstreet</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,34 +5316,34 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb41c4b9d93e0f98</t>
+          <t>https://www.indeed.com/viewjob?jk=983d0a4b6df6a34b</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer - Senior - Consulting - Location Open</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,34 +5351,34 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=599253e2d33dc75f</t>
+          <t>https://www.indeed.com/viewjob?jk=e39cfd742ca8ccb7</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Software Engineer III – Python/PySpark/AWS</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,34 +5386,34 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=991d5ceb2074b137</t>
+          <t>https://www.indeed.com/viewjob?jk=4d24b9bb7d3f81d1</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>FSO LABS - AI Developer Senior - Bay Area</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,34 +5421,34 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Hive, Spark, Kafka, NoSQL, Power BI, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d75a18fe3bc2126</t>
+          <t>https://www.indeed.com/viewjob?jk=406f01e6594b2624</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Cloud Service Desk Analyst</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, ETL, ELT, dbt, Airflow, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,24 +5466,24 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2781169a06fdef87</t>
+          <t>https://www.indeed.com/viewjob?jk=0206f3baae13d0ec</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Infrastructure Solutions Architect</t>
+          <t>Full‑Stack Developer (Java, React, Microservices) *Hybrid*</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Global Information Technology</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,24 +5491,24 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94bea5b95ba94e24</t>
+          <t>https://www.indeed.com/viewjob?jk=229f6840535c3531</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full‑Stack Developer (Java, React, Microservices) *Hybrid*</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,24 +5526,24 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=983d0a4b6df6a34b</t>
+          <t>https://www.indeed.com/viewjob?jk=606324c85c044a5d</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Smyrna, GA, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,24 +5561,24 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e39cfd742ca8ccb7</t>
+          <t>https://www.indeed.com/viewjob?jk=ef040d1b01903853</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full‑Stack Developer (Java, React, Microservices) *Hybrid*</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,34 +5596,34 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d24b9bb7d3f81d1</t>
+          <t>https://www.indeed.com/viewjob?jk=0f298bb4ddf8e9a0</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Douglas Machine Inc.</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Alexandria, MN, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5631,225 +5631,15 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=406f01e6594b2624</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D150" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0206f3baae13d0ec</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>Full‑Stack Developer (Java, React, Microservices) *Hybrid*</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D151" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=229f6840535c3531</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>Full‑Stack Developer (Java, React, Microservices) *Hybrid*</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D152" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=606324c85c044a5d</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Smyrna, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D153" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ef040d1b01903853</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>Full‑Stack Developer (Java, React, Microservices) *Hybrid*</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D154" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0f298bb4ddf8e9a0</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>Senior Business Intelligence Developer</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>Douglas Machine Inc.</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>Alexandria, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D155" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=f9d5d216fe71b48e</t>
         </is>

--- a/results/job_matches_2026-05-01.xlsx
+++ b/results/job_matches_2026-05-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G149"/>
+  <dimension ref="A1:G143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,12 +468,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Python / PySpark (Mainframe Modernization) (contract)</t>
+          <t>Senior Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Omada Health</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -482,46 +482,46 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.2</v>
+        <v>20.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Azure, Databricks, Hadoop, HDFS, Hive</t>
+          <t>AWS, Lambda, Redshift, Athena, S3, SQS, SNS, BigQuery, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=015fe1a494f266bf</t>
+          <t>https://www.indeed.com/viewjob?jk=98dbeaca2ef62c98</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Engineering</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Omada Health</t>
+          <t>Neomax</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.8</v>
+        <v>20.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Athena, S3, SQS, SNS, BigQuery, Hadoop, Spark</t>
+          <t>AWS, Kinesis, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,59 +531,59 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98dbeaca2ef62c98</t>
+          <t>https://www.indeed.com/viewjob?jk=776692a890b58814</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Neomax</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.1</v>
+        <v>19.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Dataflow, Spark, Scala, Kafka, NoSQL, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=776692a890b58814</t>
+          <t>https://www.indeed.com/viewjob?jk=49b6a92728349bc5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Linstarsolution corporation</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Ridgefield Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,112 +591,112 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Dataflow, Spark, Scala, Kafka, NoSQL, Data Modeling, ELT</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49b6a92728349bc5</t>
+          <t>https://www.indeed.com/viewjob?jk=3825710140df8183</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Technical Architect-Datawarehousing</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Linstarsolution corporation</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ridgefield Park, NJ, US USA</t>
+          <t>Marlborough, MA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, Data Modeling, ETL</t>
+          <t>AWS, S3, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3825710140df8183</t>
+          <t>https://www.indeed.com/viewjob?jk=10720f22d9d38621</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Senior Software Engineer (C#/.NET &amp; AI)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Select Minds LLC</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>19.4</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, Databricks, Spark</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9d0ac6d3cf445a9</t>
+          <t>https://www.indeed.com/viewjob?jk=93c21b258a08bd24</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Technical Architect-Datawarehousing</t>
+          <t>Sr Software Engineer II - Enterprise Architecture</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Marlborough, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,102 +706,102 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10720f22d9d38621</t>
+          <t>https://www.indeed.com/viewjob?jk=f6bd0f139eec27a7</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (C#/.NET &amp; AI)</t>
+          <t>Cloud Engineer II</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>Vibrant Emotional Health</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93c21b258a08bd24</t>
+          <t>https://www.indeed.com/viewjob?jk=3ba39b2a6826c32d</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr Software Engineer II - Enterprise Architecture</t>
+          <t>Junior Automation Engineer (Cloud)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, SQS, SNS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Splunk</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6bd0f139eec27a7</t>
+          <t>https://www.indeed.com/viewjob?jk=80278e0d3375f33b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Cloud Engineer II</t>
+          <t>Senior Engineer - AI &amp; Data Management</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Vibrant Emotional Health</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins</t>
+          <t>S3, Azure, Data Factory, Cloud Storage, Hadoop, HDFS, Spark, Scala, Kafka, Informatica PowerCenter</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,49 +811,49 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ba39b2a6826c32d</t>
+          <t>https://www.indeed.com/viewjob?jk=0f98760c842e5085</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Engineer - AI &amp; Data Management</t>
+          <t>SRE/Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Sign In Solutions</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>S3, Azure, Data Factory, Cloud Storage, Hadoop, HDFS, Spark, Scala, Kafka, Informatica PowerCenter</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f98760c842e5085</t>
+          <t>https://www.indeed.com/viewjob?jk=78107cea029977e8</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Junior Automation Engineer (Cloud)</t>
+          <t>Kubernetes Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -867,11 +867,11 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Splunk</t>
+          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Azure, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,154 +881,154 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80278e0d3375f33b</t>
+          <t>https://www.indeed.com/viewjob?jk=5f09eaf9518abf0e</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Java Compliance &amp; Governance Developer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tradeweb</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, GCP, Spark, Kafka, Dask, Snowflake</t>
+          <t>IAM, RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb2021c38a5314d9</t>
+          <t>https://www.indeed.com/viewjob?jk=8078bc6f1fdb2e7b</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SRE/Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sign In Solutions</t>
+          <t>ABCorp NA Inc.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, Splunk, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78107cea029977e8</t>
+          <t>https://www.indeed.com/viewjob?jk=1e06fd43e0f99777</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Kubernetes Engineer</t>
+          <t>Azure Data &amp; Development Architect</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SunStone Consulting</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Azure, Scala, Snowflake, Oracle</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Event Hubs, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f09eaf9518abf0e</t>
+          <t>https://www.indeed.com/viewjob?jk=1e9052cac6c7210d</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Azure Data &amp; Development Architect</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SunStone Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Event Hubs, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e9052cac6c7210d</t>
+          <t>https://www.indeed.com/viewjob?jk=dc5cd30ba1545c61</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Java Compliance &amp; Governance Developer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1042,11 +1042,11 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,59 +1056,59 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8078bc6f1fdb2e7b</t>
+          <t>https://www.indeed.com/viewjob?jk=6622c031669892fa</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer II _ Big Data, GCP _EDAI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ABCorp NA Inc.</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e06fd43e0f99777</t>
+          <t>https://www.indeed.com/viewjob?jk=d725c4b26e048534</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JUUL Labs</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, Hadoop, Spark, Scala</t>
+          <t>AWS, S3, ECS, IAM, RDS, GCP, Dataflow, Cloud Storage, Scala, Splunk</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc5cd30ba1545c61</t>
+          <t>https://www.indeed.com/viewjob?jk=c63edb85327f9aef</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, Hadoop, Spark, Scala</t>
+          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, Snowflake, SQL Server, MySQL, ELT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6622c031669892fa</t>
+          <t>https://www.indeed.com/viewjob?jk=de10d304d09880c3</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer II _ Big Data, GCP _EDAI</t>
+          <t>Platform Architect</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Google Cloud Platform, Spark, PySpark</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d725c4b26e048534</t>
+          <t>https://www.indeed.com/viewjob?jk=0ff622ef0e6ac90d</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Junior Cloud Automation Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>JUUL Labs</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, GCP, Dataflow, Cloud Storage, Scala, Splunk</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Google Cloud Platform, Spark, PySpark</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c63edb85327f9aef</t>
+          <t>https://www.indeed.com/viewjob?jk=86ef316bc56e1d98</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, Snowflake, SQL Server, MySQL, ELT</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de10d304d09880c3</t>
+          <t>https://www.indeed.com/viewjob?jk=200956ef0d629800</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Platform Architect</t>
+          <t>Software Engineer Seniors – Cloud Technologies | Fintech | Full Stack</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>FIS</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Google Cloud Platform, Spark, PySpark</t>
+          <t>AWS, Azure, Data Factory, Scala, Oracle, SQL Server, NoSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ff622ef0e6ac90d</t>
+          <t>https://www.indeed.com/viewjob?jk=d35fe7a7c554f8b5</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Junior Cloud Automation Engineer</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Matillion</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Google Cloud Platform, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86ef316bc56e1d98</t>
+          <t>https://www.indeed.com/viewjob?jk=95bbbaf8fbe8db68</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Matillion</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Scala, DynamoDB</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=200956ef0d629800</t>
+          <t>https://www.indeed.com/viewjob?jk=2c7ffe9dfedc9c5d</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer Seniors – Cloud Technologies | Fintech | Full Stack</t>
+          <t>Senior Dev Ops Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>FIS</t>
+          <t>SkyWater Technology Foundry</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Oracle, SQL Server, NoSQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Photon, GCP, Vertex AI, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,67 +1406,67 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d35fe7a7c554f8b5</t>
+          <t>https://www.indeed.com/viewjob?jk=13bfee40249f3478</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Business Intelligence Solutions Architect</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Matillion</t>
+          <t>Mars Technominds</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95bbbaf8fbe8db68</t>
+          <t>https://www.indeed.com/viewjob?jk=38246f1a187f1c7d</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>AWS SysOps Administrator</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Matillion</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, IAM, RDS, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c7ffe9dfedc9c5d</t>
+          <t>https://www.indeed.com/viewjob?jk=c1e9865761b44f05</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Dev Ops Engineer</t>
+          <t>Site AI Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SkyWater Technology Foundry</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Temple, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Photon, GCP, Vertex AI, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,67 +1511,67 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13bfee40249f3478</t>
+          <t>https://www.indeed.com/viewjob?jk=b9df42fb6f0e5b92</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Business Intelligence Solutions Architect</t>
+          <t>CloudOps Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Mars Technominds</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38246f1a187f1c7d</t>
+          <t>https://www.indeed.com/viewjob?jk=861e821c88461e16</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AWS SysOps Administrator</t>
+          <t>CloudOps Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, IAM, RDS, DynamoDB, CI/CD</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,42 +1581,42 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1e9865761b44f05</t>
+          <t>https://www.indeed.com/viewjob?jk=61fe23b5a013d06d</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Site AI Engineer</t>
+          <t>CloudOps Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Temple, TX, US USA</t>
+          <t>Lakewood, CO, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9df42fb6f0e5b92</t>
+          <t>https://www.indeed.com/viewjob?jk=0590d6bb95b36919</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Yarmouth, ME, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=861e821c88461e16</t>
+          <t>https://www.indeed.com/viewjob?jk=e9c7752d42fa52c7</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CloudOps Engineer</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61fe23b5a013d06d</t>
+          <t>https://www.indeed.com/viewjob?jk=294c6d2addcb10cf</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CloudOps Engineer</t>
+          <t>AWS Technical Apprentice / Trainee</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Lakewood, CO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Databricks</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0590d6bb95b36919</t>
+          <t>https://www.indeed.com/viewjob?jk=2223f947ee98de60</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CloudOps Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>Client Resources, Inc.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Yarmouth, ME, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,24 +1746,24 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, GCP, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9c7752d42fa52c7</t>
+          <t>https://www.indeed.com/viewjob?jk=d1e155aced1efdff</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, IAM, RDS, Azure, Scala, NoSQL, Power BI, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=294c6d2addcb10cf</t>
+          <t>https://www.indeed.com/viewjob?jk=222a5b676c08f8f0</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AWS Technical Apprentice / Trainee</t>
+          <t>Senior Engineer - Agentic AI</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Databricks</t>
+          <t>AWS, Lambda, SQS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2223f947ee98de60</t>
+          <t>https://www.indeed.com/viewjob?jk=5daf8f72a4fd9ab6</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Client Resources, Inc.</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, GCP, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1e155aced1efdff</t>
+          <t>https://www.indeed.com/viewjob?jk=79a2a043dc5cdb8f</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, S3, IAM, Hadoop, Spark, Kafka, Snowflake, Splunk</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f01d239e5c828f6</t>
+          <t>https://www.indeed.com/viewjob?jk=e387db2c2b866baa</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, NoSQL, Power BI, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=222a5b676c08f8f0</t>
+          <t>https://www.indeed.com/viewjob?jk=18a022cbc2b4d934</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Engineer - Agentic AI</t>
+          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5daf8f72a4fd9ab6</t>
+          <t>https://www.indeed.com/viewjob?jk=5cc4f959dd712f8a</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer/SRE - GM Energy</t>
+          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Yonkers, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0413ce8de5fcca6a</t>
+          <t>https://www.indeed.com/viewjob?jk=688d7763683eecad</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
+          <t>Distinguished Engineer -</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, GCP, Snowflake, ELT, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,67 +2036,67 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79a2a043dc5cdb8f</t>
+          <t>https://www.indeed.com/viewjob?jk=087eb595cff7bd93</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
+          <t>Cloud Support Associate</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Snowflake, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e387db2c2b866baa</t>
+          <t>https://www.indeed.com/viewjob?jk=39dc124339eab650</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
+          <t>AI/ML Engineer – Data &amp; Full-Stack Solutions</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>ITC Federal</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,164 +2106,164 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18a022cbc2b4d934</t>
+          <t>https://www.indeed.com/viewjob?jk=ce30a23eaa64abcd</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
+          <t>Platform Architect</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Unity Catalog, Delta Live Tables, Google Cloud Platform, Spark, PySpark, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cc4f959dd712f8a</t>
+          <t>https://www.indeed.com/viewjob?jk=4c1348f2e47cd5d6</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
+          <t>Infrastructure Engineer (Cloud Focus)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Yonkers, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, Lambda, Kinesis, Redshift, S3, API Gateway, Scala, Kafka, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=688d7763683eecad</t>
+          <t>https://www.indeed.com/viewjob?jk=00e1f01fe85665ee</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Distinguished Engineer -</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, GCP, Snowflake, ELT, Splunk, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=087eb595cff7bd93</t>
+          <t>https://www.indeed.com/viewjob?jk=3c5b06678237c00c</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AWS Systems Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Smithfield, RI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Spark, Scala, Snowflake, Oracle, ETL, Jenkins, Maven</t>
+          <t>AWS, Glue, Lambda, Athena, S3, SQS, SNS, IAM, Spark, PySpark</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cc22367a2ce3d9f</t>
+          <t>https://www.indeed.com/viewjob?jk=e5e7a473ae9d0b96</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>AI/ML Engineer – Data &amp; Full-Stack Solutions</t>
+          <t>Software Development Engineer II</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ITC Federal</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, ETL, ELT, CI/CD</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce30a23eaa64abcd</t>
+          <t>https://www.indeed.com/viewjob?jk=c0d2f3586b2ed198</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Cloud Support Associate</t>
+          <t>Artificial Intelligence/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Snowflake, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39dc124339eab650</t>
+          <t>https://www.indeed.com/viewjob?jk=8f6f11467cb82584</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Platform Architect</t>
+          <t>Artificial Intelligence/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Unity Catalog, Delta Live Tables, Google Cloud Platform, Spark, PySpark, Oracle, Data Modeling</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c1348f2e47cd5d6</t>
+          <t>https://www.indeed.com/viewjob?jk=c9ce81a6707266dd</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer (Cloud Focus)</t>
+          <t>Artificial Intelligence/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Logic, Inc.</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, S3, API Gateway, Scala, Kafka, DynamoDB, Data Modeling</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00e1f01fe85665ee</t>
+          <t>https://www.indeed.com/viewjob?jk=e34c2e31eeb33f9e</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Quality Assurance Analyst / ETL Tester</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Briljent</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, DynamoDB, NoSQL</t>
+          <t>RDS, Azure, Snowflake, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c5b06678237c00c</t>
+          <t>https://www.indeed.com/viewjob?jk=d69b1256484e3a82</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AWS Systems Engineer</t>
+          <t>Cloud Operations Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>MITSUBISHI ELECTRIC ICONICS DIGITAL SOLUTIONS</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, SQS, SNS, IAM, Spark, PySpark</t>
+          <t>AWS, Lambda, S3, ECS, RDS, DynamoDB, CI/CD, AWS CodePipeline, CodeBuild, Terraform</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,67 +2456,67 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5e7a473ae9d0b96</t>
+          <t>https://www.indeed.com/viewjob?jk=67d1ed48d145a4f1</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0d2f3586b2ed198</t>
+          <t>https://www.indeed.com/viewjob?jk=77a528b43d8d11a1</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Quality Assurance Analyst / ETL Tester</t>
+          <t>Data Engineer - Performance Management</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Briljent</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Lake Buena Vista, FL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Snowflake, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL, Data Modeling, Snowflake Schema, ETL</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d69b1256484e3a82</t>
+          <t>https://www.indeed.com/viewjob?jk=b85eeb0fd5a3a862</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Artificial Intelligence/Machine Learning Data Engineer</t>
+          <t>Systems &amp; Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Kretek International</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Moorpark, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Splunk, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f6f11467cb82584</t>
+          <t>https://www.indeed.com/viewjob?jk=a7d7d86c5d6aef50</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Artificial Intelligence/Machine Learning Data Engineer</t>
+          <t>Data Engineer - Performance Management</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Lake Buena Vista, FL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9ce81a6707266dd</t>
+          <t>https://www.indeed.com/viewjob?jk=57b0af5961338ef2</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Artificial Intelligence/Machine Learning Data Engineer</t>
+          <t>Full Stack, Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Logic, Inc.</t>
+          <t>SCAN Health Plan</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e34c2e31eeb33f9e</t>
+          <t>https://www.indeed.com/viewjob?jk=6b0db4093988ff3c</t>
         </is>
       </c>
     </row>
@@ -2708,17 +2708,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Cloud Operations Engineer</t>
+          <t>Cloud Service Desk Analyst</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MITSUBISHI ELECTRIC ICONICS DIGITAL SOLUTIONS</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, DynamoDB, CI/CD, AWS CodePipeline, CodeBuild, Terraform</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67d1ed48d145a4f1</t>
+          <t>https://www.indeed.com/viewjob?jk=68f4f33bf88f7f89</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, ETL</t>
+          <t>RDS, Databricks, Scala, Snowflake, PostgreSQL, MySQL, Splunk, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77a528b43d8d11a1</t>
+          <t>https://www.indeed.com/viewjob?jk=1869e5a8847d426e</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer - Performance Management</t>
+          <t>AI/ML Developer II (Remote)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Lake Buena Vista, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,129 +2796,129 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, NoSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b85eeb0fd5a3a862</t>
+          <t>https://www.indeed.com/viewjob?jk=fb663396a5bc1b79</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Systems &amp; Cloud Infrastructure Engineer</t>
+          <t>Junior Cloud Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Kretek International</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Moorpark, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Splunk, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Spark, Kafka, Snowflake, Oracle, ETL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7d7d86c5d6aef50</t>
+          <t>https://www.indeed.com/viewjob?jk=8d85a7cfec698363</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer - Performance Management</t>
+          <t>Junior Cloud Networking Technician</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Lake Buena Vista, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57b0af5961338ef2</t>
+          <t>https://www.indeed.com/viewjob?jk=e73f6230be428620</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Full Stack, Data &amp; Analytics Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SCAN Health Plan</t>
+          <t>Axis Residential</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Spokane, WA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Kimball, ETL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b0db4093988ff3c</t>
+          <t>https://www.indeed.com/viewjob?jk=7970a51178c2d8ba</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Cloud Service Desk Analyst</t>
+          <t>Multi-Cloud Networking Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2932,11 +2932,11 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,89 +2946,89 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68f4f33bf88f7f89</t>
+          <t>https://www.indeed.com/viewjob?jk=5089f26e49e819d7</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>AI/ML Developer II (Remote)</t>
+          <t>Software Engineer II, Global Servicing Technology</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, NoSQL, ETL, ELT</t>
+          <t>AWS, RDS, Google Cloud Platform, Cloud Storage, Hive, Spark, Scala, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb663396a5bc1b79</t>
+          <t>https://www.indeed.com/viewjob?jk=5c5c9f5bf8d54b87</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Snowflake, PostgreSQL, MySQL, Splunk, CI/CD, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1869e5a8847d426e</t>
+          <t>https://www.indeed.com/viewjob?jk=d33e81401b69b22c</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Engineer II, Global Servicing Technology</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, Cloud Storage, Hive, Spark, Scala, ETL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c5c9f5bf8d54b87</t>
+          <t>https://www.indeed.com/viewjob?jk=ffcaa5c8b2e22e2b</t>
         </is>
       </c>
     </row>
@@ -3093,17 +3093,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Junior Cloud Engineer</t>
+          <t>Data Engineer, Go to Market (Remote)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Spark, Kafka, Snowflake, Oracle, ETL</t>
+          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d85a7cfec698363</t>
+          <t>https://www.indeed.com/viewjob?jk=8c7e11f90c05edfc</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Junior Cloud Networking Technician</t>
+          <t>Sr. Infrastructure &amp; Security Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>HerculesAI</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Campbell, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Lambda, IAM, Azure, GCP, Splunk, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e73f6230be428620</t>
+          <t>https://www.indeed.com/viewjob?jk=997e47a23e0d8261</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Software Engineer III - Data, AWS, ETL, Java/Python,</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Axis Residential</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Spokane, WA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Kimball, ETL</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7970a51178c2d8ba</t>
+          <t>https://www.indeed.com/viewjob?jk=24b2eb0df8c7e284</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Multi-Cloud Networking Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Cityblock Health</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, IAM, RDS, Azure, GCP, BigQuery, PostgreSQL, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5089f26e49e819d7</t>
+          <t>https://www.indeed.com/viewjob?jk=76d763c610ac1510</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Chess.com</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, RDS, GCP, Scala, MySQL, Cassandra, Data Modeling, ETL, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d33e81401b69b22c</t>
+          <t>https://www.indeed.com/viewjob?jk=a3d15713be3da1af</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Professional Services Consultant</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Ataccama</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffcaa5c8b2e22e2b</t>
+          <t>https://www.indeed.com/viewjob?jk=e7e7f81d2e0f0ce3</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Engineer, Go to Market (Remote)</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c7e11f90c05edfc</t>
+          <t>https://www.indeed.com/viewjob?jk=c5c449cb4c336ec2</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Sr. Infrastructure &amp; Security Engineer</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>HerculesAI</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Campbell, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, Azure, GCP, Splunk, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=997e47a23e0d8261</t>
+          <t>https://www.indeed.com/viewjob?jk=e57a91ca929fec5b</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data, AWS, ETL, Java/Python,</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, ETL, CI/CD, Terraform</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24b2eb0df8c7e284</t>
+          <t>https://www.indeed.com/viewjob?jk=cd22b6d5954a33c2</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Cityblock Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, BigQuery, PostgreSQL, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76d763c610ac1510</t>
+          <t>https://www.indeed.com/viewjob?jk=2d369f55f3c43cd0</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Professional Services Consultant</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Ataccama</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7e7f81d2e0f0ce3</t>
+          <t>https://www.indeed.com/viewjob?jk=b5e852e1fb093faa</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer- GM Energy</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, GCP, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51fb08298ca2e944</t>
+          <t>https://www.indeed.com/viewjob?jk=122021b0213972fb</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>SR DBA / DATABASE ARCHITECT (AZURE / MSSQL)</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Opeeka, Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Folsom, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Bitbucket</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d57af04f58fc4f3b</t>
+          <t>https://www.indeed.com/viewjob?jk=cf263b65906b30ba</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior DBA / Database Architect</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Opeeka, Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Folsom, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Bitbucket</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5142b758be4e8f87</t>
+          <t>https://www.indeed.com/viewjob?jk=775f4b74d2e0d125</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Application Developer</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Value Truck of Arizona</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>South Jordan, UT, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6c3e26366316cc8</t>
+          <t>https://www.indeed.com/viewjob?jk=e27aa2f30115d6a9</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5c449cb4c336ec2</t>
+          <t>https://www.indeed.com/viewjob?jk=372ffe4f2e9a605d</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e57a91ca929fec5b</t>
+          <t>https://www.indeed.com/viewjob?jk=a256a77103c9ee18</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd22b6d5954a33c2</t>
+          <t>https://www.indeed.com/viewjob?jk=9b082342159bbdf7</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d369f55f3c43cd0</t>
+          <t>https://www.indeed.com/viewjob?jk=e06cd5eb56a43b5c</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5e852e1fb093faa</t>
+          <t>https://www.indeed.com/viewjob?jk=daaeb6d16db98abf</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=122021b0213972fb</t>
+          <t>https://www.indeed.com/viewjob?jk=5d61083f86948477</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf263b65906b30ba</t>
+          <t>https://www.indeed.com/viewjob?jk=71d4be4e91f6174a</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=775f4b74d2e0d125</t>
+          <t>https://www.indeed.com/viewjob?jk=912b927f8e6b0bc9</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e27aa2f30115d6a9</t>
+          <t>https://www.indeed.com/viewjob?jk=697335a3240f02f2</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=372ffe4f2e9a605d</t>
+          <t>https://www.indeed.com/viewjob?jk=e21309c64f987c4d</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a256a77103c9ee18</t>
+          <t>https://www.indeed.com/viewjob?jk=6e4114c9ced06f08</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b082342159bbdf7</t>
+          <t>https://www.indeed.com/viewjob?jk=0379c77fb1bea285</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e06cd5eb56a43b5c</t>
+          <t>https://www.indeed.com/viewjob?jk=c7404f3dbf25b5d0</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daaeb6d16db98abf</t>
+          <t>https://www.indeed.com/viewjob?jk=19a128257d3c2c77</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d61083f86948477</t>
+          <t>https://www.indeed.com/viewjob?jk=6a667aa6f915c8e9</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71d4be4e91f6174a</t>
+          <t>https://www.indeed.com/viewjob?jk=8d47c2036fa69322</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=912b927f8e6b0bc9</t>
+          <t>https://www.indeed.com/viewjob?jk=591077de2df74cfa</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=697335a3240f02f2</t>
+          <t>https://www.indeed.com/viewjob?jk=8cc254c410ba6f38</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e21309c64f987c4d</t>
+          <t>https://www.indeed.com/viewjob?jk=12339d025b6d4b6f</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e4114c9ced06f08</t>
+          <t>https://www.indeed.com/viewjob?jk=dc7db42760d4627e</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0379c77fb1bea285</t>
+          <t>https://www.indeed.com/viewjob?jk=6c024ec8f500d28f</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7404f3dbf25b5d0</t>
+          <t>https://www.indeed.com/viewjob?jk=d5c090288e0e4f79</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19a128257d3c2c77</t>
+          <t>https://www.indeed.com/viewjob?jk=c400db066fcfe868</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a667aa6f915c8e9</t>
+          <t>https://www.indeed.com/viewjob?jk=e9857bbf535b2768</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>SR DBA / DATABASE ARCHITECT (AZURE / MSSQL)</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Opeeka, Inc.</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Folsom, CA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Bitbucket</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d47c2036fa69322</t>
+          <t>https://www.indeed.com/viewjob?jk=d57af04f58fc4f3b</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>Senior DBA / Database Architect</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Opeeka, Inc.</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Folsom, CA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Bitbucket</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=591077de2df74cfa</t>
+          <t>https://www.indeed.com/viewjob?jk=5142b758be4e8f87</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>Application Developer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Value Truck of Arizona</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>South Jordan, UT, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cc254c410ba6f38</t>
+          <t>https://www.indeed.com/viewjob?jk=f6c3e26366316cc8</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,209 +4581,209 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Splunk, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12339d025b6d4b6f</t>
+          <t>https://www.indeed.com/viewjob?jk=8ccb9cb736f9f8e0</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc7db42760d4627e</t>
+          <t>https://www.indeed.com/viewjob?jk=afb2f5fe2a396169</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>AWS Systems Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c024ec8f500d28f</t>
+          <t>https://www.indeed.com/viewjob?jk=119269e5158f89e8</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>Data Engineer (Snowflake, Teradata, DB2)</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Mutual of Omaha</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, Glue, RDS, Scala, Snowflake, SQL Server, MongoDB, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5c090288e0e4f79</t>
+          <t>https://www.indeed.com/viewjob?jk=aa9d2ce9f1b5528c</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, Terraform, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c400db066fcfe868</t>
+          <t>https://www.indeed.com/viewjob?jk=5f72c641c65b5a61</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>ObjectStream</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>RDS, Azure, Data Factory, Blob Storage, Spark, PySpark, ETL, dbt, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9857bbf535b2768</t>
+          <t>https://www.indeed.com/viewjob?jk=06e3854d22cdba89</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>MuleSoft QA Engineer</t>
+          <t>PySpark Data Engineer III - Python/Java/SQL</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>UniFirst</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,34 +4791,34 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a8b7edc3d29ab01</t>
+          <t>https://www.indeed.com/viewjob?jk=926547138e49a51b</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Databricks Data Engineer - Senior - Consulting - Location Open</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,34 +4826,34 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, Terraform, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, AKS</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f72c641c65b5a61</t>
+          <t>https://www.indeed.com/viewjob?jk=599253e2d33dc75f</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Software Engineer III – Python/PySpark/AWS</t>
+          <t>MuleSoft QA Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,34 +4861,34 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=991d5ceb2074b137</t>
+          <t>https://www.indeed.com/viewjob?jk=6a8b7edc3d29ab01</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>FSO LABS - AI Developer Senior - Bay Area</t>
+          <t>Software Engineer III – Python/PySpark/AWS</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,24 +4896,24 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Hive, Spark, Kafka, NoSQL, Power BI, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, RDS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d75a18fe3bc2126</t>
+          <t>https://www.indeed.com/viewjob?jk=991d5ceb2074b137</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer - Senior - Consulting - Location Open</t>
+          <t>FSO LABS - AI Developer Senior - Bay Area</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,34 +4931,34 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, AKS</t>
+          <t>RDS, Azure, Hadoop, Hive, Spark, Kafka, NoSQL, Power BI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=599253e2d33dc75f</t>
+          <t>https://www.indeed.com/viewjob?jk=1d75a18fe3bc2126</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>AWS Systems Engineer</t>
+          <t>MuleSoft Developer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, Oracle, SQL Server, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,19 +4976,19 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=119269e5158f89e8</t>
+          <t>https://www.indeed.com/viewjob?jk=7c7c89957751c232</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Data Engineer (Snowflake, Teradata, DB2)</t>
+          <t>MuleSoft Architect / Developer Remote (Part-Time / Full-Time) – US Client</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Mutual of Omaha</t>
+          <t>Bowery Software Inc</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Scala, Snowflake, SQL Server, MongoDB, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Oracle, ETL, Talend, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,24 +5011,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa9d2ce9f1b5528c</t>
+          <t>https://www.indeed.com/viewjob?jk=fe3a1e183165a854</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Infrastructure Solutions Architect</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>ObjectStream</t>
+          <t>Global Information Technology</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Blob Storage, Spark, PySpark, ETL, dbt, Airflow, Apache Airflow</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06e3854d22cdba89</t>
+          <t>https://www.indeed.com/viewjob?jk=94bea5b95ba94e24</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>PySpark Data Engineer III - Python/Java/SQL</t>
+          <t>Cloud Service Desk Analyst</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,34 +5071,34 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, ETL, ELT, dbt, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=926547138e49a51b</t>
+          <t>https://www.indeed.com/viewjob?jk=2781169a06fdef87</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Cloud Engineering &amp; FinOps</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,34 +5106,34 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d576082b1c56db5c</t>
+          <t>https://www.indeed.com/viewjob?jk=983d0a4b6df6a34b</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Cloud Service Desk Analyst</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, ETL, ELT, dbt, Airflow, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2781169a06fdef87</t>
+          <t>https://www.indeed.com/viewjob?jk=e39cfd742ca8ccb7</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>MuleSoft Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>UniFirst</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, Oracle, SQL Server, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c7c89957751c232</t>
+          <t>https://www.indeed.com/viewjob?jk=4d24b9bb7d3f81d1</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>MuleSoft Architect / Developer Remote (Part-Time / Full-Time) – US Client</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Bowery Software Inc</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Oracle, ETL, Talend, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe3a1e183165a854</t>
+          <t>https://www.indeed.com/viewjob?jk=406f01e6594b2624</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Infrastructure Solutions Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Global Information Technology</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94bea5b95ba94e24</t>
+          <t>https://www.indeed.com/viewjob?jk=0206f3baae13d0ec</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Full‑Stack Developer (Java, React, Microservices) *Hybrid*</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,24 +5281,24 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afb2f5fe2a396169</t>
+          <t>https://www.indeed.com/viewjob?jk=229f6840535c3531</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full‑Stack Developer (Java, React, Microservices) *Hybrid*</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,24 +5316,24 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=983d0a4b6df6a34b</t>
+          <t>https://www.indeed.com/viewjob?jk=606324c85c044a5d</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Smyrna, GA, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,24 +5351,24 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e39cfd742ca8ccb7</t>
+          <t>https://www.indeed.com/viewjob?jk=ef040d1b01903853</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full‑Stack Developer (Java, React, Microservices) *Hybrid*</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,34 +5386,34 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d24b9bb7d3f81d1</t>
+          <t>https://www.indeed.com/viewjob?jk=0f298bb4ddf8e9a0</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Douglas Machine Inc.</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Alexandria, MN, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,225 +5421,15 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=406f01e6594b2624</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D144" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0206f3baae13d0ec</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Full‑Stack Developer (Java, React, Microservices) *Hybrid*</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D145" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=229f6840535c3531</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>Full‑Stack Developer (Java, React, Microservices) *Hybrid*</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D146" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=606324c85c044a5d</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Smyrna, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D147" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ef040d1b01903853</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Full‑Stack Developer (Java, React, Microservices) *Hybrid*</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D148" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0f298bb4ddf8e9a0</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>Senior Business Intelligence Developer</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>Douglas Machine Inc.</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>Alexandria, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D149" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=f9d5d216fe71b48e</t>
         </is>

--- a/results/job_matches_2026-05-01.xlsx
+++ b/results/job_matches_2026-05-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G143"/>
+  <dimension ref="A1:G150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,52 +608,52 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Technical Architect-Datawarehousing</t>
+          <t>Senior Software Engineer (C#/.NET &amp; AI)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Marlborough, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10720f22d9d38621</t>
+          <t>https://www.indeed.com/viewjob?jk=93c21b258a08bd24</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (C#/.NET &amp; AI)</t>
+          <t>Sr Software Engineer II - Enterprise Architecture</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,42 +661,42 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93c21b258a08bd24</t>
+          <t>https://www.indeed.com/viewjob?jk=f6bd0f139eec27a7</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr Software Engineer II - Enterprise Architecture</t>
+          <t>Cloud Engineer II</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Vibrant Emotional Health</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,42 +706,42 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6bd0f139eec27a7</t>
+          <t>https://www.indeed.com/viewjob?jk=3ba39b2a6826c32d</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Cloud Engineer II</t>
+          <t>Sr Associate Engineer/ Engineer, IT Data</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Vibrant Emotional Health</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, Snowflake, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ba39b2a6826c32d</t>
+          <t>https://www.indeed.com/viewjob?jk=9512ecb083976839</t>
         </is>
       </c>
     </row>
@@ -993,17 +993,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Topgolf</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, Hadoop, Spark, Scala</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, GCP, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc5cd30ba1545c61</t>
+          <t>https://www.indeed.com/viewjob?jk=5bd117f5a8f07cd9</t>
         </is>
       </c>
     </row>
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6622c031669892fa</t>
+          <t>https://www.indeed.com/viewjob?jk=dc5cd30ba1545c61</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer II _ Big Data, GCP _EDAI</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d725c4b26e048534</t>
+          <t>https://www.indeed.com/viewjob?jk=6622c031669892fa</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Data Engineer II _ Big Data, GCP _EDAI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>JUUL Labs</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, GCP, Dataflow, Cloud Storage, Scala, Splunk</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c63edb85327f9aef</t>
+          <t>https://www.indeed.com/viewjob?jk=d725c4b26e048534</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JUUL Labs</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, Snowflake, SQL Server, MySQL, ELT</t>
+          <t>AWS, S3, ECS, IAM, RDS, GCP, Dataflow, Cloud Storage, Scala, Splunk</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de10d304d09880c3</t>
+          <t>https://www.indeed.com/viewjob?jk=c63edb85327f9aef</t>
         </is>
       </c>
     </row>
@@ -1378,17 +1378,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Dev Ops Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SkyWater Technology Foundry</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Photon, GCP, Vertex AI, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13bfee40249f3478</t>
+          <t>https://www.indeed.com/viewjob?jk=1b74032a04cfaa28</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Business Intelligence Solutions Architect</t>
+          <t>Senior Dev Ops Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Mars Technominds</t>
+          <t>SkyWater Technology Foundry</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
+          <t>AWS, IAM, RDS, Photon, GCP, Vertex AI, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38246f1a187f1c7d</t>
+          <t>https://www.indeed.com/viewjob?jk=13bfee40249f3478</t>
         </is>
       </c>
     </row>
@@ -1483,17 +1483,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Site AI Engineer</t>
+          <t>IT Full Stack Developer, Commercial</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>ConocoPhillips</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Temple, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,52 +1501,52 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9df42fb6f0e5b92</t>
+          <t>https://www.indeed.com/viewjob?jk=b4afc29839d7e8be</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CloudOps Engineer</t>
+          <t>Site AI Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Temple, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=861e821c88461e16</t>
+          <t>https://www.indeed.com/viewjob?jk=b9df42fb6f0e5b92</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61fe23b5a013d06d</t>
+          <t>https://www.indeed.com/viewjob?jk=861e821c88461e16</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Lakewood, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0590d6bb95b36919</t>
+          <t>https://www.indeed.com/viewjob?jk=61fe23b5a013d06d</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Yarmouth, ME, US USA</t>
+          <t>Lakewood, CO, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9c7752d42fa52c7</t>
+          <t>https://www.indeed.com/viewjob?jk=0590d6bb95b36919</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>CloudOps Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Yarmouth, ME, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,14 +1686,14 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=294c6d2addcb10cf</t>
+          <t>https://www.indeed.com/viewjob?jk=e9c7752d42fa52c7</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AWS Technical Apprentice / Trainee</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Databricks</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2223f947ee98de60</t>
+          <t>https://www.indeed.com/viewjob?jk=294c6d2addcb10cf</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>AWS Technical Apprentice / Trainee</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Client Resources, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, GCP, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Databricks</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1e155aced1efdff</t>
+          <t>https://www.indeed.com/viewjob?jk=2223f947ee98de60</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Client Resources, Inc.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, NoSQL, Power BI, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, GCP, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=222a5b676c08f8f0</t>
+          <t>https://www.indeed.com/viewjob?jk=d1e155aced1efdff</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Engineer - Agentic AI</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Scala, NoSQL, Power BI, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5daf8f72a4fd9ab6</t>
+          <t>https://www.indeed.com/viewjob?jk=222a5b676c08f8f0</t>
         </is>
       </c>
     </row>
@@ -2113,17 +2113,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Platform Architect</t>
+          <t>Senior Data Scientist-Data &amp; Personalization Platform (Hybrid)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Rewards Network</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>City of Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Unity Catalog, Delta Live Tables, Google Cloud Platform, Spark, PySpark, Oracle, Data Modeling</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Scala, Kafka, Kafka Connect, PostgreSQL, dbt</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,14 +2141,14 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c1348f2e47cd5d6</t>
+          <t>https://www.indeed.com/viewjob?jk=b4582e40d2734ff3</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer (Cloud Focus)</t>
+          <t>Platform Architect</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, S3, API Gateway, Scala, Kafka, DynamoDB, Data Modeling</t>
+          <t>AWS, RDS, Azure, Unity Catalog, Delta Live Tables, Google Cloud Platform, Spark, PySpark, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,14 +2176,14 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00e1f01fe85665ee</t>
+          <t>https://www.indeed.com/viewjob?jk=4c1348f2e47cd5d6</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Infrastructure Engineer (Cloud Focus)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, DynamoDB, NoSQL</t>
+          <t>AWS, Lambda, Kinesis, Redshift, S3, API Gateway, Scala, Kafka, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c5b06678237c00c</t>
+          <t>https://www.indeed.com/viewjob?jk=00e1f01fe85665ee</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AWS Systems Engineer</t>
+          <t>Senior Data Scientist-Intelligent Assignment Engine (Hybrid)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Rewards Network</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, SQS, SNS, IAM, Spark, PySpark</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Scala, Kafka, Kafka Connect, PostgreSQL, dbt</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5e7a473ae9d0b96</t>
+          <t>https://www.indeed.com/viewjob?jk=28f4e0d1d3bbb168</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>Senior Data Scientist-Intelligent Assignment Engine (Hybrid)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Rewards Network</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>City of Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Scala, Kafka, Kafka Connect, PostgreSQL, dbt</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0d2f3586b2ed198</t>
+          <t>https://www.indeed.com/viewjob?jk=e0c5d2be8683ada1</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Artificial Intelligence/Machine Learning Data Engineer</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f6f11467cb82584</t>
+          <t>https://www.indeed.com/viewjob?jk=3c5b06678237c00c</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Artificial Intelligence/Machine Learning Data Engineer</t>
+          <t>AWS Systems Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow</t>
+          <t>AWS, Glue, Lambda, Athena, S3, SQS, SNS, IAM, Spark, PySpark</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9ce81a6707266dd</t>
+          <t>https://www.indeed.com/viewjob?jk=e5e7a473ae9d0b96</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Artificial Intelligence/Machine Learning Data Engineer</t>
+          <t>Software Development Engineer II</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Logic, Inc.</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e34c2e31eeb33f9e</t>
+          <t>https://www.indeed.com/viewjob?jk=c0d2f3586b2ed198</t>
         </is>
       </c>
     </row>
@@ -2428,122 +2428,122 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Cloud Operations Engineer</t>
+          <t>Artificial Intelligence/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>MITSUBISHI ELECTRIC ICONICS DIGITAL SOLUTIONS</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, DynamoDB, CI/CD, AWS CodePipeline, CodeBuild, Terraform</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67d1ed48d145a4f1</t>
+          <t>https://www.indeed.com/viewjob?jk=8f6f11467cb82584</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Artificial Intelligence/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, ETL</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77a528b43d8d11a1</t>
+          <t>https://www.indeed.com/viewjob?jk=c9ce81a6707266dd</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer - Performance Management</t>
+          <t>Artificial Intelligence/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>Logic, Inc.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Lake Buena Vista, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b85eeb0fd5a3a862</t>
+          <t>https://www.indeed.com/viewjob?jk=e34c2e31eeb33f9e</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Systems &amp; Cloud Infrastructure Engineer</t>
+          <t>Junior AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Kretek International</t>
+          <t>FuelCloud</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Moorpark, CA, US USA</t>
+          <t>Hillsboro, OR, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Splunk, Terraform</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, MySQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7d7d86c5d6aef50</t>
+          <t>https://www.indeed.com/viewjob?jk=05b0071381abb003</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer - Performance Management</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Lake Buena Vista, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, NoSQL, ELT, dbt, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57b0af5961338ef2</t>
+          <t>https://www.indeed.com/viewjob?jk=3c8001067fa855e4</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Full Stack, Data &amp; Analytics Engineer</t>
+          <t>Cloud Operations Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SCAN Health Plan</t>
+          <t>MITSUBISHI ELECTRIC ICONICS DIGITAL SOLUTIONS</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, S3, ECS, RDS, DynamoDB, CI/CD, AWS CodePipeline, CodeBuild, Terraform</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b0db4093988ff3c</t>
+          <t>https://www.indeed.com/viewjob?jk=67d1ed48d145a4f1</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Cloud Migration Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, API Gateway, ECS, RDS, Google Cloud Platform, Vertex AI, MySQL, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93321e0d50904658</t>
+          <t>https://www.indeed.com/viewjob?jk=77a528b43d8d11a1</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (Remote)</t>
+          <t>Data Engineer - Performance Management</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Lake Buena Vista, FL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, NoSQL, CI/CD, Git, Python, SQL</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdbdb16275078800</t>
+          <t>https://www.indeed.com/viewjob?jk=b85eeb0fd5a3a862</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Cloud Service Desk Analyst</t>
+          <t>Systems &amp; Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Kretek International</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Moorpark, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Splunk, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68f4f33bf88f7f89</t>
+          <t>https://www.indeed.com/viewjob?jk=a7d7d86c5d6aef50</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Data Engineer - Performance Management</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Lake Buena Vista, FL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Snowflake, PostgreSQL, MySQL, Splunk, CI/CD, Terraform, Kubernetes</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1869e5a8847d426e</t>
+          <t>https://www.indeed.com/viewjob?jk=57b0af5961338ef2</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>AI/ML Developer II (Remote)</t>
+          <t>Senior Cloud Migration Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,24 +2796,24 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, NoSQL, ETL, ELT</t>
+          <t>AWS, Lambda, SQS, API Gateway, ECS, RDS, Google Cloud Platform, Vertex AI, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb663396a5bc1b79</t>
+          <t>https://www.indeed.com/viewjob?jk=93321e0d50904658</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Junior Cloud Engineer</t>
+          <t>Cloud Service Desk Analyst</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2827,11 +2827,11 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Spark, Kafka, Snowflake, Oracle, ETL</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d85a7cfec698363</t>
+          <t>https://www.indeed.com/viewjob?jk=68f4f33bf88f7f89</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Junior Cloud Networking Technician</t>
+          <t>#Software Engineer – Senior Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e73f6230be428620</t>
+          <t>https://www.indeed.com/viewjob?jk=d197023697dc7b83</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>AI/ML Engineer - Work</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Axis Residential</t>
+          <t>Cengage</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spokane, WA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Kimball, ETL</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, MLflow, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7970a51178c2d8ba</t>
+          <t>https://www.indeed.com/viewjob?jk=e76fea76e5582b6f</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Multi-Cloud Networking Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Databricks, Scala, Snowflake, PostgreSQL, MySQL, Splunk, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5089f26e49e819d7</t>
+          <t>https://www.indeed.com/viewjob?jk=1869e5a8847d426e</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Engineer II, Global Servicing Technology</t>
+          <t>Junior Cloud Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, Cloud Storage, Hive, Spark, Scala, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Spark, Kafka, Snowflake, Oracle, ETL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c5c9f5bf8d54b87</t>
+          <t>https://www.indeed.com/viewjob?jk=8d85a7cfec698363</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Junior Cloud Networking Technician</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d33e81401b69b22c</t>
+          <t>https://www.indeed.com/viewjob?jk=e73f6230be428620</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Axis Residential</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Spokane, WA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Kimball, ETL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffcaa5c8b2e22e2b</t>
+          <t>https://www.indeed.com/viewjob?jk=7970a51178c2d8ba</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Multi-Cloud Networking Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Accompany Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Glue, Spark, Scala, Kafka, NoSQL, Data Modeling, Terraform, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f41df6bde69aeb07</t>
+          <t>https://www.indeed.com/viewjob?jk=5089f26e49e819d7</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Engineer, Go to Market (Remote)</t>
+          <t>Software Engineer II, Global Servicing Technology</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
+          <t>AWS, RDS, Google Cloud Platform, Cloud Storage, Hive, Spark, Scala, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c7e11f90c05edfc</t>
+          <t>https://www.indeed.com/viewjob?jk=5c5c9f5bf8d54b87</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Sr. Infrastructure &amp; Security Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>HerculesAI</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Campbell, CA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, Azure, GCP, Splunk, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=997e47a23e0d8261</t>
+          <t>https://www.indeed.com/viewjob?jk=d33e81401b69b22c</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data, AWS, ETL, Java/Python,</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, ETL, CI/CD, Terraform</t>
+          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24b2eb0df8c7e284</t>
+          <t>https://www.indeed.com/viewjob?jk=ffcaa5c8b2e22e2b</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Cityblock Health</t>
+          <t>Accompany Health</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, BigQuery, PostgreSQL, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Spark, Scala, Kafka, NoSQL, Data Modeling, Terraform, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76d763c610ac1510</t>
+          <t>https://www.indeed.com/viewjob?jk=f41df6bde69aeb07</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Data Engineer, Go to Market (Remote)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Chess.com</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, MySQL, Cassandra, Data Modeling, ETL, Terraform, Kubernetes</t>
+          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3d15713be3da1af</t>
+          <t>https://www.indeed.com/viewjob?jk=8c7e11f90c05edfc</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Professional Services Consultant</t>
+          <t>Sr. Infrastructure &amp; Security Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Ataccama</t>
+          <t>HerculesAI</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Campbell, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Lambda, IAM, Azure, GCP, Splunk, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7e7f81d2e0f0ce3</t>
+          <t>https://www.indeed.com/viewjob?jk=997e47a23e0d8261</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>Sr SDET - Workplace Services Engineering</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, RDS, GCP, Oracle, MongoDB, Data Modeling, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5c449cb4c336ec2</t>
+          <t>https://www.indeed.com/viewjob?jk=5c8b2a5bb6a25233</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, S3, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e57a91ca929fec5b</t>
+          <t>https://www.indeed.com/viewjob?jk=9715b780e8194a46</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>Professional Services Consultant</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Ataccama</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd22b6d5954a33c2</t>
+          <t>https://www.indeed.com/viewjob?jk=e7e7f81d2e0f0ce3</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>#Software Engineer – Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, S3, RDS, Azure, SQL Server, Data Modeling, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d369f55f3c43cd0</t>
+          <t>https://www.indeed.com/viewjob?jk=65ee9e3af0d95deb</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>AI Automation Engineer, Finance &amp; Accounting</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Cengage</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, PostgreSQL, AKS, Git</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5e852e1fb093faa</t>
+          <t>https://www.indeed.com/viewjob?jk=6fc4b4b5640d9b20</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>SR DBA / DATABASE ARCHITECT (AZURE / MSSQL)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Opeeka, Inc.</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Folsom, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Bitbucket</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=122021b0213972fb</t>
+          <t>https://www.indeed.com/viewjob?jk=d57af04f58fc4f3b</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>Senior DBA / Database Architect</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Opeeka, Inc.</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Folsom, CA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Bitbucket</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf263b65906b30ba</t>
+          <t>https://www.indeed.com/viewjob?jk=5142b758be4e8f87</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>Application Developer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Value Truck of Arizona</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>South Jordan, UT, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=775f4b74d2e0d125</t>
+          <t>https://www.indeed.com/viewjob?jk=f6c3e26366316cc8</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e27aa2f30115d6a9</t>
+          <t>https://www.indeed.com/viewjob?jk=c5c449cb4c336ec2</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=372ffe4f2e9a605d</t>
+          <t>https://www.indeed.com/viewjob?jk=e57a91ca929fec5b</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a256a77103c9ee18</t>
+          <t>https://www.indeed.com/viewjob?jk=cd22b6d5954a33c2</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b082342159bbdf7</t>
+          <t>https://www.indeed.com/viewjob?jk=2d369f55f3c43cd0</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e06cd5eb56a43b5c</t>
+          <t>https://www.indeed.com/viewjob?jk=b5e852e1fb093faa</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daaeb6d16db98abf</t>
+          <t>https://www.indeed.com/viewjob?jk=122021b0213972fb</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d61083f86948477</t>
+          <t>https://www.indeed.com/viewjob?jk=cf263b65906b30ba</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71d4be4e91f6174a</t>
+          <t>https://www.indeed.com/viewjob?jk=775f4b74d2e0d125</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=912b927f8e6b0bc9</t>
+          <t>https://www.indeed.com/viewjob?jk=e27aa2f30115d6a9</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=697335a3240f02f2</t>
+          <t>https://www.indeed.com/viewjob?jk=372ffe4f2e9a605d</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e21309c64f987c4d</t>
+          <t>https://www.indeed.com/viewjob?jk=a256a77103c9ee18</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e4114c9ced06f08</t>
+          <t>https://www.indeed.com/viewjob?jk=9b082342159bbdf7</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0379c77fb1bea285</t>
+          <t>https://www.indeed.com/viewjob?jk=e06cd5eb56a43b5c</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7404f3dbf25b5d0</t>
+          <t>https://www.indeed.com/viewjob?jk=daaeb6d16db98abf</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19a128257d3c2c77</t>
+          <t>https://www.indeed.com/viewjob?jk=5d61083f86948477</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a667aa6f915c8e9</t>
+          <t>https://www.indeed.com/viewjob?jk=71d4be4e91f6174a</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d47c2036fa69322</t>
+          <t>https://www.indeed.com/viewjob?jk=912b927f8e6b0bc9</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=591077de2df74cfa</t>
+          <t>https://www.indeed.com/viewjob?jk=697335a3240f02f2</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cc254c410ba6f38</t>
+          <t>https://www.indeed.com/viewjob?jk=e21309c64f987c4d</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12339d025b6d4b6f</t>
+          <t>https://www.indeed.com/viewjob?jk=6e4114c9ced06f08</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc7db42760d4627e</t>
+          <t>https://www.indeed.com/viewjob?jk=0379c77fb1bea285</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c024ec8f500d28f</t>
+          <t>https://www.indeed.com/viewjob?jk=c7404f3dbf25b5d0</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5c090288e0e4f79</t>
+          <t>https://www.indeed.com/viewjob?jk=19a128257d3c2c77</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c400db066fcfe868</t>
+          <t>https://www.indeed.com/viewjob?jk=6a667aa6f915c8e9</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9857bbf535b2768</t>
+          <t>https://www.indeed.com/viewjob?jk=8d47c2036fa69322</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>SR DBA / DATABASE ARCHITECT (AZURE / MSSQL)</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Opeeka, Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Folsom, CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Bitbucket</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d57af04f58fc4f3b</t>
+          <t>https://www.indeed.com/viewjob?jk=591077de2df74cfa</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior DBA / Database Architect</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Opeeka, Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Folsom, CA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Bitbucket</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5142b758be4e8f87</t>
+          <t>https://www.indeed.com/viewjob?jk=8cc254c410ba6f38</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Application Developer</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Value Truck of Arizona</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>South Jordan, UT, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6c3e26366316cc8</t>
+          <t>https://www.indeed.com/viewjob?jk=12339d025b6d4b6f</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,29 +4581,29 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Splunk, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ccb9cb736f9f8e0</t>
+          <t>https://www.indeed.com/viewjob?jk=dc7db42760d4627e</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4612,151 +4612,151 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afb2f5fe2a396169</t>
+          <t>https://www.indeed.com/viewjob?jk=6c024ec8f500d28f</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>AWS Systems Engineer</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Scala, CI/CD, Terraform</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=119269e5158f89e8</t>
+          <t>https://www.indeed.com/viewjob?jk=d5c090288e0e4f79</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Data Engineer (Snowflake, Teradata, DB2)</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Mutual of Omaha</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Scala, Snowflake, SQL Server, MongoDB, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa9d2ce9f1b5528c</t>
+          <t>https://www.indeed.com/viewjob?jk=c400db066fcfe868</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, Terraform, Airflow, Apache Airflow</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f72c641c65b5a61</t>
+          <t>https://www.indeed.com/viewjob?jk=e9857bbf535b2768</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>ObjectStream</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Blob Storage, Spark, PySpark, ETL, dbt, Airflow, Apache Airflow</t>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Splunk, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06e3854d22cdba89</t>
+          <t>https://www.indeed.com/viewjob?jk=8ccb9cb736f9f8e0</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>PySpark Data Engineer III - Python/Java/SQL</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,34 +4791,34 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>RDS, Hadoop, Hive, HBase, Spark, Scala, MySQL, NoSQL, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=926547138e49a51b</t>
+          <t>https://www.indeed.com/viewjob?jk=e151f8f8376a065d</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer - Senior - Consulting - Location Open</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,34 +4826,34 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, AKS</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=599253e2d33dc75f</t>
+          <t>https://www.indeed.com/viewjob?jk=afb2f5fe2a396169</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>MuleSoft QA Engineer</t>
+          <t>AWS Systems Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>UniFirst</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a8b7edc3d29ab01</t>
+          <t>https://www.indeed.com/viewjob?jk=119269e5158f89e8</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Software Engineer III – Python/PySpark/AWS</t>
+          <t>Data Engineer (Snowflake, Teradata, DB2)</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Mutual of Omaha</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,34 +4896,34 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Glue, RDS, Scala, Snowflake, SQL Server, MongoDB, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=991d5ceb2074b137</t>
+          <t>https://www.indeed.com/viewjob?jk=aa9d2ce9f1b5528c</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>FSO LABS - AI Developer Senior - Bay Area</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,34 +4931,34 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Hive, Spark, Kafka, NoSQL, Power BI, Docker, Kubernetes</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, Terraform, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d75a18fe3bc2126</t>
+          <t>https://www.indeed.com/viewjob?jk=5f72c641c65b5a61</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>MuleSoft Developer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>UniFirst</t>
+          <t>ObjectStream</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, Oracle, SQL Server, NoSQL, Splunk, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Blob Storage, Spark, PySpark, ETL, dbt, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c7c89957751c232</t>
+          <t>https://www.indeed.com/viewjob?jk=06e3854d22cdba89</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>MuleSoft Architect / Developer Remote (Part-Time / Full-Time) – US Client</t>
+          <t>Databricks Data Engineer - Senior - Consulting - Location Open</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Bowery Software Inc</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,34 +5001,34 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Oracle, ETL, Talend, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, AKS</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe3a1e183165a854</t>
+          <t>https://www.indeed.com/viewjob?jk=599253e2d33dc75f</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Infrastructure Solutions Architect</t>
+          <t>MuleSoft QA Engineer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Global Information Technology</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94bea5b95ba94e24</t>
+          <t>https://www.indeed.com/viewjob?jk=6a8b7edc3d29ab01</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Cloud Service Desk Analyst</t>
+          <t>FSO LABS - AI Developer Senior - Bay Area</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,34 +5071,34 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, ETL, ELT, dbt, Airflow, Git, Python</t>
+          <t>RDS, Azure, Hadoop, Hive, Spark, Kafka, NoSQL, Power BI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2781169a06fdef87</t>
+          <t>https://www.indeed.com/viewjob?jk=1d75a18fe3bc2126</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Southwest Airlines</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, IAM, RDS, Scala, SQL Server, CI/CD</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=983d0a4b6df6a34b</t>
+          <t>https://www.indeed.com/viewjob?jk=042c9624648e5202</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior DevSecOps Architect</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Dragonfli Group LLC</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e39cfd742ca8ccb7</t>
+          <t>https://www.indeed.com/viewjob?jk=c0e0643fbf1288ad</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Principle AI &amp; Data Scientist</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Alignment Healthcare</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, MLOps, MLflow, Git, Python</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d24b9bb7d3f81d1</t>
+          <t>https://www.indeed.com/viewjob?jk=f42f8cc79a272b87</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>MuleSoft Developer</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, Oracle, SQL Server, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=406f01e6594b2624</t>
+          <t>https://www.indeed.com/viewjob?jk=7c7c89957751c232</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>MuleSoft Architect / Developer Remote (Part-Time / Full-Time) – US Client</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Bowery Software Inc</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Oracle, ETL, Talend, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0206f3baae13d0ec</t>
+          <t>https://www.indeed.com/viewjob?jk=fe3a1e183165a854</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Full‑Stack Developer (Java, React, Microservices) *Hybrid*</t>
+          <t>Infrastructure Solutions Architect</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Global Information Technology</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,34 +5281,34 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=229f6840535c3531</t>
+          <t>https://www.indeed.com/viewjob?jk=94bea5b95ba94e24</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Full‑Stack Developer (Java, React, Microservices) *Hybrid*</t>
+          <t>Senior SDET</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>CyberArk</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,34 +5316,34 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606324c85c044a5d</t>
+          <t>https://www.indeed.com/viewjob?jk=5322d19f930d0670</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
+          <t>Cloud Service Desk Analyst</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Smyrna, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,24 +5351,24 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, ETL, ELT, dbt, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef040d1b01903853</t>
+          <t>https://www.indeed.com/viewjob?jk=2781169a06fdef87</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Full‑Stack Developer (Java, React, Microservices) *Hybrid*</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,34 +5386,34 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f298bb4ddf8e9a0</t>
+          <t>https://www.indeed.com/viewjob?jk=983d0a4b6df6a34b</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Douglas Machine Inc.</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Alexandria, MN, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,17 +5421,262 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9d5d216fe71b48e</t>
+          <t>https://www.indeed.com/viewjob?jk=e39cfd742ca8ccb7</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4d24b9bb7d3f81d1</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=406f01e6594b2624</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0206f3baae13d0ec</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Full‑Stack Developer (Java, React, Microservices) *Hybrid*</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=229f6840535c3531</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Full‑Stack Developer (Java, React, Microservices) *Hybrid*</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=606324c85c044a5d</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Smyrna, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ef040d1b01903853</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Full‑Stack Developer (Java, React, Microservices) *Hybrid*</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0f298bb4ddf8e9a0</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-01.xlsx
+++ b/results/job_matches_2026-05-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G150"/>
+  <dimension ref="A1:G127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,17 +538,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Linstarsolution corporation</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Ridgefield Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,42 +556,42 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Dataflow, Spark, Scala, Kafka, NoSQL, Data Modeling, ELT</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49b6a92728349bc5</t>
+          <t>https://www.indeed.com/viewjob?jk=3825710140df8183</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Software Engineer (C#/.NET &amp; AI)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Linstarsolution corporation</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ridgefield Park, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>19.4</v>
+        <v>18.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, Data Modeling, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3825710140df8183</t>
+          <t>https://www.indeed.com/viewjob?jk=93c21b258a08bd24</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (C#/.NET &amp; AI)</t>
+          <t>Sr Software Engineer II - Enterprise Architecture</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,42 +626,42 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93c21b258a08bd24</t>
+          <t>https://www.indeed.com/viewjob?jk=f6bd0f139eec27a7</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr Software Engineer II - Enterprise Architecture</t>
+          <t>Cloud Engineer II</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Vibrant Emotional Health</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6bd0f139eec27a7</t>
+          <t>https://www.indeed.com/viewjob?jk=3ba39b2a6826c32d</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cloud Engineer II</t>
+          <t>Senior Engineer - AI &amp; Data Management</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Vibrant Emotional Health</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins</t>
+          <t>S3, Azure, Data Factory, Cloud Storage, Hadoop, HDFS, Spark, Scala, Kafka, Informatica PowerCenter</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ba39b2a6826c32d</t>
+          <t>https://www.indeed.com/viewjob?jk=0f98760c842e5085</t>
         </is>
       </c>
     </row>
@@ -783,52 +783,52 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Engineer - AI &amp; Data Management</t>
+          <t>SRE/Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Sign In Solutions</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>S3, Azure, Data Factory, Cloud Storage, Hadoop, HDFS, Spark, Scala, Kafka, Informatica PowerCenter</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f98760c842e5085</t>
+          <t>https://www.indeed.com/viewjob?jk=78107cea029977e8</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SRE/Engineer</t>
+          <t>Kubernetes Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sign In Solutions</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, Splunk, CI/CD</t>
+          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Azure, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,42 +846,42 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78107cea029977e8</t>
+          <t>https://www.indeed.com/viewjob?jk=5f09eaf9518abf0e</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Kubernetes Engineer</t>
+          <t>Azure Data &amp; Development Architect</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SunStone Consulting</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Azure, Scala, Snowflake, Oracle</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Event Hubs, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f09eaf9518abf0e</t>
+          <t>https://www.indeed.com/viewjob?jk=1e9052cac6c7210d</t>
         </is>
       </c>
     </row>
@@ -958,17 +958,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Azure Data &amp; Development Architect</t>
+          <t>Senior Professional Services Sales Solutions Architect</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SunStone Consulting</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Event Hubs, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e9052cac6c7210d</t>
+          <t>https://www.indeed.com/viewjob?jk=aad68ba091ed0805</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Topgolf</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, GCP, Scala, Data Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bd117f5a8f07cd9</t>
+          <t>https://www.indeed.com/viewjob?jk=dc5cd30ba1545c61</t>
         </is>
       </c>
     </row>
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc5cd30ba1545c61</t>
+          <t>https://www.indeed.com/viewjob?jk=6622c031669892fa</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Data Engineer II _ Big Data, GCP _EDAI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, Hadoop, Spark, Scala</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6622c031669892fa</t>
+          <t>https://www.indeed.com/viewjob?jk=d725c4b26e048534</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer II _ Big Data, GCP _EDAI</t>
+          <t>Dev Ops Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>innoVet Health, LLC</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, Data Modeling, dbt, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Scala, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d725c4b26e048534</t>
+          <t>https://www.indeed.com/viewjob?jk=4d7bdd0c563a121a</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>JUUL Labs</t>
+          <t>Topgolf</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,17 +1151,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, GCP, Dataflow, Cloud Storage, Scala, Splunk</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, GCP, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c63edb85327f9aef</t>
+          <t>https://www.indeed.com/viewjob?jk=5bd117f5a8f07cd9</t>
         </is>
       </c>
     </row>
@@ -1378,17 +1378,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Senior Dev Ops Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>SkyWater Technology Foundry</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Snowflake, SQL Server</t>
+          <t>AWS, IAM, RDS, Photon, GCP, Vertex AI, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b74032a04cfaa28</t>
+          <t>https://www.indeed.com/viewjob?jk=13bfee40249f3478</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Dev Ops Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SkyWater Technology Foundry</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Photon, GCP, Vertex AI, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13bfee40249f3478</t>
+          <t>https://www.indeed.com/viewjob?jk=1b74032a04cfaa28</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AWS SysOps Administrator</t>
+          <t>IT Full Stack Developer, Commercial</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ConocoPhillips</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, IAM, RDS, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1e9865761b44f05</t>
+          <t>https://www.indeed.com/viewjob?jk=b4afc29839d7e8be</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>IT Full Stack Developer, Commercial</t>
+          <t>Site AI Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ConocoPhillips</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Temple, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,52 +1501,52 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, PostgreSQL, MongoDB</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4afc29839d7e8be</t>
+          <t>https://www.indeed.com/viewjob?jk=b9df42fb6f0e5b92</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Site AI Engineer</t>
+          <t>CloudOps Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Temple, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9df42fb6f0e5b92</t>
+          <t>https://www.indeed.com/viewjob?jk=861e821c88461e16</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=861e821c88461e16</t>
+          <t>https://www.indeed.com/viewjob?jk=61fe23b5a013d06d</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Lakewood, CO, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61fe23b5a013d06d</t>
+          <t>https://www.indeed.com/viewjob?jk=0590d6bb95b36919</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Lakewood, CO, US USA</t>
+          <t>Yarmouth, ME, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0590d6bb95b36919</t>
+          <t>https://www.indeed.com/viewjob?jk=e9c7752d42fa52c7</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CloudOps Engineer</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Yarmouth, ME, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,14 +1686,14 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9c7752d42fa52c7</t>
+          <t>https://www.indeed.com/viewjob?jk=294c6d2addcb10cf</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>AWS Technical Apprentice / Trainee</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Databricks</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=294c6d2addcb10cf</t>
+          <t>https://www.indeed.com/viewjob?jk=2223f947ee98de60</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AWS Technical Apprentice / Trainee</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Client Resources, Inc.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Databricks</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, GCP, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2223f947ee98de60</t>
+          <t>https://www.indeed.com/viewjob?jk=d1e155aced1efdff</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Full-Stack Software Engineer (On-Site)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Client Resources, Inc.</t>
+          <t>PTI</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, GCP, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, DynamoDB, NoSQL, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1e155aced1efdff</t>
+          <t>https://www.indeed.com/viewjob?jk=959a027d133a3e5f</t>
         </is>
       </c>
     </row>
@@ -1833,25 +1833,25 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
+          <t>AI/ML Engineer – Data &amp; Full-Stack Solutions</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>ITC Federal</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,172 +1861,172 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79a2a043dc5cdb8f</t>
+          <t>https://www.indeed.com/viewjob?jk=ce30a23eaa64abcd</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
+          <t>Cloud Support Associate</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Snowflake, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e387db2c2b866baa</t>
+          <t>https://www.indeed.com/viewjob?jk=39dc124339eab650</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
+          <t>AWS Systems Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Athena, S3, SQS, SNS, IAM, Spark, PySpark</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18a022cbc2b4d934</t>
+          <t>https://www.indeed.com/viewjob?jk=e5e7a473ae9d0b96</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
+          <t>DevOps/AI Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>MITRE</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, Azure, GCP, Scala, MySQL, MongoDB, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cc4f959dd712f8a</t>
+          <t>https://www.indeed.com/viewjob?jk=8dd360cfdc686b9a</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
+          <t>Platform Architect</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Yonkers, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Unity Catalog, Delta Live Tables, Google Cloud Platform, Spark, PySpark, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=688d7763683eecad</t>
+          <t>https://www.indeed.com/viewjob?jk=4c1348f2e47cd5d6</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Distinguished Engineer -</t>
+          <t>Software Development Engineer II</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, GCP, Snowflake, ELT, Splunk, CI/CD</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=087eb595cff7bd93</t>
+          <t>https://www.indeed.com/viewjob?jk=c0d2f3586b2ed198</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Cloud Support Associate</t>
+          <t>Quality Assurance Analyst / ETL Tester</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Briljent</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Snowflake, MLOps, CI/CD, Terraform</t>
+          <t>RDS, Azure, Snowflake, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39dc124339eab650</t>
+          <t>https://www.indeed.com/viewjob?jk=d69b1256484e3a82</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>AI/ML Engineer – Data &amp; Full-Stack Solutions</t>
+          <t>Artificial Intelligence/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ITC Federal</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, ETL, ELT, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce30a23eaa64abcd</t>
+          <t>https://www.indeed.com/viewjob?jk=8f6f11467cb82584</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Scientist-Data &amp; Personalization Platform (Hybrid)</t>
+          <t>Artificial Intelligence/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Rewards Network</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>City of Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,24 +2131,24 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Scala, Kafka, Kafka Connect, PostgreSQL, dbt</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4582e40d2734ff3</t>
+          <t>https://www.indeed.com/viewjob?jk=c9ce81a6707266dd</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Platform Architect</t>
+          <t>Senior Cloud Migration Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2162,11 +2162,11 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Unity Catalog, Delta Live Tables, Google Cloud Platform, Spark, PySpark, Oracle, Data Modeling</t>
+          <t>AWS, Lambda, SQS, API Gateway, ECS, RDS, Google Cloud Platform, Vertex AI, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c1348f2e47cd5d6</t>
+          <t>https://www.indeed.com/viewjob?jk=93321e0d50904658</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer (Cloud Focus)</t>
+          <t>Junior AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>FuelCloud</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Hillsboro, OR, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, S3, API Gateway, Scala, Kafka, DynamoDB, Data Modeling</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, MySQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00e1f01fe85665ee</t>
+          <t>https://www.indeed.com/viewjob?jk=05b0071381abb003</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Scientist-Intelligent Assignment Engine (Hybrid)</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Rewards Network</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Scala, Kafka, Kafka Connect, PostgreSQL, dbt</t>
+          <t>AWS, RDS, Scala, Snowflake, NoSQL, ELT, dbt, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28f4e0d1d3bbb168</t>
+          <t>https://www.indeed.com/viewjob?jk=3c8001067fa855e4</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Scientist-Intelligent Assignment Engine (Hybrid)</t>
+          <t>Cloud Operations Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Rewards Network</t>
+          <t>MITSUBISHI ELECTRIC ICONICS DIGITAL SOLUTIONS</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>City of Chicago, IL, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Scala, Kafka, Kafka Connect, PostgreSQL, dbt</t>
+          <t>AWS, Lambda, S3, ECS, RDS, DynamoDB, CI/CD, AWS CodePipeline, CodeBuild, Terraform</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0c5d2be8683ada1</t>
+          <t>https://www.indeed.com/viewjob?jk=67d1ed48d145a4f1</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, DynamoDB, NoSQL</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c5b06678237c00c</t>
+          <t>https://www.indeed.com/viewjob?jk=77a528b43d8d11a1</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AWS Systems Engineer</t>
+          <t>Data Engineer - Performance Management</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Lake Buena Vista, FL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, SQS, SNS, IAM, Spark, PySpark</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5e7a473ae9d0b96</t>
+          <t>https://www.indeed.com/viewjob?jk=b85eeb0fd5a3a862</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>Systems &amp; Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Kretek International</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Moorpark, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Splunk, Terraform</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,164 +2386,164 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0d2f3586b2ed198</t>
+          <t>https://www.indeed.com/viewjob?jk=a7d7d86c5d6aef50</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Quality Assurance Analyst / ETL Tester</t>
+          <t>Senior Software Engineer — Data Platform &amp; MAI</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Briljent</t>
+          <t>Uniphore</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Snowflake, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL, Data Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d69b1256484e3a82</t>
+          <t>https://www.indeed.com/viewjob?jk=0ad11f3ec32fe272</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Artificial Intelligence/Machine Learning Data Engineer</t>
+          <t>#Software Engineer – Senior Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f6f11467cb82584</t>
+          <t>https://www.indeed.com/viewjob?jk=d197023697dc7b83</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Artificial Intelligence/Machine Learning Data Engineer</t>
+          <t>Cloud Service Desk Analyst</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9ce81a6707266dd</t>
+          <t>https://www.indeed.com/viewjob?jk=68f4f33bf88f7f89</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence/Machine Learning Data Engineer</t>
+          <t>Snowflake/Tableau Developer / Dallas Texas</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Logic, Inc.</t>
+          <t>FirstNet Global</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Napa, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e34c2e31eeb33f9e</t>
+          <t>https://www.indeed.com/viewjob?jk=6515eadf095c7486</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Junior AWS Cloud Engineer</t>
+          <t>AI/ML Engineer - Work</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>FuelCloud</t>
+          <t>Cengage</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Hillsboro, OR, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, MySQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, MLflow, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05b0071381abb003</t>
+          <t>https://www.indeed.com/viewjob?jk=e76fea76e5582b6f</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, NoSQL, ELT, dbt, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Databricks, Scala, Snowflake, PostgreSQL, MySQL, Splunk, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c8001067fa855e4</t>
+          <t>https://www.indeed.com/viewjob?jk=1869e5a8847d426e</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Cloud Operations Engineer</t>
+          <t>Software Engineer II, Global Servicing Technology</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>MITSUBISHI ELECTRIC ICONICS DIGITAL SOLUTIONS</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, DynamoDB, CI/CD, AWS CodePipeline, CodeBuild, Terraform</t>
+          <t>AWS, RDS, Google Cloud Platform, Cloud Storage, Hive, Spark, Scala, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,67 +2631,67 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67d1ed48d145a4f1</t>
+          <t>https://www.indeed.com/viewjob?jk=5c5c9f5bf8d54b87</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>Accompany Health</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, ETL</t>
+          <t>AWS, Glue, Spark, Scala, Kafka, NoSQL, Data Modeling, Terraform, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77a528b43d8d11a1</t>
+          <t>https://www.indeed.com/viewjob?jk=f41df6bde69aeb07</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer - Performance Management</t>
+          <t>Junior Cloud Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Lake Buena Vista, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Spark, Kafka, Snowflake, Oracle, ETL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,84 +2701,84 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b85eeb0fd5a3a862</t>
+          <t>https://www.indeed.com/viewjob?jk=8d85a7cfec698363</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Systems &amp; Cloud Infrastructure Engineer</t>
+          <t>Junior Cloud Networking Technician</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Kretek International</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Moorpark, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Splunk, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7d7d86c5d6aef50</t>
+          <t>https://www.indeed.com/viewjob?jk=e73f6230be428620</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer - Performance Management</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>Axis Residential</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Lake Buena Vista, FL, US USA</t>
+          <t>Spokane, WA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Kimball, ETL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57b0af5961338ef2</t>
+          <t>https://www.indeed.com/viewjob?jk=7970a51178c2d8ba</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Cloud Migration Engineer</t>
+          <t>Multi-Cloud Networking Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2792,11 +2792,11 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, API Gateway, ECS, RDS, Google Cloud Platform, Vertex AI, MySQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,164 +2806,164 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93321e0d50904658</t>
+          <t>https://www.indeed.com/viewjob?jk=5089f26e49e819d7</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Cloud Service Desk Analyst</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68f4f33bf88f7f89</t>
+          <t>https://www.indeed.com/viewjob?jk=d33e81401b69b22c</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>#Software Engineer – Senior Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d197023697dc7b83</t>
+          <t>https://www.indeed.com/viewjob?jk=ffcaa5c8b2e22e2b</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>AI/ML Engineer - Work</t>
+          <t>Data Engineer, Go to Market (Remote)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Cengage</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, MLflow, CI/CD, GitHub Actions, Terraform</t>
+          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e76fea76e5582b6f</t>
+          <t>https://www.indeed.com/viewjob?jk=8c7e11f90c05edfc</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Sr. Infrastructure &amp; Security Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>HerculesAI</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Campbell, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Snowflake, PostgreSQL, MySQL, Splunk, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, IAM, Azure, GCP, Splunk, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1869e5a8847d426e</t>
+          <t>https://www.indeed.com/viewjob?jk=997e47a23e0d8261</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Junior Cloud Engineer</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Spark, Kafka, Snowflake, Oracle, ETL</t>
+          <t>AWS, S3, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d85a7cfec698363</t>
+          <t>https://www.indeed.com/viewjob?jk=62599143d69ab642</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Junior Cloud Networking Technician</t>
+          <t>#Software Engineer – Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, S3, RDS, Azure, SQL Server, Data Modeling, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e73f6230be428620</t>
+          <t>https://www.indeed.com/viewjob?jk=65ee9e3af0d95deb</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Professional Services Consultant</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Axis Residential</t>
+          <t>Ataccama</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spokane, WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Kimball, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7970a51178c2d8ba</t>
+          <t>https://www.indeed.com/viewjob?jk=e7e7f81d2e0f0ce3</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Multi-Cloud Networking Engineer</t>
+          <t>SR DBA / DATABASE ARCHITECT (AZURE / MSSQL)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Opeeka, Inc.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Folsom, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Bitbucket</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5089f26e49e819d7</t>
+          <t>https://www.indeed.com/viewjob?jk=d57af04f58fc4f3b</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Software Engineer II, Global Servicing Technology</t>
+          <t>Senior DBA / Database Architect</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Opeeka, Inc.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Folsom, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, Cloud Storage, Hive, Spark, Scala, ETL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Bitbucket</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c5c9f5bf8d54b87</t>
+          <t>https://www.indeed.com/viewjob?jk=5142b758be4e8f87</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Application Developer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Value Truck of Arizona</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>South Jordan, UT, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d33e81401b69b22c</t>
+          <t>https://www.indeed.com/viewjob?jk=f6c3e26366316cc8</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Automation Engineer, Finance &amp; Accounting</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Cengage</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, PostgreSQL, AKS, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffcaa5c8b2e22e2b</t>
+          <t>https://www.indeed.com/viewjob?jk=6fc4b4b5640d9b20</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Accompany Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Glue, Spark, Scala, Kafka, NoSQL, Data Modeling, Terraform, Airflow, Apache Airflow</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f41df6bde69aeb07</t>
+          <t>https://www.indeed.com/viewjob?jk=c5c449cb4c336ec2</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Engineer, Go to Market (Remote)</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c7e11f90c05edfc</t>
+          <t>https://www.indeed.com/viewjob?jk=e57a91ca929fec5b</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Sr. Infrastructure &amp; Security Engineer</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>HerculesAI</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Campbell, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, Azure, GCP, Splunk, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=997e47a23e0d8261</t>
+          <t>https://www.indeed.com/viewjob?jk=cd22b6d5954a33c2</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Sr SDET - Workplace Services Engineering</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Oracle, MongoDB, Data Modeling, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c8b2a5bb6a25233</t>
+          <t>https://www.indeed.com/viewjob?jk=2d369f55f3c43cd0</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Dimensional Modeling, ETL</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9715b780e8194a46</t>
+          <t>https://www.indeed.com/viewjob?jk=b5e852e1fb093faa</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Professional Services Consultant</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Ataccama</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7e7f81d2e0f0ce3</t>
+          <t>https://www.indeed.com/viewjob?jk=122021b0213972fb</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>#Software Engineer – Engineer</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, SQL Server, Data Modeling, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65ee9e3af0d95deb</t>
+          <t>https://www.indeed.com/viewjob?jk=cf263b65906b30ba</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>AI Automation Engineer, Finance &amp; Accounting</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Cengage</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, PostgreSQL, AKS, Git</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fc4b4b5640d9b20</t>
+          <t>https://www.indeed.com/viewjob?jk=775f4b74d2e0d125</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>SR DBA / DATABASE ARCHITECT (AZURE / MSSQL)</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Opeeka, Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Folsom, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Bitbucket</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d57af04f58fc4f3b</t>
+          <t>https://www.indeed.com/viewjob?jk=e27aa2f30115d6a9</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior DBA / Database Architect</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Opeeka, Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Folsom, CA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Bitbucket</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5142b758be4e8f87</t>
+          <t>https://www.indeed.com/viewjob?jk=372ffe4f2e9a605d</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Application Developer</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Value Truck of Arizona</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>South Jordan, UT, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6c3e26366316cc8</t>
+          <t>https://www.indeed.com/viewjob?jk=a256a77103c9ee18</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5c449cb4c336ec2</t>
+          <t>https://www.indeed.com/viewjob?jk=9b082342159bbdf7</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e57a91ca929fec5b</t>
+          <t>https://www.indeed.com/viewjob?jk=e06cd5eb56a43b5c</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd22b6d5954a33c2</t>
+          <t>https://www.indeed.com/viewjob?jk=daaeb6d16db98abf</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d369f55f3c43cd0</t>
+          <t>https://www.indeed.com/viewjob?jk=5d61083f86948477</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5e852e1fb093faa</t>
+          <t>https://www.indeed.com/viewjob?jk=71d4be4e91f6174a</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=122021b0213972fb</t>
+          <t>https://www.indeed.com/viewjob?jk=912b927f8e6b0bc9</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf263b65906b30ba</t>
+          <t>https://www.indeed.com/viewjob?jk=697335a3240f02f2</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=775f4b74d2e0d125</t>
+          <t>https://www.indeed.com/viewjob?jk=e21309c64f987c4d</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e27aa2f30115d6a9</t>
+          <t>https://www.indeed.com/viewjob?jk=6e4114c9ced06f08</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=372ffe4f2e9a605d</t>
+          <t>https://www.indeed.com/viewjob?jk=0379c77fb1bea285</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a256a77103c9ee18</t>
+          <t>https://www.indeed.com/viewjob?jk=c7404f3dbf25b5d0</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b082342159bbdf7</t>
+          <t>https://www.indeed.com/viewjob?jk=19a128257d3c2c77</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e06cd5eb56a43b5c</t>
+          <t>https://www.indeed.com/viewjob?jk=6a667aa6f915c8e9</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daaeb6d16db98abf</t>
+          <t>https://www.indeed.com/viewjob?jk=8d47c2036fa69322</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d61083f86948477</t>
+          <t>https://www.indeed.com/viewjob?jk=591077de2df74cfa</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71d4be4e91f6174a</t>
+          <t>https://www.indeed.com/viewjob?jk=8cc254c410ba6f38</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=912b927f8e6b0bc9</t>
+          <t>https://www.indeed.com/viewjob?jk=12339d025b6d4b6f</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=697335a3240f02f2</t>
+          <t>https://www.indeed.com/viewjob?jk=dc7db42760d4627e</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e21309c64f987c4d</t>
+          <t>https://www.indeed.com/viewjob?jk=6c024ec8f500d28f</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e4114c9ced06f08</t>
+          <t>https://www.indeed.com/viewjob?jk=d5c090288e0e4f79</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0379c77fb1bea285</t>
+          <t>https://www.indeed.com/viewjob?jk=c400db066fcfe868</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,417 +4346,417 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7404f3dbf25b5d0</t>
+          <t>https://www.indeed.com/viewjob?jk=e9857bbf535b2768</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>RDS, Hadoop, Hive, HBase, Spark, Scala, MySQL, NoSQL, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19a128257d3c2c77</t>
+          <t>https://www.indeed.com/viewjob?jk=e151f8f8376a065d</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>MuleSoft QA Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a667aa6f915c8e9</t>
+          <t>https://www.indeed.com/viewjob?jk=6a8b7edc3d29ab01</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, Terraform, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d47c2036fa69322</t>
+          <t>https://www.indeed.com/viewjob?jk=5f72c641c65b5a61</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>FSO LABS - AI Developer Senior - Bay Area</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>RDS, Azure, Hadoop, Hive, Spark, Kafka, NoSQL, Power BI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=591077de2df74cfa</t>
+          <t>https://www.indeed.com/viewjob?jk=1d75a18fe3bc2126</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>Databricks Data Engineer - Senior - Consulting - Location Open</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, AKS</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cc254c410ba6f38</t>
+          <t>https://www.indeed.com/viewjob?jk=599253e2d33dc75f</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12339d025b6d4b6f</t>
+          <t>https://www.indeed.com/viewjob?jk=afb2f5fe2a396169</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>AWS Systems Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc7db42760d4627e</t>
+          <t>https://www.indeed.com/viewjob?jk=119269e5158f89e8</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>Data Engineer (Snowflake, Teradata, DB2)</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Mutual of Omaha</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, Glue, RDS, Scala, Snowflake, SQL Server, MongoDB, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c024ec8f500d28f</t>
+          <t>https://www.indeed.com/viewjob?jk=aa9d2ce9f1b5528c</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>ObjectStream</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>RDS, Azure, Data Factory, Blob Storage, Spark, PySpark, ETL, dbt, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5c090288e0e4f79</t>
+          <t>https://www.indeed.com/viewjob?jk=06e3854d22cdba89</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c400db066fcfe868</t>
+          <t>https://www.indeed.com/viewjob?jk=983d0a4b6df6a34b</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9857bbf535b2768</t>
+          <t>https://www.indeed.com/viewjob?jk=e39cfd742ca8ccb7</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Splunk, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ccb9cb736f9f8e0</t>
+          <t>https://www.indeed.com/viewjob?jk=4d24b9bb7d3f81d1</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, HBase, Spark, Scala, MySQL, NoSQL, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e151f8f8376a065d</t>
+          <t>https://www.indeed.com/viewjob?jk=406f01e6594b2624</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afb2f5fe2a396169</t>
+          <t>https://www.indeed.com/viewjob?jk=0206f3baae13d0ec</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>AWS Systems Engineer</t>
+          <t>MuleSoft Architect / Developer Remote (Part-Time / Full-Time) – US Client</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bowery Software Inc</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Scala, CI/CD, Terraform</t>
+          <t>AWS, Azure, GCP, Oracle, ETL, Talend, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,812 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=119269e5158f89e8</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Data Engineer (Snowflake, Teradata, DB2)</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Mutual of Omaha</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>AWS, Glue, RDS, Scala, Snowflake, SQL Server, MongoDB, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=aa9d2ce9f1b5528c</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Wells Fargo</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, Terraform, Airflow, Apache Airflow</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5f72c641c65b5a61</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>Sr. Data Engineer</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>ObjectStream</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Oklahoma City, OK, US USA</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Blob Storage, Spark, PySpark, ETL, dbt, Airflow, Apache Airflow</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=06e3854d22cdba89</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>Databricks Data Engineer - Senior - Consulting - Location Open</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>EY</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D131" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, AKS</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=599253e2d33dc75f</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>MuleSoft QA Engineer</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>UniFirst</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Wilmington, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D132" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6a8b7edc3d29ab01</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>FSO LABS - AI Developer Senior - Bay Area</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>EY</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D133" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Hadoop, Hive, Spark, Kafka, NoSQL, Power BI, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1d75a18fe3bc2126</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Southwest Airlines</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D134" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, IAM, RDS, Scala, SQL Server, CI/CD</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=042c9624648e5202</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Senior DevSecOps Architect</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>Dragonfli Group LLC</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D135" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c0e0643fbf1288ad</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>Principle AI &amp; Data Scientist</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>Alignment Healthcare</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Orange, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D136" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, MLOps, MLflow, Git, Python</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f42f8cc79a272b87</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>MuleSoft Developer</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>UniFirst</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Wilmington, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D137" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, Oracle, SQL Server, NoSQL, Splunk, CI/CD</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7c7c89957751c232</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>MuleSoft Architect / Developer Remote (Part-Time / Full-Time) – US Client</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>Bowery Software Inc</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D138" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Oracle, ETL, Talend, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=fe3a1e183165a854</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>Infrastructure Solutions Architect</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>Global Information Technology</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Lansing, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D139" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, CI/CD, Jenkins, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=94bea5b95ba94e24</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>Senior SDET</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>CyberArk</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D140" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5322d19f930d0670</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>Cloud Service Desk Analyst</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D141" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, ETL, ELT, dbt, Airflow, Git, Python</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2781169a06fdef87</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D142" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=983d0a4b6df6a34b</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D143" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e39cfd742ca8ccb7</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D144" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4d24b9bb7d3f81d1</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D145" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=406f01e6594b2624</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D146" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0206f3baae13d0ec</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Full‑Stack Developer (Java, React, Microservices) *Hybrid*</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D147" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=229f6840535c3531</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Full‑Stack Developer (Java, React, Microservices) *Hybrid*</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D148" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=606324c85c044a5d</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>Smyrna, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D149" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ef040d1b01903853</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>Full‑Stack Developer (Java, React, Microservices) *Hybrid*</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D150" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0f298bb4ddf8e9a0</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-01.xlsx
+++ b/results/job_matches_2026-05-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G127"/>
+  <dimension ref="A1:G125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -783,17 +783,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SRE/Engineer</t>
+          <t>Senior Data Engineer, Solutions Architecture</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sign In Solutions</t>
+          <t>Clearway Energy</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, Splunk, CI/CD</t>
+          <t>AWS, S3, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78107cea029977e8</t>
+          <t>https://www.indeed.com/viewjob?jk=3112f4731f8647ad</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Kubernetes Engineer</t>
+          <t>Senior Data Engineer, Solutions Architecture</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Clearway Energy</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Azure, Scala, Snowflake, Oracle</t>
+          <t>AWS, S3, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,67 +846,67 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f09eaf9518abf0e</t>
+          <t>https://www.indeed.com/viewjob?jk=bb476f597eb7b458</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Azure Data &amp; Development Architect</t>
+          <t>Senior Data Engineer, Solutions Architecture</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SunStone Consulting</t>
+          <t>Clearway Energy</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Event Hubs, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, S3, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e9052cac6c7210d</t>
+          <t>https://www.indeed.com/viewjob?jk=d082d61c4f4a5b69</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Java Compliance &amp; Governance Developer</t>
+          <t>SRE/Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Sign In Solutions</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,59 +916,59 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8078bc6f1fdb2e7b</t>
+          <t>https://www.indeed.com/viewjob?jk=78107cea029977e8</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Kubernetes Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ABCorp NA Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Azure, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e06fd43e0f99777</t>
+          <t>https://www.indeed.com/viewjob?jk=5f09eaf9518abf0e</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Professional Services Sales Solutions Architect</t>
+          <t>Java Compliance &amp; Governance Developer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
+          <t>IAM, RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,67 +986,67 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aad68ba091ed0805</t>
+          <t>https://www.indeed.com/viewjob?jk=8078bc6f1fdb2e7b</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ABCorp NA Inc.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, Hadoop, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc5cd30ba1545c61</t>
+          <t>https://www.indeed.com/viewjob?jk=1e06fd43e0f99777</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Professional Services Sales Solutions Architect</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, Hadoop, Spark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6622c031669892fa</t>
+          <t>https://www.indeed.com/viewjob?jk=aad68ba091ed0805</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer II _ Big Data, GCP _EDAI</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d725c4b26e048534</t>
+          <t>https://www.indeed.com/viewjob?jk=dc5cd30ba1545c61</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Dev Ops Data Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>innoVet Health, LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Scala, Oracle, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d7bdd0c563a121a</t>
+          <t>https://www.indeed.com/viewjob?jk=6622c031669892fa</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer II _ Big Data, GCP _EDAI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Topgolf</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, GCP, Scala, Data Modeling</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bd117f5a8f07cd9</t>
+          <t>https://www.indeed.com/viewjob?jk=d725c4b26e048534</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Platform Architect</t>
+          <t>Dev Ops Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>innoVet Health, LLC</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Google Cloud Platform, Spark, PySpark</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Scala, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ff622ef0e6ac90d</t>
+          <t>https://www.indeed.com/viewjob?jk=4d7bdd0c563a121a</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Junior Cloud Automation Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Topgolf</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Google Cloud Platform, Spark, PySpark</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, GCP, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,14 +1231,14 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86ef316bc56e1d98</t>
+          <t>https://www.indeed.com/viewjob?jk=5bd117f5a8f07cd9</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Platform Architect</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Scala, DynamoDB</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Google Cloud Platform, Spark, PySpark</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=200956ef0d629800</t>
+          <t>https://www.indeed.com/viewjob?jk=0ff622ef0e6ac90d</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer Seniors – Cloud Technologies | Fintech | Full Stack</t>
+          <t>Junior Cloud Automation Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FIS</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Oracle, SQL Server, NoSQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Google Cloud Platform, Spark, PySpark</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d35fe7a7c554f8b5</t>
+          <t>https://www.indeed.com/viewjob?jk=86ef316bc56e1d98</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Matillion</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95bbbaf8fbe8db68</t>
+          <t>https://www.indeed.com/viewjob?jk=200956ef0d629800</t>
         </is>
       </c>
     </row>
@@ -1371,59 +1371,59 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c7ffe9dfedc9c5d</t>
+          <t>https://www.indeed.com/viewjob?jk=95bbbaf8fbe8db68</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Dev Ops Engineer</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SkyWater Technology Foundry</t>
+          <t>Matillion</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Photon, GCP, Vertex AI, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13bfee40249f3478</t>
+          <t>https://www.indeed.com/viewjob?jk=2c7ffe9dfedc9c5d</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Alignment Healthcare</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Snowflake, SQL Server</t>
+          <t>AWS, Redshift, S3, Azure, Data Factory, GCP, Hadoop, Hive, HBase, Spark</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b74032a04cfaa28</t>
+          <t>https://www.indeed.com/viewjob?jk=b4cf4da858734131</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>IT Full Stack Developer, Commercial</t>
+          <t>Senior Dev Ops Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ConocoPhillips</t>
+          <t>SkyWater Technology Foundry</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, PostgreSQL, MongoDB</t>
+          <t>AWS, IAM, RDS, Photon, GCP, Vertex AI, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4afc29839d7e8be</t>
+          <t>https://www.indeed.com/viewjob?jk=13bfee40249f3478</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Site AI Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Temple, TX, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,42 +1501,42 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9df42fb6f0e5b92</t>
+          <t>https://www.indeed.com/viewjob?jk=1b74032a04cfaa28</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CloudOps Engineer</t>
+          <t>IT Full Stack Developer, Commercial</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>ConocoPhillips</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,42 +1546,42 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=861e821c88461e16</t>
+          <t>https://www.indeed.com/viewjob?jk=b4afc29839d7e8be</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CloudOps Engineer</t>
+          <t>Site AI Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Temple, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61fe23b5a013d06d</t>
+          <t>https://www.indeed.com/viewjob?jk=b9df42fb6f0e5b92</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Lakewood, CO, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0590d6bb95b36919</t>
+          <t>https://www.indeed.com/viewjob?jk=861e821c88461e16</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Yarmouth, ME, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9c7752d42fa52c7</t>
+          <t>https://www.indeed.com/viewjob?jk=61fe23b5a013d06d</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>CloudOps Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Lakewood, CO, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=294c6d2addcb10cf</t>
+          <t>https://www.indeed.com/viewjob?jk=0590d6bb95b36919</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AWS Technical Apprentice / Trainee</t>
+          <t>CloudOps Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Yarmouth, ME, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Databricks</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2223f947ee98de60</t>
+          <t>https://www.indeed.com/viewjob?jk=e9c7752d42fa52c7</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Client Resources, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, GCP, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1e155aced1efdff</t>
+          <t>https://www.indeed.com/viewjob?jk=294c6d2addcb10cf</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Full-Stack Software Engineer (On-Site)</t>
+          <t>AWS Technical Apprentice / Trainee</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>PTI</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, DynamoDB, NoSQL, ELT</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Databricks</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=959a027d133a3e5f</t>
+          <t>https://www.indeed.com/viewjob?jk=2223f947ee98de60</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Client Resources, Inc.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,59 +1816,59 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, NoSQL, Power BI, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, GCP, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=222a5b676c08f8f0</t>
+          <t>https://www.indeed.com/viewjob?jk=d1e155aced1efdff</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AI/ML Engineer – Data &amp; Full-Stack Solutions</t>
+          <t>Full-Stack Software Engineer (On-Site)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ITC Federal</t>
+          <t>PTI</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, DynamoDB, NoSQL, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce30a23eaa64abcd</t>
+          <t>https://www.indeed.com/viewjob?jk=959a027d133a3e5f</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Cloud Support Associate</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1882,11 +1882,11 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Snowflake, MLOps, CI/CD, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, Scala, NoSQL, Power BI, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39dc124339eab650</t>
+          <t>https://www.indeed.com/viewjob?jk=222a5b676c08f8f0</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AWS Systems Engineer</t>
+          <t>AI/ML Engineer – Data &amp; Full-Stack Solutions</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ITC Federal</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, SQS, SNS, IAM, Spark, PySpark</t>
+          <t>AWS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5e7a473ae9d0b96</t>
+          <t>https://www.indeed.com/viewjob?jk=ce30a23eaa64abcd</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>DevOps/AI Engineer</t>
+          <t>Cloud Support Associate</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>MITRE</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MySQL, MongoDB, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Snowflake, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8dd360cfdc686b9a</t>
+          <t>https://www.indeed.com/viewjob?jk=39dc124339eab650</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Platform Architect</t>
+          <t>Senior Applied AI Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Paramount</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Unity Catalog, Delta Live Tables, Google Cloud Platform, Spark, PySpark, Oracle, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c1348f2e47cd5d6</t>
+          <t>https://www.indeed.com/viewjob?jk=f086cee5e98c30b6</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>AWS Systems Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, Glue, Lambda, Athena, S3, SQS, SNS, IAM, Spark, PySpark</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0d2f3586b2ed198</t>
+          <t>https://www.indeed.com/viewjob?jk=e5e7a473ae9d0b96</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Quality Assurance Analyst / ETL Tester</t>
+          <t>DevOps/AI Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Briljent</t>
+          <t>MITRE</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Snowflake, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL, Data Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, Azure, GCP, Scala, MySQL, MongoDB, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d69b1256484e3a82</t>
+          <t>https://www.indeed.com/viewjob?jk=8dd360cfdc686b9a</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Artificial Intelligence/Machine Learning Data Engineer</t>
+          <t>Platform Architect</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow</t>
+          <t>AWS, RDS, Azure, Unity Catalog, Delta Live Tables, Google Cloud Platform, Spark, PySpark, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f6f11467cb82584</t>
+          <t>https://www.indeed.com/viewjob?jk=4c1348f2e47cd5d6</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Artificial Intelligence/Machine Learning Data Engineer</t>
+          <t>Quality Assurance Analyst / ETL Tester</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Briljent</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,104 +2131,104 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow</t>
+          <t>RDS, Azure, Snowflake, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9ce81a6707266dd</t>
+          <t>https://www.indeed.com/viewjob?jk=d69b1256484e3a82</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Cloud Migration Engineer</t>
+          <t>Artificial Intelligence/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, API Gateway, ECS, RDS, Google Cloud Platform, Vertex AI, MySQL, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93321e0d50904658</t>
+          <t>https://www.indeed.com/viewjob?jk=8f6f11467cb82584</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Junior AWS Cloud Engineer</t>
+          <t>Artificial Intelligence/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>FuelCloud</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Hillsboro, OR, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, MySQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05b0071381abb003</t>
+          <t>https://www.indeed.com/viewjob?jk=c9ce81a6707266dd</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Senior Cloud Migration Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, NoSQL, ELT, dbt, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, SQS, API Gateway, ECS, RDS, Google Cloud Platform, Vertex AI, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c8001067fa855e4</t>
+          <t>https://www.indeed.com/viewjob?jk=93321e0d50904658</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Cloud Operations Engineer</t>
+          <t>Junior AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>MITSUBISHI ELECTRIC ICONICS DIGITAL SOLUTIONS</t>
+          <t>FuelCloud</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Hillsboro, OR, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, DynamoDB, CI/CD, AWS CodePipeline, CodeBuild, Terraform</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, MySQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67d1ed48d145a4f1</t>
+          <t>https://www.indeed.com/viewjob?jk=05b0071381abb003</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, ETL</t>
+          <t>AWS, RDS, Scala, Snowflake, NoSQL, ELT, dbt, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77a528b43d8d11a1</t>
+          <t>https://www.indeed.com/viewjob?jk=3c8001067fa855e4</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer - Performance Management</t>
+          <t>Cloud Operations Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>MITSUBISHI ELECTRIC ICONICS DIGITAL SOLUTIONS</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Lake Buena Vista, FL, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, RDS, DynamoDB, CI/CD, AWS CodePipeline, CodeBuild, Terraform</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b85eeb0fd5a3a862</t>
+          <t>https://www.indeed.com/viewjob?jk=67d1ed48d145a4f1</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Systems &amp; Cloud Infrastructure Engineer</t>
+          <t>Data Engineer - Performance Management</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Kretek International</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Moorpark, CA, US USA</t>
+          <t>Lake Buena Vista, FL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,17 +2376,17 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Splunk, Terraform</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7d7d86c5d6aef50</t>
+          <t>https://www.indeed.com/viewjob?jk=b85eeb0fd5a3a862</t>
         </is>
       </c>
     </row>
@@ -2918,17 +2918,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sr. Infrastructure &amp; Security Engineer</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>HerculesAI</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Campbell, CA, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, Azure, GCP, Splunk, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, S3, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=997e47a23e0d8261</t>
+          <t>https://www.indeed.com/viewjob?jk=62599143d69ab642</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>#Software Engineer – Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Dimensional Modeling, ETL</t>
+          <t>AWS, S3, RDS, Azure, SQL Server, Data Modeling, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62599143d69ab642</t>
+          <t>https://www.indeed.com/viewjob?jk=65ee9e3af0d95deb</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>#Software Engineer – Engineer</t>
+          <t>Professional Services Consultant</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Ataccama</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, SQL Server, Data Modeling, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65ee9e3af0d95deb</t>
+          <t>https://www.indeed.com/viewjob?jk=e7e7f81d2e0f0ce3</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Professional Services Consultant</t>
+          <t>SR DBA / DATABASE ARCHITECT (AZURE / MSSQL)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Ataccama</t>
+          <t>Opeeka, Inc.</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Folsom, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,24 +3041,24 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Kafka, Snowflake, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Bitbucket</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7e7f81d2e0f0ce3</t>
+          <t>https://www.indeed.com/viewjob?jk=d57af04f58fc4f3b</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>SR DBA / DATABASE ARCHITECT (AZURE / MSSQL)</t>
+          <t>Senior DBA / Database Architect</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d57af04f58fc4f3b</t>
+          <t>https://www.indeed.com/viewjob?jk=5142b758be4e8f87</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior DBA / Database Architect</t>
+          <t>AI Automation Engineer, Finance &amp; Accounting</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Opeeka, Inc.</t>
+          <t>Cengage</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Folsom, CA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Bitbucket</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, PostgreSQL, AKS, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5142b758be4e8f87</t>
+          <t>https://www.indeed.com/viewjob?jk=6fc4b4b5640d9b20</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Application Developer</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Value Truck of Arizona</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>South Jordan, UT, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6c3e26366316cc8</t>
+          <t>https://www.indeed.com/viewjob?jk=c5c449cb4c336ec2</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>AI Automation Engineer, Finance &amp; Accounting</t>
+          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Cengage</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,17 +3181,17 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, PostgreSQL, AKS, Git</t>
+          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fc4b4b5640d9b20</t>
+          <t>https://www.indeed.com/viewjob?jk=e57a91ca929fec5b</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5c449cb4c336ec2</t>
+          <t>https://www.indeed.com/viewjob?jk=cd22b6d5954a33c2</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e57a91ca929fec5b</t>
+          <t>https://www.indeed.com/viewjob?jk=2d369f55f3c43cd0</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd22b6d5954a33c2</t>
+          <t>https://www.indeed.com/viewjob?jk=b5e852e1fb093faa</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d369f55f3c43cd0</t>
+          <t>https://www.indeed.com/viewjob?jk=122021b0213972fb</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5e852e1fb093faa</t>
+          <t>https://www.indeed.com/viewjob?jk=cf263b65906b30ba</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=122021b0213972fb</t>
+          <t>https://www.indeed.com/viewjob?jk=775f4b74d2e0d125</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf263b65906b30ba</t>
+          <t>https://www.indeed.com/viewjob?jk=e27aa2f30115d6a9</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=775f4b74d2e0d125</t>
+          <t>https://www.indeed.com/viewjob?jk=372ffe4f2e9a605d</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e27aa2f30115d6a9</t>
+          <t>https://www.indeed.com/viewjob?jk=a256a77103c9ee18</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=372ffe4f2e9a605d</t>
+          <t>https://www.indeed.com/viewjob?jk=9b082342159bbdf7</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a256a77103c9ee18</t>
+          <t>https://www.indeed.com/viewjob?jk=e06cd5eb56a43b5c</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b082342159bbdf7</t>
+          <t>https://www.indeed.com/viewjob?jk=daaeb6d16db98abf</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e06cd5eb56a43b5c</t>
+          <t>https://www.indeed.com/viewjob?jk=5d61083f86948477</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daaeb6d16db98abf</t>
+          <t>https://www.indeed.com/viewjob?jk=71d4be4e91f6174a</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d61083f86948477</t>
+          <t>https://www.indeed.com/viewjob?jk=912b927f8e6b0bc9</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71d4be4e91f6174a</t>
+          <t>https://www.indeed.com/viewjob?jk=697335a3240f02f2</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=912b927f8e6b0bc9</t>
+          <t>https://www.indeed.com/viewjob?jk=e21309c64f987c4d</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=697335a3240f02f2</t>
+          <t>https://www.indeed.com/viewjob?jk=6e4114c9ced06f08</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e21309c64f987c4d</t>
+          <t>https://www.indeed.com/viewjob?jk=0379c77fb1bea285</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e4114c9ced06f08</t>
+          <t>https://www.indeed.com/viewjob?jk=c7404f3dbf25b5d0</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0379c77fb1bea285</t>
+          <t>https://www.indeed.com/viewjob?jk=19a128257d3c2c77</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7404f3dbf25b5d0</t>
+          <t>https://www.indeed.com/viewjob?jk=6a667aa6f915c8e9</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19a128257d3c2c77</t>
+          <t>https://www.indeed.com/viewjob?jk=8d47c2036fa69322</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a667aa6f915c8e9</t>
+          <t>https://www.indeed.com/viewjob?jk=591077de2df74cfa</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d47c2036fa69322</t>
+          <t>https://www.indeed.com/viewjob?jk=8cc254c410ba6f38</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=591077de2df74cfa</t>
+          <t>https://www.indeed.com/viewjob?jk=12339d025b6d4b6f</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cc254c410ba6f38</t>
+          <t>https://www.indeed.com/viewjob?jk=dc7db42760d4627e</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12339d025b6d4b6f</t>
+          <t>https://www.indeed.com/viewjob?jk=6c024ec8f500d28f</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc7db42760d4627e</t>
+          <t>https://www.indeed.com/viewjob?jk=d5c090288e0e4f79</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c024ec8f500d28f</t>
+          <t>https://www.indeed.com/viewjob?jk=c400db066fcfe868</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,94 +4276,94 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5c090288e0e4f79</t>
+          <t>https://www.indeed.com/viewjob?jk=e9857bbf535b2768</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>RDS, Hadoop, Hive, HBase, Spark, Scala, MySQL, NoSQL, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c400db066fcfe868</t>
+          <t>https://www.indeed.com/viewjob?jk=e151f8f8376a065d</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>GenAI Solution Engineer (Databricks AI/Snowflake AI pref'd)</t>
+          <t>MuleSoft QA Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, Spark, Snowflake, Data Modeling, dbt, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9857bbf535b2768</t>
+          <t>https://www.indeed.com/viewjob?jk=6a8b7edc3d29ab01</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, HBase, Spark, Scala, MySQL, NoSQL, Jenkins, Jenkins</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, Terraform, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e151f8f8376a065d</t>
+          <t>https://www.indeed.com/viewjob?jk=5f72c641c65b5a61</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>MuleSoft QA Engineer</t>
+          <t>FSO LABS - AI Developer Senior - Bay Area</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>UniFirst</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,34 +4406,34 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Hadoop, Hive, Spark, Kafka, NoSQL, Power BI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a8b7edc3d29ab01</t>
+          <t>https://www.indeed.com/viewjob?jk=1d75a18fe3bc2126</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Databricks Data Engineer - Senior - Consulting - Location Open</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, Terraform, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, AKS</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f72c641c65b5a61</t>
+          <t>https://www.indeed.com/viewjob?jk=599253e2d33dc75f</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>FSO LABS - AI Developer Senior - Bay Area</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Hive, Spark, Kafka, NoSQL, Power BI, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d75a18fe3bc2126</t>
+          <t>https://www.indeed.com/viewjob?jk=afb2f5fe2a396169</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer - Senior - Consulting - Location Open</t>
+          <t>AWS Systems Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,34 +4511,34 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, AKS</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=599253e2d33dc75f</t>
+          <t>https://www.indeed.com/viewjob?jk=119269e5158f89e8</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Data Engineer (Snowflake, Teradata, DB2)</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Mutual of Omaha</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
+          <t>AWS, Glue, RDS, Scala, Snowflake, SQL Server, MongoDB, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afb2f5fe2a396169</t>
+          <t>https://www.indeed.com/viewjob?jk=aa9d2ce9f1b5528c</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>AWS Systems Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ObjectStream</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Scala, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Blob Storage, Spark, PySpark, ETL, dbt, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=119269e5158f89e8</t>
+          <t>https://www.indeed.com/viewjob?jk=06e3854d22cdba89</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Data Engineer (Snowflake, Teradata, DB2)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Mutual of Omaha</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Scala, Snowflake, SQL Server, MongoDB, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa9d2ce9f1b5528c</t>
+          <t>https://www.indeed.com/viewjob?jk=983d0a4b6df6a34b</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>ObjectStream</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Blob Storage, Spark, PySpark, ETL, dbt, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06e3854d22cdba89</t>
+          <t>https://www.indeed.com/viewjob?jk=e39cfd742ca8ccb7</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=983d0a4b6df6a34b</t>
+          <t>https://www.indeed.com/viewjob?jk=4d24b9bb7d3f81d1</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e39cfd742ca8ccb7</t>
+          <t>https://www.indeed.com/viewjob?jk=406f01e6594b2624</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d24b9bb7d3f81d1</t>
+          <t>https://www.indeed.com/viewjob?jk=0206f3baae13d0ec</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>MuleSoft Architect / Developer Remote (Part-Time / Full-Time) – US Client</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Bowery Software Inc</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Oracle, ETL, Talend, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4800,76 +4800,6 @@
         </is>
       </c>
       <c r="G125" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=406f01e6594b2624</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0206f3baae13d0ec</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>MuleSoft Architect / Developer Remote (Part-Time / Full-Time) – US Client</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Bowery Software Inc</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Oracle, ETL, Talend, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=fe3a1e183165a854</t>
         </is>
